--- a/source/stock_data.xlsx
+++ b/source/stock_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32740" windowHeight="14840" activeTab="1"/>
+    <workbookView windowWidth="32740" windowHeight="14840"/>
   </bookViews>
   <sheets>
     <sheet name="STOCK IQOO" sheetId="3" r:id="rId1"/>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="35">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="36"/>
       <c r="D1" s="36"/>
@@ -6271,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>

--- a/source/stock_data.xlsx
+++ b/source/stock_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32740" windowHeight="14840"/>
+    <workbookView windowWidth="32740" windowHeight="14840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="STOCK IQOO" sheetId="3" r:id="rId1"/>
@@ -441,12 +441,6 @@
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1F3864"/>
@@ -456,6 +450,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
     </font>
@@ -669,12 +669,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="65"/>
         <bgColor rgb="FFBDD7EE"/>
       </patternFill>
@@ -682,6 +676,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1269,19 +1269,19 @@
     <xf numFmtId="1" fontId="11" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="178" fontId="14" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="15" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1290,7 +1290,7 @@
     <xf numFmtId="178" fontId="2" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1342,7 +1342,7 @@
     <xf numFmtId="178" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="35">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="36"/>
       <c r="D1" s="36"/>
@@ -1876,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
@@ -1940,7 +1940,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="35">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
@@ -2371,7 +2371,7 @@
       <c r="I8" s="43">
         <v>1</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="21">
         <v>0</v>
       </c>
       <c r="K8" s="17">
@@ -2395,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="S8" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T8" s="17">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="AS8" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT8" s="23">
         <v>4</v>
@@ -2470,7 +2470,7 @@
         <v>3</v>
       </c>
       <c r="AV8" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:48">
@@ -2497,7 +2497,7 @@
       <c r="I9" s="43">
         <v>1</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="21">
         <v>0</v>
       </c>
       <c r="K9" s="17">
@@ -2515,13 +2515,13 @@
       </c>
       <c r="P9" s="16"/>
       <c r="Q9" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="43">
         <v>2</v>
       </c>
-      <c r="S9" s="18">
-        <v>0</v>
+      <c r="S9" s="20">
+        <v>6</v>
       </c>
       <c r="T9" s="17">
         <v>0</v>
@@ -2588,13 +2588,13 @@
       </c>
       <c r="AS9" s="16"/>
       <c r="AT9" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU9" s="24">
         <v>3</v>
       </c>
       <c r="AV9" s="24">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:48">
@@ -2622,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" s="17">
         <v>1</v>
@@ -2630,7 +2630,7 @@
       <c r="L10" s="43">
         <v>2</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="20">
         <v>6</v>
       </c>
       <c r="N10" s="17">
@@ -2647,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" s="17">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>4</v>
       </c>
       <c r="AV10" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:48">
@@ -2747,7 +2747,7 @@
       <c r="I11" s="43">
         <v>1</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="21">
         <v>0</v>
       </c>
       <c r="K11" s="17">
@@ -2828,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="AP11" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ11" s="17">
         <v>3</v>
@@ -2844,7 +2844,7 @@
         <v>2</v>
       </c>
       <c r="AV11" s="24">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:48">
@@ -2878,7 +2878,7 @@
       <c r="L12" s="43">
         <v>1</v>
       </c>
-      <c r="M12" s="18">
+      <c r="M12" s="21">
         <v>0</v>
       </c>
       <c r="N12" s="17">
@@ -2895,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="S12" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T12" s="17">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>2</v>
       </c>
       <c r="AV12" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:48">
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="S13" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T13" s="17">
         <v>0</v>
@@ -3060,14 +3060,16 @@
         <v>0</v>
       </c>
       <c r="AJ13" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK13" s="43">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="16"/>
-      <c r="AM13" s="44">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AL13" s="16">
+        <v>24</v>
+      </c>
+      <c r="AM13" s="45">
+        <v>1</v>
       </c>
       <c r="AN13" s="14">
         <v>1</v>
@@ -3084,13 +3086,13 @@
       </c>
       <c r="AS13" s="16"/>
       <c r="AT13" s="23">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU13" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV13" s="24">
-        <v>132</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:48">
@@ -3117,7 +3119,7 @@
       <c r="I14" s="43">
         <v>1</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="21">
         <v>0</v>
       </c>
       <c r="K14" s="17">
@@ -3127,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N14" s="17">
         <v>1</v>
@@ -3136,7 +3138,7 @@
         <v>1</v>
       </c>
       <c r="P14" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q14" s="17">
         <v>2</v>
@@ -3145,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="S14" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T14" s="17">
         <v>0</v>
@@ -3218,7 +3220,7 @@
         <v>4</v>
       </c>
       <c r="AV14" s="24">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:48">
@@ -3253,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N15" s="17">
         <v>1</v>
@@ -3268,7 +3270,7 @@
       <c r="R15" s="43">
         <v>1</v>
       </c>
-      <c r="S15" s="18">
+      <c r="S15" s="21">
         <v>0</v>
       </c>
       <c r="T15" s="17">
@@ -3335,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="AS15" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT15" s="23">
         <v>4</v>
@@ -3344,7 +3346,7 @@
         <v>3</v>
       </c>
       <c r="AV15" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:48">
@@ -3430,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="AH16" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI16" s="44">
         <v>1</v>
@@ -3466,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="AV16" s="24">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:48">
@@ -3507,7 +3509,7 @@
       <c r="O17" s="43">
         <v>1</v>
       </c>
-      <c r="P17" s="18">
+      <c r="P17" s="21">
         <v>0</v>
       </c>
       <c r="Q17" s="17">
@@ -3563,7 +3565,7 @@
       <c r="AK17" s="43">
         <v>1</v>
       </c>
-      <c r="AL17" s="18">
+      <c r="AL17" s="21">
         <v>0</v>
       </c>
       <c r="AM17" s="45">
@@ -3590,7 +3592,7 @@
         <v>2</v>
       </c>
       <c r="AV17" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:48">
@@ -3744,7 +3746,7 @@
       <c r="L19" s="43">
         <v>1</v>
       </c>
-      <c r="M19" s="18">
+      <c r="M19" s="21">
         <v>0</v>
       </c>
       <c r="N19" s="17">
@@ -3761,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="S19" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T19" s="17">
         <v>0</v>
@@ -3834,7 +3836,7 @@
         <v>2</v>
       </c>
       <c r="AV19" s="24">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:48">
@@ -3995,7 +3997,7 @@
       <c r="O21" s="43">
         <v>3</v>
       </c>
-      <c r="P21" s="18">
+      <c r="P21" s="21">
         <v>0</v>
       </c>
       <c r="Q21" s="17">
@@ -4042,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="AH21" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI21" s="44">
         <v>1</v>
@@ -4078,7 +4080,7 @@
         <v>4</v>
       </c>
       <c r="AV21" s="24">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:48">
@@ -4113,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N22" s="17">
         <v>1</v>
@@ -4166,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="AH22" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI22" s="44">
         <v>1</v>
@@ -4188,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="AP22" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ22" s="17">
         <v>2</v>
@@ -4204,7 +4206,7 @@
         <v>3</v>
       </c>
       <c r="AV22" s="24">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:48">
@@ -4238,7 +4240,7 @@
       <c r="L23" s="43">
         <v>1</v>
       </c>
-      <c r="M23" s="18">
+      <c r="M23" s="21">
         <v>0</v>
       </c>
       <c r="N23" s="17">
@@ -4312,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="AP23" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ23" s="17">
         <v>1</v>
@@ -4328,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="AV23" s="24">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:48">
@@ -4355,7 +4357,7 @@
       <c r="I24" s="43">
         <v>1</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="21">
         <v>0</v>
       </c>
       <c r="K24" s="17">
@@ -4365,7 +4367,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N24" s="17">
         <v>2</v>
@@ -4374,7 +4376,7 @@
         <v>2</v>
       </c>
       <c r="P24" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q24" s="17">
         <v>0</v>
@@ -4420,22 +4422,22 @@
         <v>1</v>
       </c>
       <c r="AH24" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI24" s="44">
         <v>1</v>
       </c>
       <c r="AJ24" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="43">
-        <v>1</v>
-      </c>
-      <c r="AL24" s="16">
-        <v>11</v>
-      </c>
-      <c r="AM24" s="44">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AL24" s="21">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="45">
+        <v>2</v>
       </c>
       <c r="AN24" s="14">
         <v>2</v>
@@ -4452,13 +4454,13 @@
       </c>
       <c r="AS24" s="16"/>
       <c r="AT24" s="23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU24" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV24" s="24">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:48">
@@ -4627,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="S26" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T26" s="17">
         <v>0</v>
@@ -4665,7 +4667,7 @@
       <c r="AG26" s="43">
         <v>2</v>
       </c>
-      <c r="AH26" s="18">
+      <c r="AH26" s="21">
         <v>0</v>
       </c>
       <c r="AI26" s="44">
@@ -4694,7 +4696,7 @@
       <c r="AR26" s="43">
         <v>1</v>
       </c>
-      <c r="AS26" s="18">
+      <c r="AS26" s="21">
         <v>0</v>
       </c>
       <c r="AT26" s="23">
@@ -4704,7 +4706,7 @@
         <v>4</v>
       </c>
       <c r="AV26" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:48">
@@ -4731,7 +4733,7 @@
       <c r="I27" s="43">
         <v>1</v>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="21">
         <v>0</v>
       </c>
       <c r="K27" s="17">
@@ -4826,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="AV27" s="24">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:48">
@@ -4853,7 +4855,7 @@
       <c r="I28" s="43">
         <v>1</v>
       </c>
-      <c r="J28" s="18">
+      <c r="J28" s="21">
         <v>0</v>
       </c>
       <c r="K28" s="17">
@@ -4862,7 +4864,7 @@
       <c r="L28" s="43">
         <v>1</v>
       </c>
-      <c r="M28" s="18">
+      <c r="M28" s="21">
         <v>0</v>
       </c>
       <c r="N28" s="17">
@@ -4950,7 +4952,7 @@
         <v>2</v>
       </c>
       <c r="AV28" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:48">
@@ -4992,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="P29" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q29" s="17">
         <v>1</v>
@@ -5001,7 +5003,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T29" s="17">
         <v>0</v>
@@ -5039,7 +5041,7 @@
       <c r="AG29" s="43">
         <v>1</v>
       </c>
-      <c r="AH29" s="18">
+      <c r="AH29" s="21">
         <v>0</v>
       </c>
       <c r="AI29" s="44">
@@ -5063,22 +5065,22 @@
       </c>
       <c r="AP29" s="16"/>
       <c r="AQ29" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR29" s="43">
         <v>1</v>
       </c>
-      <c r="AS29" s="18">
-        <v>0</v>
+      <c r="AS29" s="16">
+        <v>12</v>
       </c>
       <c r="AT29" s="23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU29" s="24">
         <v>4</v>
       </c>
       <c r="AV29" s="24">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:48">
@@ -5112,7 +5114,7 @@
       <c r="L30" s="43">
         <v>2</v>
       </c>
-      <c r="M30" s="18">
+      <c r="M30" s="21">
         <v>0</v>
       </c>
       <c r="N30" s="17">
@@ -5122,7 +5124,7 @@
         <v>2</v>
       </c>
       <c r="P30" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q30" s="17">
         <v>1</v>
@@ -5130,7 +5132,7 @@
       <c r="R30" s="43">
         <v>2</v>
       </c>
-      <c r="S30" s="21">
+      <c r="S30" s="20">
         <v>6</v>
       </c>
       <c r="T30" s="17">
@@ -5204,7 +5206,7 @@
         <v>6</v>
       </c>
       <c r="AV30" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:48">
@@ -5519,7 +5521,7 @@
       <c r="AC33" s="43">
         <v>1</v>
       </c>
-      <c r="AD33" s="18">
+      <c r="AD33" s="21">
         <v>0</v>
       </c>
       <c r="AE33" s="45">
@@ -5551,7 +5553,7 @@
       <c r="AO33" s="43">
         <v>1</v>
       </c>
-      <c r="AP33" s="18">
+      <c r="AP33" s="21">
         <v>0</v>
       </c>
       <c r="AQ33" s="17">
@@ -5560,7 +5562,7 @@
       <c r="AR33" s="43">
         <v>1</v>
       </c>
-      <c r="AS33" s="18">
+      <c r="AS33" s="21">
         <v>0</v>
       </c>
       <c r="AT33" s="23">
@@ -5570,7 +5572,7 @@
         <v>3</v>
       </c>
       <c r="AV33" s="24">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:48">
@@ -5619,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="S34" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T34" s="17">
         <v>0</v>
@@ -5692,7 +5694,7 @@
         <v>1</v>
       </c>
       <c r="AV34" s="24">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:48">
@@ -5734,7 +5736,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q35" s="17">
         <v>0</v>
@@ -5742,7 +5744,7 @@
       <c r="R35" s="43">
         <v>1</v>
       </c>
-      <c r="S35" s="18">
+      <c r="S35" s="21">
         <v>0</v>
       </c>
       <c r="T35" s="17">
@@ -5816,7 +5818,7 @@
         <v>2</v>
       </c>
       <c r="AV35" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:48">
@@ -5844,7 +5846,7 @@
         <v>8</v>
       </c>
       <c r="J36" s="16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K36" s="31">
         <v>15</v>
@@ -5853,7 +5855,7 @@
         <v>12</v>
       </c>
       <c r="M36" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N36" s="31">
         <v>34</v>
@@ -5862,16 +5864,16 @@
         <v>11</v>
       </c>
       <c r="P36" s="16">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q36" s="31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R36" s="48">
         <v>15</v>
       </c>
       <c r="S36" s="16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="T36" s="31">
         <v>0</v>
@@ -5899,7 +5901,7 @@
       <c r="AC36" s="48">
         <v>1</v>
       </c>
-      <c r="AD36" s="18">
+      <c r="AD36" s="21">
         <v>0</v>
       </c>
       <c r="AE36" s="49">
@@ -5912,22 +5914,22 @@
         <v>7</v>
       </c>
       <c r="AH36" s="16">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AI36" s="49">
         <v>6</v>
       </c>
       <c r="AJ36" s="29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK36" s="48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL36" s="16">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="AM36" s="49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN36" s="29">
         <v>24</v>
@@ -5936,25 +5938,25 @@
         <v>4</v>
       </c>
       <c r="AP36" s="16">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AQ36" s="31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AR36" s="48">
         <v>5</v>
       </c>
       <c r="AS36" s="16">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AT36" s="23">
         <v>177</v>
       </c>
       <c r="AU36" s="24">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AV36" s="24">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -6271,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -6375,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -6509,7 +6511,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -7235,15 +7237,15 @@
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="15">
         <v>1</v>
       </c>
-      <c r="J7" s="18">
-        <v>0</v>
-      </c>
-      <c r="K7" s="19">
+      <c r="J7" s="16">
+        <v>12</v>
+      </c>
+      <c r="K7" s="18">
         <v>1</v>
       </c>
       <c r="L7" s="14">
@@ -7253,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="16"/>
-      <c r="O7" s="20">
+      <c r="O7" s="19">
         <v>0</v>
       </c>
       <c r="P7" s="14">
@@ -7271,40 +7273,40 @@
       </c>
       <c r="U7" s="16"/>
       <c r="V7" s="17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W7" s="15">
         <v>11</v>
       </c>
-      <c r="X7" s="18">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="19">
+      <c r="X7" s="20">
+        <v>7</v>
+      </c>
+      <c r="Y7" s="18">
         <v>5</v>
       </c>
       <c r="Z7" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA7" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB7" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC7" s="22">
         <v>3</v>
       </c>
       <c r="AD7" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE7" s="15">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="16">
-        <v>44</v>
-      </c>
-      <c r="AG7" s="19">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AF7" s="20">
+        <v>8</v>
+      </c>
+      <c r="AG7" s="18">
+        <v>1</v>
       </c>
       <c r="AH7" s="14">
         <v>6</v>
@@ -7313,7 +7315,7 @@
         <v>3</v>
       </c>
       <c r="AJ7" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK7" s="17">
         <v>0</v>
@@ -7321,19 +7323,19 @@
       <c r="AL7" s="15">
         <v>10</v>
       </c>
-      <c r="AM7" s="18">
+      <c r="AM7" s="21">
         <v>0</v>
       </c>
       <c r="AN7" s="17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO7" s="15">
         <v>9</v>
       </c>
-      <c r="AP7" s="18">
-        <v>1</v>
-      </c>
-      <c r="AQ7" s="19">
+      <c r="AP7" s="20">
+        <v>5</v>
+      </c>
+      <c r="AQ7" s="18">
         <v>4</v>
       </c>
       <c r="AR7" s="14">
@@ -7343,9 +7345,9 @@
         <v>4</v>
       </c>
       <c r="AT7" s="16">
-        <v>11</v>
-      </c>
-      <c r="AU7" s="19">
+        <v>12</v>
+      </c>
+      <c r="AU7" s="18">
         <v>2</v>
       </c>
       <c r="AV7" s="14">
@@ -7354,10 +7356,10 @@
       <c r="AW7" s="15">
         <v>4</v>
       </c>
-      <c r="AX7" s="21">
+      <c r="AX7" s="20">
         <v>6</v>
       </c>
-      <c r="AY7" s="19">
+      <c r="AY7" s="18">
         <v>2</v>
       </c>
       <c r="AZ7" s="14">
@@ -7373,10 +7375,10 @@
       <c r="BD7" s="15">
         <v>2</v>
       </c>
-      <c r="BE7" s="18">
-        <v>0</v>
-      </c>
-      <c r="BF7" s="19">
+      <c r="BE7" s="21">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="18">
         <v>1</v>
       </c>
       <c r="BG7" s="14">
@@ -7386,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="16"/>
-      <c r="BJ7" s="20">
+      <c r="BJ7" s="19">
         <v>0</v>
       </c>
       <c r="BK7" s="14">
@@ -7396,7 +7398,7 @@
         <v>0</v>
       </c>
       <c r="BM7" s="16"/>
-      <c r="BN7" s="20">
+      <c r="BN7" s="19">
         <v>0</v>
       </c>
       <c r="BO7" s="14">
@@ -7406,9 +7408,9 @@
         <v>2</v>
       </c>
       <c r="BQ7" s="16">
-        <v>11</v>
-      </c>
-      <c r="BR7" s="19">
+        <v>12</v>
+      </c>
+      <c r="BR7" s="18">
         <v>1</v>
       </c>
       <c r="BS7" s="14">
@@ -7418,17 +7420,17 @@
         <v>0</v>
       </c>
       <c r="BU7" s="16"/>
-      <c r="BV7" s="20">
+      <c r="BV7" s="19">
         <v>0</v>
       </c>
       <c r="BW7" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BX7" s="15">
         <v>0</v>
       </c>
       <c r="BY7" s="16"/>
-      <c r="BZ7" s="20">
+      <c r="BZ7" s="19">
         <v>0</v>
       </c>
       <c r="CA7" s="14">
@@ -7438,22 +7440,22 @@
         <v>4</v>
       </c>
       <c r="CC7" s="16">
-        <v>44</v>
-      </c>
-      <c r="CD7" s="19">
+        <v>48</v>
+      </c>
+      <c r="CD7" s="18">
         <v>2</v>
       </c>
       <c r="CE7" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CF7" s="15">
         <v>19</v>
       </c>
-      <c r="CG7" s="21">
-        <v>5</v>
-      </c>
-      <c r="CH7" s="19">
-        <v>12</v>
+      <c r="CG7" s="20">
+        <v>6</v>
+      </c>
+      <c r="CH7" s="18">
+        <v>11</v>
       </c>
       <c r="CI7" s="14">
         <v>5</v>
@@ -7462,7 +7464,7 @@
         <v>1</v>
       </c>
       <c r="CK7" s="16">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="CL7" s="17">
         <v>4</v>
@@ -7471,7 +7473,7 @@
         <v>2</v>
       </c>
       <c r="CN7" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CO7" s="17">
         <v>15</v>
@@ -7479,17 +7481,17 @@
       <c r="CP7" s="15">
         <v>23</v>
       </c>
-      <c r="CQ7" s="21">
-        <v>7</v>
+      <c r="CQ7" s="20">
+        <v>8</v>
       </c>
       <c r="CR7" s="23">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="CS7" s="24">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="CT7" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:98">
@@ -7517,7 +7519,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="16"/>
-      <c r="K8" s="20">
+      <c r="K8" s="19">
         <v>0</v>
       </c>
       <c r="L8" s="14">
@@ -7527,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="16"/>
-      <c r="O8" s="20">
+      <c r="O8" s="19">
         <v>0</v>
       </c>
       <c r="P8" s="14">
@@ -7545,28 +7547,28 @@
       </c>
       <c r="U8" s="16"/>
       <c r="V8" s="17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W8" s="15">
-        <v>17</v>
-      </c>
-      <c r="X8" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="19">
+        <v>18</v>
+      </c>
+      <c r="X8" s="21">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="18">
         <v>8</v>
       </c>
       <c r="Z8" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="15">
         <v>8</v>
       </c>
-      <c r="AB8" s="18">
-        <v>3</v>
+      <c r="AB8" s="20">
+        <v>6</v>
       </c>
       <c r="AC8" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD8" s="14">
         <v>3</v>
@@ -7575,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="AF8" s="16"/>
-      <c r="AG8" s="20">
+      <c r="AG8" s="19">
         <v>0</v>
       </c>
       <c r="AH8" s="14">
@@ -7592,42 +7594,42 @@
         <v>3</v>
       </c>
       <c r="AM8" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN8" s="17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO8" s="15">
         <v>10</v>
       </c>
-      <c r="AP8" s="18">
-        <v>1</v>
-      </c>
-      <c r="AQ8" s="19">
+      <c r="AP8" s="21">
         <v>5</v>
       </c>
+      <c r="AQ8" s="18">
+        <v>4</v>
+      </c>
       <c r="AR8" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS8" s="15">
         <v>5</v>
       </c>
-      <c r="AT8" s="18">
+      <c r="AT8" s="20">
+        <v>10</v>
+      </c>
+      <c r="AU8" s="18">
+        <v>2</v>
+      </c>
+      <c r="AV8" s="14">
         <v>4</v>
       </c>
-      <c r="AU8" s="19">
-        <v>2</v>
-      </c>
-      <c r="AV8" s="14">
-        <v>3</v>
-      </c>
       <c r="AW8" s="15">
         <v>1</v>
       </c>
       <c r="AX8" s="16">
-        <v>33</v>
-      </c>
-      <c r="AY8" s="19">
+        <v>48</v>
+      </c>
+      <c r="AY8" s="18">
         <v>0</v>
       </c>
       <c r="AZ8" s="14">
@@ -7643,10 +7645,10 @@
       <c r="BD8" s="15">
         <v>2</v>
       </c>
-      <c r="BE8" s="21">
+      <c r="BE8" s="20">
         <v>6</v>
       </c>
-      <c r="BF8" s="19">
+      <c r="BF8" s="18">
         <v>1</v>
       </c>
       <c r="BG8" s="14">
@@ -7656,7 +7658,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="16"/>
-      <c r="BJ8" s="20">
+      <c r="BJ8" s="19">
         <v>0</v>
       </c>
       <c r="BK8" s="14">
@@ -7666,19 +7668,19 @@
         <v>0</v>
       </c>
       <c r="BM8" s="16"/>
-      <c r="BN8" s="20">
+      <c r="BN8" s="19">
         <v>0</v>
       </c>
       <c r="BO8" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP8" s="15">
         <v>1</v>
       </c>
       <c r="BQ8" s="16">
-        <v>11</v>
-      </c>
-      <c r="BR8" s="19">
+        <v>24</v>
+      </c>
+      <c r="BR8" s="18">
         <v>1</v>
       </c>
       <c r="BS8" s="14">
@@ -7688,80 +7690,80 @@
         <v>0</v>
       </c>
       <c r="BU8" s="16"/>
-      <c r="BV8" s="20">
+      <c r="BV8" s="19">
         <v>0</v>
       </c>
       <c r="BW8" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BX8" s="15">
         <v>1</v>
       </c>
       <c r="BY8" s="16">
-        <v>11</v>
-      </c>
-      <c r="BZ8" s="19">
+        <v>24</v>
+      </c>
+      <c r="BZ8" s="18">
         <v>1</v>
       </c>
       <c r="CA8" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="CB8" s="15">
         <v>6</v>
       </c>
       <c r="CC8" s="16">
-        <v>18</v>
-      </c>
-      <c r="CD8" s="19">
+        <v>30</v>
+      </c>
+      <c r="CD8" s="18">
         <v>3</v>
       </c>
       <c r="CE8" s="14">
+        <v>11</v>
+      </c>
+      <c r="CF8" s="15">
+        <v>14</v>
+      </c>
+      <c r="CG8" s="20">
+        <v>9</v>
+      </c>
+      <c r="CH8" s="18">
+        <v>8</v>
+      </c>
+      <c r="CI8" s="14">
+        <v>3</v>
+      </c>
+      <c r="CJ8" s="15">
+        <v>3</v>
+      </c>
+      <c r="CK8" s="16">
         <v>12</v>
       </c>
-      <c r="CF8" s="15">
-        <v>13</v>
-      </c>
-      <c r="CG8" s="16">
+      <c r="CL8" s="17">
+        <v>4</v>
+      </c>
+      <c r="CM8" s="15">
+        <v>1</v>
+      </c>
+      <c r="CN8" s="16">
+        <v>48</v>
+      </c>
+      <c r="CO8" s="17">
         <v>10</v>
       </c>
-      <c r="CH8" s="19">
+      <c r="CP8" s="15">
+        <v>44</v>
+      </c>
+      <c r="CQ8" s="21">
+        <v>3</v>
+      </c>
+      <c r="CR8" s="23">
+        <v>82</v>
+      </c>
+      <c r="CS8" s="24">
+        <v>117</v>
+      </c>
+      <c r="CT8" s="24">
         <v>8</v>
-      </c>
-      <c r="CI8" s="14">
-        <v>3</v>
-      </c>
-      <c r="CJ8" s="15">
-        <v>2</v>
-      </c>
-      <c r="CK8" s="16">
-        <v>17</v>
-      </c>
-      <c r="CL8" s="17">
-        <v>3</v>
-      </c>
-      <c r="CM8" s="15">
-        <v>1</v>
-      </c>
-      <c r="CN8" s="16">
-        <v>33</v>
-      </c>
-      <c r="CO8" s="17">
-        <v>16</v>
-      </c>
-      <c r="CP8" s="15">
-        <v>35</v>
-      </c>
-      <c r="CQ8" s="21">
-        <v>5</v>
-      </c>
-      <c r="CR8" s="23">
-        <v>70</v>
-      </c>
-      <c r="CS8" s="24">
-        <v>105</v>
-      </c>
-      <c r="CT8" s="24">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:98">
@@ -7789,7 +7791,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="16"/>
-      <c r="K9" s="20">
+      <c r="K9" s="19">
         <v>0</v>
       </c>
       <c r="L9" s="14">
@@ -7799,7 +7801,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="16"/>
-      <c r="O9" s="20">
+      <c r="O9" s="19">
         <v>0</v>
       </c>
       <c r="P9" s="14">
@@ -7817,25 +7819,25 @@
       </c>
       <c r="U9" s="16"/>
       <c r="V9" s="17">
+        <v>8</v>
+      </c>
+      <c r="W9" s="15">
+        <v>26</v>
+      </c>
+      <c r="X9" s="21">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="18">
+        <v>11</v>
+      </c>
+      <c r="Z9" s="14">
         <v>6</v>
       </c>
-      <c r="W9" s="15">
-        <v>25</v>
-      </c>
-      <c r="X9" s="18">
-        <v>3</v>
-      </c>
-      <c r="Y9" s="19">
-        <v>11</v>
-      </c>
-      <c r="Z9" s="14">
-        <v>8</v>
-      </c>
       <c r="AA9" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AB9" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC9" s="25">
         <v>8</v>
@@ -7846,20 +7848,20 @@
       <c r="AE9" s="15">
         <v>3</v>
       </c>
-      <c r="AF9" s="21">
-        <v>7</v>
-      </c>
-      <c r="AG9" s="19">
+      <c r="AF9" s="20">
+        <v>8</v>
+      </c>
+      <c r="AG9" s="18">
         <v>1</v>
       </c>
       <c r="AH9" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AI9" s="15">
-        <v>14</v>
-      </c>
-      <c r="AJ9" s="18">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="AJ9" s="20">
+        <v>6</v>
       </c>
       <c r="AK9" s="17">
         <v>5</v>
@@ -7867,8 +7869,8 @@
       <c r="AL9" s="15">
         <v>13</v>
       </c>
-      <c r="AM9" s="18">
-        <v>4</v>
+      <c r="AM9" s="21">
+        <v>5</v>
       </c>
       <c r="AN9" s="17">
         <v>8</v>
@@ -7877,33 +7879,33 @@
         <v>8</v>
       </c>
       <c r="AP9" s="16">
-        <v>11</v>
-      </c>
-      <c r="AQ9" s="19">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="AQ9" s="18">
+        <v>3</v>
       </c>
       <c r="AR9" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS9" s="15">
         <v>2</v>
       </c>
-      <c r="AT9" s="18">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="19">
+      <c r="AT9" s="16">
+        <v>12</v>
+      </c>
+      <c r="AU9" s="18">
         <v>1</v>
       </c>
       <c r="AV9" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW9" s="15">
         <v>1</v>
       </c>
       <c r="AX9" s="16">
-        <v>11</v>
-      </c>
-      <c r="AY9" s="19">
+        <v>24</v>
+      </c>
+      <c r="AY9" s="18">
         <v>0</v>
       </c>
       <c r="AZ9" s="14">
@@ -7919,10 +7921,10 @@
       <c r="BD9" s="15">
         <v>2</v>
       </c>
-      <c r="BE9" s="18">
-        <v>0</v>
-      </c>
-      <c r="BF9" s="19">
+      <c r="BE9" s="21">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="18">
         <v>1</v>
       </c>
       <c r="BG9" s="14">
@@ -7932,7 +7934,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="16"/>
-      <c r="BJ9" s="20">
+      <c r="BJ9" s="19">
         <v>0</v>
       </c>
       <c r="BK9" s="14">
@@ -7941,22 +7943,22 @@
       <c r="BL9" s="15">
         <v>1</v>
       </c>
-      <c r="BM9" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN9" s="19">
+      <c r="BM9" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN9" s="18">
         <v>1</v>
       </c>
       <c r="BO9" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP9" s="15">
-        <v>1</v>
-      </c>
-      <c r="BQ9" s="16">
-        <v>22</v>
-      </c>
-      <c r="BR9" s="19">
+        <v>2</v>
+      </c>
+      <c r="BQ9" s="20">
+        <v>6</v>
+      </c>
+      <c r="BR9" s="18">
         <v>1</v>
       </c>
       <c r="BS9" s="14">
@@ -7966,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="BU9" s="16"/>
-      <c r="BV9" s="20">
+      <c r="BV9" s="19">
         <v>0</v>
       </c>
       <c r="BW9" s="14">
@@ -7975,71 +7977,71 @@
       <c r="BX9" s="15">
         <v>4</v>
       </c>
-      <c r="BY9" s="21">
+      <c r="BY9" s="20">
         <v>6</v>
       </c>
-      <c r="BZ9" s="19">
+      <c r="BZ9" s="18">
         <v>3</v>
       </c>
       <c r="CA9" s="14">
+        <v>10</v>
+      </c>
+      <c r="CB9" s="15">
+        <v>16</v>
+      </c>
+      <c r="CC9" s="20">
+        <v>8</v>
+      </c>
+      <c r="CD9" s="18">
+        <v>7</v>
+      </c>
+      <c r="CE9" s="14">
         <v>12</v>
-      </c>
-      <c r="CB9" s="15">
-        <v>14</v>
-      </c>
-      <c r="CC9" s="21">
-        <v>9</v>
-      </c>
-      <c r="CD9" s="19">
-        <v>6</v>
-      </c>
-      <c r="CE9" s="14">
-        <v>4</v>
       </c>
       <c r="CF9" s="15">
         <v>29</v>
       </c>
-      <c r="CG9" s="18">
-        <v>2</v>
-      </c>
-      <c r="CH9" s="19">
-        <v>18</v>
+      <c r="CG9" s="20">
+        <v>5</v>
+      </c>
+      <c r="CH9" s="18">
+        <v>17</v>
       </c>
       <c r="CI9" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CJ9" s="15">
         <v>5</v>
       </c>
-      <c r="CK9" s="18">
+      <c r="CK9" s="20">
+        <v>10</v>
+      </c>
+      <c r="CL9" s="17">
+        <v>3</v>
+      </c>
+      <c r="CM9" s="15">
+        <v>2</v>
+      </c>
+      <c r="CN9" s="16">
+        <v>18</v>
+      </c>
+      <c r="CO9" s="17">
+        <v>41</v>
+      </c>
+      <c r="CP9" s="15">
+        <v>141</v>
+      </c>
+      <c r="CQ9" s="21">
         <v>4</v>
       </c>
-      <c r="CL9" s="17">
-        <v>3</v>
-      </c>
-      <c r="CM9" s="15">
-        <v>2</v>
-      </c>
-      <c r="CN9" s="16">
-        <v>17</v>
-      </c>
-      <c r="CO9" s="17">
-        <v>11</v>
-      </c>
-      <c r="CP9" s="15">
-        <v>131</v>
-      </c>
-      <c r="CQ9" s="18">
-        <v>1</v>
-      </c>
       <c r="CR9" s="23">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="CS9" s="24">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="CT9" s="24">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:98">
@@ -8067,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="16"/>
-      <c r="K10" s="20">
+      <c r="K10" s="19">
         <v>0</v>
       </c>
       <c r="L10" s="14">
@@ -8077,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="16"/>
-      <c r="O10" s="20">
+      <c r="O10" s="19">
         <v>0</v>
       </c>
       <c r="P10" s="14">
@@ -8101,9 +8103,9 @@
         <v>2</v>
       </c>
       <c r="X10" s="16">
-        <v>11</v>
-      </c>
-      <c r="Y10" s="19">
+        <v>12</v>
+      </c>
+      <c r="Y10" s="18">
         <v>1</v>
       </c>
       <c r="Z10" s="14">
@@ -8113,7 +8115,7 @@
         <v>2</v>
       </c>
       <c r="AB10" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC10" s="22">
         <v>1</v>
@@ -8125,7 +8127,7 @@
         <v>0</v>
       </c>
       <c r="AF10" s="16"/>
-      <c r="AG10" s="20">
+      <c r="AG10" s="19">
         <v>0</v>
       </c>
       <c r="AH10" s="14">
@@ -8148,10 +8150,10 @@
       <c r="AO10" s="15">
         <v>4</v>
       </c>
-      <c r="AP10" s="21">
-        <v>8</v>
-      </c>
-      <c r="AQ10" s="19">
+      <c r="AP10" s="20">
+        <v>9</v>
+      </c>
+      <c r="AQ10" s="18">
         <v>2</v>
       </c>
       <c r="AR10" s="14">
@@ -8161,7 +8163,7 @@
         <v>0</v>
       </c>
       <c r="AT10" s="16"/>
-      <c r="AU10" s="20">
+      <c r="AU10" s="19">
         <v>0</v>
       </c>
       <c r="AV10" s="14">
@@ -8170,10 +8172,10 @@
       <c r="AW10" s="15">
         <v>1</v>
       </c>
-      <c r="AX10" s="18">
-        <v>0</v>
-      </c>
-      <c r="AY10" s="19">
+      <c r="AX10" s="21">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="18">
         <v>0</v>
       </c>
       <c r="AZ10" s="14">
@@ -8190,9 +8192,9 @@
         <v>1</v>
       </c>
       <c r="BE10" s="16">
-        <v>22</v>
-      </c>
-      <c r="BF10" s="19">
+        <v>24</v>
+      </c>
+      <c r="BF10" s="18">
         <v>1</v>
       </c>
       <c r="BG10" s="14">
@@ -8202,7 +8204,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="16"/>
-      <c r="BJ10" s="20">
+      <c r="BJ10" s="19">
         <v>0</v>
       </c>
       <c r="BK10" s="14">
@@ -8212,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="BM10" s="16"/>
-      <c r="BN10" s="20">
+      <c r="BN10" s="19">
         <v>0</v>
       </c>
       <c r="BO10" s="14">
@@ -8222,9 +8224,9 @@
         <v>1</v>
       </c>
       <c r="BQ10" s="16">
-        <v>66</v>
-      </c>
-      <c r="BR10" s="19">
+        <v>72</v>
+      </c>
+      <c r="BR10" s="18">
         <v>1</v>
       </c>
       <c r="BS10" s="14">
@@ -8234,7 +8236,7 @@
         <v>0</v>
       </c>
       <c r="BU10" s="16"/>
-      <c r="BV10" s="20">
+      <c r="BV10" s="19">
         <v>0</v>
       </c>
       <c r="BW10" s="14">
@@ -8244,9 +8246,9 @@
         <v>4</v>
       </c>
       <c r="BY10" s="16">
-        <v>11</v>
-      </c>
-      <c r="BZ10" s="19">
+        <v>12</v>
+      </c>
+      <c r="BZ10" s="18">
         <v>3</v>
       </c>
       <c r="CA10" s="14">
@@ -8255,21 +8257,23 @@
       <c r="CB10" s="15">
         <v>7</v>
       </c>
-      <c r="CC10" s="21">
-        <v>6</v>
-      </c>
-      <c r="CD10" s="19">
+      <c r="CC10" s="20">
+        <v>7</v>
+      </c>
+      <c r="CD10" s="18">
         <v>3</v>
       </c>
       <c r="CE10" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CF10" s="15">
-        <v>0</v>
-      </c>
-      <c r="CG10" s="16"/>
-      <c r="CH10" s="20">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CG10" s="16">
+        <v>60</v>
+      </c>
+      <c r="CH10" s="18">
+        <v>1</v>
       </c>
       <c r="CI10" s="14">
         <v>1</v>
@@ -8278,7 +8282,7 @@
         <v>1</v>
       </c>
       <c r="CK10" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CL10" s="17">
         <v>2</v>
@@ -8288,22 +8292,22 @@
       </c>
       <c r="CN10" s="16"/>
       <c r="CO10" s="17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CP10" s="15">
-        <v>4</v>
-      </c>
-      <c r="CQ10" s="16">
-        <v>14</v>
+        <v>6</v>
+      </c>
+      <c r="CQ10" s="20">
+        <v>6</v>
       </c>
       <c r="CR10" s="23">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="CS10" s="24">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="CT10" s="24">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:98">
@@ -8331,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="16"/>
-      <c r="K11" s="20">
+      <c r="K11" s="19">
         <v>0</v>
       </c>
       <c r="L11" s="14">
@@ -8341,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="16"/>
-      <c r="O11" s="20">
+      <c r="O11" s="19">
         <v>0</v>
       </c>
       <c r="P11" s="14">
@@ -8364,10 +8368,10 @@
       <c r="W11" s="15">
         <v>9</v>
       </c>
-      <c r="X11" s="18">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="19">
+      <c r="X11" s="21">
+        <v>3</v>
+      </c>
+      <c r="Y11" s="18">
         <v>4</v>
       </c>
       <c r="Z11" s="14">
@@ -8387,17 +8391,17 @@
         <v>0</v>
       </c>
       <c r="AF11" s="16"/>
-      <c r="AG11" s="20">
+      <c r="AG11" s="19">
         <v>0</v>
       </c>
       <c r="AH11" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="15">
-        <v>5</v>
-      </c>
-      <c r="AJ11" s="18">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="AJ11" s="21">
+        <v>4</v>
       </c>
       <c r="AK11" s="17">
         <v>1</v>
@@ -8405,7 +8409,7 @@
       <c r="AL11" s="15">
         <v>4</v>
       </c>
-      <c r="AM11" s="18">
+      <c r="AM11" s="21">
         <v>3</v>
       </c>
       <c r="AN11" s="17">
@@ -8414,10 +8418,10 @@
       <c r="AO11" s="15">
         <v>4</v>
       </c>
-      <c r="AP11" s="18">
-        <v>3</v>
-      </c>
-      <c r="AQ11" s="19">
+      <c r="AP11" s="21">
+        <v>3</v>
+      </c>
+      <c r="AQ11" s="18">
         <v>2</v>
       </c>
       <c r="AR11" s="14">
@@ -8426,22 +8430,22 @@
       <c r="AS11" s="15">
         <v>2</v>
       </c>
-      <c r="AT11" s="21">
+      <c r="AT11" s="20">
         <v>6</v>
       </c>
-      <c r="AU11" s="19">
+      <c r="AU11" s="18">
         <v>1</v>
       </c>
       <c r="AV11" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW11" s="15">
         <v>1</v>
       </c>
-      <c r="AX11" s="18">
-        <v>0</v>
-      </c>
-      <c r="AY11" s="19">
+      <c r="AX11" s="16">
+        <v>12</v>
+      </c>
+      <c r="AY11" s="18">
         <v>0</v>
       </c>
       <c r="AZ11" s="14">
@@ -8458,7 +8462,7 @@
         <v>0</v>
       </c>
       <c r="BE11" s="16"/>
-      <c r="BF11" s="20">
+      <c r="BF11" s="19">
         <v>0</v>
       </c>
       <c r="BG11" s="14">
@@ -8468,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="16"/>
-      <c r="BJ11" s="20">
+      <c r="BJ11" s="19">
         <v>0</v>
       </c>
       <c r="BK11" s="14">
@@ -8477,22 +8481,22 @@
       <c r="BL11" s="15">
         <v>1</v>
       </c>
-      <c r="BM11" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN11" s="19">
+      <c r="BM11" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN11" s="18">
         <v>1</v>
       </c>
       <c r="BO11" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP11" s="15">
         <v>1</v>
       </c>
-      <c r="BQ11" s="18">
-        <v>0</v>
-      </c>
-      <c r="BR11" s="19">
+      <c r="BQ11" s="16">
+        <v>12</v>
+      </c>
+      <c r="BR11" s="18">
         <v>1</v>
       </c>
       <c r="BS11" s="14">
@@ -8501,10 +8505,10 @@
       <c r="BT11" s="15">
         <v>1</v>
       </c>
-      <c r="BU11" s="18">
-        <v>0</v>
-      </c>
-      <c r="BV11" s="19">
+      <c r="BU11" s="21">
+        <v>0</v>
+      </c>
+      <c r="BV11" s="18">
         <v>1</v>
       </c>
       <c r="BW11" s="14">
@@ -8513,35 +8517,35 @@
       <c r="BX11" s="15">
         <v>3</v>
       </c>
-      <c r="BY11" s="18">
-        <v>0</v>
-      </c>
-      <c r="BZ11" s="19">
+      <c r="BY11" s="21">
+        <v>0</v>
+      </c>
+      <c r="BZ11" s="18">
         <v>2</v>
       </c>
       <c r="CA11" s="14">
+        <v>5</v>
+      </c>
+      <c r="CB11" s="15">
+        <v>9</v>
+      </c>
+      <c r="CC11" s="20">
+        <v>7</v>
+      </c>
+      <c r="CD11" s="18">
+        <v>4</v>
+      </c>
+      <c r="CE11" s="14">
         <v>6</v>
       </c>
-      <c r="CB11" s="15">
+      <c r="CF11" s="15">
         <v>8</v>
       </c>
-      <c r="CC11" s="21">
-        <v>8</v>
-      </c>
-      <c r="CD11" s="19">
-        <v>4</v>
-      </c>
-      <c r="CE11" s="14">
-        <v>7</v>
-      </c>
-      <c r="CF11" s="15">
-        <v>7</v>
-      </c>
-      <c r="CG11" s="16">
-        <v>11</v>
-      </c>
-      <c r="CH11" s="19">
-        <v>4</v>
+      <c r="CG11" s="20">
+        <v>9</v>
+      </c>
+      <c r="CH11" s="18">
+        <v>5</v>
       </c>
       <c r="CI11" s="14">
         <v>2</v>
@@ -8556,26 +8560,26 @@
       <c r="CM11" s="15">
         <v>2</v>
       </c>
-      <c r="CN11" s="18">
+      <c r="CN11" s="21">
         <v>0</v>
       </c>
       <c r="CO11" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CP11" s="15">
-        <v>7</v>
-      </c>
-      <c r="CQ11" s="18">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="CQ11" s="21">
+        <v>3</v>
       </c>
       <c r="CR11" s="23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CS11" s="24">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="CT11" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:98">
@@ -8596,18 +8600,18 @@
         <v>1</v>
       </c>
       <c r="G12" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" s="17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12" s="15">
         <v>2</v>
       </c>
-      <c r="J12" s="18">
-        <v>0</v>
-      </c>
-      <c r="K12" s="19">
+      <c r="J12" s="16">
+        <v>24</v>
+      </c>
+      <c r="K12" s="18">
         <v>2</v>
       </c>
       <c r="L12" s="14">
@@ -8617,7 +8621,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="16"/>
-      <c r="O12" s="20">
+      <c r="O12" s="19">
         <v>0</v>
       </c>
       <c r="P12" s="14">
@@ -8635,16 +8639,16 @@
       </c>
       <c r="U12" s="16"/>
       <c r="V12" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" s="16">
-        <v>66</v>
-      </c>
-      <c r="Y12" s="19">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="Y12" s="18">
+        <v>1</v>
       </c>
       <c r="Z12" s="14">
         <v>3</v>
@@ -8652,7 +8656,7 @@
       <c r="AA12" s="15">
         <v>6</v>
       </c>
-      <c r="AB12" s="21">
+      <c r="AB12" s="20">
         <v>6</v>
       </c>
       <c r="AC12" s="22">
@@ -8665,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="AF12" s="16"/>
-      <c r="AG12" s="20">
+      <c r="AG12" s="19">
         <v>0</v>
       </c>
       <c r="AH12" s="14">
@@ -8682,7 +8686,7 @@
         <v>2</v>
       </c>
       <c r="AM12" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN12" s="17">
         <v>2</v>
@@ -8691,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="AP12" s="16"/>
-      <c r="AQ12" s="20">
+      <c r="AQ12" s="19">
         <v>0</v>
       </c>
       <c r="AR12" s="14">
@@ -8701,9 +8705,9 @@
         <v>2</v>
       </c>
       <c r="AT12" s="16">
-        <v>11</v>
-      </c>
-      <c r="AU12" s="19">
+        <v>12</v>
+      </c>
+      <c r="AU12" s="18">
         <v>1</v>
       </c>
       <c r="AV12" s="14">
@@ -8713,9 +8717,9 @@
         <v>1</v>
       </c>
       <c r="AX12" s="16">
-        <v>22</v>
-      </c>
-      <c r="AY12" s="19">
+        <v>24</v>
+      </c>
+      <c r="AY12" s="18">
         <v>0</v>
       </c>
       <c r="AZ12" s="14">
@@ -8732,9 +8736,9 @@
         <v>2</v>
       </c>
       <c r="BE12" s="16">
-        <v>11</v>
-      </c>
-      <c r="BF12" s="19">
+        <v>12</v>
+      </c>
+      <c r="BF12" s="18">
         <v>1</v>
       </c>
       <c r="BG12" s="14">
@@ -8744,7 +8748,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="16"/>
-      <c r="BJ12" s="20">
+      <c r="BJ12" s="19">
         <v>0</v>
       </c>
       <c r="BK12" s="14">
@@ -8753,22 +8757,22 @@
       <c r="BL12" s="15">
         <v>2</v>
       </c>
-      <c r="BM12" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN12" s="19">
+      <c r="BM12" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN12" s="18">
         <v>1</v>
       </c>
       <c r="BO12" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BP12" s="15">
         <v>2</v>
       </c>
       <c r="BQ12" s="16">
-        <v>11</v>
-      </c>
-      <c r="BR12" s="19">
+        <v>24</v>
+      </c>
+      <c r="BR12" s="18">
         <v>1</v>
       </c>
       <c r="BS12" s="14">
@@ -8778,19 +8782,19 @@
         <v>0</v>
       </c>
       <c r="BU12" s="16"/>
-      <c r="BV12" s="20">
+      <c r="BV12" s="19">
         <v>0</v>
       </c>
       <c r="BW12" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BX12" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BY12" s="16">
-        <v>11</v>
-      </c>
-      <c r="BZ12" s="19">
+        <v>12</v>
+      </c>
+      <c r="BZ12" s="18">
         <v>1</v>
       </c>
       <c r="CA12" s="14">
@@ -8800,21 +8804,21 @@
         <v>1</v>
       </c>
       <c r="CC12" s="16">
-        <v>77</v>
-      </c>
-      <c r="CD12" s="19">
+        <v>84</v>
+      </c>
+      <c r="CD12" s="18">
         <v>0</v>
       </c>
       <c r="CE12" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CF12" s="15">
         <v>6</v>
       </c>
-      <c r="CG12" s="18">
-        <v>4</v>
-      </c>
-      <c r="CH12" s="19">
+      <c r="CG12" s="20">
+        <v>8</v>
+      </c>
+      <c r="CH12" s="18">
         <v>4</v>
       </c>
       <c r="CI12" s="14">
@@ -8832,22 +8836,22 @@
       </c>
       <c r="CN12" s="16"/>
       <c r="CO12" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CP12" s="15">
         <v>3</v>
       </c>
-      <c r="CQ12" s="21">
-        <v>7</v>
+      <c r="CQ12" s="16">
+        <v>16</v>
       </c>
       <c r="CR12" s="23">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="CS12" s="24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CT12" s="24">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:98">
@@ -8875,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="16"/>
-      <c r="K13" s="20">
+      <c r="K13" s="19">
         <v>0</v>
       </c>
       <c r="L13" s="14">
@@ -8885,7 +8889,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="16"/>
-      <c r="O13" s="20">
+      <c r="O13" s="19">
         <v>0</v>
       </c>
       <c r="P13" s="14">
@@ -8908,10 +8912,10 @@
       <c r="W13" s="15">
         <v>5</v>
       </c>
-      <c r="X13" s="21">
+      <c r="X13" s="20">
         <v>7</v>
       </c>
-      <c r="Y13" s="19">
+      <c r="Y13" s="18">
         <v>2</v>
       </c>
       <c r="Z13" s="14">
@@ -8931,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="AF13" s="16"/>
-      <c r="AG13" s="20">
+      <c r="AG13" s="19">
         <v>0</v>
       </c>
       <c r="AH13" s="14">
@@ -8955,9 +8959,9 @@
         <v>1</v>
       </c>
       <c r="AP13" s="16">
-        <v>22</v>
-      </c>
-      <c r="AQ13" s="19">
+        <v>24</v>
+      </c>
+      <c r="AQ13" s="18">
         <v>0</v>
       </c>
       <c r="AR13" s="14">
@@ -8967,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="AT13" s="16"/>
-      <c r="AU13" s="20">
+      <c r="AU13" s="19">
         <v>0</v>
       </c>
       <c r="AV13" s="14">
@@ -8977,9 +8981,9 @@
         <v>1</v>
       </c>
       <c r="AX13" s="16">
-        <v>22</v>
-      </c>
-      <c r="AY13" s="19">
+        <v>24</v>
+      </c>
+      <c r="AY13" s="18">
         <v>0</v>
       </c>
       <c r="AZ13" s="14">
@@ -8996,9 +9000,9 @@
         <v>2</v>
       </c>
       <c r="BE13" s="16">
-        <v>11</v>
-      </c>
-      <c r="BF13" s="19">
+        <v>12</v>
+      </c>
+      <c r="BF13" s="18">
         <v>1</v>
       </c>
       <c r="BG13" s="14">
@@ -9008,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="16"/>
-      <c r="BJ13" s="20">
+      <c r="BJ13" s="19">
         <v>0</v>
       </c>
       <c r="BK13" s="14">
@@ -9017,10 +9021,10 @@
       <c r="BL13" s="15">
         <v>2</v>
       </c>
-      <c r="BM13" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN13" s="19">
+      <c r="BM13" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN13" s="18">
         <v>1</v>
       </c>
       <c r="BO13" s="14">
@@ -9030,7 +9034,7 @@
         <v>0</v>
       </c>
       <c r="BQ13" s="16"/>
-      <c r="BR13" s="20">
+      <c r="BR13" s="19">
         <v>0</v>
       </c>
       <c r="BS13" s="14">
@@ -9040,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="BU13" s="16"/>
-      <c r="BV13" s="20">
+      <c r="BV13" s="19">
         <v>0</v>
       </c>
       <c r="BW13" s="14">
@@ -9050,9 +9054,9 @@
         <v>1</v>
       </c>
       <c r="BY13" s="16">
-        <v>22</v>
-      </c>
-      <c r="BZ13" s="19">
+        <v>24</v>
+      </c>
+      <c r="BZ13" s="18">
         <v>1</v>
       </c>
       <c r="CA13" s="14">
@@ -9062,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="CC13" s="16"/>
-      <c r="CD13" s="20">
+      <c r="CD13" s="19">
         <v>0</v>
       </c>
       <c r="CE13" s="14">
@@ -9072,9 +9076,9 @@
         <v>1</v>
       </c>
       <c r="CG13" s="16">
-        <v>44</v>
-      </c>
-      <c r="CH13" s="19">
+        <v>48</v>
+      </c>
+      <c r="CH13" s="18">
         <v>1</v>
       </c>
       <c r="CI13" s="14">
@@ -9098,7 +9102,7 @@
         <v>1</v>
       </c>
       <c r="CQ13" s="16">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="CR13" s="23">
         <v>52</v>
@@ -9107,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="CT13" s="24">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:98">
@@ -9135,7 +9139,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="16"/>
-      <c r="K14" s="20">
+      <c r="K14" s="19">
         <v>0</v>
       </c>
       <c r="L14" s="14">
@@ -9145,7 +9149,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="16"/>
-      <c r="O14" s="20">
+      <c r="O14" s="19">
         <v>0</v>
       </c>
       <c r="P14" s="14">
@@ -9168,10 +9172,10 @@
       <c r="W14" s="15">
         <v>6</v>
       </c>
-      <c r="X14" s="21">
+      <c r="X14" s="20">
         <v>6</v>
       </c>
-      <c r="Y14" s="19">
+      <c r="Y14" s="18">
         <v>3</v>
       </c>
       <c r="Z14" s="14">
@@ -9181,7 +9185,7 @@
         <v>2</v>
       </c>
       <c r="AB14" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC14" s="22">
         <v>1</v>
@@ -9193,9 +9197,9 @@
         <v>1</v>
       </c>
       <c r="AF14" s="16">
-        <v>11</v>
-      </c>
-      <c r="AG14" s="19">
+        <v>12</v>
+      </c>
+      <c r="AG14" s="18">
         <v>0</v>
       </c>
       <c r="AH14" s="14">
@@ -9211,31 +9215,31 @@
       <c r="AL14" s="15">
         <v>3</v>
       </c>
-      <c r="AM14" s="21">
-        <v>7</v>
+      <c r="AM14" s="20">
+        <v>8</v>
       </c>
       <c r="AN14" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO14" s="15">
         <v>4</v>
       </c>
-      <c r="AP14" s="18">
-        <v>3</v>
-      </c>
-      <c r="AQ14" s="19">
+      <c r="AP14" s="20">
+        <v>6</v>
+      </c>
+      <c r="AQ14" s="18">
         <v>2</v>
       </c>
       <c r="AR14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS14" s="15">
         <v>1</v>
       </c>
       <c r="AT14" s="16">
-        <v>22</v>
-      </c>
-      <c r="AU14" s="19">
+        <v>36</v>
+      </c>
+      <c r="AU14" s="18">
         <v>0</v>
       </c>
       <c r="AV14" s="14">
@@ -9245,9 +9249,9 @@
         <v>1</v>
       </c>
       <c r="AX14" s="16">
-        <v>22</v>
-      </c>
-      <c r="AY14" s="19">
+        <v>24</v>
+      </c>
+      <c r="AY14" s="18">
         <v>0</v>
       </c>
       <c r="AZ14" s="14">
@@ -9264,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="BE14" s="16"/>
-      <c r="BF14" s="20">
+      <c r="BF14" s="19">
         <v>0</v>
       </c>
       <c r="BG14" s="14">
@@ -9274,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="16"/>
-      <c r="BJ14" s="20">
+      <c r="BJ14" s="19">
         <v>0</v>
       </c>
       <c r="BK14" s="14">
@@ -9284,7 +9288,7 @@
         <v>0</v>
       </c>
       <c r="BM14" s="16"/>
-      <c r="BN14" s="20">
+      <c r="BN14" s="19">
         <v>0</v>
       </c>
       <c r="BO14" s="14">
@@ -9294,7 +9298,7 @@
         <v>0</v>
       </c>
       <c r="BQ14" s="16"/>
-      <c r="BR14" s="20">
+      <c r="BR14" s="19">
         <v>0</v>
       </c>
       <c r="BS14" s="14">
@@ -9303,10 +9307,10 @@
       <c r="BT14" s="15">
         <v>1</v>
       </c>
-      <c r="BU14" s="18">
-        <v>0</v>
-      </c>
-      <c r="BV14" s="19">
+      <c r="BU14" s="21">
+        <v>0</v>
+      </c>
+      <c r="BV14" s="18">
         <v>1</v>
       </c>
       <c r="BW14" s="14">
@@ -9316,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="BY14" s="16"/>
-      <c r="BZ14" s="20">
+      <c r="BZ14" s="19">
         <v>0</v>
       </c>
       <c r="CA14" s="14">
@@ -9326,22 +9330,22 @@
         <v>1</v>
       </c>
       <c r="CC14" s="16">
-        <v>55</v>
-      </c>
-      <c r="CD14" s="19">
+        <v>60</v>
+      </c>
+      <c r="CD14" s="18">
         <v>0</v>
       </c>
       <c r="CE14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CF14" s="15">
         <v>4</v>
       </c>
-      <c r="CG14" s="21">
-        <v>8</v>
-      </c>
-      <c r="CH14" s="19">
-        <v>3</v>
+      <c r="CG14" s="16">
+        <v>12</v>
+      </c>
+      <c r="CH14" s="18">
+        <v>2</v>
       </c>
       <c r="CI14" s="14">
         <v>4</v>
@@ -9351,31 +9355,31 @@
       </c>
       <c r="CK14" s="16"/>
       <c r="CL14" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM14" s="15">
         <v>2</v>
       </c>
       <c r="CN14" s="16">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="CO14" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP14" s="15">
         <v>2</v>
       </c>
       <c r="CQ14" s="16">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="CR14" s="23">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="CS14" s="24">
         <v>28</v>
       </c>
       <c r="CT14" s="24">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:98">
@@ -9403,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="16"/>
-      <c r="K15" s="20">
+      <c r="K15" s="19">
         <v>0</v>
       </c>
       <c r="L15" s="14">
@@ -9413,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="16"/>
-      <c r="O15" s="20">
+      <c r="O15" s="19">
         <v>0</v>
       </c>
       <c r="P15" s="14">
@@ -9436,11 +9440,11 @@
       <c r="W15" s="15">
         <v>8</v>
       </c>
-      <c r="X15" s="18">
-        <v>3</v>
-      </c>
-      <c r="Y15" s="19">
-        <v>4</v>
+      <c r="X15" s="21">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="18">
+        <v>3</v>
       </c>
       <c r="Z15" s="14">
         <v>3</v>
@@ -9448,8 +9452,8 @@
       <c r="AA15" s="15">
         <v>4</v>
       </c>
-      <c r="AB15" s="21">
-        <v>8</v>
+      <c r="AB15" s="20">
+        <v>9</v>
       </c>
       <c r="AC15" s="22">
         <v>2</v>
@@ -9461,7 +9465,7 @@
         <v>0</v>
       </c>
       <c r="AF15" s="16"/>
-      <c r="AG15" s="20">
+      <c r="AG15" s="19">
         <v>0</v>
       </c>
       <c r="AH15" s="14">
@@ -9477,7 +9481,7 @@
       <c r="AL15" s="15">
         <v>4</v>
       </c>
-      <c r="AM15" s="21">
+      <c r="AM15" s="20">
         <v>6</v>
       </c>
       <c r="AN15" s="17">
@@ -9487,9 +9491,9 @@
         <v>2</v>
       </c>
       <c r="AP15" s="16">
-        <v>11</v>
-      </c>
-      <c r="AQ15" s="19">
+        <v>12</v>
+      </c>
+      <c r="AQ15" s="18">
         <v>1</v>
       </c>
       <c r="AR15" s="14">
@@ -9499,7 +9503,7 @@
         <v>0</v>
       </c>
       <c r="AT15" s="16"/>
-      <c r="AU15" s="20">
+      <c r="AU15" s="19">
         <v>0</v>
       </c>
       <c r="AV15" s="14">
@@ -9508,10 +9512,10 @@
       <c r="AW15" s="15">
         <v>4</v>
       </c>
-      <c r="AX15" s="21">
+      <c r="AX15" s="20">
         <v>6</v>
       </c>
-      <c r="AY15" s="19">
+      <c r="AY15" s="18">
         <v>2</v>
       </c>
       <c r="AZ15" s="14">
@@ -9528,9 +9532,9 @@
         <v>1</v>
       </c>
       <c r="BE15" s="16">
-        <v>11</v>
-      </c>
-      <c r="BF15" s="19">
+        <v>12</v>
+      </c>
+      <c r="BF15" s="18">
         <v>1</v>
       </c>
       <c r="BG15" s="14">
@@ -9539,10 +9543,10 @@
       <c r="BH15" s="15">
         <v>1</v>
       </c>
-      <c r="BI15" s="18">
-        <v>0</v>
-      </c>
-      <c r="BJ15" s="19">
+      <c r="BI15" s="21">
+        <v>0</v>
+      </c>
+      <c r="BJ15" s="18">
         <v>1</v>
       </c>
       <c r="BK15" s="14">
@@ -9551,10 +9555,10 @@
       <c r="BL15" s="15">
         <v>2</v>
       </c>
-      <c r="BM15" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN15" s="19">
+      <c r="BM15" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN15" s="18">
         <v>1</v>
       </c>
       <c r="BO15" s="14">
@@ -9564,9 +9568,9 @@
         <v>1</v>
       </c>
       <c r="BQ15" s="16">
-        <v>33</v>
-      </c>
-      <c r="BR15" s="19">
+        <v>36</v>
+      </c>
+      <c r="BR15" s="18">
         <v>1</v>
       </c>
       <c r="BS15" s="14">
@@ -9575,10 +9579,10 @@
       <c r="BT15" s="15">
         <v>2</v>
       </c>
-      <c r="BU15" s="21">
+      <c r="BU15" s="20">
         <v>6</v>
       </c>
-      <c r="BV15" s="19">
+      <c r="BV15" s="18">
         <v>1</v>
       </c>
       <c r="BW15" s="14">
@@ -9588,7 +9592,7 @@
         <v>0</v>
       </c>
       <c r="BY15" s="16"/>
-      <c r="BZ15" s="20">
+      <c r="BZ15" s="19">
         <v>0</v>
       </c>
       <c r="CA15" s="14">
@@ -9597,10 +9601,10 @@
       <c r="CB15" s="15">
         <v>6</v>
       </c>
-      <c r="CC15" s="21">
-        <v>7</v>
-      </c>
-      <c r="CD15" s="19">
+      <c r="CC15" s="20">
+        <v>8</v>
+      </c>
+      <c r="CD15" s="18">
         <v>3</v>
       </c>
       <c r="CE15" s="14">
@@ -9610,9 +9614,9 @@
         <v>1</v>
       </c>
       <c r="CG15" s="16">
-        <v>33</v>
-      </c>
-      <c r="CH15" s="19">
+        <v>36</v>
+      </c>
+      <c r="CH15" s="18">
         <v>1</v>
       </c>
       <c r="CI15" s="14">
@@ -9622,7 +9626,7 @@
         <v>2</v>
       </c>
       <c r="CK15" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL15" s="17">
         <v>1</v>
@@ -9630,26 +9634,26 @@
       <c r="CM15" s="15">
         <v>2</v>
       </c>
-      <c r="CN15" s="21">
+      <c r="CN15" s="20">
         <v>6</v>
       </c>
       <c r="CO15" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CQ15" s="16">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="CR15" s="23">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="CS15" s="24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CT15" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:98">
@@ -9677,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="16"/>
-      <c r="K16" s="20">
+      <c r="K16" s="19">
         <v>0</v>
       </c>
       <c r="L16" s="14">
@@ -9687,7 +9691,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="16"/>
-      <c r="O16" s="20">
+      <c r="O16" s="19">
         <v>0</v>
       </c>
       <c r="P16" s="14">
@@ -9710,10 +9714,10 @@
       <c r="W16" s="15">
         <v>5</v>
       </c>
-      <c r="X16" s="21">
+      <c r="X16" s="20">
         <v>7</v>
       </c>
-      <c r="Y16" s="19">
+      <c r="Y16" s="18">
         <v>2</v>
       </c>
       <c r="Z16" s="14">
@@ -9723,7 +9727,7 @@
         <v>2</v>
       </c>
       <c r="AB16" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC16" s="22">
         <v>1</v>
@@ -9735,7 +9739,7 @@
         <v>0</v>
       </c>
       <c r="AF16" s="16"/>
-      <c r="AG16" s="20">
+      <c r="AG16" s="19">
         <v>0</v>
       </c>
       <c r="AH16" s="14">
@@ -9745,7 +9749,7 @@
         <v>1</v>
       </c>
       <c r="AJ16" s="16">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AK16" s="17">
         <v>0</v>
@@ -9753,7 +9757,7 @@
       <c r="AL16" s="15">
         <v>3</v>
       </c>
-      <c r="AM16" s="18">
+      <c r="AM16" s="21">
         <v>0</v>
       </c>
       <c r="AN16" s="17">
@@ -9763,9 +9767,9 @@
         <v>1</v>
       </c>
       <c r="AP16" s="16">
-        <v>22</v>
-      </c>
-      <c r="AQ16" s="19">
+        <v>24</v>
+      </c>
+      <c r="AQ16" s="18">
         <v>0</v>
       </c>
       <c r="AR16" s="14">
@@ -9775,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="AT16" s="16"/>
-      <c r="AU16" s="20">
+      <c r="AU16" s="19">
         <v>0</v>
       </c>
       <c r="AV16" s="14">
@@ -9785,9 +9789,9 @@
         <v>1</v>
       </c>
       <c r="AX16" s="16">
-        <v>11</v>
-      </c>
-      <c r="AY16" s="19">
+        <v>12</v>
+      </c>
+      <c r="AY16" s="18">
         <v>0</v>
       </c>
       <c r="AZ16" s="14">
@@ -9803,10 +9807,10 @@
       <c r="BD16" s="15">
         <v>2</v>
       </c>
-      <c r="BE16" s="18">
-        <v>0</v>
-      </c>
-      <c r="BF16" s="19">
+      <c r="BE16" s="21">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="18">
         <v>1</v>
       </c>
       <c r="BG16" s="14">
@@ -9816,7 +9820,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="16"/>
-      <c r="BJ16" s="20">
+      <c r="BJ16" s="19">
         <v>0</v>
       </c>
       <c r="BK16" s="14">
@@ -9826,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="BM16" s="16"/>
-      <c r="BN16" s="20">
+      <c r="BN16" s="19">
         <v>0</v>
       </c>
       <c r="BO16" s="14">
@@ -9836,9 +9840,9 @@
         <v>2</v>
       </c>
       <c r="BQ16" s="16">
-        <v>11</v>
-      </c>
-      <c r="BR16" s="19">
+        <v>12</v>
+      </c>
+      <c r="BR16" s="18">
         <v>1</v>
       </c>
       <c r="BS16" s="14">
@@ -9848,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="BU16" s="16"/>
-      <c r="BV16" s="20">
+      <c r="BV16" s="19">
         <v>0</v>
       </c>
       <c r="BW16" s="14">
@@ -9858,9 +9862,9 @@
         <v>2</v>
       </c>
       <c r="BY16" s="16">
-        <v>22</v>
-      </c>
-      <c r="BZ16" s="19">
+        <v>24</v>
+      </c>
+      <c r="BZ16" s="18">
         <v>1</v>
       </c>
       <c r="CA16" s="14">
@@ -9869,10 +9873,10 @@
       <c r="CB16" s="15">
         <v>3</v>
       </c>
-      <c r="CC16" s="21">
-        <v>7</v>
-      </c>
-      <c r="CD16" s="19">
+      <c r="CC16" s="20">
+        <v>8</v>
+      </c>
+      <c r="CD16" s="18">
         <v>1</v>
       </c>
       <c r="CE16" s="14">
@@ -9881,10 +9885,10 @@
       <c r="CF16" s="15">
         <v>3</v>
       </c>
-      <c r="CG16" s="21">
-        <v>7</v>
-      </c>
-      <c r="CH16" s="19">
+      <c r="CG16" s="20">
+        <v>8</v>
+      </c>
+      <c r="CH16" s="18">
         <v>2</v>
       </c>
       <c r="CI16" s="14">
@@ -9901,7 +9905,7 @@
         <v>1</v>
       </c>
       <c r="CN16" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CO16" s="17">
         <v>4</v>
@@ -9909,8 +9913,8 @@
       <c r="CP16" s="15">
         <v>13</v>
       </c>
-      <c r="CQ16" s="18">
-        <v>3</v>
+      <c r="CQ16" s="21">
+        <v>4</v>
       </c>
       <c r="CR16" s="23">
         <v>35</v>
@@ -9919,7 +9923,7 @@
         <v>39</v>
       </c>
       <c r="CT16" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:98">
@@ -9947,7 +9951,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="16"/>
-      <c r="K17" s="20">
+      <c r="K17" s="19">
         <v>0</v>
       </c>
       <c r="L17" s="14">
@@ -9957,7 +9961,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="16"/>
-      <c r="O17" s="20">
+      <c r="O17" s="19">
         <v>0</v>
       </c>
       <c r="P17" s="14">
@@ -9981,9 +9985,9 @@
         <v>2</v>
       </c>
       <c r="X17" s="16">
-        <v>11</v>
-      </c>
-      <c r="Y17" s="19">
+        <v>12</v>
+      </c>
+      <c r="Y17" s="18">
         <v>1</v>
       </c>
       <c r="Z17" s="14">
@@ -9993,7 +9997,7 @@
         <v>2</v>
       </c>
       <c r="AB17" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC17" s="22">
         <v>1</v>
@@ -10005,7 +10009,7 @@
         <v>0</v>
       </c>
       <c r="AF17" s="16"/>
-      <c r="AG17" s="20">
+      <c r="AG17" s="19">
         <v>0</v>
       </c>
       <c r="AH17" s="14">
@@ -10015,7 +10019,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK17" s="17">
         <v>0</v>
@@ -10031,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="AP17" s="16"/>
-      <c r="AQ17" s="20">
+      <c r="AQ17" s="19">
         <v>0</v>
       </c>
       <c r="AR17" s="14">
@@ -10041,9 +10045,9 @@
         <v>1</v>
       </c>
       <c r="AT17" s="16">
-        <v>22</v>
-      </c>
-      <c r="AU17" s="19">
+        <v>24</v>
+      </c>
+      <c r="AU17" s="18">
         <v>0</v>
       </c>
       <c r="AV17" s="14">
@@ -10053,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="AX17" s="16"/>
-      <c r="AY17" s="20">
+      <c r="AY17" s="19">
         <v>0</v>
       </c>
       <c r="AZ17" s="14">
@@ -10070,7 +10074,7 @@
         <v>0</v>
       </c>
       <c r="BE17" s="16"/>
-      <c r="BF17" s="20">
+      <c r="BF17" s="19">
         <v>0</v>
       </c>
       <c r="BG17" s="14">
@@ -10080,7 +10084,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="16"/>
-      <c r="BJ17" s="20">
+      <c r="BJ17" s="19">
         <v>0</v>
       </c>
       <c r="BK17" s="14">
@@ -10090,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="BM17" s="16"/>
-      <c r="BN17" s="20">
+      <c r="BN17" s="19">
         <v>0</v>
       </c>
       <c r="BO17" s="14">
@@ -10100,7 +10104,7 @@
         <v>0</v>
       </c>
       <c r="BQ17" s="16"/>
-      <c r="BR17" s="20">
+      <c r="BR17" s="19">
         <v>0</v>
       </c>
       <c r="BS17" s="14">
@@ -10110,7 +10114,7 @@
         <v>0</v>
       </c>
       <c r="BU17" s="16"/>
-      <c r="BV17" s="20">
+      <c r="BV17" s="19">
         <v>0</v>
       </c>
       <c r="BW17" s="14">
@@ -10120,7 +10124,7 @@
         <v>0</v>
       </c>
       <c r="BY17" s="16"/>
-      <c r="BZ17" s="20">
+      <c r="BZ17" s="19">
         <v>0</v>
       </c>
       <c r="CA17" s="14">
@@ -10130,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="CC17" s="16"/>
-      <c r="CD17" s="20">
+      <c r="CD17" s="19">
         <v>0</v>
       </c>
       <c r="CE17" s="14">
@@ -10140,7 +10144,7 @@
         <v>0</v>
       </c>
       <c r="CG17" s="16"/>
-      <c r="CH17" s="20">
+      <c r="CH17" s="19">
         <v>0</v>
       </c>
       <c r="CI17" s="14">
@@ -10171,7 +10175,7 @@
         <v>6</v>
       </c>
       <c r="CT17" s="24">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:98">
@@ -10199,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="16"/>
-      <c r="K18" s="20">
+      <c r="K18" s="19">
         <v>0</v>
       </c>
       <c r="L18" s="14">
@@ -10209,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="16"/>
-      <c r="O18" s="20">
+      <c r="O18" s="19">
         <v>0</v>
       </c>
       <c r="P18" s="14">
@@ -10227,25 +10231,25 @@
       </c>
       <c r="U18" s="16"/>
       <c r="V18" s="17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W18" s="15">
         <v>14</v>
       </c>
-      <c r="X18" s="18">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="19">
+      <c r="X18" s="20">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="18">
         <v>6</v>
       </c>
       <c r="Z18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA18" s="15">
         <v>11</v>
       </c>
-      <c r="AB18" s="18">
-        <v>3</v>
+      <c r="AB18" s="20">
+        <v>6</v>
       </c>
       <c r="AC18" s="22">
         <v>5</v>
@@ -10257,7 +10261,7 @@
         <v>0</v>
       </c>
       <c r="AF18" s="16"/>
-      <c r="AG18" s="20">
+      <c r="AG18" s="19">
         <v>0</v>
       </c>
       <c r="AH18" s="14">
@@ -10273,7 +10277,7 @@
       <c r="AL18" s="15">
         <v>3</v>
       </c>
-      <c r="AM18" s="18">
+      <c r="AM18" s="21">
         <v>4</v>
       </c>
       <c r="AN18" s="17">
@@ -10282,22 +10286,22 @@
       <c r="AO18" s="15">
         <v>2</v>
       </c>
-      <c r="AP18" s="21">
+      <c r="AP18" s="20">
         <v>6</v>
       </c>
-      <c r="AQ18" s="19">
+      <c r="AQ18" s="18">
         <v>1</v>
       </c>
       <c r="AR18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS18" s="15">
         <v>3</v>
       </c>
-      <c r="AT18" s="21">
-        <v>7</v>
-      </c>
-      <c r="AU18" s="19">
+      <c r="AT18" s="16">
+        <v>16</v>
+      </c>
+      <c r="AU18" s="18">
         <v>1</v>
       </c>
       <c r="AV18" s="14">
@@ -10307,9 +10311,9 @@
         <v>1</v>
       </c>
       <c r="AX18" s="16">
-        <v>33</v>
-      </c>
-      <c r="AY18" s="19">
+        <v>36</v>
+      </c>
+      <c r="AY18" s="18">
         <v>0</v>
       </c>
       <c r="AZ18" s="14">
@@ -10325,10 +10329,10 @@
       <c r="BD18" s="15">
         <v>2</v>
       </c>
-      <c r="BE18" s="18">
-        <v>0</v>
-      </c>
-      <c r="BF18" s="19">
+      <c r="BE18" s="21">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="18">
         <v>1</v>
       </c>
       <c r="BG18" s="14">
@@ -10338,7 +10342,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="16"/>
-      <c r="BJ18" s="20">
+      <c r="BJ18" s="19">
         <v>0</v>
       </c>
       <c r="BK18" s="14">
@@ -10347,10 +10351,10 @@
       <c r="BL18" s="15">
         <v>1</v>
       </c>
-      <c r="BM18" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN18" s="19">
+      <c r="BM18" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN18" s="18">
         <v>1</v>
       </c>
       <c r="BO18" s="14">
@@ -10360,9 +10364,9 @@
         <v>2</v>
       </c>
       <c r="BQ18" s="16">
-        <v>11</v>
-      </c>
-      <c r="BR18" s="19">
+        <v>12</v>
+      </c>
+      <c r="BR18" s="18">
         <v>1</v>
       </c>
       <c r="BS18" s="14">
@@ -10372,32 +10376,32 @@
         <v>0</v>
       </c>
       <c r="BU18" s="16"/>
-      <c r="BV18" s="20">
+      <c r="BV18" s="19">
         <v>0</v>
       </c>
       <c r="BW18" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BX18" s="15">
         <v>6</v>
       </c>
-      <c r="BY18" s="18">
-        <v>0</v>
-      </c>
-      <c r="BZ18" s="19">
+      <c r="BY18" s="21">
         <v>4</v>
       </c>
+      <c r="BZ18" s="18">
+        <v>4</v>
+      </c>
       <c r="CA18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CB18" s="15">
         <v>8</v>
       </c>
-      <c r="CC18" s="21">
-        <v>6</v>
-      </c>
-      <c r="CD18" s="19">
-        <v>4</v>
+      <c r="CC18" s="20">
+        <v>9</v>
+      </c>
+      <c r="CD18" s="18">
+        <v>3</v>
       </c>
       <c r="CE18" s="14">
         <v>6</v>
@@ -10406,19 +10410,19 @@
         <v>4</v>
       </c>
       <c r="CG18" s="16">
-        <v>17</v>
-      </c>
-      <c r="CH18" s="19">
-        <v>3</v>
+        <v>18</v>
+      </c>
+      <c r="CH18" s="18">
+        <v>2</v>
       </c>
       <c r="CI18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ18" s="15">
         <v>3</v>
       </c>
-      <c r="CK18" s="18">
-        <v>4</v>
+      <c r="CK18" s="20">
+        <v>8</v>
       </c>
       <c r="CL18" s="17">
         <v>2</v>
@@ -10428,22 +10432,22 @@
       </c>
       <c r="CN18" s="16"/>
       <c r="CO18" s="17">
+        <v>9</v>
+      </c>
+      <c r="CP18" s="15">
+        <v>11</v>
+      </c>
+      <c r="CQ18" s="20">
         <v>10</v>
       </c>
-      <c r="CP18" s="15">
+      <c r="CR18" s="23">
+        <v>58</v>
+      </c>
+      <c r="CS18" s="24">
+        <v>71</v>
+      </c>
+      <c r="CT18" s="24">
         <v>10</v>
-      </c>
-      <c r="CQ18" s="16">
-        <v>11</v>
-      </c>
-      <c r="CR18" s="23">
-        <v>45</v>
-      </c>
-      <c r="CS18" s="24">
-        <v>70</v>
-      </c>
-      <c r="CT18" s="24">
-        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:98">
@@ -10471,7 +10475,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="16"/>
-      <c r="K19" s="20">
+      <c r="K19" s="19">
         <v>0</v>
       </c>
       <c r="L19" s="14">
@@ -10481,7 +10485,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="16"/>
-      <c r="O19" s="20">
+      <c r="O19" s="19">
         <v>0</v>
       </c>
       <c r="P19" s="14">
@@ -10505,7 +10509,7 @@
         <v>0</v>
       </c>
       <c r="X19" s="16"/>
-      <c r="Y19" s="20">
+      <c r="Y19" s="19">
         <v>0</v>
       </c>
       <c r="Z19" s="14">
@@ -10514,7 +10518,7 @@
       <c r="AA19" s="15">
         <v>2</v>
       </c>
-      <c r="AB19" s="18">
+      <c r="AB19" s="21">
         <v>0</v>
       </c>
       <c r="AC19" s="22">
@@ -10527,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="AF19" s="16"/>
-      <c r="AG19" s="20">
+      <c r="AG19" s="19">
         <v>0</v>
       </c>
       <c r="AH19" s="14">
@@ -10536,7 +10540,7 @@
       <c r="AI19" s="15">
         <v>1</v>
       </c>
-      <c r="AJ19" s="18">
+      <c r="AJ19" s="21">
         <v>0</v>
       </c>
       <c r="AK19" s="17">
@@ -10553,7 +10557,7 @@
         <v>0</v>
       </c>
       <c r="AP19" s="16"/>
-      <c r="AQ19" s="20">
+      <c r="AQ19" s="19">
         <v>0</v>
       </c>
       <c r="AR19" s="14">
@@ -10563,7 +10567,7 @@
         <v>0</v>
       </c>
       <c r="AT19" s="16"/>
-      <c r="AU19" s="20">
+      <c r="AU19" s="19">
         <v>0</v>
       </c>
       <c r="AV19" s="14">
@@ -10573,7 +10577,7 @@
         <v>0</v>
       </c>
       <c r="AX19" s="16"/>
-      <c r="AY19" s="20">
+      <c r="AY19" s="19">
         <v>0</v>
       </c>
       <c r="AZ19" s="14">
@@ -10589,10 +10593,10 @@
       <c r="BD19" s="15">
         <v>1</v>
       </c>
-      <c r="BE19" s="18">
-        <v>0</v>
-      </c>
-      <c r="BF19" s="19">
+      <c r="BE19" s="21">
+        <v>0</v>
+      </c>
+      <c r="BF19" s="18">
         <v>1</v>
       </c>
       <c r="BG19" s="14">
@@ -10602,7 +10606,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="16"/>
-      <c r="BJ19" s="20">
+      <c r="BJ19" s="19">
         <v>0</v>
       </c>
       <c r="BK19" s="14">
@@ -10611,10 +10615,10 @@
       <c r="BL19" s="15">
         <v>1</v>
       </c>
-      <c r="BM19" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN19" s="19">
+      <c r="BM19" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN19" s="18">
         <v>1</v>
       </c>
       <c r="BO19" s="14">
@@ -10624,7 +10628,7 @@
         <v>0</v>
       </c>
       <c r="BQ19" s="16"/>
-      <c r="BR19" s="20">
+      <c r="BR19" s="19">
         <v>0</v>
       </c>
       <c r="BS19" s="14">
@@ -10634,7 +10638,7 @@
         <v>0</v>
       </c>
       <c r="BU19" s="16"/>
-      <c r="BV19" s="20">
+      <c r="BV19" s="19">
         <v>0</v>
       </c>
       <c r="BW19" s="14">
@@ -10644,7 +10648,7 @@
         <v>0</v>
       </c>
       <c r="BY19" s="16"/>
-      <c r="BZ19" s="20">
+      <c r="BZ19" s="19">
         <v>0</v>
       </c>
       <c r="CA19" s="14">
@@ -10654,9 +10658,9 @@
         <v>1</v>
       </c>
       <c r="CC19" s="16">
-        <v>22</v>
-      </c>
-      <c r="CD19" s="19">
+        <v>24</v>
+      </c>
+      <c r="CD19" s="18">
         <v>0</v>
       </c>
       <c r="CE19" s="14">
@@ -10666,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="CG19" s="16"/>
-      <c r="CH19" s="20">
+      <c r="CH19" s="19">
         <v>0</v>
       </c>
       <c r="CI19" s="14">
@@ -10675,7 +10679,7 @@
       <c r="CJ19" s="15">
         <v>1</v>
       </c>
-      <c r="CK19" s="18">
+      <c r="CK19" s="21">
         <v>0</v>
       </c>
       <c r="CL19" s="17">
@@ -10699,7 +10703,7 @@
         <v>7</v>
       </c>
       <c r="CT19" s="24">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:98">
@@ -10726,10 +10730,10 @@
       <c r="I20" s="15">
         <v>2</v>
       </c>
-      <c r="J20" s="18">
-        <v>0</v>
-      </c>
-      <c r="K20" s="19">
+      <c r="J20" s="21">
+        <v>0</v>
+      </c>
+      <c r="K20" s="18">
         <v>2</v>
       </c>
       <c r="L20" s="14">
@@ -10739,7 +10743,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="16"/>
-      <c r="O20" s="20">
+      <c r="O20" s="19">
         <v>0</v>
       </c>
       <c r="P20" s="14">
@@ -10762,20 +10766,20 @@
       <c r="W20" s="15">
         <v>12</v>
       </c>
-      <c r="X20" s="21">
+      <c r="X20" s="20">
         <v>6</v>
       </c>
-      <c r="Y20" s="19">
+      <c r="Y20" s="18">
         <v>5</v>
       </c>
       <c r="Z20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA20" s="15">
-        <v>10</v>
-      </c>
-      <c r="AB20" s="18">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="AB20" s="21">
+        <v>3</v>
       </c>
       <c r="AC20" s="22">
         <v>5</v>
@@ -10786,10 +10790,10 @@
       <c r="AE20" s="15">
         <v>2</v>
       </c>
-      <c r="AF20" s="21">
+      <c r="AF20" s="20">
         <v>6</v>
       </c>
-      <c r="AG20" s="19">
+      <c r="AG20" s="18">
         <v>1</v>
       </c>
       <c r="AH20" s="14">
@@ -10800,13 +10804,13 @@
       </c>
       <c r="AJ20" s="16"/>
       <c r="AK20" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL20" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM20" s="21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN20" s="17">
         <v>4</v>
@@ -10815,9 +10819,9 @@
         <v>4</v>
       </c>
       <c r="AP20" s="16">
-        <v>11</v>
-      </c>
-      <c r="AQ20" s="19">
+        <v>12</v>
+      </c>
+      <c r="AQ20" s="18">
         <v>2</v>
       </c>
       <c r="AR20" s="14">
@@ -10827,7 +10831,7 @@
         <v>0</v>
       </c>
       <c r="AT20" s="16"/>
-      <c r="AU20" s="20">
+      <c r="AU20" s="19">
         <v>0</v>
       </c>
       <c r="AV20" s="14">
@@ -10837,9 +10841,9 @@
         <v>2</v>
       </c>
       <c r="AX20" s="16">
-        <v>11</v>
-      </c>
-      <c r="AY20" s="19">
+        <v>12</v>
+      </c>
+      <c r="AY20" s="18">
         <v>1</v>
       </c>
       <c r="AZ20" s="14">
@@ -10856,9 +10860,9 @@
         <v>2</v>
       </c>
       <c r="BE20" s="16">
-        <v>22</v>
-      </c>
-      <c r="BF20" s="19">
+        <v>24</v>
+      </c>
+      <c r="BF20" s="18">
         <v>1</v>
       </c>
       <c r="BG20" s="14">
@@ -10868,7 +10872,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="16"/>
-      <c r="BJ20" s="20">
+      <c r="BJ20" s="19">
         <v>0</v>
       </c>
       <c r="BK20" s="14">
@@ -10878,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="BM20" s="16"/>
-      <c r="BN20" s="20">
+      <c r="BN20" s="19">
         <v>0</v>
       </c>
       <c r="BO20" s="14">
@@ -10887,10 +10891,10 @@
       <c r="BP20" s="15">
         <v>4</v>
       </c>
-      <c r="BQ20" s="18">
-        <v>3</v>
-      </c>
-      <c r="BR20" s="19">
+      <c r="BQ20" s="21">
+        <v>3</v>
+      </c>
+      <c r="BR20" s="18">
         <v>3</v>
       </c>
       <c r="BS20" s="14">
@@ -10900,7 +10904,7 @@
         <v>0</v>
       </c>
       <c r="BU20" s="16"/>
-      <c r="BV20" s="20">
+      <c r="BV20" s="19">
         <v>0</v>
       </c>
       <c r="BW20" s="14">
@@ -10910,9 +10914,9 @@
         <v>3</v>
       </c>
       <c r="BY20" s="16">
-        <v>11</v>
-      </c>
-      <c r="BZ20" s="19">
+        <v>12</v>
+      </c>
+      <c r="BZ20" s="18">
         <v>2</v>
       </c>
       <c r="CA20" s="14">
@@ -10922,22 +10926,22 @@
         <v>7</v>
       </c>
       <c r="CC20" s="16">
-        <v>13</v>
-      </c>
-      <c r="CD20" s="19">
+        <v>14</v>
+      </c>
+      <c r="CD20" s="18">
         <v>3</v>
       </c>
       <c r="CE20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CF20" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CG20" s="16">
-        <v>20</v>
-      </c>
-      <c r="CH20" s="19">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="CH20" s="18">
+        <v>4</v>
       </c>
       <c r="CI20" s="14">
         <v>2</v>
@@ -10945,8 +10949,8 @@
       <c r="CJ20" s="15">
         <v>3</v>
       </c>
-      <c r="CK20" s="21">
-        <v>7</v>
+      <c r="CK20" s="20">
+        <v>8</v>
       </c>
       <c r="CL20" s="17">
         <v>4</v>
@@ -10956,19 +10960,19 @@
       </c>
       <c r="CN20" s="16"/>
       <c r="CO20" s="17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CP20" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CQ20" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CR20" s="23">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="CS20" s="24">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="CT20" s="24">
         <v>9</v>
@@ -10999,7 +11003,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="16"/>
-      <c r="K21" s="20">
+      <c r="K21" s="19">
         <v>0</v>
       </c>
       <c r="L21" s="14">
@@ -11009,7 +11013,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="16"/>
-      <c r="O21" s="20">
+      <c r="O21" s="19">
         <v>0</v>
       </c>
       <c r="P21" s="14">
@@ -11033,9 +11037,9 @@
         <v>1</v>
       </c>
       <c r="X21" s="16">
-        <v>22</v>
-      </c>
-      <c r="Y21" s="19">
+        <v>24</v>
+      </c>
+      <c r="Y21" s="18">
         <v>0</v>
       </c>
       <c r="Z21" s="14">
@@ -11045,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="AB21" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC21" s="22">
         <v>0</v>
@@ -11057,7 +11061,7 @@
         <v>0</v>
       </c>
       <c r="AF21" s="16"/>
-      <c r="AG21" s="20">
+      <c r="AG21" s="19">
         <v>0</v>
       </c>
       <c r="AH21" s="14">
@@ -11066,8 +11070,8 @@
       <c r="AI21" s="15">
         <v>3</v>
       </c>
-      <c r="AJ21" s="21">
-        <v>7</v>
+      <c r="AJ21" s="20">
+        <v>8</v>
       </c>
       <c r="AK21" s="17">
         <v>2</v>
@@ -11076,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="AM21" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AN21" s="17">
         <v>2</v>
@@ -11085,9 +11089,9 @@
         <v>1</v>
       </c>
       <c r="AP21" s="16">
-        <v>22</v>
-      </c>
-      <c r="AQ21" s="19">
+        <v>24</v>
+      </c>
+      <c r="AQ21" s="18">
         <v>0</v>
       </c>
       <c r="AR21" s="14">
@@ -11097,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="AT21" s="16"/>
-      <c r="AU21" s="20">
+      <c r="AU21" s="19">
         <v>0</v>
       </c>
       <c r="AV21" s="14">
@@ -11107,7 +11111,7 @@
         <v>0</v>
       </c>
       <c r="AX21" s="16"/>
-      <c r="AY21" s="20">
+      <c r="AY21" s="19">
         <v>0</v>
       </c>
       <c r="AZ21" s="14">
@@ -11124,7 +11128,7 @@
         <v>0</v>
       </c>
       <c r="BE21" s="16"/>
-      <c r="BF21" s="20">
+      <c r="BF21" s="19">
         <v>0</v>
       </c>
       <c r="BG21" s="14">
@@ -11134,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="16"/>
-      <c r="BJ21" s="20">
+      <c r="BJ21" s="19">
         <v>0</v>
       </c>
       <c r="BK21" s="14">
@@ -11144,7 +11148,7 @@
         <v>0</v>
       </c>
       <c r="BM21" s="16"/>
-      <c r="BN21" s="20">
+      <c r="BN21" s="19">
         <v>0</v>
       </c>
       <c r="BO21" s="14">
@@ -11154,7 +11158,7 @@
         <v>0</v>
       </c>
       <c r="BQ21" s="16"/>
-      <c r="BR21" s="20">
+      <c r="BR21" s="19">
         <v>0</v>
       </c>
       <c r="BS21" s="14">
@@ -11164,7 +11168,7 @@
         <v>0</v>
       </c>
       <c r="BU21" s="16"/>
-      <c r="BV21" s="20">
+      <c r="BV21" s="19">
         <v>0</v>
       </c>
       <c r="BW21" s="14">
@@ -11174,9 +11178,9 @@
         <v>2</v>
       </c>
       <c r="BY21" s="16">
-        <v>17</v>
-      </c>
-      <c r="BZ21" s="19">
+        <v>18</v>
+      </c>
+      <c r="BZ21" s="18">
         <v>1</v>
       </c>
       <c r="CA21" s="14">
@@ -11186,7 +11190,7 @@
         <v>0</v>
       </c>
       <c r="CC21" s="16"/>
-      <c r="CD21" s="20">
+      <c r="CD21" s="19">
         <v>0</v>
       </c>
       <c r="CE21" s="14">
@@ -11196,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="CG21" s="16"/>
-      <c r="CH21" s="20">
+      <c r="CH21" s="19">
         <v>0</v>
       </c>
       <c r="CI21" s="14">
@@ -11220,7 +11224,7 @@
         <v>1</v>
       </c>
       <c r="CQ21" s="16">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="CR21" s="23">
         <v>44</v>
@@ -11229,7 +11233,7 @@
         <v>10</v>
       </c>
       <c r="CT21" s="24">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:98">
@@ -11256,10 +11260,10 @@
       <c r="I22" s="15">
         <v>1</v>
       </c>
-      <c r="J22" s="18">
-        <v>0</v>
-      </c>
-      <c r="K22" s="19">
+      <c r="J22" s="21">
+        <v>0</v>
+      </c>
+      <c r="K22" s="18">
         <v>1</v>
       </c>
       <c r="L22" s="14">
@@ -11269,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="16"/>
-      <c r="O22" s="20">
+      <c r="O22" s="19">
         <v>0</v>
       </c>
       <c r="P22" s="14">
@@ -11287,25 +11291,25 @@
       </c>
       <c r="U22" s="16"/>
       <c r="V22" s="17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W22" s="15">
-        <v>27</v>
-      </c>
-      <c r="X22" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="19">
+        <v>28</v>
+      </c>
+      <c r="X22" s="21">
+        <v>2</v>
+      </c>
+      <c r="Y22" s="18">
         <v>12</v>
       </c>
       <c r="Z22" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA22" s="15">
         <v>12</v>
       </c>
-      <c r="AB22" s="18">
-        <v>0</v>
+      <c r="AB22" s="20">
+        <v>6</v>
       </c>
       <c r="AC22" s="22">
         <v>5</v>
@@ -11317,9 +11321,9 @@
         <v>1</v>
       </c>
       <c r="AF22" s="16">
-        <v>11</v>
-      </c>
-      <c r="AG22" s="19">
+        <v>12</v>
+      </c>
+      <c r="AG22" s="18">
         <v>0</v>
       </c>
       <c r="AH22" s="14">
@@ -11329,16 +11333,16 @@
         <v>2</v>
       </c>
       <c r="AJ22" s="16">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AK22" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" s="15">
-        <v>11</v>
-      </c>
-      <c r="AM22" s="18">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="AM22" s="21">
+        <v>0</v>
       </c>
       <c r="AN22" s="17">
         <v>1</v>
@@ -11346,10 +11350,10 @@
       <c r="AO22" s="15">
         <v>6</v>
       </c>
-      <c r="AP22" s="18">
-        <v>2</v>
-      </c>
-      <c r="AQ22" s="19">
+      <c r="AP22" s="21">
+        <v>2</v>
+      </c>
+      <c r="AQ22" s="18">
         <v>3</v>
       </c>
       <c r="AR22" s="14">
@@ -11359,21 +11363,21 @@
         <v>2</v>
       </c>
       <c r="AT22" s="16">
-        <v>11</v>
-      </c>
-      <c r="AU22" s="19">
+        <v>12</v>
+      </c>
+      <c r="AU22" s="18">
         <v>1</v>
       </c>
       <c r="AV22" s="14">
         <v>0</v>
       </c>
       <c r="AW22" s="15">
-        <v>2</v>
-      </c>
-      <c r="AX22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AY22" s="19">
+        <v>3</v>
+      </c>
+      <c r="AX22" s="21">
+        <v>0</v>
+      </c>
+      <c r="AY22" s="18">
         <v>1</v>
       </c>
       <c r="AZ22" s="14">
@@ -11389,10 +11393,10 @@
       <c r="BD22" s="15">
         <v>2</v>
       </c>
-      <c r="BE22" s="18">
-        <v>0</v>
-      </c>
-      <c r="BF22" s="19">
+      <c r="BE22" s="21">
+        <v>0</v>
+      </c>
+      <c r="BF22" s="18">
         <v>1</v>
       </c>
       <c r="BG22" s="14">
@@ -11402,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="16"/>
-      <c r="BJ22" s="20">
+      <c r="BJ22" s="19">
         <v>0</v>
       </c>
       <c r="BK22" s="14">
@@ -11411,23 +11415,23 @@
       <c r="BL22" s="15">
         <v>1</v>
       </c>
-      <c r="BM22" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN22" s="19">
+      <c r="BM22" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN22" s="18">
         <v>1</v>
       </c>
       <c r="BO22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BP22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ22" s="16">
-        <v>22</v>
-      </c>
-      <c r="BR22" s="19">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="BR22" s="18">
+        <v>2</v>
       </c>
       <c r="BS22" s="14">
         <v>0</v>
@@ -11436,7 +11440,7 @@
         <v>0</v>
       </c>
       <c r="BU22" s="16"/>
-      <c r="BV22" s="20">
+      <c r="BV22" s="19">
         <v>0</v>
       </c>
       <c r="BW22" s="14">
@@ -11445,22 +11449,22 @@
       <c r="BX22" s="15">
         <v>5</v>
       </c>
-      <c r="BY22" s="21">
-        <v>9</v>
-      </c>
-      <c r="BZ22" s="19">
-        <v>4</v>
+      <c r="BY22" s="20">
+        <v>10</v>
+      </c>
+      <c r="BZ22" s="18">
+        <v>3</v>
       </c>
       <c r="CA22" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CB22" s="15">
-        <v>12</v>
-      </c>
-      <c r="CC22" s="21">
+        <v>13</v>
+      </c>
+      <c r="CC22" s="20">
         <v>6</v>
       </c>
-      <c r="CD22" s="19">
+      <c r="CD22" s="18">
         <v>5</v>
       </c>
       <c r="CE22" s="14">
@@ -11469,20 +11473,20 @@
       <c r="CF22" s="15">
         <v>8</v>
       </c>
-      <c r="CG22" s="21">
-        <v>8</v>
-      </c>
-      <c r="CH22" s="19">
+      <c r="CG22" s="20">
+        <v>9</v>
+      </c>
+      <c r="CH22" s="18">
         <v>5</v>
       </c>
       <c r="CI22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CJ22" s="15">
         <v>1</v>
       </c>
       <c r="CK22" s="16">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="CL22" s="17">
         <v>2</v>
@@ -11491,25 +11495,25 @@
         <v>2</v>
       </c>
       <c r="CN22" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CO22" s="17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CP22" s="15">
         <v>18</v>
       </c>
-      <c r="CQ22" s="18">
-        <v>0</v>
+      <c r="CQ22" s="21">
+        <v>5</v>
       </c>
       <c r="CR22" s="23">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="CS22" s="24">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="CT22" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:98">
@@ -11537,7 +11541,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="16"/>
-      <c r="K23" s="20">
+      <c r="K23" s="19">
         <v>0</v>
       </c>
       <c r="L23" s="14">
@@ -11547,7 +11551,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="16"/>
-      <c r="O23" s="20">
+      <c r="O23" s="19">
         <v>0</v>
       </c>
       <c r="P23" s="14">
@@ -11570,11 +11574,11 @@
       <c r="W23" s="15">
         <v>15</v>
       </c>
-      <c r="X23" s="21">
+      <c r="X23" s="20">
         <v>7</v>
       </c>
-      <c r="Y23" s="19">
-        <v>7</v>
+      <c r="Y23" s="18">
+        <v>6</v>
       </c>
       <c r="Z23" s="14">
         <v>8</v>
@@ -11582,8 +11586,8 @@
       <c r="AA23" s="15">
         <v>11</v>
       </c>
-      <c r="AB23" s="21">
-        <v>8</v>
+      <c r="AB23" s="20">
+        <v>9</v>
       </c>
       <c r="AC23" s="22">
         <v>5</v>
@@ -11595,7 +11599,7 @@
         <v>0</v>
       </c>
       <c r="AF23" s="16"/>
-      <c r="AG23" s="20">
+      <c r="AG23" s="19">
         <v>0</v>
       </c>
       <c r="AH23" s="14">
@@ -11606,13 +11610,13 @@
       </c>
       <c r="AJ23" s="16"/>
       <c r="AK23" s="17">
+        <v>3</v>
+      </c>
+      <c r="AL23" s="15">
         <v>5</v>
       </c>
-      <c r="AL23" s="15">
-        <v>3</v>
-      </c>
-      <c r="AM23" s="16">
-        <v>18</v>
+      <c r="AM23" s="20">
+        <v>7</v>
       </c>
       <c r="AN23" s="17">
         <v>6</v>
@@ -11621,9 +11625,9 @@
         <v>4</v>
       </c>
       <c r="AP23" s="16">
-        <v>17</v>
-      </c>
-      <c r="AQ23" s="19">
+        <v>18</v>
+      </c>
+      <c r="AQ23" s="18">
         <v>2</v>
       </c>
       <c r="AR23" s="14">
@@ -11633,9 +11637,9 @@
         <v>1</v>
       </c>
       <c r="AT23" s="16">
-        <v>33</v>
-      </c>
-      <c r="AU23" s="19">
+        <v>36</v>
+      </c>
+      <c r="AU23" s="18">
         <v>0</v>
       </c>
       <c r="AV23" s="14">
@@ -11644,10 +11648,10 @@
       <c r="AW23" s="15">
         <v>7</v>
       </c>
-      <c r="AX23" s="21">
-        <v>6</v>
-      </c>
-      <c r="AY23" s="19">
+      <c r="AX23" s="20">
+        <v>7</v>
+      </c>
+      <c r="AY23" s="18">
         <v>3</v>
       </c>
       <c r="AZ23" s="14">
@@ -11664,9 +11668,9 @@
         <v>3</v>
       </c>
       <c r="BE23" s="16">
-        <v>11</v>
-      </c>
-      <c r="BF23" s="19">
+        <v>12</v>
+      </c>
+      <c r="BF23" s="18">
         <v>2</v>
       </c>
       <c r="BG23" s="14">
@@ -11676,7 +11680,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="16"/>
-      <c r="BJ23" s="20">
+      <c r="BJ23" s="19">
         <v>0</v>
       </c>
       <c r="BK23" s="14">
@@ -11685,10 +11689,10 @@
       <c r="BL23" s="15">
         <v>1</v>
       </c>
-      <c r="BM23" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN23" s="19">
+      <c r="BM23" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN23" s="18">
         <v>1</v>
       </c>
       <c r="BO23" s="14">
@@ -11698,9 +11702,9 @@
         <v>4</v>
       </c>
       <c r="BQ23" s="16">
-        <v>19</v>
-      </c>
-      <c r="BR23" s="19">
+        <v>21</v>
+      </c>
+      <c r="BR23" s="18">
         <v>3</v>
       </c>
       <c r="BS23" s="14">
@@ -11710,7 +11714,7 @@
         <v>0</v>
       </c>
       <c r="BU23" s="16"/>
-      <c r="BV23" s="20">
+      <c r="BV23" s="19">
         <v>0</v>
       </c>
       <c r="BW23" s="14">
@@ -11720,33 +11724,33 @@
         <v>3</v>
       </c>
       <c r="BY23" s="16">
-        <v>11</v>
-      </c>
-      <c r="BZ23" s="19">
+        <v>12</v>
+      </c>
+      <c r="BZ23" s="18">
         <v>2</v>
       </c>
       <c r="CA23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CB23" s="15">
+        <v>9</v>
+      </c>
+      <c r="CC23" s="20">
         <v>8</v>
       </c>
-      <c r="CC23" s="21">
+      <c r="CD23" s="18">
+        <v>4</v>
+      </c>
+      <c r="CE23" s="14">
+        <v>8</v>
+      </c>
+      <c r="CF23" s="15">
         <v>10</v>
       </c>
-      <c r="CD23" s="19">
-        <v>4</v>
-      </c>
-      <c r="CE23" s="14">
-        <v>9</v>
-      </c>
-      <c r="CF23" s="15">
-        <v>9</v>
-      </c>
-      <c r="CG23" s="16">
-        <v>11</v>
-      </c>
-      <c r="CH23" s="19">
+      <c r="CG23" s="20">
+        <v>10</v>
+      </c>
+      <c r="CH23" s="18">
         <v>6</v>
       </c>
       <c r="CI23" s="14">
@@ -11756,7 +11760,7 @@
         <v>2</v>
       </c>
       <c r="CK23" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CL23" s="17">
         <v>2</v>
@@ -11766,22 +11770,22 @@
       </c>
       <c r="CN23" s="16"/>
       <c r="CO23" s="17">
+        <v>4</v>
+      </c>
+      <c r="CP23" s="15">
+        <v>27</v>
+      </c>
+      <c r="CQ23" s="21">
+        <v>2</v>
+      </c>
+      <c r="CR23" s="23">
+        <v>76</v>
+      </c>
+      <c r="CS23" s="24">
+        <v>102</v>
+      </c>
+      <c r="CT23" s="24">
         <v>9</v>
-      </c>
-      <c r="CP23" s="15">
-        <v>22</v>
-      </c>
-      <c r="CQ23" s="18">
-        <v>5</v>
-      </c>
-      <c r="CR23" s="23">
-        <v>85</v>
-      </c>
-      <c r="CS23" s="24">
-        <v>93</v>
-      </c>
-      <c r="CT23" s="24">
-        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:98">
@@ -11803,13 +11807,13 @@
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="15">
         <v>0</v>
       </c>
       <c r="J24" s="16"/>
-      <c r="K24" s="20">
+      <c r="K24" s="19">
         <v>0</v>
       </c>
       <c r="L24" s="14">
@@ -11819,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="16"/>
-      <c r="O24" s="20">
+      <c r="O24" s="19">
         <v>0</v>
       </c>
       <c r="P24" s="14">
@@ -11843,9 +11847,9 @@
         <v>2</v>
       </c>
       <c r="X24" s="16">
-        <v>17</v>
-      </c>
-      <c r="Y24" s="19">
+        <v>18</v>
+      </c>
+      <c r="Y24" s="18">
         <v>1</v>
       </c>
       <c r="Z24" s="14">
@@ -11865,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="AF24" s="16"/>
-      <c r="AG24" s="20">
+      <c r="AG24" s="19">
         <v>0</v>
       </c>
       <c r="AH24" s="14">
@@ -11889,9 +11893,9 @@
         <v>1</v>
       </c>
       <c r="AP24" s="16">
-        <v>11</v>
-      </c>
-      <c r="AQ24" s="19">
+        <v>12</v>
+      </c>
+      <c r="AQ24" s="18">
         <v>0</v>
       </c>
       <c r="AR24" s="14">
@@ -11901,7 +11905,7 @@
         <v>0</v>
       </c>
       <c r="AT24" s="16"/>
-      <c r="AU24" s="20">
+      <c r="AU24" s="19">
         <v>0</v>
       </c>
       <c r="AV24" s="14">
@@ -11911,7 +11915,7 @@
         <v>0</v>
       </c>
       <c r="AX24" s="16"/>
-      <c r="AY24" s="20">
+      <c r="AY24" s="19">
         <v>0</v>
       </c>
       <c r="AZ24" s="14">
@@ -11927,10 +11931,10 @@
       <c r="BD24" s="15">
         <v>2</v>
       </c>
-      <c r="BE24" s="18">
-        <v>0</v>
-      </c>
-      <c r="BF24" s="19">
+      <c r="BE24" s="21">
+        <v>0</v>
+      </c>
+      <c r="BF24" s="18">
         <v>1</v>
       </c>
       <c r="BG24" s="14">
@@ -11940,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="16"/>
-      <c r="BJ24" s="20">
+      <c r="BJ24" s="19">
         <v>0</v>
       </c>
       <c r="BK24" s="14">
@@ -11949,22 +11953,22 @@
       <c r="BL24" s="15">
         <v>1</v>
       </c>
-      <c r="BM24" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN24" s="19">
+      <c r="BM24" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN24" s="18">
         <v>1</v>
       </c>
       <c r="BO24" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BP24" s="15">
         <v>1</v>
       </c>
       <c r="BQ24" s="16">
-        <v>22</v>
-      </c>
-      <c r="BR24" s="19">
+        <v>36</v>
+      </c>
+      <c r="BR24" s="18">
         <v>1</v>
       </c>
       <c r="BS24" s="14">
@@ -11974,7 +11978,7 @@
         <v>0</v>
       </c>
       <c r="BU24" s="16"/>
-      <c r="BV24" s="20">
+      <c r="BV24" s="19">
         <v>0</v>
       </c>
       <c r="BW24" s="14">
@@ -11984,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="BY24" s="16"/>
-      <c r="BZ24" s="20">
+      <c r="BZ24" s="19">
         <v>0</v>
       </c>
       <c r="CA24" s="14">
@@ -11994,9 +11998,9 @@
         <v>1</v>
       </c>
       <c r="CC24" s="16">
-        <v>55</v>
-      </c>
-      <c r="CD24" s="19">
+        <v>60</v>
+      </c>
+      <c r="CD24" s="18">
         <v>0</v>
       </c>
       <c r="CE24" s="14">
@@ -12006,17 +12010,17 @@
         <v>0</v>
       </c>
       <c r="CG24" s="16"/>
-      <c r="CH24" s="20">
+      <c r="CH24" s="19">
         <v>0</v>
       </c>
       <c r="CI24" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ24" s="15">
         <v>3</v>
       </c>
-      <c r="CK24" s="18">
-        <v>4</v>
+      <c r="CK24" s="20">
+        <v>8</v>
       </c>
       <c r="CL24" s="17">
         <v>2</v>
@@ -12032,16 +12036,16 @@
         <v>1</v>
       </c>
       <c r="CQ24" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CR24" s="23">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="CS24" s="24">
         <v>12</v>
       </c>
       <c r="CT24" s="24">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:98">
@@ -12069,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="16"/>
-      <c r="K25" s="20">
+      <c r="K25" s="19">
         <v>0</v>
       </c>
       <c r="L25" s="14">
@@ -12079,7 +12083,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="16"/>
-      <c r="O25" s="20">
+      <c r="O25" s="19">
         <v>0</v>
       </c>
       <c r="P25" s="14">
@@ -12103,16 +12107,18 @@
         <v>0</v>
       </c>
       <c r="X25" s="16"/>
-      <c r="Y25" s="20">
+      <c r="Y25" s="19">
         <v>0</v>
       </c>
       <c r="Z25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA25" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="AB25" s="16">
+        <v>24</v>
+      </c>
       <c r="AC25" s="22">
         <v>0</v>
       </c>
@@ -12123,7 +12129,7 @@
         <v>0</v>
       </c>
       <c r="AF25" s="16"/>
-      <c r="AG25" s="20">
+      <c r="AG25" s="19">
         <v>0</v>
       </c>
       <c r="AH25" s="14">
@@ -12133,7 +12139,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK25" s="17">
         <v>2</v>
@@ -12149,7 +12155,7 @@
         <v>0</v>
       </c>
       <c r="AP25" s="16"/>
-      <c r="AQ25" s="20">
+      <c r="AQ25" s="19">
         <v>0</v>
       </c>
       <c r="AR25" s="14">
@@ -12159,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="AT25" s="16"/>
-      <c r="AU25" s="20">
+      <c r="AU25" s="19">
         <v>0</v>
       </c>
       <c r="AV25" s="14">
@@ -12169,7 +12175,7 @@
         <v>0</v>
       </c>
       <c r="AX25" s="16"/>
-      <c r="AY25" s="20">
+      <c r="AY25" s="19">
         <v>0</v>
       </c>
       <c r="AZ25" s="14">
@@ -12186,7 +12192,7 @@
         <v>0</v>
       </c>
       <c r="BE25" s="16"/>
-      <c r="BF25" s="20">
+      <c r="BF25" s="19">
         <v>0</v>
       </c>
       <c r="BG25" s="14">
@@ -12195,10 +12201,10 @@
       <c r="BH25" s="15">
         <v>1</v>
       </c>
-      <c r="BI25" s="18">
-        <v>0</v>
-      </c>
-      <c r="BJ25" s="19">
+      <c r="BI25" s="21">
+        <v>0</v>
+      </c>
+      <c r="BJ25" s="18">
         <v>1</v>
       </c>
       <c r="BK25" s="14">
@@ -12207,10 +12213,10 @@
       <c r="BL25" s="15">
         <v>1</v>
       </c>
-      <c r="BM25" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN25" s="19">
+      <c r="BM25" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN25" s="18">
         <v>1</v>
       </c>
       <c r="BO25" s="14">
@@ -12220,7 +12226,7 @@
         <v>0</v>
       </c>
       <c r="BQ25" s="16"/>
-      <c r="BR25" s="20">
+      <c r="BR25" s="19">
         <v>0</v>
       </c>
       <c r="BS25" s="14">
@@ -12230,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="BU25" s="16"/>
-      <c r="BV25" s="20">
+      <c r="BV25" s="19">
         <v>0</v>
       </c>
       <c r="BW25" s="14">
@@ -12240,7 +12246,7 @@
         <v>0</v>
       </c>
       <c r="BY25" s="16"/>
-      <c r="BZ25" s="20">
+      <c r="BZ25" s="19">
         <v>0</v>
       </c>
       <c r="CA25" s="14">
@@ -12250,56 +12256,56 @@
         <v>2</v>
       </c>
       <c r="CC25" s="16">
+        <v>12</v>
+      </c>
+      <c r="CD25" s="18">
+        <v>1</v>
+      </c>
+      <c r="CE25" s="14">
+        <v>3</v>
+      </c>
+      <c r="CF25" s="15">
+        <v>0</v>
+      </c>
+      <c r="CG25" s="16"/>
+      <c r="CH25" s="19">
+        <v>0</v>
+      </c>
+      <c r="CI25" s="14">
+        <v>2</v>
+      </c>
+      <c r="CJ25" s="15">
+        <v>1</v>
+      </c>
+      <c r="CK25" s="16">
+        <v>24</v>
+      </c>
+      <c r="CL25" s="17">
+        <v>2</v>
+      </c>
+      <c r="CM25" s="15">
+        <v>1</v>
+      </c>
+      <c r="CN25" s="16">
+        <v>24</v>
+      </c>
+      <c r="CO25" s="17">
+        <v>2</v>
+      </c>
+      <c r="CP25" s="15">
+        <v>3</v>
+      </c>
+      <c r="CQ25" s="20">
+        <v>8</v>
+      </c>
+      <c r="CR25" s="23">
+        <v>28</v>
+      </c>
+      <c r="CS25" s="24">
         <v>11</v>
       </c>
-      <c r="CD25" s="19">
-        <v>1</v>
-      </c>
-      <c r="CE25" s="14">
-        <v>3</v>
-      </c>
-      <c r="CF25" s="15">
-        <v>0</v>
-      </c>
-      <c r="CG25" s="16"/>
-      <c r="CH25" s="20">
-        <v>0</v>
-      </c>
-      <c r="CI25" s="14">
-        <v>2</v>
-      </c>
-      <c r="CJ25" s="15">
-        <v>1</v>
-      </c>
-      <c r="CK25" s="16">
-        <v>22</v>
-      </c>
-      <c r="CL25" s="17">
-        <v>2</v>
-      </c>
-      <c r="CM25" s="15">
-        <v>1</v>
-      </c>
-      <c r="CN25" s="16">
-        <v>22</v>
-      </c>
-      <c r="CO25" s="17">
-        <v>2</v>
-      </c>
-      <c r="CP25" s="15">
-        <v>3</v>
-      </c>
-      <c r="CQ25" s="21">
-        <v>7</v>
-      </c>
-      <c r="CR25" s="23">
-        <v>29</v>
-      </c>
-      <c r="CS25" s="24">
-        <v>10</v>
-      </c>
       <c r="CT25" s="24">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:98">
@@ -12327,7 +12333,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="16"/>
-      <c r="K26" s="20">
+      <c r="K26" s="19">
         <v>0</v>
       </c>
       <c r="L26" s="14">
@@ -12337,7 +12343,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="16"/>
-      <c r="O26" s="20">
+      <c r="O26" s="19">
         <v>0</v>
       </c>
       <c r="P26" s="14">
@@ -12355,15 +12361,15 @@
       </c>
       <c r="U26" s="16"/>
       <c r="V26" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W26" s="15">
         <v>5</v>
       </c>
-      <c r="X26" s="18">
-        <v>4</v>
-      </c>
-      <c r="Y26" s="19">
+      <c r="X26" s="20">
+        <v>10</v>
+      </c>
+      <c r="Y26" s="18">
         <v>2</v>
       </c>
       <c r="Z26" s="14">
@@ -12373,7 +12379,7 @@
         <v>1</v>
       </c>
       <c r="AB26" s="16">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AC26" s="22">
         <v>0</v>
@@ -12385,7 +12391,7 @@
         <v>0</v>
       </c>
       <c r="AF26" s="16"/>
-      <c r="AG26" s="20">
+      <c r="AG26" s="19">
         <v>0</v>
       </c>
       <c r="AH26" s="14">
@@ -12402,7 +12408,7 @@
         <v>1</v>
       </c>
       <c r="AM26" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AN26" s="17">
         <v>0</v>
@@ -12410,10 +12416,10 @@
       <c r="AO26" s="15">
         <v>2</v>
       </c>
-      <c r="AP26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="19">
+      <c r="AP26" s="21">
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="18">
         <v>1</v>
       </c>
       <c r="AR26" s="14">
@@ -12423,7 +12429,7 @@
         <v>0</v>
       </c>
       <c r="AT26" s="16"/>
-      <c r="AU26" s="20">
+      <c r="AU26" s="19">
         <v>0</v>
       </c>
       <c r="AV26" s="14">
@@ -12433,9 +12439,9 @@
         <v>1</v>
       </c>
       <c r="AX26" s="16">
-        <v>22</v>
-      </c>
-      <c r="AY26" s="19">
+        <v>24</v>
+      </c>
+      <c r="AY26" s="18">
         <v>0</v>
       </c>
       <c r="AZ26" s="14">
@@ -12452,9 +12458,9 @@
         <v>1</v>
       </c>
       <c r="BE26" s="16">
-        <v>33</v>
-      </c>
-      <c r="BF26" s="19">
+        <v>36</v>
+      </c>
+      <c r="BF26" s="18">
         <v>1</v>
       </c>
       <c r="BG26" s="14">
@@ -12464,7 +12470,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="16"/>
-      <c r="BJ26" s="20">
+      <c r="BJ26" s="19">
         <v>0</v>
       </c>
       <c r="BK26" s="14">
@@ -12474,7 +12480,7 @@
         <v>0</v>
       </c>
       <c r="BM26" s="16"/>
-      <c r="BN26" s="20">
+      <c r="BN26" s="19">
         <v>0</v>
       </c>
       <c r="BO26" s="14">
@@ -12484,7 +12490,7 @@
         <v>0</v>
       </c>
       <c r="BQ26" s="16"/>
-      <c r="BR26" s="20">
+      <c r="BR26" s="19">
         <v>0</v>
       </c>
       <c r="BS26" s="14">
@@ -12494,7 +12500,7 @@
         <v>0</v>
       </c>
       <c r="BU26" s="16"/>
-      <c r="BV26" s="20">
+      <c r="BV26" s="19">
         <v>0</v>
       </c>
       <c r="BW26" s="14">
@@ -12503,20 +12509,22 @@
       <c r="BX26" s="15">
         <v>1</v>
       </c>
-      <c r="BY26" s="18">
-        <v>0</v>
-      </c>
-      <c r="BZ26" s="19">
+      <c r="BY26" s="21">
+        <v>0</v>
+      </c>
+      <c r="BZ26" s="18">
         <v>1</v>
       </c>
       <c r="CA26" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CB26" s="15">
-        <v>0</v>
-      </c>
-      <c r="CC26" s="16"/>
-      <c r="CD26" s="20">
+        <v>1</v>
+      </c>
+      <c r="CC26" s="16">
+        <v>36</v>
+      </c>
+      <c r="CD26" s="18">
         <v>0</v>
       </c>
       <c r="CE26" s="14">
@@ -12526,9 +12534,9 @@
         <v>2</v>
       </c>
       <c r="CG26" s="16">
-        <v>11</v>
-      </c>
-      <c r="CH26" s="19">
+        <v>12</v>
+      </c>
+      <c r="CH26" s="18">
         <v>1</v>
       </c>
       <c r="CI26" s="14">
@@ -12546,22 +12554,22 @@
       </c>
       <c r="CN26" s="16"/>
       <c r="CO26" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CP26" s="15">
         <v>3</v>
       </c>
-      <c r="CQ26" s="18">
-        <v>4</v>
+      <c r="CQ26" s="16">
+        <v>12</v>
       </c>
       <c r="CR26" s="23">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="CS26" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CT26" s="24">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:98">
@@ -12589,7 +12597,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="16"/>
-      <c r="K27" s="20">
+      <c r="K27" s="19">
         <v>0</v>
       </c>
       <c r="L27" s="14">
@@ -12599,7 +12607,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="16"/>
-      <c r="O27" s="20">
+      <c r="O27" s="19">
         <v>0</v>
       </c>
       <c r="P27" s="14">
@@ -12623,18 +12631,20 @@
         <v>1</v>
       </c>
       <c r="X27" s="16">
-        <v>22</v>
-      </c>
-      <c r="Y27" s="19">
+        <v>24</v>
+      </c>
+      <c r="Y27" s="18">
         <v>0</v>
       </c>
       <c r="Z27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA27" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="AB27" s="16">
+        <v>48</v>
+      </c>
       <c r="AC27" s="22">
         <v>0</v>
       </c>
@@ -12645,7 +12655,7 @@
         <v>0</v>
       </c>
       <c r="AF27" s="16"/>
-      <c r="AG27" s="20">
+      <c r="AG27" s="19">
         <v>0</v>
       </c>
       <c r="AH27" s="14">
@@ -12662,7 +12672,7 @@
         <v>1</v>
       </c>
       <c r="AM27" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN27" s="17">
         <v>1</v>
@@ -12671,9 +12681,9 @@
         <v>1</v>
       </c>
       <c r="AP27" s="16">
-        <v>11</v>
-      </c>
-      <c r="AQ27" s="19">
+        <v>12</v>
+      </c>
+      <c r="AQ27" s="18">
         <v>0</v>
       </c>
       <c r="AR27" s="14">
@@ -12683,9 +12693,9 @@
         <v>1</v>
       </c>
       <c r="AT27" s="16">
-        <v>11</v>
-      </c>
-      <c r="AU27" s="19">
+        <v>12</v>
+      </c>
+      <c r="AU27" s="18">
         <v>0</v>
       </c>
       <c r="AV27" s="14">
@@ -12695,7 +12705,7 @@
         <v>0</v>
       </c>
       <c r="AX27" s="16"/>
-      <c r="AY27" s="20">
+      <c r="AY27" s="19">
         <v>0</v>
       </c>
       <c r="AZ27" s="14">
@@ -12712,9 +12722,9 @@
         <v>1</v>
       </c>
       <c r="BE27" s="16">
-        <v>33</v>
-      </c>
-      <c r="BF27" s="19">
+        <v>36</v>
+      </c>
+      <c r="BF27" s="18">
         <v>1</v>
       </c>
       <c r="BG27" s="14">
@@ -12724,7 +12734,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="16"/>
-      <c r="BJ27" s="20">
+      <c r="BJ27" s="19">
         <v>0</v>
       </c>
       <c r="BK27" s="14">
@@ -12733,10 +12743,10 @@
       <c r="BL27" s="15">
         <v>2</v>
       </c>
-      <c r="BM27" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN27" s="19">
+      <c r="BM27" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN27" s="18">
         <v>1</v>
       </c>
       <c r="BO27" s="14">
@@ -12746,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BQ27" s="16"/>
-      <c r="BR27" s="20">
+      <c r="BR27" s="19">
         <v>0</v>
       </c>
       <c r="BS27" s="14">
@@ -12756,18 +12766,20 @@
         <v>0</v>
       </c>
       <c r="BU27" s="16"/>
-      <c r="BV27" s="20">
+      <c r="BV27" s="19">
         <v>0</v>
       </c>
       <c r="BW27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BX27" s="15">
-        <v>0</v>
-      </c>
-      <c r="BY27" s="16"/>
-      <c r="BZ27" s="20">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BY27" s="16">
+        <v>24</v>
+      </c>
+      <c r="BZ27" s="18">
+        <v>1</v>
       </c>
       <c r="CA27" s="14">
         <v>4</v>
@@ -12776,7 +12788,7 @@
         <v>0</v>
       </c>
       <c r="CC27" s="16"/>
-      <c r="CD27" s="20">
+      <c r="CD27" s="19">
         <v>0</v>
       </c>
       <c r="CE27" s="14">
@@ -12786,9 +12798,9 @@
         <v>2</v>
       </c>
       <c r="CG27" s="16">
-        <v>11</v>
-      </c>
-      <c r="CH27" s="19">
+        <v>12</v>
+      </c>
+      <c r="CH27" s="18">
         <v>1</v>
       </c>
       <c r="CI27" s="14">
@@ -12805,7 +12817,7 @@
         <v>1</v>
       </c>
       <c r="CN27" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CO27" s="17">
         <v>2</v>
@@ -12814,16 +12826,16 @@
         <v>1</v>
       </c>
       <c r="CQ27" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CR27" s="23">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CS27" s="24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CT27" s="24">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:98">
@@ -12851,9 +12863,9 @@
         <v>1</v>
       </c>
       <c r="J28" s="16">
-        <v>22</v>
-      </c>
-      <c r="K28" s="19">
+        <v>24</v>
+      </c>
+      <c r="K28" s="18">
         <v>1</v>
       </c>
       <c r="L28" s="14">
@@ -12863,7 +12875,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="16"/>
-      <c r="O28" s="20">
+      <c r="O28" s="19">
         <v>0</v>
       </c>
       <c r="P28" s="14">
@@ -12887,7 +12899,7 @@
         <v>0</v>
       </c>
       <c r="X28" s="16"/>
-      <c r="Y28" s="20">
+      <c r="Y28" s="19">
         <v>0</v>
       </c>
       <c r="Z28" s="14">
@@ -12897,7 +12909,7 @@
         <v>2</v>
       </c>
       <c r="AB28" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC28" s="22">
         <v>1</v>
@@ -12909,7 +12921,7 @@
         <v>0</v>
       </c>
       <c r="AF28" s="16"/>
-      <c r="AG28" s="20">
+      <c r="AG28" s="19">
         <v>0</v>
       </c>
       <c r="AH28" s="14">
@@ -12926,7 +12938,7 @@
         <v>2</v>
       </c>
       <c r="AM28" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN28" s="17">
         <v>1</v>
@@ -12934,10 +12946,10 @@
       <c r="AO28" s="15">
         <v>2</v>
       </c>
-      <c r="AP28" s="21">
+      <c r="AP28" s="20">
         <v>6</v>
       </c>
-      <c r="AQ28" s="19">
+      <c r="AQ28" s="18">
         <v>1</v>
       </c>
       <c r="AR28" s="14">
@@ -12947,7 +12959,7 @@
         <v>0</v>
       </c>
       <c r="AT28" s="16"/>
-      <c r="AU28" s="20">
+      <c r="AU28" s="19">
         <v>0</v>
       </c>
       <c r="AV28" s="14">
@@ -12957,7 +12969,7 @@
         <v>0</v>
       </c>
       <c r="AX28" s="16"/>
-      <c r="AY28" s="20">
+      <c r="AY28" s="19">
         <v>0</v>
       </c>
       <c r="AZ28" s="14">
@@ -12974,9 +12986,9 @@
         <v>2</v>
       </c>
       <c r="BE28" s="16">
-        <v>17</v>
-      </c>
-      <c r="BF28" s="19">
+        <v>18</v>
+      </c>
+      <c r="BF28" s="18">
         <v>1</v>
       </c>
       <c r="BG28" s="14">
@@ -12986,7 +12998,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="16"/>
-      <c r="BJ28" s="20">
+      <c r="BJ28" s="19">
         <v>0</v>
       </c>
       <c r="BK28" s="14">
@@ -12995,10 +13007,10 @@
       <c r="BL28" s="15">
         <v>2</v>
       </c>
-      <c r="BM28" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN28" s="19">
+      <c r="BM28" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN28" s="18">
         <v>1</v>
       </c>
       <c r="BO28" s="14">
@@ -13008,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="BQ28" s="16"/>
-      <c r="BR28" s="20">
+      <c r="BR28" s="19">
         <v>0</v>
       </c>
       <c r="BS28" s="14">
@@ -13018,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="BU28" s="16"/>
-      <c r="BV28" s="20">
+      <c r="BV28" s="19">
         <v>0</v>
       </c>
       <c r="BW28" s="14">
@@ -13028,9 +13040,9 @@
         <v>1</v>
       </c>
       <c r="BY28" s="16">
-        <v>22</v>
-      </c>
-      <c r="BZ28" s="19">
+        <v>24</v>
+      </c>
+      <c r="BZ28" s="18">
         <v>1</v>
       </c>
       <c r="CA28" s="14">
@@ -13040,7 +13052,7 @@
         <v>0</v>
       </c>
       <c r="CC28" s="16"/>
-      <c r="CD28" s="20">
+      <c r="CD28" s="19">
         <v>0</v>
       </c>
       <c r="CE28" s="14">
@@ -13050,7 +13062,7 @@
         <v>0</v>
       </c>
       <c r="CG28" s="16"/>
-      <c r="CH28" s="20">
+      <c r="CH28" s="19">
         <v>0</v>
       </c>
       <c r="CI28" s="14">
@@ -13068,22 +13080,22 @@
       </c>
       <c r="CN28" s="16"/>
       <c r="CO28" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP28" s="15">
-        <v>2</v>
-      </c>
-      <c r="CQ28" s="16">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="CQ28" s="20">
+        <v>8</v>
       </c>
       <c r="CR28" s="23">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="CS28" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CT28" s="24">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:98">
@@ -13110,10 +13122,10 @@
       <c r="I29" s="15">
         <v>1</v>
       </c>
-      <c r="J29" s="18">
-        <v>0</v>
-      </c>
-      <c r="K29" s="19">
+      <c r="J29" s="21">
+        <v>0</v>
+      </c>
+      <c r="K29" s="18">
         <v>1</v>
       </c>
       <c r="L29" s="14">
@@ -13123,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="16"/>
-      <c r="O29" s="20">
+      <c r="O29" s="19">
         <v>0</v>
       </c>
       <c r="P29" s="14">
@@ -13147,9 +13159,9 @@
         <v>1</v>
       </c>
       <c r="X29" s="16">
-        <v>33</v>
-      </c>
-      <c r="Y29" s="19">
+        <v>36</v>
+      </c>
+      <c r="Y29" s="18">
         <v>0</v>
       </c>
       <c r="Z29" s="14">
@@ -13159,7 +13171,7 @@
         <v>1</v>
       </c>
       <c r="AB29" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC29" s="22">
         <v>0</v>
@@ -13171,7 +13183,7 @@
         <v>0</v>
       </c>
       <c r="AF29" s="16"/>
-      <c r="AG29" s="20">
+      <c r="AG29" s="19">
         <v>0</v>
       </c>
       <c r="AH29" s="14">
@@ -13188,7 +13200,7 @@
         <v>1</v>
       </c>
       <c r="AM29" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN29" s="17">
         <v>2</v>
@@ -13197,7 +13209,7 @@
         <v>0</v>
       </c>
       <c r="AP29" s="16"/>
-      <c r="AQ29" s="20">
+      <c r="AQ29" s="19">
         <v>0</v>
       </c>
       <c r="AR29" s="14">
@@ -13207,7 +13219,7 @@
         <v>0</v>
       </c>
       <c r="AT29" s="16"/>
-      <c r="AU29" s="20">
+      <c r="AU29" s="19">
         <v>0</v>
       </c>
       <c r="AV29" s="14">
@@ -13217,7 +13229,7 @@
         <v>0</v>
       </c>
       <c r="AX29" s="16"/>
-      <c r="AY29" s="20">
+      <c r="AY29" s="19">
         <v>0</v>
       </c>
       <c r="AZ29" s="14">
@@ -13234,9 +13246,9 @@
         <v>1</v>
       </c>
       <c r="BE29" s="16">
-        <v>44</v>
-      </c>
-      <c r="BF29" s="19">
+        <v>48</v>
+      </c>
+      <c r="BF29" s="18">
         <v>1</v>
       </c>
       <c r="BG29" s="14">
@@ -13246,7 +13258,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="16"/>
-      <c r="BJ29" s="20">
+      <c r="BJ29" s="19">
         <v>0</v>
       </c>
       <c r="BK29" s="14">
@@ -13256,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="BM29" s="16"/>
-      <c r="BN29" s="20">
+      <c r="BN29" s="19">
         <v>0</v>
       </c>
       <c r="BO29" s="14">
@@ -13266,7 +13278,7 @@
         <v>0</v>
       </c>
       <c r="BQ29" s="16"/>
-      <c r="BR29" s="20">
+      <c r="BR29" s="19">
         <v>0</v>
       </c>
       <c r="BS29" s="14">
@@ -13276,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="BU29" s="16"/>
-      <c r="BV29" s="20">
+      <c r="BV29" s="19">
         <v>0</v>
       </c>
       <c r="BW29" s="14">
@@ -13286,7 +13298,7 @@
         <v>0</v>
       </c>
       <c r="BY29" s="16"/>
-      <c r="BZ29" s="20">
+      <c r="BZ29" s="19">
         <v>0</v>
       </c>
       <c r="CA29" s="14">
@@ -13296,7 +13308,7 @@
         <v>0</v>
       </c>
       <c r="CC29" s="16"/>
-      <c r="CD29" s="20">
+      <c r="CD29" s="19">
         <v>0</v>
       </c>
       <c r="CE29" s="14">
@@ -13306,7 +13318,7 @@
         <v>0</v>
       </c>
       <c r="CG29" s="16"/>
-      <c r="CH29" s="20">
+      <c r="CH29" s="19">
         <v>0</v>
       </c>
       <c r="CI29" s="14">
@@ -13337,7 +13349,7 @@
         <v>5</v>
       </c>
       <c r="CT29" s="24">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:98">
@@ -13365,7 +13377,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="16"/>
-      <c r="K30" s="20">
+      <c r="K30" s="19">
         <v>0</v>
       </c>
       <c r="L30" s="14">
@@ -13375,7 +13387,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="16"/>
-      <c r="O30" s="20">
+      <c r="O30" s="19">
         <v>0</v>
       </c>
       <c r="P30" s="14">
@@ -13399,7 +13411,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="16"/>
-      <c r="Y30" s="20">
+      <c r="Y30" s="19">
         <v>0</v>
       </c>
       <c r="Z30" s="14">
@@ -13419,7 +13431,7 @@
         <v>0</v>
       </c>
       <c r="AF30" s="16"/>
-      <c r="AG30" s="20">
+      <c r="AG30" s="19">
         <v>0</v>
       </c>
       <c r="AH30" s="14">
@@ -13429,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="AJ30" s="16">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AK30" s="17">
         <v>2</v>
@@ -13444,10 +13456,10 @@
       <c r="AO30" s="15">
         <v>1</v>
       </c>
-      <c r="AP30" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ30" s="19">
+      <c r="AP30" s="21">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="18">
         <v>0</v>
       </c>
       <c r="AR30" s="14">
@@ -13457,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="AT30" s="16"/>
-      <c r="AU30" s="20">
+      <c r="AU30" s="19">
         <v>0</v>
       </c>
       <c r="AV30" s="14">
@@ -13467,7 +13479,7 @@
         <v>0</v>
       </c>
       <c r="AX30" s="16"/>
-      <c r="AY30" s="20">
+      <c r="AY30" s="19">
         <v>0</v>
       </c>
       <c r="AZ30" s="14">
@@ -13484,7 +13496,7 @@
         <v>0</v>
       </c>
       <c r="BE30" s="16"/>
-      <c r="BF30" s="20">
+      <c r="BF30" s="19">
         <v>0</v>
       </c>
       <c r="BG30" s="14">
@@ -13494,7 +13506,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="16"/>
-      <c r="BJ30" s="20">
+      <c r="BJ30" s="19">
         <v>0</v>
       </c>
       <c r="BK30" s="14">
@@ -13504,7 +13516,7 @@
         <v>0</v>
       </c>
       <c r="BM30" s="16"/>
-      <c r="BN30" s="20">
+      <c r="BN30" s="19">
         <v>0</v>
       </c>
       <c r="BO30" s="14">
@@ -13514,7 +13526,7 @@
         <v>0</v>
       </c>
       <c r="BQ30" s="16"/>
-      <c r="BR30" s="20">
+      <c r="BR30" s="19">
         <v>0</v>
       </c>
       <c r="BS30" s="14">
@@ -13524,7 +13536,7 @@
         <v>0</v>
       </c>
       <c r="BU30" s="16"/>
-      <c r="BV30" s="20">
+      <c r="BV30" s="19">
         <v>0</v>
       </c>
       <c r="BW30" s="14">
@@ -13534,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="BY30" s="16"/>
-      <c r="BZ30" s="20">
+      <c r="BZ30" s="19">
         <v>0</v>
       </c>
       <c r="CA30" s="14">
@@ -13544,7 +13556,7 @@
         <v>0</v>
       </c>
       <c r="CC30" s="16"/>
-      <c r="CD30" s="20">
+      <c r="CD30" s="19">
         <v>0</v>
       </c>
       <c r="CE30" s="14">
@@ -13554,7 +13566,7 @@
         <v>0</v>
       </c>
       <c r="CG30" s="16"/>
-      <c r="CH30" s="20">
+      <c r="CH30" s="19">
         <v>0</v>
       </c>
       <c r="CI30" s="14">
@@ -13564,7 +13576,7 @@
         <v>1</v>
       </c>
       <c r="CK30" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CL30" s="17">
         <v>2</v>
@@ -13587,7 +13599,7 @@
         <v>3</v>
       </c>
       <c r="CT30" s="24">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:98">
@@ -13615,7 +13627,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="16"/>
-      <c r="K31" s="20">
+      <c r="K31" s="19">
         <v>0</v>
       </c>
       <c r="L31" s="14">
@@ -13625,7 +13637,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="16"/>
-      <c r="O31" s="20">
+      <c r="O31" s="19">
         <v>0</v>
       </c>
       <c r="P31" s="14">
@@ -13649,9 +13661,9 @@
         <v>2</v>
       </c>
       <c r="X31" s="16">
-        <v>22</v>
-      </c>
-      <c r="Y31" s="19">
+        <v>24</v>
+      </c>
+      <c r="Y31" s="18">
         <v>1</v>
       </c>
       <c r="Z31" s="14">
@@ -13661,7 +13673,7 @@
         <v>1</v>
       </c>
       <c r="AB31" s="16">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AC31" s="22">
         <v>0</v>
@@ -13673,9 +13685,9 @@
         <v>1</v>
       </c>
       <c r="AF31" s="16">
-        <v>22</v>
-      </c>
-      <c r="AG31" s="19">
+        <v>24</v>
+      </c>
+      <c r="AG31" s="18">
         <v>0</v>
       </c>
       <c r="AH31" s="14">
@@ -13686,13 +13698,13 @@
       </c>
       <c r="AJ31" s="16"/>
       <c r="AK31" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL31" s="15">
-        <v>3</v>
-      </c>
-      <c r="AM31" s="16">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="AM31" s="20">
+        <v>6</v>
       </c>
       <c r="AN31" s="17">
         <v>0</v>
@@ -13700,10 +13712,10 @@
       <c r="AO31" s="15">
         <v>3</v>
       </c>
-      <c r="AP31" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="19">
+      <c r="AP31" s="21">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="18">
         <v>1</v>
       </c>
       <c r="AR31" s="14">
@@ -13713,7 +13725,7 @@
         <v>0</v>
       </c>
       <c r="AT31" s="16"/>
-      <c r="AU31" s="20">
+      <c r="AU31" s="19">
         <v>0</v>
       </c>
       <c r="AV31" s="14">
@@ -13723,7 +13735,7 @@
         <v>0</v>
       </c>
       <c r="AX31" s="16"/>
-      <c r="AY31" s="20">
+      <c r="AY31" s="19">
         <v>0</v>
       </c>
       <c r="AZ31" s="14">
@@ -13740,7 +13752,7 @@
         <v>0</v>
       </c>
       <c r="BE31" s="16"/>
-      <c r="BF31" s="20">
+      <c r="BF31" s="19">
         <v>0</v>
       </c>
       <c r="BG31" s="14">
@@ -13750,7 +13762,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="16"/>
-      <c r="BJ31" s="20">
+      <c r="BJ31" s="19">
         <v>0</v>
       </c>
       <c r="BK31" s="14">
@@ -13759,10 +13771,10 @@
       <c r="BL31" s="15">
         <v>1</v>
       </c>
-      <c r="BM31" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN31" s="19">
+      <c r="BM31" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN31" s="18">
         <v>1</v>
       </c>
       <c r="BO31" s="14">
@@ -13772,9 +13784,9 @@
         <v>1</v>
       </c>
       <c r="BQ31" s="16">
-        <v>33</v>
-      </c>
-      <c r="BR31" s="19">
+        <v>36</v>
+      </c>
+      <c r="BR31" s="18">
         <v>1</v>
       </c>
       <c r="BS31" s="14">
@@ -13784,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="BU31" s="16"/>
-      <c r="BV31" s="20">
+      <c r="BV31" s="19">
         <v>0</v>
       </c>
       <c r="BW31" s="14">
@@ -13794,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="BY31" s="16"/>
-      <c r="BZ31" s="20">
+      <c r="BZ31" s="19">
         <v>0</v>
       </c>
       <c r="CA31" s="14">
@@ -13804,7 +13816,7 @@
         <v>0</v>
       </c>
       <c r="CC31" s="16"/>
-      <c r="CD31" s="20">
+      <c r="CD31" s="19">
         <v>0</v>
       </c>
       <c r="CE31" s="14">
@@ -13814,9 +13826,9 @@
         <v>1</v>
       </c>
       <c r="CG31" s="16">
-        <v>55</v>
-      </c>
-      <c r="CH31" s="19">
+        <v>60</v>
+      </c>
+      <c r="CH31" s="18">
         <v>1</v>
       </c>
       <c r="CI31" s="14">
@@ -13826,7 +13838,7 @@
         <v>1</v>
       </c>
       <c r="CK31" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CL31" s="17">
         <v>2</v>
@@ -13842,16 +13854,16 @@
         <v>1</v>
       </c>
       <c r="CQ31" s="16">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="CR31" s="23">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="CS31" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CT31" s="24">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:98">
@@ -13872,7 +13884,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H32" s="17">
         <v>1</v>
@@ -13880,10 +13892,10 @@
       <c r="I32" s="15">
         <v>2</v>
       </c>
-      <c r="J32" s="21">
+      <c r="J32" s="20">
         <v>6</v>
       </c>
-      <c r="K32" s="19">
+      <c r="K32" s="18">
         <v>2</v>
       </c>
       <c r="L32" s="14">
@@ -13893,7 +13905,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="16"/>
-      <c r="O32" s="20">
+      <c r="O32" s="19">
         <v>0</v>
       </c>
       <c r="P32" s="14">
@@ -13917,9 +13929,9 @@
         <v>3</v>
       </c>
       <c r="X32" s="16">
-        <v>11</v>
-      </c>
-      <c r="Y32" s="19">
+        <v>12</v>
+      </c>
+      <c r="Y32" s="18">
         <v>1</v>
       </c>
       <c r="Z32" s="14">
@@ -13929,7 +13941,7 @@
         <v>1</v>
       </c>
       <c r="AB32" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC32" s="22">
         <v>0</v>
@@ -13941,7 +13953,7 @@
         <v>0</v>
       </c>
       <c r="AF32" s="16"/>
-      <c r="AG32" s="20">
+      <c r="AG32" s="19">
         <v>0</v>
       </c>
       <c r="AH32" s="14">
@@ -13958,7 +13970,7 @@
         <v>2</v>
       </c>
       <c r="AM32" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN32" s="17">
         <v>2</v>
@@ -13967,9 +13979,9 @@
         <v>2</v>
       </c>
       <c r="AP32" s="16">
-        <v>11</v>
-      </c>
-      <c r="AQ32" s="19">
+        <v>12</v>
+      </c>
+      <c r="AQ32" s="18">
         <v>1</v>
       </c>
       <c r="AR32" s="14">
@@ -13979,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="AT32" s="16"/>
-      <c r="AU32" s="20">
+      <c r="AU32" s="19">
         <v>0</v>
       </c>
       <c r="AV32" s="14">
@@ -13989,7 +14001,7 @@
         <v>0</v>
       </c>
       <c r="AX32" s="16"/>
-      <c r="AY32" s="20">
+      <c r="AY32" s="19">
         <v>0</v>
       </c>
       <c r="AZ32" s="14">
@@ -14006,7 +14018,7 @@
         <v>0</v>
       </c>
       <c r="BE32" s="16"/>
-      <c r="BF32" s="20">
+      <c r="BF32" s="19">
         <v>0</v>
       </c>
       <c r="BG32" s="14">
@@ -14016,7 +14028,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="16"/>
-      <c r="BJ32" s="20">
+      <c r="BJ32" s="19">
         <v>0</v>
       </c>
       <c r="BK32" s="14">
@@ -14026,7 +14038,7 @@
         <v>0</v>
       </c>
       <c r="BM32" s="16"/>
-      <c r="BN32" s="20">
+      <c r="BN32" s="19">
         <v>0</v>
       </c>
       <c r="BO32" s="14">
@@ -14036,7 +14048,7 @@
         <v>0</v>
       </c>
       <c r="BQ32" s="16"/>
-      <c r="BR32" s="20">
+      <c r="BR32" s="19">
         <v>0</v>
       </c>
       <c r="BS32" s="14">
@@ -14045,10 +14057,10 @@
       <c r="BT32" s="15">
         <v>1</v>
       </c>
-      <c r="BU32" s="18">
-        <v>0</v>
-      </c>
-      <c r="BV32" s="19">
+      <c r="BU32" s="21">
+        <v>0</v>
+      </c>
+      <c r="BV32" s="18">
         <v>1</v>
       </c>
       <c r="BW32" s="14">
@@ -14058,7 +14070,7 @@
         <v>0</v>
       </c>
       <c r="BY32" s="16"/>
-      <c r="BZ32" s="20">
+      <c r="BZ32" s="19">
         <v>0</v>
       </c>
       <c r="CA32" s="14">
@@ -14068,9 +14080,9 @@
         <v>1</v>
       </c>
       <c r="CC32" s="16">
-        <v>55</v>
-      </c>
-      <c r="CD32" s="19">
+        <v>60</v>
+      </c>
+      <c r="CD32" s="18">
         <v>0</v>
       </c>
       <c r="CE32" s="14">
@@ -14080,9 +14092,9 @@
         <v>2</v>
       </c>
       <c r="CG32" s="16">
-        <v>11</v>
-      </c>
-      <c r="CH32" s="19">
+        <v>12</v>
+      </c>
+      <c r="CH32" s="18">
         <v>1</v>
       </c>
       <c r="CI32" s="14">
@@ -14092,7 +14104,7 @@
         <v>1</v>
       </c>
       <c r="CK32" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CL32" s="17">
         <v>2</v>
@@ -14108,7 +14120,7 @@
         <v>2</v>
       </c>
       <c r="CQ32" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CR32" s="23">
         <v>45</v>
@@ -14117,7 +14129,7 @@
         <v>18</v>
       </c>
       <c r="CT32" s="24">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:98">
@@ -14145,7 +14157,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="16"/>
-      <c r="K33" s="20">
+      <c r="K33" s="19">
         <v>0</v>
       </c>
       <c r="L33" s="14">
@@ -14155,7 +14167,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="16"/>
-      <c r="O33" s="20">
+      <c r="O33" s="19">
         <v>0</v>
       </c>
       <c r="P33" s="14">
@@ -14179,9 +14191,9 @@
         <v>5</v>
       </c>
       <c r="X33" s="16">
-        <v>11</v>
-      </c>
-      <c r="Y33" s="19">
+        <v>12</v>
+      </c>
+      <c r="Y33" s="18">
         <v>2</v>
       </c>
       <c r="Z33" s="14">
@@ -14190,8 +14202,8 @@
       <c r="AA33" s="15">
         <v>3</v>
       </c>
-      <c r="AB33" s="21">
-        <v>7</v>
+      <c r="AB33" s="20">
+        <v>8</v>
       </c>
       <c r="AC33" s="22">
         <v>1</v>
@@ -14203,7 +14215,7 @@
         <v>0</v>
       </c>
       <c r="AF33" s="16"/>
-      <c r="AG33" s="20">
+      <c r="AG33" s="19">
         <v>0</v>
       </c>
       <c r="AH33" s="14">
@@ -14221,16 +14233,16 @@
       </c>
       <c r="AM33" s="16"/>
       <c r="AN33" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO33" s="15">
-        <v>1</v>
-      </c>
-      <c r="AP33" s="16">
-        <v>22</v>
-      </c>
-      <c r="AQ33" s="19">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AP33" s="20">
+        <v>6</v>
+      </c>
+      <c r="AQ33" s="18">
+        <v>1</v>
       </c>
       <c r="AR33" s="14">
         <v>2</v>
@@ -14239,7 +14251,7 @@
         <v>0</v>
       </c>
       <c r="AT33" s="16"/>
-      <c r="AU33" s="20">
+      <c r="AU33" s="19">
         <v>0</v>
       </c>
       <c r="AV33" s="14">
@@ -14249,7 +14261,7 @@
         <v>0</v>
       </c>
       <c r="AX33" s="16"/>
-      <c r="AY33" s="20">
+      <c r="AY33" s="19">
         <v>0</v>
       </c>
       <c r="AZ33" s="14">
@@ -14266,7 +14278,7 @@
         <v>0</v>
       </c>
       <c r="BE33" s="16"/>
-      <c r="BF33" s="20">
+      <c r="BF33" s="19">
         <v>0</v>
       </c>
       <c r="BG33" s="14">
@@ -14276,7 +14288,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="16"/>
-      <c r="BJ33" s="20">
+      <c r="BJ33" s="19">
         <v>0</v>
       </c>
       <c r="BK33" s="14">
@@ -14286,9 +14298,9 @@
         <v>1</v>
       </c>
       <c r="BM33" s="16">
-        <v>11</v>
-      </c>
-      <c r="BN33" s="19">
+        <v>12</v>
+      </c>
+      <c r="BN33" s="18">
         <v>1</v>
       </c>
       <c r="BO33" s="14">
@@ -14298,7 +14310,7 @@
         <v>0</v>
       </c>
       <c r="BQ33" s="16"/>
-      <c r="BR33" s="20">
+      <c r="BR33" s="19">
         <v>0</v>
       </c>
       <c r="BS33" s="14">
@@ -14308,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="BU33" s="16"/>
-      <c r="BV33" s="20">
+      <c r="BV33" s="19">
         <v>0</v>
       </c>
       <c r="BW33" s="14">
@@ -14318,7 +14330,7 @@
         <v>0</v>
       </c>
       <c r="BY33" s="16"/>
-      <c r="BZ33" s="20">
+      <c r="BZ33" s="19">
         <v>0</v>
       </c>
       <c r="CA33" s="14">
@@ -14327,10 +14339,10 @@
       <c r="CB33" s="15">
         <v>5</v>
       </c>
-      <c r="CC33" s="21">
+      <c r="CC33" s="20">
         <v>7</v>
       </c>
-      <c r="CD33" s="19">
+      <c r="CD33" s="18">
         <v>2</v>
       </c>
       <c r="CE33" s="14">
@@ -14340,19 +14352,19 @@
         <v>1</v>
       </c>
       <c r="CG33" s="16">
-        <v>44</v>
-      </c>
-      <c r="CH33" s="19">
+        <v>48</v>
+      </c>
+      <c r="CH33" s="18">
         <v>1</v>
       </c>
       <c r="CI33" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CJ33" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CK33" s="16">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="CL33" s="17">
         <v>4</v>
@@ -14361,7 +14373,7 @@
         <v>1</v>
       </c>
       <c r="CN33" s="16">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="CO33" s="17">
         <v>6</v>
@@ -14371,13 +14383,13 @@
       </c>
       <c r="CQ33" s="16"/>
       <c r="CR33" s="23">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="CS33" s="24">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CT33" s="24">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:98">
@@ -14405,9 +14417,9 @@
         <v>1</v>
       </c>
       <c r="J34" s="16">
-        <v>11</v>
-      </c>
-      <c r="K34" s="19">
+        <v>12</v>
+      </c>
+      <c r="K34" s="18">
         <v>1</v>
       </c>
       <c r="L34" s="14">
@@ -14417,7 +14429,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="16"/>
-      <c r="O34" s="20">
+      <c r="O34" s="19">
         <v>0</v>
       </c>
       <c r="P34" s="14">
@@ -14441,9 +14453,9 @@
         <v>1</v>
       </c>
       <c r="X34" s="16">
-        <v>33</v>
-      </c>
-      <c r="Y34" s="19">
+        <v>36</v>
+      </c>
+      <c r="Y34" s="18">
         <v>0</v>
       </c>
       <c r="Z34" s="14">
@@ -14453,7 +14465,7 @@
         <v>1</v>
       </c>
       <c r="AB34" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC34" s="22">
         <v>0</v>
@@ -14465,7 +14477,7 @@
         <v>0</v>
       </c>
       <c r="AF34" s="16"/>
-      <c r="AG34" s="20">
+      <c r="AG34" s="19">
         <v>0</v>
       </c>
       <c r="AH34" s="14">
@@ -14482,7 +14494,7 @@
         <v>1</v>
       </c>
       <c r="AM34" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AN34" s="17">
         <v>3</v>
@@ -14491,7 +14503,7 @@
         <v>0</v>
       </c>
       <c r="AP34" s="16"/>
-      <c r="AQ34" s="20">
+      <c r="AQ34" s="19">
         <v>0</v>
       </c>
       <c r="AR34" s="14">
@@ -14501,7 +14513,7 @@
         <v>0</v>
       </c>
       <c r="AT34" s="16"/>
-      <c r="AU34" s="20">
+      <c r="AU34" s="19">
         <v>0</v>
       </c>
       <c r="AV34" s="14">
@@ -14511,7 +14523,7 @@
         <v>0</v>
       </c>
       <c r="AX34" s="16"/>
-      <c r="AY34" s="20">
+      <c r="AY34" s="19">
         <v>0</v>
       </c>
       <c r="AZ34" s="14">
@@ -14528,7 +14540,7 @@
         <v>0</v>
       </c>
       <c r="BE34" s="16"/>
-      <c r="BF34" s="20">
+      <c r="BF34" s="19">
         <v>0</v>
       </c>
       <c r="BG34" s="14">
@@ -14538,7 +14550,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="16"/>
-      <c r="BJ34" s="20">
+      <c r="BJ34" s="19">
         <v>0</v>
       </c>
       <c r="BK34" s="14">
@@ -14547,10 +14559,10 @@
       <c r="BL34" s="15">
         <v>1</v>
       </c>
-      <c r="BM34" s="18">
-        <v>0</v>
-      </c>
-      <c r="BN34" s="19">
+      <c r="BM34" s="21">
+        <v>0</v>
+      </c>
+      <c r="BN34" s="18">
         <v>1</v>
       </c>
       <c r="BO34" s="14">
@@ -14560,9 +14572,9 @@
         <v>1</v>
       </c>
       <c r="BQ34" s="16">
-        <v>11</v>
-      </c>
-      <c r="BR34" s="19">
+        <v>12</v>
+      </c>
+      <c r="BR34" s="18">
         <v>1</v>
       </c>
       <c r="BS34" s="14">
@@ -14572,7 +14584,7 @@
         <v>0</v>
       </c>
       <c r="BU34" s="16"/>
-      <c r="BV34" s="20">
+      <c r="BV34" s="19">
         <v>0</v>
       </c>
       <c r="BW34" s="14">
@@ -14582,7 +14594,7 @@
         <v>0</v>
       </c>
       <c r="BY34" s="16"/>
-      <c r="BZ34" s="20">
+      <c r="BZ34" s="19">
         <v>0</v>
       </c>
       <c r="CA34" s="14">
@@ -14592,9 +14604,9 @@
         <v>3</v>
       </c>
       <c r="CC34" s="16">
-        <v>11</v>
-      </c>
-      <c r="CD34" s="19">
+        <v>12</v>
+      </c>
+      <c r="CD34" s="18">
         <v>1</v>
       </c>
       <c r="CE34" s="14">
@@ -14604,7 +14616,7 @@
         <v>0</v>
       </c>
       <c r="CG34" s="16"/>
-      <c r="CH34" s="20">
+      <c r="CH34" s="19">
         <v>0</v>
       </c>
       <c r="CI34" s="14">
@@ -14621,7 +14633,7 @@
         <v>1</v>
       </c>
       <c r="CN34" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CO34" s="17">
         <v>2</v>
@@ -14630,7 +14642,7 @@
         <v>1</v>
       </c>
       <c r="CQ34" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CR34" s="23">
         <v>38</v>
@@ -14639,7 +14651,7 @@
         <v>11</v>
       </c>
       <c r="CT34" s="24">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:98">
@@ -14660,19 +14672,19 @@
         <v>2</v>
       </c>
       <c r="G35" s="16">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="H35" s="31">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I35" s="30">
         <v>11</v>
       </c>
       <c r="J35" s="16">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K35" s="32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L35" s="29">
         <v>0</v>
@@ -14699,91 +14711,91 @@
       </c>
       <c r="U35" s="16"/>
       <c r="V35" s="31">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="W35" s="30">
-        <v>180</v>
-      </c>
-      <c r="X35" s="21">
+        <v>184</v>
+      </c>
+      <c r="X35" s="20">
+        <v>7</v>
+      </c>
+      <c r="Y35" s="32">
+        <v>77</v>
+      </c>
+      <c r="Z35" s="29">
+        <v>82</v>
+      </c>
+      <c r="AA35" s="30">
+        <v>113</v>
+      </c>
+      <c r="AB35" s="20">
+        <v>9</v>
+      </c>
+      <c r="AC35" s="32">
+        <v>47</v>
+      </c>
+      <c r="AD35" s="29">
+        <v>42</v>
+      </c>
+      <c r="AE35" s="30">
+        <v>11</v>
+      </c>
+      <c r="AF35" s="16">
+        <v>46</v>
+      </c>
+      <c r="AG35" s="32">
         <v>5</v>
       </c>
-      <c r="Y35" s="32">
-        <v>82</v>
-      </c>
-      <c r="Z35" s="29">
-        <v>78</v>
-      </c>
-      <c r="AA35" s="30">
-        <v>106</v>
-      </c>
-      <c r="AB35" s="21">
+      <c r="AH35" s="29">
+        <v>101</v>
+      </c>
+      <c r="AI35" s="30">
+        <v>34</v>
+      </c>
+      <c r="AJ35" s="16">
+        <v>36</v>
+      </c>
+      <c r="AK35" s="31">
+        <v>59</v>
+      </c>
+      <c r="AL35" s="30">
+        <v>88</v>
+      </c>
+      <c r="AM35" s="20">
         <v>8</v>
       </c>
-      <c r="AC35" s="32">
-        <v>48</v>
-      </c>
-      <c r="AD35" s="29">
-        <v>44</v>
-      </c>
-      <c r="AE35" s="30">
-        <v>9</v>
-      </c>
-      <c r="AF35" s="16">
-        <v>54</v>
-      </c>
-      <c r="AG35" s="32">
-        <v>4</v>
-      </c>
-      <c r="AH35" s="29">
-        <v>95</v>
-      </c>
-      <c r="AI35" s="30">
-        <v>32</v>
-      </c>
-      <c r="AJ35" s="16">
-        <v>33</v>
-      </c>
-      <c r="AK35" s="31">
-        <v>64</v>
-      </c>
-      <c r="AL35" s="30">
-        <v>83</v>
-      </c>
-      <c r="AM35" s="21">
-        <v>9</v>
-      </c>
       <c r="AN35" s="31">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AO35" s="30">
-        <v>73</v>
-      </c>
-      <c r="AP35" s="21">
-        <v>8</v>
+        <v>74</v>
+      </c>
+      <c r="AP35" s="16">
+        <v>10</v>
       </c>
       <c r="AQ35" s="32">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AR35" s="29">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AS35" s="30">
         <v>24</v>
       </c>
       <c r="AT35" s="16">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AU35" s="32">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV35" s="29">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AW35" s="30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX35" s="16">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY35" s="32">
         <v>13</v>
@@ -14802,10 +14814,10 @@
         <v>31</v>
       </c>
       <c r="BE35" s="16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BF35" s="32">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BG35" s="29">
         <v>0</v>
@@ -14813,7 +14825,7 @@
       <c r="BH35" s="30">
         <v>2</v>
       </c>
-      <c r="BI35" s="18">
+      <c r="BI35" s="21">
         <v>0</v>
       </c>
       <c r="BJ35" s="32">
@@ -14825,20 +14837,20 @@
       <c r="BL35" s="30">
         <v>21</v>
       </c>
-      <c r="BM35" s="18">
-        <v>4</v>
+      <c r="BM35" s="21">
+        <v>5</v>
       </c>
       <c r="BN35" s="32">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BO35" s="29">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="BP35" s="30">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BQ35" s="16">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BR35" s="32">
         <v>19</v>
@@ -14850,82 +14862,82 @@
         <v>5</v>
       </c>
       <c r="BU35" s="16">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BV35" s="32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BW35" s="29">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="BX35" s="30">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="BY35" s="16">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BZ35" s="32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA35" s="29">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="CB35" s="30">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="CC35" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CD35" s="32">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="CE35" s="29">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="CF35" s="30">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="CG35" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CH35" s="32">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="CI35" s="29">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="CJ35" s="30">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="CK35" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CL35" s="31">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="CM35" s="30">
         <v>18</v>
       </c>
       <c r="CN35" s="16">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="CO35" s="31">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="CP35" s="30">
-        <v>297</v>
-      </c>
-      <c r="CQ35" s="18">
-        <v>5</v>
+        <v>329</v>
+      </c>
+      <c r="CQ35" s="20">
+        <v>6</v>
       </c>
       <c r="CR35" s="23">
-        <v>1280</v>
+        <v>1370</v>
       </c>
       <c r="CS35" s="24">
-        <v>1230</v>
+        <v>1301</v>
       </c>
       <c r="CT35" s="24">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/source/stock_data.xlsx
+++ b/source/stock_data.xlsx
@@ -681,14 +681,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor indexed="65"/>
+        <bgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="65"/>
-        <bgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
@@ -1278,10 +1278,10 @@
     <xf numFmtId="178" fontId="14" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="15" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="15" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="35">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="36"/>
       <c r="D1" s="36"/>
@@ -1876,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
@@ -2371,7 +2371,7 @@
       <c r="I8" s="43">
         <v>1</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="22">
         <v>0</v>
       </c>
       <c r="K8" s="17">
@@ -2395,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="S8" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" s="17">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="AS8" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT8" s="23">
         <v>4</v>
@@ -2470,7 +2470,7 @@
         <v>3</v>
       </c>
       <c r="AV8" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:48">
@@ -2497,7 +2497,7 @@
       <c r="I9" s="43">
         <v>1</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="22">
         <v>0</v>
       </c>
       <c r="K9" s="17">
@@ -2521,7 +2521,7 @@
         <v>2</v>
       </c>
       <c r="S9" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T9" s="17">
         <v>0</v>
@@ -2594,7 +2594,7 @@
         <v>3</v>
       </c>
       <c r="AV9" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:48">
@@ -2622,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" s="17">
         <v>1</v>
@@ -2631,7 +2631,7 @@
         <v>2</v>
       </c>
       <c r="M10" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N10" s="17">
         <v>2</v>
@@ -2647,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T10" s="17">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>4</v>
       </c>
       <c r="AV10" s="24">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:48">
@@ -2747,7 +2747,7 @@
       <c r="I11" s="43">
         <v>1</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="22">
         <v>0</v>
       </c>
       <c r="K11" s="17">
@@ -2828,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="AP11" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ11" s="17">
         <v>3</v>
@@ -2844,7 +2844,7 @@
         <v>2</v>
       </c>
       <c r="AV11" s="24">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:48">
@@ -2878,7 +2878,7 @@
       <c r="L12" s="43">
         <v>1</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="22">
         <v>0</v>
       </c>
       <c r="N12" s="17">
@@ -2895,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="S12" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T12" s="17">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>2</v>
       </c>
       <c r="AV12" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:48">
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="S13" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T13" s="17">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="AL13" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AM13" s="45">
         <v>1</v>
@@ -3092,7 +3092,7 @@
         <v>2</v>
       </c>
       <c r="AV13" s="24">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:48">
@@ -3119,7 +3119,7 @@
       <c r="I14" s="43">
         <v>1</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="22">
         <v>0</v>
       </c>
       <c r="K14" s="17">
@@ -3129,16 +3129,16 @@
         <v>1</v>
       </c>
       <c r="M14" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N14" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="43">
-        <v>1</v>
-      </c>
-      <c r="P14" s="16">
-        <v>12</v>
+        <v>2</v>
+      </c>
+      <c r="P14" s="22">
+        <v>0</v>
       </c>
       <c r="Q14" s="17">
         <v>2</v>
@@ -3147,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="S14" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T14" s="17">
         <v>0</v>
@@ -3214,13 +3214,13 @@
       </c>
       <c r="AS14" s="16"/>
       <c r="AT14" s="23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU14" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV14" s="24">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:48">
@@ -3255,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N15" s="17">
         <v>1</v>
@@ -3270,7 +3270,7 @@
       <c r="R15" s="43">
         <v>1</v>
       </c>
-      <c r="S15" s="21">
+      <c r="S15" s="22">
         <v>0</v>
       </c>
       <c r="T15" s="17">
@@ -3337,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="AS15" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT15" s="23">
         <v>4</v>
@@ -3346,7 +3346,7 @@
         <v>3</v>
       </c>
       <c r="AV15" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:48">
@@ -3432,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="AH16" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI16" s="44">
         <v>1</v>
@@ -3468,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="AV16" s="24">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:48">
@@ -3509,7 +3509,7 @@
       <c r="O17" s="43">
         <v>1</v>
       </c>
-      <c r="P17" s="21">
+      <c r="P17" s="22">
         <v>0</v>
       </c>
       <c r="Q17" s="17">
@@ -3565,7 +3565,7 @@
       <c r="AK17" s="43">
         <v>1</v>
       </c>
-      <c r="AL17" s="21">
+      <c r="AL17" s="22">
         <v>0</v>
       </c>
       <c r="AM17" s="45">
@@ -3592,7 +3592,7 @@
         <v>2</v>
       </c>
       <c r="AV17" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:48">
@@ -3734,19 +3734,21 @@
       </c>
       <c r="G19" s="16"/>
       <c r="H19" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="43">
-        <v>0</v>
-      </c>
-      <c r="J19" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="J19" s="16">
+        <v>13</v>
+      </c>
       <c r="K19" s="17">
         <v>0</v>
       </c>
       <c r="L19" s="43">
         <v>1</v>
       </c>
-      <c r="M19" s="21">
+      <c r="M19" s="22">
         <v>0</v>
       </c>
       <c r="N19" s="17">
@@ -3763,7 +3765,7 @@
         <v>1</v>
       </c>
       <c r="S19" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T19" s="17">
         <v>0</v>
@@ -3830,13 +3832,13 @@
       </c>
       <c r="AS19" s="16"/>
       <c r="AT19" s="23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU19" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV19" s="24">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:48">
@@ -3978,12 +3980,14 @@
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="43">
-        <v>0</v>
-      </c>
-      <c r="J21" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="J21" s="16">
+        <v>13</v>
+      </c>
       <c r="K21" s="17">
         <v>1</v>
       </c>
@@ -3997,7 +4001,7 @@
       <c r="O21" s="43">
         <v>3</v>
       </c>
-      <c r="P21" s="21">
+      <c r="P21" s="22">
         <v>0</v>
       </c>
       <c r="Q21" s="17">
@@ -4044,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="AH21" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI21" s="44">
         <v>1</v>
@@ -4074,13 +4078,13 @@
       </c>
       <c r="AS21" s="16"/>
       <c r="AT21" s="23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU21" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV21" s="24">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:48">
@@ -4115,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N22" s="17">
         <v>1</v>
@@ -4168,7 +4172,7 @@
         <v>1</v>
       </c>
       <c r="AH22" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI22" s="44">
         <v>1</v>
@@ -4190,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="AP22" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ22" s="17">
         <v>2</v>
@@ -4206,7 +4210,7 @@
         <v>3</v>
       </c>
       <c r="AV22" s="24">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:48">
@@ -4240,16 +4244,18 @@
       <c r="L23" s="43">
         <v>1</v>
       </c>
-      <c r="M23" s="21">
+      <c r="M23" s="22">
         <v>0</v>
       </c>
       <c r="N23" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O23" s="43">
-        <v>0</v>
-      </c>
-      <c r="P23" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="P23" s="16">
+        <v>26</v>
+      </c>
       <c r="Q23" s="17">
         <v>1</v>
       </c>
@@ -4314,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="AP23" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ23" s="17">
         <v>1</v>
@@ -4324,13 +4330,13 @@
       </c>
       <c r="AS23" s="16"/>
       <c r="AT23" s="23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU23" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV23" s="24">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:48">
@@ -4357,7 +4363,7 @@
       <c r="I24" s="43">
         <v>1</v>
       </c>
-      <c r="J24" s="21">
+      <c r="J24" s="22">
         <v>0</v>
       </c>
       <c r="K24" s="17">
@@ -4367,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N24" s="17">
         <v>2</v>
@@ -4376,7 +4382,7 @@
         <v>2</v>
       </c>
       <c r="P24" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q24" s="17">
         <v>0</v>
@@ -4422,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="AH24" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI24" s="44">
         <v>1</v>
@@ -4433,7 +4439,7 @@
       <c r="AK24" s="43">
         <v>2</v>
       </c>
-      <c r="AL24" s="21">
+      <c r="AL24" s="22">
         <v>0</v>
       </c>
       <c r="AM24" s="45">
@@ -4460,7 +4466,7 @@
         <v>7</v>
       </c>
       <c r="AV24" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:48">
@@ -4503,12 +4509,14 @@
       </c>
       <c r="P25" s="16"/>
       <c r="Q25" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" s="43">
-        <v>0</v>
-      </c>
-      <c r="S25" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="S25" s="22">
+        <v>0</v>
+      </c>
       <c r="T25" s="17">
         <v>0</v>
       </c>
@@ -4574,13 +4582,13 @@
       </c>
       <c r="AS25" s="16"/>
       <c r="AT25" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU25" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV25" s="24">
-        <v>1000</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:48">
@@ -4629,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="S26" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T26" s="17">
         <v>0</v>
@@ -4667,7 +4675,7 @@
       <c r="AG26" s="43">
         <v>2</v>
       </c>
-      <c r="AH26" s="21">
+      <c r="AH26" s="22">
         <v>0</v>
       </c>
       <c r="AI26" s="44">
@@ -4691,22 +4699,22 @@
       </c>
       <c r="AP26" s="16"/>
       <c r="AQ26" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR26" s="43">
         <v>1</v>
       </c>
-      <c r="AS26" s="21">
-        <v>0</v>
+      <c r="AS26" s="16">
+        <v>13</v>
       </c>
       <c r="AT26" s="23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU26" s="24">
         <v>4</v>
       </c>
       <c r="AV26" s="24">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:48">
@@ -4733,7 +4741,7 @@
       <c r="I27" s="43">
         <v>1</v>
       </c>
-      <c r="J27" s="21">
+      <c r="J27" s="22">
         <v>0</v>
       </c>
       <c r="K27" s="17">
@@ -4828,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="AV27" s="24">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:48">
@@ -4855,7 +4863,7 @@
       <c r="I28" s="43">
         <v>1</v>
       </c>
-      <c r="J28" s="21">
+      <c r="J28" s="22">
         <v>0</v>
       </c>
       <c r="K28" s="17">
@@ -4864,7 +4872,7 @@
       <c r="L28" s="43">
         <v>1</v>
       </c>
-      <c r="M28" s="21">
+      <c r="M28" s="22">
         <v>0</v>
       </c>
       <c r="N28" s="17">
@@ -4952,7 +4960,7 @@
         <v>2</v>
       </c>
       <c r="AV28" s="24">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:48">
@@ -4994,7 +5002,7 @@
         <v>1</v>
       </c>
       <c r="P29" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q29" s="17">
         <v>1</v>
@@ -5003,7 +5011,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T29" s="17">
         <v>0</v>
@@ -5041,7 +5049,7 @@
       <c r="AG29" s="43">
         <v>1</v>
       </c>
-      <c r="AH29" s="21">
+      <c r="AH29" s="22">
         <v>0</v>
       </c>
       <c r="AI29" s="44">
@@ -5071,7 +5079,7 @@
         <v>1</v>
       </c>
       <c r="AS29" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT29" s="23">
         <v>5</v>
@@ -5080,7 +5088,7 @@
         <v>4</v>
       </c>
       <c r="AV29" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:48">
@@ -5114,7 +5122,7 @@
       <c r="L30" s="43">
         <v>2</v>
       </c>
-      <c r="M30" s="21">
+      <c r="M30" s="22">
         <v>0</v>
       </c>
       <c r="N30" s="17">
@@ -5124,7 +5132,7 @@
         <v>2</v>
       </c>
       <c r="P30" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q30" s="17">
         <v>1</v>
@@ -5133,7 +5141,7 @@
         <v>2</v>
       </c>
       <c r="S30" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T30" s="17">
         <v>0</v>
@@ -5206,7 +5214,7 @@
         <v>6</v>
       </c>
       <c r="AV30" s="24">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:48">
@@ -5362,7 +5370,7 @@
       </c>
       <c r="M32" s="16"/>
       <c r="N32" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" s="43">
         <v>0</v>
@@ -5406,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="AF32" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG32" s="43">
         <v>0</v>
@@ -5416,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK32" s="43">
         <v>0</v>
@@ -5440,7 +5448,7 @@
       </c>
       <c r="AS32" s="16"/>
       <c r="AT32" s="23">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AU32" s="24">
         <v>0</v>
@@ -5521,7 +5529,7 @@
       <c r="AC33" s="43">
         <v>1</v>
       </c>
-      <c r="AD33" s="21">
+      <c r="AD33" s="22">
         <v>0</v>
       </c>
       <c r="AE33" s="45">
@@ -5548,31 +5556,31 @@
         <v>0</v>
       </c>
       <c r="AN33" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33" s="43">
         <v>1</v>
       </c>
-      <c r="AP33" s="21">
-        <v>0</v>
+      <c r="AP33" s="16">
+        <v>13</v>
       </c>
       <c r="AQ33" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR33" s="43">
         <v>1</v>
       </c>
-      <c r="AS33" s="21">
-        <v>0</v>
+      <c r="AS33" s="16">
+        <v>13</v>
       </c>
       <c r="AT33" s="23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU33" s="24">
         <v>3</v>
       </c>
       <c r="AV33" s="24">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:48">
@@ -5621,7 +5629,7 @@
         <v>1</v>
       </c>
       <c r="S34" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T34" s="17">
         <v>0</v>
@@ -5694,7 +5702,7 @@
         <v>1</v>
       </c>
       <c r="AV34" s="24">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:48">
@@ -5736,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q35" s="17">
         <v>0</v>
@@ -5744,7 +5752,7 @@
       <c r="R35" s="43">
         <v>1</v>
       </c>
-      <c r="S35" s="21">
+      <c r="S35" s="22">
         <v>0</v>
       </c>
       <c r="T35" s="17">
@@ -5818,7 +5826,7 @@
         <v>2</v>
       </c>
       <c r="AV35" s="24">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:48">
@@ -5840,13 +5848,13 @@
       </c>
       <c r="G36" s="16"/>
       <c r="H36" s="31">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I36" s="48">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J36" s="16">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K36" s="31">
         <v>15</v>
@@ -5855,22 +5863,22 @@
         <v>12</v>
       </c>
       <c r="M36" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N36" s="31">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O36" s="48">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P36" s="16">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Q36" s="31">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R36" s="48">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S36" s="16">
         <v>24</v>
@@ -5901,59 +5909,59 @@
       <c r="AC36" s="48">
         <v>1</v>
       </c>
-      <c r="AD36" s="21">
+      <c r="AD36" s="22">
         <v>0</v>
       </c>
       <c r="AE36" s="49">
         <v>1</v>
       </c>
       <c r="AF36" s="29">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG36" s="48">
         <v>7</v>
       </c>
       <c r="AH36" s="16">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AI36" s="49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ36" s="29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK36" s="48">
         <v>4</v>
       </c>
       <c r="AL36" s="16">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AM36" s="49">
         <v>3</v>
       </c>
       <c r="AN36" s="29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO36" s="48">
         <v>4</v>
       </c>
       <c r="AP36" s="16">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="AQ36" s="31">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AR36" s="48">
         <v>5</v>
       </c>
       <c r="AS36" s="16">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="AT36" s="23">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AU36" s="24">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AV36" s="24">
         <v>32</v>
@@ -6273,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -6377,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -7243,7 +7251,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" s="18">
         <v>1</v>
@@ -7282,18 +7290,18 @@
         <v>7</v>
       </c>
       <c r="Y7" s="18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z7" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA7" s="15">
-        <v>8</v>
-      </c>
-      <c r="AB7" s="21">
-        <v>3</v>
-      </c>
-      <c r="AC7" s="22">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="20">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="21">
         <v>3</v>
       </c>
       <c r="AD7" s="14">
@@ -7303,7 +7311,7 @@
         <v>3</v>
       </c>
       <c r="AF7" s="20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG7" s="18">
         <v>1</v>
@@ -7315,7 +7323,7 @@
         <v>3</v>
       </c>
       <c r="AJ7" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK7" s="17">
         <v>0</v>
@@ -7323,29 +7331,29 @@
       <c r="AL7" s="15">
         <v>10</v>
       </c>
-      <c r="AM7" s="21">
+      <c r="AM7" s="22">
         <v>0</v>
       </c>
       <c r="AN7" s="17">
+        <v>3</v>
+      </c>
+      <c r="AO7" s="15">
+        <v>10</v>
+      </c>
+      <c r="AP7" s="22">
         <v>4</v>
-      </c>
-      <c r="AO7" s="15">
-        <v>9</v>
-      </c>
-      <c r="AP7" s="20">
-        <v>5</v>
       </c>
       <c r="AQ7" s="18">
         <v>4</v>
       </c>
       <c r="AR7" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS7" s="15">
-        <v>4</v>
-      </c>
-      <c r="AT7" s="16">
-        <v>12</v>
+        <v>5</v>
+      </c>
+      <c r="AT7" s="20">
+        <v>8</v>
       </c>
       <c r="AU7" s="18">
         <v>2</v>
@@ -7357,7 +7365,7 @@
         <v>4</v>
       </c>
       <c r="AX7" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY7" s="18">
         <v>2</v>
@@ -7375,7 +7383,7 @@
       <c r="BD7" s="15">
         <v>2</v>
       </c>
-      <c r="BE7" s="21">
+      <c r="BE7" s="22">
         <v>0</v>
       </c>
       <c r="BF7" s="18">
@@ -7402,16 +7410,16 @@
         <v>0</v>
       </c>
       <c r="BO7" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP7" s="15">
-        <v>2</v>
-      </c>
-      <c r="BQ7" s="16">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="BQ7" s="22">
+        <v>4</v>
       </c>
       <c r="BR7" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS7" s="14">
         <v>0</v>
@@ -7440,22 +7448,22 @@
         <v>4</v>
       </c>
       <c r="CC7" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CD7" s="18">
         <v>2</v>
       </c>
       <c r="CE7" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CF7" s="15">
         <v>19</v>
       </c>
       <c r="CG7" s="20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CH7" s="18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CI7" s="14">
         <v>5</v>
@@ -7464,7 +7472,7 @@
         <v>1</v>
       </c>
       <c r="CK7" s="16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CL7" s="17">
         <v>4</v>
@@ -7473,25 +7481,25 @@
         <v>2</v>
       </c>
       <c r="CN7" s="16">
+        <v>26</v>
+      </c>
+      <c r="CO7" s="17">
+        <v>14</v>
+      </c>
+      <c r="CP7" s="15">
         <v>24</v>
-      </c>
-      <c r="CO7" s="17">
-        <v>15</v>
-      </c>
-      <c r="CP7" s="15">
-        <v>23</v>
       </c>
       <c r="CQ7" s="20">
         <v>8</v>
       </c>
       <c r="CR7" s="23">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="CS7" s="24">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="CT7" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:98">
@@ -7547,27 +7555,27 @@
       </c>
       <c r="U8" s="16"/>
       <c r="V8" s="17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W8" s="15">
         <v>18</v>
       </c>
-      <c r="X8" s="21">
-        <v>2</v>
+      <c r="X8" s="22">
+        <v>4</v>
       </c>
       <c r="Y8" s="18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="15">
+        <v>9</v>
+      </c>
+      <c r="AB8" s="22">
         <v>4</v>
       </c>
-      <c r="AA8" s="15">
-        <v>8</v>
-      </c>
-      <c r="AB8" s="20">
-        <v>6</v>
-      </c>
-      <c r="AC8" s="22">
+      <c r="AC8" s="21">
         <v>3</v>
       </c>
       <c r="AD8" s="14">
@@ -7594,16 +7602,16 @@
         <v>3</v>
       </c>
       <c r="AM8" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN8" s="17">
+        <v>3</v>
+      </c>
+      <c r="AO8" s="15">
+        <v>11</v>
+      </c>
+      <c r="AP8" s="22">
         <v>4</v>
-      </c>
-      <c r="AO8" s="15">
-        <v>10</v>
-      </c>
-      <c r="AP8" s="21">
-        <v>5</v>
       </c>
       <c r="AQ8" s="18">
         <v>4</v>
@@ -7614,7 +7622,7 @@
       <c r="AS8" s="15">
         <v>5</v>
       </c>
-      <c r="AT8" s="20">
+      <c r="AT8" s="16">
         <v>10</v>
       </c>
       <c r="AU8" s="18">
@@ -7627,7 +7635,7 @@
         <v>1</v>
       </c>
       <c r="AX8" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AY8" s="18">
         <v>0</v>
@@ -7646,7 +7654,7 @@
         <v>2</v>
       </c>
       <c r="BE8" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF8" s="18">
         <v>1</v>
@@ -7678,7 +7686,7 @@
         <v>1</v>
       </c>
       <c r="BQ8" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BR8" s="18">
         <v>1</v>
@@ -7700,7 +7708,7 @@
         <v>1</v>
       </c>
       <c r="BY8" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BZ8" s="18">
         <v>1</v>
@@ -7712,31 +7720,31 @@
         <v>6</v>
       </c>
       <c r="CC8" s="16">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="CD8" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CE8" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CF8" s="15">
-        <v>14</v>
-      </c>
-      <c r="CG8" s="20">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="CG8" s="16">
+        <v>10</v>
       </c>
       <c r="CH8" s="18">
         <v>8</v>
       </c>
       <c r="CI8" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CJ8" s="15">
         <v>3</v>
       </c>
       <c r="CK8" s="16">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CL8" s="17">
         <v>4</v>
@@ -7745,25 +7753,25 @@
         <v>1</v>
       </c>
       <c r="CN8" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CO8" s="17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CP8" s="15">
-        <v>44</v>
-      </c>
-      <c r="CQ8" s="21">
+        <v>50</v>
+      </c>
+      <c r="CQ8" s="22">
         <v>3</v>
       </c>
       <c r="CR8" s="23">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="CS8" s="24">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="CT8" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:98">
@@ -7824,20 +7832,20 @@
       <c r="W9" s="15">
         <v>26</v>
       </c>
-      <c r="X9" s="21">
+      <c r="X9" s="22">
         <v>4</v>
       </c>
       <c r="Y9" s="18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z9" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA9" s="15">
-        <v>19</v>
-      </c>
-      <c r="AB9" s="21">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="AB9" s="22">
+        <v>3</v>
       </c>
       <c r="AC9" s="25">
         <v>8</v>
@@ -7849,7 +7857,7 @@
         <v>3</v>
       </c>
       <c r="AF9" s="20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG9" s="18">
         <v>1</v>
@@ -7861,7 +7869,7 @@
         <v>15</v>
       </c>
       <c r="AJ9" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK9" s="17">
         <v>5</v>
@@ -7869,29 +7877,29 @@
       <c r="AL9" s="15">
         <v>13</v>
       </c>
-      <c r="AM9" s="21">
+      <c r="AM9" s="20">
         <v>5</v>
       </c>
       <c r="AN9" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO9" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP9" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ9" s="18">
         <v>3</v>
       </c>
       <c r="AR9" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS9" s="15">
-        <v>2</v>
-      </c>
-      <c r="AT9" s="16">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="AT9" s="22">
+        <v>4</v>
       </c>
       <c r="AU9" s="18">
         <v>1</v>
@@ -7903,7 +7911,7 @@
         <v>1</v>
       </c>
       <c r="AX9" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY9" s="18">
         <v>0</v>
@@ -7921,7 +7929,7 @@
       <c r="BD9" s="15">
         <v>2</v>
       </c>
-      <c r="BE9" s="21">
+      <c r="BE9" s="22">
         <v>0</v>
       </c>
       <c r="BF9" s="18">
@@ -7943,7 +7951,7 @@
       <c r="BL9" s="15">
         <v>1</v>
       </c>
-      <c r="BM9" s="21">
+      <c r="BM9" s="22">
         <v>0</v>
       </c>
       <c r="BN9" s="18">
@@ -7956,7 +7964,7 @@
         <v>2</v>
       </c>
       <c r="BQ9" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BR9" s="18">
         <v>1</v>
@@ -7972,13 +7980,13 @@
         <v>0</v>
       </c>
       <c r="BW9" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BX9" s="15">
-        <v>4</v>
-      </c>
-      <c r="BY9" s="20">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="BY9" s="22">
+        <v>3</v>
       </c>
       <c r="BZ9" s="18">
         <v>3</v>
@@ -7993,19 +8001,19 @@
         <v>8</v>
       </c>
       <c r="CD9" s="18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CE9" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CF9" s="15">
-        <v>29</v>
-      </c>
-      <c r="CG9" s="20">
+        <v>30</v>
+      </c>
+      <c r="CG9" s="22">
         <v>5</v>
       </c>
       <c r="CH9" s="18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CI9" s="14">
         <v>4</v>
@@ -8013,7 +8021,7 @@
       <c r="CJ9" s="15">
         <v>5</v>
       </c>
-      <c r="CK9" s="20">
+      <c r="CK9" s="16">
         <v>10</v>
       </c>
       <c r="CL9" s="17">
@@ -8023,22 +8031,22 @@
         <v>2</v>
       </c>
       <c r="CN9" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CO9" s="17">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="CP9" s="15">
-        <v>141</v>
-      </c>
-      <c r="CQ9" s="21">
+        <v>142</v>
+      </c>
+      <c r="CQ9" s="22">
         <v>4</v>
       </c>
       <c r="CR9" s="23">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="CS9" s="24">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="CT9" s="24">
         <v>5</v>
@@ -8097,13 +8105,13 @@
       </c>
       <c r="U10" s="16"/>
       <c r="V10" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W10" s="15">
         <v>2</v>
       </c>
       <c r="X10" s="16">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y10" s="18">
         <v>1</v>
@@ -8115,9 +8123,9 @@
         <v>2</v>
       </c>
       <c r="AB10" s="16">
-        <v>24</v>
-      </c>
-      <c r="AC10" s="22">
+        <v>26</v>
+      </c>
+      <c r="AC10" s="21">
         <v>1</v>
       </c>
       <c r="AD10" s="14">
@@ -8145,19 +8153,19 @@
       </c>
       <c r="AM10" s="16"/>
       <c r="AN10" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO10" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP10" s="20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AQ10" s="18">
         <v>2</v>
       </c>
       <c r="AR10" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS10" s="15">
         <v>0</v>
@@ -8167,13 +8175,13 @@
         <v>0</v>
       </c>
       <c r="AV10" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10" s="15">
         <v>1</v>
       </c>
-      <c r="AX10" s="21">
-        <v>0</v>
+      <c r="AX10" s="16">
+        <v>13</v>
       </c>
       <c r="AY10" s="18">
         <v>0</v>
@@ -8192,7 +8200,7 @@
         <v>1</v>
       </c>
       <c r="BE10" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BF10" s="18">
         <v>1</v>
@@ -8218,13 +8226,13 @@
         <v>0</v>
       </c>
       <c r="BO10" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BP10" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ10" s="16">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="BR10" s="18">
         <v>1</v>
@@ -8240,16 +8248,16 @@
         <v>0</v>
       </c>
       <c r="BW10" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BX10" s="15">
         <v>4</v>
       </c>
       <c r="BY10" s="16">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BZ10" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CA10" s="14">
         <v>4</v>
@@ -8270,19 +8278,19 @@
         <v>1</v>
       </c>
       <c r="CG10" s="16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CH10" s="18">
         <v>1</v>
       </c>
       <c r="CI10" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ10" s="15">
         <v>1</v>
       </c>
       <c r="CK10" s="16">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="CL10" s="17">
         <v>2</v>
@@ -8292,22 +8300,22 @@
       </c>
       <c r="CN10" s="16"/>
       <c r="CO10" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CP10" s="15">
         <v>6</v>
       </c>
-      <c r="CQ10" s="20">
-        <v>6</v>
+      <c r="CQ10" s="16">
+        <v>11</v>
       </c>
       <c r="CR10" s="23">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="CS10" s="24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CT10" s="24">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:98">
@@ -8368,11 +8376,11 @@
       <c r="W11" s="15">
         <v>9</v>
       </c>
-      <c r="X11" s="21">
+      <c r="X11" s="22">
         <v>3</v>
       </c>
       <c r="Y11" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z11" s="14">
         <v>0</v>
@@ -8381,7 +8389,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="16"/>
-      <c r="AC11" s="22">
+      <c r="AC11" s="21">
         <v>0</v>
       </c>
       <c r="AD11" s="14">
@@ -8400,7 +8408,7 @@
       <c r="AI11" s="15">
         <v>6</v>
       </c>
-      <c r="AJ11" s="21">
+      <c r="AJ11" s="22">
         <v>4</v>
       </c>
       <c r="AK11" s="17">
@@ -8409,17 +8417,17 @@
       <c r="AL11" s="15">
         <v>4</v>
       </c>
-      <c r="AM11" s="21">
+      <c r="AM11" s="22">
         <v>3</v>
       </c>
       <c r="AN11" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="15">
-        <v>4</v>
-      </c>
-      <c r="AP11" s="21">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AP11" s="22">
+        <v>0</v>
       </c>
       <c r="AQ11" s="18">
         <v>2</v>
@@ -8431,7 +8439,7 @@
         <v>2</v>
       </c>
       <c r="AT11" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU11" s="18">
         <v>1</v>
@@ -8443,7 +8451,7 @@
         <v>1</v>
       </c>
       <c r="AX11" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY11" s="18">
         <v>0</v>
@@ -8481,7 +8489,7 @@
       <c r="BL11" s="15">
         <v>1</v>
       </c>
-      <c r="BM11" s="21">
+      <c r="BM11" s="22">
         <v>0</v>
       </c>
       <c r="BN11" s="18">
@@ -8494,7 +8502,7 @@
         <v>1</v>
       </c>
       <c r="BQ11" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BR11" s="18">
         <v>1</v>
@@ -8505,20 +8513,20 @@
       <c r="BT11" s="15">
         <v>1</v>
       </c>
-      <c r="BU11" s="21">
+      <c r="BU11" s="22">
         <v>0</v>
       </c>
       <c r="BV11" s="18">
         <v>1</v>
       </c>
       <c r="BW11" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BX11" s="15">
         <v>3</v>
       </c>
-      <c r="BY11" s="21">
-        <v>0</v>
+      <c r="BY11" s="16">
+        <v>13</v>
       </c>
       <c r="BZ11" s="18">
         <v>2</v>
@@ -8533,7 +8541,7 @@
         <v>7</v>
       </c>
       <c r="CD11" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CE11" s="14">
         <v>6</v>
@@ -8542,10 +8550,10 @@
         <v>8</v>
       </c>
       <c r="CG11" s="20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CH11" s="18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CI11" s="14">
         <v>2</v>
@@ -8560,23 +8568,23 @@
       <c r="CM11" s="15">
         <v>2</v>
       </c>
-      <c r="CN11" s="21">
+      <c r="CN11" s="22">
         <v>0</v>
       </c>
       <c r="CO11" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP11" s="15">
-        <v>8</v>
-      </c>
-      <c r="CQ11" s="21">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="CQ11" s="22">
+        <v>1</v>
       </c>
       <c r="CR11" s="23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CS11" s="24">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="CT11" s="24">
         <v>5</v>
@@ -8600,16 +8608,16 @@
         <v>1</v>
       </c>
       <c r="G12" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="16">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K12" s="18">
         <v>2</v>
@@ -8645,7 +8653,7 @@
         <v>2</v>
       </c>
       <c r="X12" s="16">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Y12" s="18">
         <v>1</v>
@@ -8657,10 +8665,10 @@
         <v>6</v>
       </c>
       <c r="AB12" s="20">
-        <v>6</v>
-      </c>
-      <c r="AC12" s="22">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="AC12" s="21">
+        <v>2</v>
       </c>
       <c r="AD12" s="14">
         <v>3</v>
@@ -8686,7 +8694,7 @@
         <v>2</v>
       </c>
       <c r="AM12" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN12" s="17">
         <v>2</v>
@@ -8705,7 +8713,7 @@
         <v>2</v>
       </c>
       <c r="AT12" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU12" s="18">
         <v>1</v>
@@ -8717,7 +8725,7 @@
         <v>1</v>
       </c>
       <c r="AX12" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY12" s="18">
         <v>0</v>
@@ -8736,7 +8744,7 @@
         <v>2</v>
       </c>
       <c r="BE12" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF12" s="18">
         <v>1</v>
@@ -8757,7 +8765,7 @@
       <c r="BL12" s="15">
         <v>2</v>
       </c>
-      <c r="BM12" s="21">
+      <c r="BM12" s="22">
         <v>0</v>
       </c>
       <c r="BN12" s="18">
@@ -8770,7 +8778,7 @@
         <v>2</v>
       </c>
       <c r="BQ12" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BR12" s="18">
         <v>1</v>
@@ -8792,7 +8800,7 @@
         <v>2</v>
       </c>
       <c r="BY12" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ12" s="18">
         <v>1</v>
@@ -8804,7 +8812,7 @@
         <v>1</v>
       </c>
       <c r="CC12" s="16">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="CD12" s="18">
         <v>0</v>
@@ -8816,18 +8824,20 @@
         <v>6</v>
       </c>
       <c r="CG12" s="20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CH12" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CI12" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CJ12" s="15">
-        <v>0</v>
-      </c>
-      <c r="CK12" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="CK12" s="16">
+        <v>13</v>
+      </c>
       <c r="CL12" s="17">
         <v>2</v>
       </c>
@@ -8842,13 +8852,13 @@
         <v>3</v>
       </c>
       <c r="CQ12" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CR12" s="23">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="CS12" s="24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CT12" s="24">
         <v>19</v>
@@ -8913,7 +8923,7 @@
         <v>5</v>
       </c>
       <c r="X13" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13" s="18">
         <v>2</v>
@@ -8925,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="16"/>
-      <c r="AC13" s="22">
+      <c r="AC13" s="21">
         <v>0</v>
       </c>
       <c r="AD13" s="14">
@@ -8959,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="AP13" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ13" s="18">
         <v>0</v>
@@ -8981,7 +8991,7 @@
         <v>1</v>
       </c>
       <c r="AX13" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY13" s="18">
         <v>0</v>
@@ -9000,7 +9010,7 @@
         <v>2</v>
       </c>
       <c r="BE13" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF13" s="18">
         <v>1</v>
@@ -9021,7 +9031,7 @@
       <c r="BL13" s="15">
         <v>2</v>
       </c>
-      <c r="BM13" s="21">
+      <c r="BM13" s="22">
         <v>0</v>
       </c>
       <c r="BN13" s="18">
@@ -9054,7 +9064,7 @@
         <v>1</v>
       </c>
       <c r="BY13" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BZ13" s="18">
         <v>1</v>
@@ -9076,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="CG13" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CH13" s="18">
         <v>1</v>
@@ -9102,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="CQ13" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CR13" s="23">
         <v>52</v>
@@ -9111,7 +9121,7 @@
         <v>14</v>
       </c>
       <c r="CT13" s="24">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:98">
@@ -9167,13 +9177,13 @@
       </c>
       <c r="U14" s="16"/>
       <c r="V14" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W14" s="15">
-        <v>6</v>
-      </c>
-      <c r="X14" s="20">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="X14" s="22">
+        <v>4</v>
       </c>
       <c r="Y14" s="18">
         <v>3</v>
@@ -9185,9 +9195,9 @@
         <v>2</v>
       </c>
       <c r="AB14" s="16">
-        <v>12</v>
-      </c>
-      <c r="AC14" s="22">
+        <v>13</v>
+      </c>
+      <c r="AC14" s="21">
         <v>1</v>
       </c>
       <c r="AD14" s="14">
@@ -9197,7 +9207,7 @@
         <v>1</v>
       </c>
       <c r="AF14" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG14" s="18">
         <v>0</v>
@@ -9210,13 +9220,13 @@
       </c>
       <c r="AJ14" s="16"/>
       <c r="AK14" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL14" s="15">
-        <v>3</v>
-      </c>
-      <c r="AM14" s="20">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="AM14" s="22">
+        <v>3</v>
       </c>
       <c r="AN14" s="17">
         <v>2</v>
@@ -9225,7 +9235,7 @@
         <v>4</v>
       </c>
       <c r="AP14" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ14" s="18">
         <v>2</v>
@@ -9237,7 +9247,7 @@
         <v>1</v>
       </c>
       <c r="AT14" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AU14" s="18">
         <v>0</v>
@@ -9249,7 +9259,7 @@
         <v>1</v>
       </c>
       <c r="AX14" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY14" s="18">
         <v>0</v>
@@ -9307,7 +9317,7 @@
       <c r="BT14" s="15">
         <v>1</v>
       </c>
-      <c r="BU14" s="21">
+      <c r="BU14" s="22">
         <v>0</v>
       </c>
       <c r="BV14" s="18">
@@ -9330,22 +9340,22 @@
         <v>1</v>
       </c>
       <c r="CC14" s="16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CD14" s="18">
         <v>0</v>
       </c>
       <c r="CE14" s="14">
+        <v>2</v>
+      </c>
+      <c r="CF14" s="15">
+        <v>6</v>
+      </c>
+      <c r="CG14" s="22">
         <v>4</v>
       </c>
-      <c r="CF14" s="15">
-        <v>4</v>
-      </c>
-      <c r="CG14" s="16">
-        <v>12</v>
-      </c>
       <c r="CH14" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CI14" s="14">
         <v>4</v>
@@ -9361,7 +9371,7 @@
         <v>2</v>
       </c>
       <c r="CN14" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CO14" s="17">
         <v>5</v>
@@ -9370,16 +9380,16 @@
         <v>2</v>
       </c>
       <c r="CQ14" s="16">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="CR14" s="23">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="CS14" s="24">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="CT14" s="24">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:98">
@@ -9435,13 +9445,13 @@
       </c>
       <c r="U15" s="16"/>
       <c r="V15" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W15" s="15">
         <v>8</v>
       </c>
-      <c r="X15" s="21">
-        <v>3</v>
+      <c r="X15" s="20">
+        <v>7</v>
       </c>
       <c r="Y15" s="18">
         <v>3</v>
@@ -9453,9 +9463,9 @@
         <v>4</v>
       </c>
       <c r="AB15" s="20">
-        <v>9</v>
-      </c>
-      <c r="AC15" s="22">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="21">
         <v>2</v>
       </c>
       <c r="AD15" s="14">
@@ -9482,16 +9492,16 @@
         <v>4</v>
       </c>
       <c r="AM15" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN15" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO15" s="15">
-        <v>2</v>
-      </c>
-      <c r="AP15" s="16">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="AP15" s="22">
+        <v>4</v>
       </c>
       <c r="AQ15" s="18">
         <v>1</v>
@@ -9513,7 +9523,7 @@
         <v>4</v>
       </c>
       <c r="AX15" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY15" s="18">
         <v>2</v>
@@ -9532,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="BE15" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF15" s="18">
         <v>1</v>
@@ -9543,7 +9553,7 @@
       <c r="BH15" s="15">
         <v>1</v>
       </c>
-      <c r="BI15" s="21">
+      <c r="BI15" s="22">
         <v>0</v>
       </c>
       <c r="BJ15" s="18">
@@ -9555,7 +9565,7 @@
       <c r="BL15" s="15">
         <v>2</v>
       </c>
-      <c r="BM15" s="21">
+      <c r="BM15" s="22">
         <v>0</v>
       </c>
       <c r="BN15" s="18">
@@ -9568,7 +9578,7 @@
         <v>1</v>
       </c>
       <c r="BQ15" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BR15" s="18">
         <v>1</v>
@@ -9580,7 +9590,7 @@
         <v>2</v>
       </c>
       <c r="BU15" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BV15" s="18">
         <v>1</v>
@@ -9602,55 +9612,55 @@
         <v>6</v>
       </c>
       <c r="CC15" s="20">
+        <v>9</v>
+      </c>
+      <c r="CD15" s="18">
+        <v>2</v>
+      </c>
+      <c r="CE15" s="14">
+        <v>3</v>
+      </c>
+      <c r="CF15" s="15">
+        <v>1</v>
+      </c>
+      <c r="CG15" s="16">
+        <v>39</v>
+      </c>
+      <c r="CH15" s="18">
+        <v>1</v>
+      </c>
+      <c r="CI15" s="14">
+        <v>3</v>
+      </c>
+      <c r="CJ15" s="15">
+        <v>2</v>
+      </c>
+      <c r="CK15" s="16">
+        <v>20</v>
+      </c>
+      <c r="CL15" s="17">
+        <v>2</v>
+      </c>
+      <c r="CM15" s="15">
+        <v>2</v>
+      </c>
+      <c r="CN15" s="16">
+        <v>13</v>
+      </c>
+      <c r="CO15" s="17">
+        <v>3</v>
+      </c>
+      <c r="CP15" s="15">
+        <v>5</v>
+      </c>
+      <c r="CQ15" s="20">
         <v>8</v>
       </c>
-      <c r="CD15" s="18">
-        <v>3</v>
-      </c>
-      <c r="CE15" s="14">
-        <v>3</v>
-      </c>
-      <c r="CF15" s="15">
-        <v>1</v>
-      </c>
-      <c r="CG15" s="16">
-        <v>36</v>
-      </c>
-      <c r="CH15" s="18">
-        <v>1</v>
-      </c>
-      <c r="CI15" s="14">
-        <v>3</v>
-      </c>
-      <c r="CJ15" s="15">
-        <v>2</v>
-      </c>
-      <c r="CK15" s="16">
-        <v>18</v>
-      </c>
-      <c r="CL15" s="17">
-        <v>1</v>
-      </c>
-      <c r="CM15" s="15">
-        <v>2</v>
-      </c>
-      <c r="CN15" s="20">
-        <v>6</v>
-      </c>
-      <c r="CO15" s="17">
-        <v>4</v>
-      </c>
-      <c r="CP15" s="15">
-        <v>3</v>
-      </c>
-      <c r="CQ15" s="16">
-        <v>16</v>
-      </c>
       <c r="CR15" s="23">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CS15" s="24">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="CT15" s="24">
         <v>11</v>
@@ -9715,7 +9725,7 @@
         <v>5</v>
       </c>
       <c r="X16" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16" s="18">
         <v>2</v>
@@ -9727,9 +9737,9 @@
         <v>2</v>
       </c>
       <c r="AB16" s="16">
-        <v>12</v>
-      </c>
-      <c r="AC16" s="22">
+        <v>13</v>
+      </c>
+      <c r="AC16" s="21">
         <v>1</v>
       </c>
       <c r="AD16" s="14">
@@ -9749,7 +9759,7 @@
         <v>1</v>
       </c>
       <c r="AJ16" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AK16" s="17">
         <v>0</v>
@@ -9757,7 +9767,7 @@
       <c r="AL16" s="15">
         <v>3</v>
       </c>
-      <c r="AM16" s="21">
+      <c r="AM16" s="22">
         <v>0</v>
       </c>
       <c r="AN16" s="17">
@@ -9767,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="AP16" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ16" s="18">
         <v>0</v>
@@ -9789,7 +9799,7 @@
         <v>1</v>
       </c>
       <c r="AX16" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY16" s="18">
         <v>0</v>
@@ -9807,7 +9817,7 @@
       <c r="BD16" s="15">
         <v>2</v>
       </c>
-      <c r="BE16" s="21">
+      <c r="BE16" s="22">
         <v>0</v>
       </c>
       <c r="BF16" s="18">
@@ -9834,16 +9844,16 @@
         <v>0</v>
       </c>
       <c r="BO16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP16" s="15">
-        <v>2</v>
-      </c>
-      <c r="BQ16" s="16">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="BQ16" s="22">
+        <v>4</v>
       </c>
       <c r="BR16" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS16" s="14">
         <v>0</v>
@@ -9862,7 +9872,7 @@
         <v>2</v>
       </c>
       <c r="BY16" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BZ16" s="18">
         <v>1</v>
@@ -9874,7 +9884,7 @@
         <v>3</v>
       </c>
       <c r="CC16" s="20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CD16" s="18">
         <v>1</v>
@@ -9886,7 +9896,7 @@
         <v>3</v>
       </c>
       <c r="CG16" s="20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CH16" s="18">
         <v>2</v>
@@ -9905,7 +9915,7 @@
         <v>1</v>
       </c>
       <c r="CN16" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CO16" s="17">
         <v>4</v>
@@ -9913,14 +9923,14 @@
       <c r="CP16" s="15">
         <v>13</v>
       </c>
-      <c r="CQ16" s="21">
+      <c r="CQ16" s="22">
         <v>4</v>
       </c>
       <c r="CR16" s="23">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CS16" s="24">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CT16" s="24">
         <v>11</v>
@@ -9985,7 +9995,7 @@
         <v>2</v>
       </c>
       <c r="X17" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y17" s="18">
         <v>1</v>
@@ -9997,9 +10007,9 @@
         <v>2</v>
       </c>
       <c r="AB17" s="16">
-        <v>12</v>
-      </c>
-      <c r="AC17" s="22">
+        <v>13</v>
+      </c>
+      <c r="AC17" s="21">
         <v>1</v>
       </c>
       <c r="AD17" s="14">
@@ -10019,7 +10029,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK17" s="17">
         <v>0</v>
@@ -10045,7 +10055,7 @@
         <v>1</v>
       </c>
       <c r="AT17" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU17" s="18">
         <v>0</v>
@@ -10088,14 +10098,16 @@
         <v>0</v>
       </c>
       <c r="BK17" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL17" s="15">
-        <v>0</v>
-      </c>
-      <c r="BM17" s="16"/>
-      <c r="BN17" s="19">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="BM17" s="22">
+        <v>0</v>
+      </c>
+      <c r="BN17" s="18">
+        <v>1</v>
       </c>
       <c r="BO17" s="14">
         <v>0</v>
@@ -10128,24 +10140,28 @@
         <v>0</v>
       </c>
       <c r="CA17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CB17" s="15">
-        <v>0</v>
-      </c>
-      <c r="CC17" s="16"/>
-      <c r="CD17" s="19">
+        <v>1</v>
+      </c>
+      <c r="CC17" s="16">
+        <v>26</v>
+      </c>
+      <c r="CD17" s="18">
         <v>0</v>
       </c>
       <c r="CE17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF17" s="15">
-        <v>0</v>
-      </c>
-      <c r="CG17" s="16"/>
-      <c r="CH17" s="19">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CG17" s="16">
+        <v>13</v>
+      </c>
+      <c r="CH17" s="18">
+        <v>1</v>
       </c>
       <c r="CI17" s="14">
         <v>2</v>
@@ -10169,13 +10185,13 @@
       </c>
       <c r="CQ17" s="16"/>
       <c r="CR17" s="23">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CS17" s="24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CT17" s="24">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:98">
@@ -10237,21 +10253,21 @@
         <v>14</v>
       </c>
       <c r="X18" s="20">
+        <v>6</v>
+      </c>
+      <c r="Y18" s="18">
         <v>5</v>
       </c>
-      <c r="Y18" s="18">
-        <v>6</v>
-      </c>
       <c r="Z18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA18" s="15">
-        <v>11</v>
-      </c>
-      <c r="AB18" s="20">
-        <v>6</v>
-      </c>
-      <c r="AC18" s="22">
+        <v>12</v>
+      </c>
+      <c r="AB18" s="22">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="21">
         <v>5</v>
       </c>
       <c r="AD18" s="14">
@@ -10272,14 +10288,14 @@
       </c>
       <c r="AJ18" s="16"/>
       <c r="AK18" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" s="15">
-        <v>3</v>
-      </c>
-      <c r="AM18" s="21">
         <v>4</v>
       </c>
+      <c r="AM18" s="22">
+        <v>0</v>
+      </c>
       <c r="AN18" s="17">
         <v>1</v>
       </c>
@@ -10287,7 +10303,7 @@
         <v>2</v>
       </c>
       <c r="AP18" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ18" s="18">
         <v>1</v>
@@ -10299,7 +10315,7 @@
         <v>3</v>
       </c>
       <c r="AT18" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU18" s="18">
         <v>1</v>
@@ -10311,7 +10327,7 @@
         <v>1</v>
       </c>
       <c r="AX18" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AY18" s="18">
         <v>0</v>
@@ -10329,7 +10345,7 @@
       <c r="BD18" s="15">
         <v>2</v>
       </c>
-      <c r="BE18" s="21">
+      <c r="BE18" s="22">
         <v>0</v>
       </c>
       <c r="BF18" s="18">
@@ -10351,7 +10367,7 @@
       <c r="BL18" s="15">
         <v>1</v>
       </c>
-      <c r="BM18" s="21">
+      <c r="BM18" s="22">
         <v>0</v>
       </c>
       <c r="BN18" s="18">
@@ -10364,7 +10380,7 @@
         <v>2</v>
       </c>
       <c r="BQ18" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BR18" s="18">
         <v>1</v>
@@ -10385,7 +10401,7 @@
       <c r="BX18" s="15">
         <v>6</v>
       </c>
-      <c r="BY18" s="21">
+      <c r="BY18" s="22">
         <v>4</v>
       </c>
       <c r="BZ18" s="18">
@@ -10398,7 +10414,7 @@
         <v>8</v>
       </c>
       <c r="CC18" s="20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CD18" s="18">
         <v>3</v>
@@ -10410,7 +10426,7 @@
         <v>4</v>
       </c>
       <c r="CG18" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CH18" s="18">
         <v>2</v>
@@ -10422,7 +10438,7 @@
         <v>3</v>
       </c>
       <c r="CK18" s="20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CL18" s="17">
         <v>2</v>
@@ -10432,19 +10448,19 @@
       </c>
       <c r="CN18" s="16"/>
       <c r="CO18" s="17">
+        <v>8</v>
+      </c>
+      <c r="CP18" s="15">
+        <v>12</v>
+      </c>
+      <c r="CQ18" s="20">
         <v>9</v>
       </c>
-      <c r="CP18" s="15">
-        <v>11</v>
-      </c>
-      <c r="CQ18" s="20">
-        <v>10</v>
-      </c>
       <c r="CR18" s="23">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="CS18" s="24">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="CT18" s="24">
         <v>10</v>
@@ -10518,10 +10534,10 @@
       <c r="AA19" s="15">
         <v>2</v>
       </c>
-      <c r="AB19" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="22">
+      <c r="AB19" s="22">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="21">
         <v>1</v>
       </c>
       <c r="AD19" s="14">
@@ -10540,7 +10556,7 @@
       <c r="AI19" s="15">
         <v>1</v>
       </c>
-      <c r="AJ19" s="21">
+      <c r="AJ19" s="22">
         <v>0</v>
       </c>
       <c r="AK19" s="17">
@@ -10593,7 +10609,7 @@
       <c r="BD19" s="15">
         <v>1</v>
       </c>
-      <c r="BE19" s="21">
+      <c r="BE19" s="22">
         <v>0</v>
       </c>
       <c r="BF19" s="18">
@@ -10615,7 +10631,7 @@
       <c r="BL19" s="15">
         <v>1</v>
       </c>
-      <c r="BM19" s="21">
+      <c r="BM19" s="22">
         <v>0</v>
       </c>
       <c r="BN19" s="18">
@@ -10658,7 +10674,7 @@
         <v>1</v>
       </c>
       <c r="CC19" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CD19" s="18">
         <v>0</v>
@@ -10679,7 +10695,7 @@
       <c r="CJ19" s="15">
         <v>1</v>
       </c>
-      <c r="CK19" s="21">
+      <c r="CK19" s="22">
         <v>0</v>
       </c>
       <c r="CL19" s="17">
@@ -10703,7 +10719,7 @@
         <v>7</v>
       </c>
       <c r="CT19" s="24">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:98">
@@ -10725,13 +10741,13 @@
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="15">
         <v>2</v>
       </c>
-      <c r="J20" s="21">
-        <v>0</v>
+      <c r="J20" s="20">
+        <v>7</v>
       </c>
       <c r="K20" s="18">
         <v>2</v>
@@ -10761,27 +10777,27 @@
       </c>
       <c r="U20" s="16"/>
       <c r="V20" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W20" s="15">
         <v>12</v>
       </c>
       <c r="X20" s="20">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y20" s="18">
         <v>5</v>
       </c>
       <c r="Z20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA20" s="15">
-        <v>11</v>
-      </c>
-      <c r="AB20" s="21">
-        <v>3</v>
-      </c>
-      <c r="AC20" s="22">
+        <v>13</v>
+      </c>
+      <c r="AB20" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="21">
         <v>5</v>
       </c>
       <c r="AD20" s="14">
@@ -10791,7 +10807,7 @@
         <v>2</v>
       </c>
       <c r="AF20" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG20" s="18">
         <v>1</v>
@@ -10804,13 +10820,13 @@
       </c>
       <c r="AJ20" s="16"/>
       <c r="AK20" s="17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AL20" s="15">
-        <v>13</v>
-      </c>
-      <c r="AM20" s="21">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="AM20" s="22">
+        <v>2</v>
       </c>
       <c r="AN20" s="17">
         <v>4</v>
@@ -10819,7 +10835,7 @@
         <v>4</v>
       </c>
       <c r="AP20" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ20" s="18">
         <v>2</v>
@@ -10841,7 +10857,7 @@
         <v>2</v>
       </c>
       <c r="AX20" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY20" s="18">
         <v>1</v>
@@ -10854,13 +10870,13 @@
       </c>
       <c r="BB20" s="16"/>
       <c r="BC20" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD20" s="15">
         <v>2</v>
       </c>
       <c r="BE20" s="16">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="BF20" s="18">
         <v>1</v>
@@ -10886,16 +10902,16 @@
         <v>0</v>
       </c>
       <c r="BO20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BP20" s="15">
         <v>4</v>
       </c>
-      <c r="BQ20" s="21">
-        <v>3</v>
+      <c r="BQ20" s="20">
+        <v>10</v>
       </c>
       <c r="BR20" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS20" s="14">
         <v>0</v>
@@ -10914,7 +10930,7 @@
         <v>3</v>
       </c>
       <c r="BY20" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ20" s="18">
         <v>2</v>
@@ -10926,7 +10942,7 @@
         <v>7</v>
       </c>
       <c r="CC20" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CD20" s="18">
         <v>3</v>
@@ -10938,19 +10954,19 @@
         <v>6</v>
       </c>
       <c r="CG20" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CH20" s="18">
+        <v>3</v>
+      </c>
+      <c r="CI20" s="14">
+        <v>1</v>
+      </c>
+      <c r="CJ20" s="15">
         <v>4</v>
       </c>
-      <c r="CI20" s="14">
-        <v>2</v>
-      </c>
-      <c r="CJ20" s="15">
-        <v>3</v>
-      </c>
-      <c r="CK20" s="20">
-        <v>8</v>
+      <c r="CK20" s="22">
+        <v>3</v>
       </c>
       <c r="CL20" s="17">
         <v>4</v>
@@ -10960,19 +10976,19 @@
       </c>
       <c r="CN20" s="16"/>
       <c r="CO20" s="17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CP20" s="15">
         <v>13</v>
       </c>
-      <c r="CQ20" s="21">
-        <v>3</v>
+      <c r="CQ20" s="20">
+        <v>6</v>
       </c>
       <c r="CR20" s="23">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="CS20" s="24">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="CT20" s="24">
         <v>9</v>
@@ -11037,7 +11053,7 @@
         <v>1</v>
       </c>
       <c r="X21" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y21" s="18">
         <v>0</v>
@@ -11049,9 +11065,9 @@
         <v>1</v>
       </c>
       <c r="AB21" s="16">
-        <v>24</v>
-      </c>
-      <c r="AC21" s="22">
+        <v>26</v>
+      </c>
+      <c r="AC21" s="21">
         <v>0</v>
       </c>
       <c r="AD21" s="14">
@@ -11071,7 +11087,7 @@
         <v>3</v>
       </c>
       <c r="AJ21" s="20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK21" s="17">
         <v>2</v>
@@ -11080,7 +11096,7 @@
         <v>1</v>
       </c>
       <c r="AM21" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AN21" s="17">
         <v>2</v>
@@ -11089,7 +11105,7 @@
         <v>1</v>
       </c>
       <c r="AP21" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ21" s="18">
         <v>0</v>
@@ -11178,7 +11194,7 @@
         <v>2</v>
       </c>
       <c r="BY21" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BZ21" s="18">
         <v>1</v>
@@ -11224,7 +11240,7 @@
         <v>1</v>
       </c>
       <c r="CQ21" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="CR21" s="23">
         <v>44</v>
@@ -11233,7 +11249,7 @@
         <v>10</v>
       </c>
       <c r="CT21" s="24">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:98">
@@ -11260,7 +11276,7 @@
       <c r="I22" s="15">
         <v>1</v>
       </c>
-      <c r="J22" s="21">
+      <c r="J22" s="22">
         <v>0</v>
       </c>
       <c r="K22" s="18">
@@ -11291,27 +11307,27 @@
       </c>
       <c r="U22" s="16"/>
       <c r="V22" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W22" s="15">
-        <v>28</v>
-      </c>
-      <c r="X22" s="21">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="X22" s="22">
+        <v>1</v>
       </c>
       <c r="Y22" s="18">
         <v>12</v>
       </c>
       <c r="Z22" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA22" s="15">
-        <v>12</v>
-      </c>
-      <c r="AB22" s="20">
-        <v>6</v>
-      </c>
-      <c r="AC22" s="22">
+        <v>14</v>
+      </c>
+      <c r="AB22" s="22">
+        <v>4</v>
+      </c>
+      <c r="AC22" s="21">
         <v>5</v>
       </c>
       <c r="AD22" s="14">
@@ -11321,19 +11337,19 @@
         <v>1</v>
       </c>
       <c r="AF22" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG22" s="18">
         <v>0</v>
       </c>
       <c r="AH22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ22" s="16">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AK22" s="17">
         <v>0</v>
@@ -11341,17 +11357,17 @@
       <c r="AL22" s="15">
         <v>12</v>
       </c>
-      <c r="AM22" s="21">
+      <c r="AM22" s="22">
         <v>0</v>
       </c>
       <c r="AN22" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO22" s="15">
-        <v>6</v>
-      </c>
-      <c r="AP22" s="21">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="AP22" s="22">
+        <v>0</v>
       </c>
       <c r="AQ22" s="18">
         <v>3</v>
@@ -11363,19 +11379,19 @@
         <v>2</v>
       </c>
       <c r="AT22" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU22" s="18">
         <v>1</v>
       </c>
       <c r="AV22" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW22" s="15">
         <v>3</v>
       </c>
-      <c r="AX22" s="21">
-        <v>0</v>
+      <c r="AX22" s="22">
+        <v>4</v>
       </c>
       <c r="AY22" s="18">
         <v>1</v>
@@ -11393,7 +11409,7 @@
       <c r="BD22" s="15">
         <v>2</v>
       </c>
-      <c r="BE22" s="21">
+      <c r="BE22" s="22">
         <v>0</v>
       </c>
       <c r="BF22" s="18">
@@ -11415,20 +11431,20 @@
       <c r="BL22" s="15">
         <v>1</v>
       </c>
-      <c r="BM22" s="21">
+      <c r="BM22" s="22">
         <v>0</v>
       </c>
       <c r="BN22" s="18">
         <v>1</v>
       </c>
       <c r="BO22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BP22" s="15">
         <v>3</v>
       </c>
       <c r="BQ22" s="16">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BR22" s="18">
         <v>2</v>
@@ -11449,7 +11465,7 @@
       <c r="BX22" s="15">
         <v>5</v>
       </c>
-      <c r="BY22" s="20">
+      <c r="BY22" s="16">
         <v>10</v>
       </c>
       <c r="BZ22" s="18">
@@ -11468,17 +11484,17 @@
         <v>5</v>
       </c>
       <c r="CE22" s="14">
+        <v>3</v>
+      </c>
+      <c r="CF22" s="15">
+        <v>11</v>
+      </c>
+      <c r="CG22" s="22">
+        <v>4</v>
+      </c>
+      <c r="CH22" s="18">
         <v>6</v>
       </c>
-      <c r="CF22" s="15">
-        <v>8</v>
-      </c>
-      <c r="CG22" s="20">
-        <v>9</v>
-      </c>
-      <c r="CH22" s="18">
-        <v>5</v>
-      </c>
       <c r="CI22" s="14">
         <v>3</v>
       </c>
@@ -11486,7 +11502,7 @@
         <v>1</v>
       </c>
       <c r="CK22" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="CL22" s="17">
         <v>2</v>
@@ -11495,7 +11511,7 @@
         <v>2</v>
       </c>
       <c r="CN22" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CO22" s="17">
         <v>7</v>
@@ -11503,14 +11519,14 @@
       <c r="CP22" s="15">
         <v>18</v>
       </c>
-      <c r="CQ22" s="21">
+      <c r="CQ22" s="20">
         <v>5</v>
       </c>
       <c r="CR22" s="23">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="CS22" s="24">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="CT22" s="24">
         <v>5</v>
@@ -11535,7 +11551,7 @@
       </c>
       <c r="G23" s="16"/>
       <c r="H23" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="15">
         <v>0</v>
@@ -11575,21 +11591,21 @@
         <v>15</v>
       </c>
       <c r="X23" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23" s="18">
         <v>6</v>
       </c>
       <c r="Z23" s="14">
+        <v>7</v>
+      </c>
+      <c r="AA23" s="15">
+        <v>12</v>
+      </c>
+      <c r="AB23" s="20">
         <v>8</v>
       </c>
-      <c r="AA23" s="15">
-        <v>11</v>
-      </c>
-      <c r="AB23" s="20">
-        <v>9</v>
-      </c>
-      <c r="AC23" s="22">
+      <c r="AC23" s="21">
         <v>5</v>
       </c>
       <c r="AD23" s="14">
@@ -11610,13 +11626,13 @@
       </c>
       <c r="AJ23" s="16"/>
       <c r="AK23" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL23" s="15">
-        <v>5</v>
-      </c>
-      <c r="AM23" s="20">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="AM23" s="22">
+        <v>4</v>
       </c>
       <c r="AN23" s="17">
         <v>6</v>
@@ -11625,7 +11641,7 @@
         <v>4</v>
       </c>
       <c r="AP23" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ23" s="18">
         <v>2</v>
@@ -11637,7 +11653,7 @@
         <v>1</v>
       </c>
       <c r="AT23" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AU23" s="18">
         <v>0</v>
@@ -11668,7 +11684,7 @@
         <v>3</v>
       </c>
       <c r="BE23" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF23" s="18">
         <v>2</v>
@@ -11689,23 +11705,23 @@
       <c r="BL23" s="15">
         <v>1</v>
       </c>
-      <c r="BM23" s="21">
+      <c r="BM23" s="22">
         <v>0</v>
       </c>
       <c r="BN23" s="18">
         <v>1</v>
       </c>
       <c r="BO23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BP23" s="15">
         <v>4</v>
       </c>
       <c r="BQ23" s="16">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BR23" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS23" s="14">
         <v>0</v>
@@ -11718,40 +11734,40 @@
         <v>0</v>
       </c>
       <c r="BW23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BX23" s="15">
         <v>3</v>
       </c>
       <c r="BY23" s="16">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="BZ23" s="18">
         <v>2</v>
       </c>
       <c r="CA23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CB23" s="15">
+        <v>10</v>
+      </c>
+      <c r="CC23" s="20">
         <v>9</v>
-      </c>
-      <c r="CC23" s="20">
-        <v>8</v>
       </c>
       <c r="CD23" s="18">
         <v>4</v>
       </c>
       <c r="CE23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CF23" s="15">
         <v>10</v>
       </c>
-      <c r="CG23" s="20">
-        <v>10</v>
+      <c r="CG23" s="16">
+        <v>13</v>
       </c>
       <c r="CH23" s="18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CI23" s="14">
         <v>2</v>
@@ -11760,7 +11776,7 @@
         <v>2</v>
       </c>
       <c r="CK23" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CL23" s="17">
         <v>2</v>
@@ -11770,22 +11786,22 @@
       </c>
       <c r="CN23" s="16"/>
       <c r="CO23" s="17">
+        <v>9</v>
+      </c>
+      <c r="CP23" s="15">
+        <v>28</v>
+      </c>
+      <c r="CQ23" s="22">
         <v>4</v>
       </c>
-      <c r="CP23" s="15">
-        <v>27</v>
-      </c>
-      <c r="CQ23" s="21">
-        <v>2</v>
-      </c>
       <c r="CR23" s="23">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="CS23" s="24">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="CT23" s="24">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:98">
@@ -11847,19 +11863,21 @@
         <v>2</v>
       </c>
       <c r="X24" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y24" s="18">
         <v>1</v>
       </c>
       <c r="Z24" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA24" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="16"/>
-      <c r="AC24" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="16">
+        <v>26</v>
+      </c>
+      <c r="AC24" s="21">
         <v>0</v>
       </c>
       <c r="AD24" s="14">
@@ -11893,7 +11911,7 @@
         <v>1</v>
       </c>
       <c r="AP24" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ24" s="18">
         <v>0</v>
@@ -11931,7 +11949,7 @@
       <c r="BD24" s="15">
         <v>2</v>
       </c>
-      <c r="BE24" s="21">
+      <c r="BE24" s="22">
         <v>0</v>
       </c>
       <c r="BF24" s="18">
@@ -11953,7 +11971,7 @@
       <c r="BL24" s="15">
         <v>1</v>
       </c>
-      <c r="BM24" s="21">
+      <c r="BM24" s="22">
         <v>0</v>
       </c>
       <c r="BN24" s="18">
@@ -11966,7 +11984,7 @@
         <v>1</v>
       </c>
       <c r="BQ24" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BR24" s="18">
         <v>1</v>
@@ -11998,7 +12016,7 @@
         <v>1</v>
       </c>
       <c r="CC24" s="16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CD24" s="18">
         <v>0</v>
@@ -12020,7 +12038,7 @@
         <v>3</v>
       </c>
       <c r="CK24" s="20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CL24" s="17">
         <v>2</v>
@@ -12036,16 +12054,16 @@
         <v>1</v>
       </c>
       <c r="CQ24" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CR24" s="23">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="CS24" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CT24" s="24">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:98">
@@ -12101,13 +12119,15 @@
       </c>
       <c r="U25" s="16"/>
       <c r="V25" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W25" s="15">
-        <v>0</v>
-      </c>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="19">
+        <v>1</v>
+      </c>
+      <c r="X25" s="16">
+        <v>13</v>
+      </c>
+      <c r="Y25" s="18">
         <v>0</v>
       </c>
       <c r="Z25" s="14">
@@ -12117,9 +12137,9 @@
         <v>1</v>
       </c>
       <c r="AB25" s="16">
-        <v>24</v>
-      </c>
-      <c r="AC25" s="22">
+        <v>26</v>
+      </c>
+      <c r="AC25" s="21">
         <v>0</v>
       </c>
       <c r="AD25" s="14">
@@ -12139,7 +12159,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK25" s="17">
         <v>2</v>
@@ -12201,7 +12221,7 @@
       <c r="BH25" s="15">
         <v>1</v>
       </c>
-      <c r="BI25" s="21">
+      <c r="BI25" s="22">
         <v>0</v>
       </c>
       <c r="BJ25" s="18">
@@ -12213,7 +12233,7 @@
       <c r="BL25" s="15">
         <v>1</v>
       </c>
-      <c r="BM25" s="21">
+      <c r="BM25" s="22">
         <v>0</v>
       </c>
       <c r="BN25" s="18">
@@ -12256,7 +12276,7 @@
         <v>2</v>
       </c>
       <c r="CC25" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CD25" s="18">
         <v>1</v>
@@ -12278,7 +12298,7 @@
         <v>1</v>
       </c>
       <c r="CK25" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CL25" s="17">
         <v>2</v>
@@ -12287,25 +12307,25 @@
         <v>1</v>
       </c>
       <c r="CN25" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CO25" s="17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CP25" s="15">
-        <v>3</v>
-      </c>
-      <c r="CQ25" s="20">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="CQ25" s="22">
+        <v>0</v>
       </c>
       <c r="CR25" s="23">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CS25" s="24">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CT25" s="24">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:98">
@@ -12366,7 +12386,7 @@
       <c r="W26" s="15">
         <v>5</v>
       </c>
-      <c r="X26" s="20">
+      <c r="X26" s="16">
         <v>10</v>
       </c>
       <c r="Y26" s="18">
@@ -12379,9 +12399,9 @@
         <v>1</v>
       </c>
       <c r="AB26" s="16">
-        <v>36</v>
-      </c>
-      <c r="AC26" s="22">
+        <v>39</v>
+      </c>
+      <c r="AC26" s="21">
         <v>0</v>
       </c>
       <c r="AD26" s="14">
@@ -12408,16 +12428,16 @@
         <v>1</v>
       </c>
       <c r="AM26" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AN26" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO26" s="15">
         <v>2</v>
       </c>
-      <c r="AP26" s="21">
-        <v>0</v>
+      <c r="AP26" s="16">
+        <v>13</v>
       </c>
       <c r="AQ26" s="18">
         <v>1</v>
@@ -12439,7 +12459,7 @@
         <v>1</v>
       </c>
       <c r="AX26" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY26" s="18">
         <v>0</v>
@@ -12458,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="BE26" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BF26" s="18">
         <v>1</v>
@@ -12509,7 +12529,7 @@
       <c r="BX26" s="15">
         <v>1</v>
       </c>
-      <c r="BY26" s="21">
+      <c r="BY26" s="22">
         <v>0</v>
       </c>
       <c r="BZ26" s="18">
@@ -12522,19 +12542,19 @@
         <v>1</v>
       </c>
       <c r="CC26" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="CD26" s="18">
         <v>0</v>
       </c>
       <c r="CE26" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CF26" s="15">
         <v>2</v>
       </c>
       <c r="CG26" s="16">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CH26" s="18">
         <v>1</v>
@@ -12560,16 +12580,16 @@
         <v>3</v>
       </c>
       <c r="CQ26" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CR26" s="23">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="CS26" s="24">
         <v>18</v>
       </c>
       <c r="CT26" s="24">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:98">
@@ -12625,16 +12645,16 @@
       </c>
       <c r="U27" s="16"/>
       <c r="V27" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X27" s="16">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y27" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" s="14">
         <v>4</v>
@@ -12643,9 +12663,9 @@
         <v>1</v>
       </c>
       <c r="AB27" s="16">
-        <v>48</v>
-      </c>
-      <c r="AC27" s="22">
+        <v>52</v>
+      </c>
+      <c r="AC27" s="21">
         <v>0</v>
       </c>
       <c r="AD27" s="14">
@@ -12672,28 +12692,28 @@
         <v>1</v>
       </c>
       <c r="AM27" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN27" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO27" s="15">
         <v>1</v>
       </c>
       <c r="AP27" s="16">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AQ27" s="18">
         <v>0</v>
       </c>
       <c r="AR27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS27" s="15">
         <v>1</v>
       </c>
       <c r="AT27" s="16">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AU27" s="18">
         <v>0</v>
@@ -12722,7 +12742,7 @@
         <v>1</v>
       </c>
       <c r="BE27" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BF27" s="18">
         <v>1</v>
@@ -12743,7 +12763,7 @@
       <c r="BL27" s="15">
         <v>2</v>
       </c>
-      <c r="BM27" s="21">
+      <c r="BM27" s="22">
         <v>0</v>
       </c>
       <c r="BN27" s="18">
@@ -12776,7 +12796,7 @@
         <v>1</v>
       </c>
       <c r="BY27" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BZ27" s="18">
         <v>1</v>
@@ -12792,13 +12812,13 @@
         <v>0</v>
       </c>
       <c r="CE27" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CF27" s="15">
         <v>2</v>
       </c>
       <c r="CG27" s="16">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="CH27" s="18">
         <v>1</v>
@@ -12817,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="CN27" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CO27" s="17">
         <v>2</v>
@@ -12826,16 +12846,16 @@
         <v>1</v>
       </c>
       <c r="CQ27" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CR27" s="23">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="CS27" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CT27" s="24">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:98">
@@ -12863,7 +12883,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K28" s="18">
         <v>1</v>
@@ -12909,9 +12929,9 @@
         <v>2</v>
       </c>
       <c r="AB28" s="16">
-        <v>12</v>
-      </c>
-      <c r="AC28" s="22">
+        <v>13</v>
+      </c>
+      <c r="AC28" s="21">
         <v>1</v>
       </c>
       <c r="AD28" s="14">
@@ -12932,22 +12952,22 @@
       </c>
       <c r="AJ28" s="16"/>
       <c r="AK28" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL28" s="15">
-        <v>2</v>
-      </c>
-      <c r="AM28" s="16">
-        <v>18</v>
+        <v>3</v>
+      </c>
+      <c r="AM28" s="20">
+        <v>9</v>
       </c>
       <c r="AN28" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO28" s="15">
         <v>2</v>
       </c>
-      <c r="AP28" s="20">
-        <v>6</v>
+      <c r="AP28" s="16">
+        <v>20</v>
       </c>
       <c r="AQ28" s="18">
         <v>1</v>
@@ -12986,7 +13006,7 @@
         <v>2</v>
       </c>
       <c r="BE28" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BF28" s="18">
         <v>1</v>
@@ -13007,7 +13027,7 @@
       <c r="BL28" s="15">
         <v>2</v>
       </c>
-      <c r="BM28" s="21">
+      <c r="BM28" s="22">
         <v>0</v>
       </c>
       <c r="BN28" s="18">
@@ -13040,7 +13060,7 @@
         <v>1</v>
       </c>
       <c r="BY28" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BZ28" s="18">
         <v>1</v>
@@ -13080,22 +13100,22 @@
       </c>
       <c r="CN28" s="16"/>
       <c r="CO28" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CP28" s="15">
         <v>3</v>
       </c>
-      <c r="CQ28" s="20">
-        <v>8</v>
+      <c r="CQ28" s="16">
+        <v>17</v>
       </c>
       <c r="CR28" s="23">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="CS28" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CT28" s="24">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:98">
@@ -13117,13 +13137,13 @@
       </c>
       <c r="G29" s="16"/>
       <c r="H29" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="15">
         <v>1</v>
       </c>
-      <c r="J29" s="21">
-        <v>0</v>
+      <c r="J29" s="16">
+        <v>26</v>
       </c>
       <c r="K29" s="18">
         <v>1</v>
@@ -13159,25 +13179,25 @@
         <v>1</v>
       </c>
       <c r="X29" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Y29" s="18">
         <v>0</v>
       </c>
       <c r="Z29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA29" s="15">
         <v>1</v>
       </c>
       <c r="AB29" s="16">
-        <v>12</v>
-      </c>
-      <c r="AC29" s="22">
+        <v>26</v>
+      </c>
+      <c r="AC29" s="21">
         <v>0</v>
       </c>
       <c r="AD29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE29" s="15">
         <v>0</v>
@@ -13194,13 +13214,13 @@
       </c>
       <c r="AJ29" s="16"/>
       <c r="AK29" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL29" s="15">
         <v>1</v>
       </c>
       <c r="AM29" s="16">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="AN29" s="17">
         <v>2</v>
@@ -13246,7 +13266,7 @@
         <v>1</v>
       </c>
       <c r="BE29" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="BF29" s="18">
         <v>1</v>
@@ -13339,17 +13359,19 @@
         <v>2</v>
       </c>
       <c r="CP29" s="15">
-        <v>0</v>
-      </c>
-      <c r="CQ29" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="CQ29" s="16">
+        <v>26</v>
+      </c>
       <c r="CR29" s="23">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="CS29" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CT29" s="24">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:98">
@@ -13421,7 +13443,7 @@
         <v>0</v>
       </c>
       <c r="AB30" s="16"/>
-      <c r="AC30" s="22">
+      <c r="AC30" s="21">
         <v>0</v>
       </c>
       <c r="AD30" s="14">
@@ -13441,7 +13463,7 @@
         <v>1</v>
       </c>
       <c r="AJ30" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AK30" s="17">
         <v>2</v>
@@ -13456,7 +13478,7 @@
       <c r="AO30" s="15">
         <v>1</v>
       </c>
-      <c r="AP30" s="21">
+      <c r="AP30" s="22">
         <v>0</v>
       </c>
       <c r="AQ30" s="18">
@@ -13576,7 +13598,7 @@
         <v>1</v>
       </c>
       <c r="CK30" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CL30" s="17">
         <v>2</v>
@@ -13599,7 +13621,7 @@
         <v>3</v>
       </c>
       <c r="CT30" s="24">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:98">
@@ -13661,7 +13683,7 @@
         <v>2</v>
       </c>
       <c r="X31" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y31" s="18">
         <v>1</v>
@@ -13673,9 +13695,9 @@
         <v>1</v>
       </c>
       <c r="AB31" s="16">
-        <v>48</v>
-      </c>
-      <c r="AC31" s="22">
+        <v>52</v>
+      </c>
+      <c r="AC31" s="21">
         <v>0</v>
       </c>
       <c r="AD31" s="14">
@@ -13685,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="AF31" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG31" s="18">
         <v>0</v>
@@ -13704,7 +13726,7 @@
         <v>4</v>
       </c>
       <c r="AM31" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN31" s="17">
         <v>0</v>
@@ -13712,7 +13734,7 @@
       <c r="AO31" s="15">
         <v>3</v>
       </c>
-      <c r="AP31" s="21">
+      <c r="AP31" s="22">
         <v>0</v>
       </c>
       <c r="AQ31" s="18">
@@ -13771,7 +13793,7 @@
       <c r="BL31" s="15">
         <v>1</v>
       </c>
-      <c r="BM31" s="21">
+      <c r="BM31" s="22">
         <v>0</v>
       </c>
       <c r="BN31" s="18">
@@ -13784,7 +13806,7 @@
         <v>1</v>
       </c>
       <c r="BQ31" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BR31" s="18">
         <v>1</v>
@@ -13826,7 +13848,7 @@
         <v>1</v>
       </c>
       <c r="CG31" s="16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CH31" s="18">
         <v>1</v>
@@ -13838,7 +13860,7 @@
         <v>1</v>
       </c>
       <c r="CK31" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CL31" s="17">
         <v>2</v>
@@ -13854,7 +13876,7 @@
         <v>1</v>
       </c>
       <c r="CQ31" s="16">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="CR31" s="23">
         <v>50</v>
@@ -13863,7 +13885,7 @@
         <v>16</v>
       </c>
       <c r="CT31" s="24">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:98">
@@ -13884,16 +13906,16 @@
         <v>1</v>
       </c>
       <c r="G32" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H32" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="15">
         <v>2</v>
       </c>
-      <c r="J32" s="20">
-        <v>6</v>
+      <c r="J32" s="16">
+        <v>13</v>
       </c>
       <c r="K32" s="18">
         <v>2</v>
@@ -13923,13 +13945,13 @@
       </c>
       <c r="U32" s="16"/>
       <c r="V32" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W32" s="15">
         <v>3</v>
       </c>
       <c r="X32" s="16">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Y32" s="18">
         <v>1</v>
@@ -13941,9 +13963,9 @@
         <v>1</v>
       </c>
       <c r="AB32" s="16">
-        <v>24</v>
-      </c>
-      <c r="AC32" s="22">
+        <v>26</v>
+      </c>
+      <c r="AC32" s="21">
         <v>0</v>
       </c>
       <c r="AD32" s="14">
@@ -13970,7 +13992,7 @@
         <v>2</v>
       </c>
       <c r="AM32" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN32" s="17">
         <v>2</v>
@@ -13979,7 +14001,7 @@
         <v>2</v>
       </c>
       <c r="AP32" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ32" s="18">
         <v>1</v>
@@ -14057,7 +14079,7 @@
       <c r="BT32" s="15">
         <v>1</v>
       </c>
-      <c r="BU32" s="21">
+      <c r="BU32" s="22">
         <v>0</v>
       </c>
       <c r="BV32" s="18">
@@ -14080,7 +14102,7 @@
         <v>1</v>
       </c>
       <c r="CC32" s="16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CD32" s="18">
         <v>0</v>
@@ -14092,7 +14114,7 @@
         <v>2</v>
       </c>
       <c r="CG32" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CH32" s="18">
         <v>1</v>
@@ -14104,7 +14126,7 @@
         <v>1</v>
       </c>
       <c r="CK32" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CL32" s="17">
         <v>2</v>
@@ -14120,16 +14142,16 @@
         <v>2</v>
       </c>
       <c r="CQ32" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CR32" s="23">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="CS32" s="24">
         <v>18</v>
       </c>
       <c r="CT32" s="24">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:98">
@@ -14191,7 +14213,7 @@
         <v>5</v>
       </c>
       <c r="X33" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y33" s="18">
         <v>2</v>
@@ -14203,9 +14225,9 @@
         <v>3</v>
       </c>
       <c r="AB33" s="20">
-        <v>8</v>
-      </c>
-      <c r="AC33" s="22">
+        <v>9</v>
+      </c>
+      <c r="AC33" s="21">
         <v>1</v>
       </c>
       <c r="AD33" s="14">
@@ -14239,7 +14261,7 @@
         <v>2</v>
       </c>
       <c r="AP33" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ33" s="18">
         <v>1</v>
@@ -14298,7 +14320,7 @@
         <v>1</v>
       </c>
       <c r="BM33" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN33" s="18">
         <v>1</v>
@@ -14340,7 +14362,7 @@
         <v>5</v>
       </c>
       <c r="CC33" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CD33" s="18">
         <v>2</v>
@@ -14352,7 +14374,7 @@
         <v>1</v>
       </c>
       <c r="CG33" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CH33" s="18">
         <v>1</v>
@@ -14364,7 +14386,7 @@
         <v>2</v>
       </c>
       <c r="CK33" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CL33" s="17">
         <v>4</v>
@@ -14373,7 +14395,7 @@
         <v>1</v>
       </c>
       <c r="CN33" s="16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CO33" s="17">
         <v>6</v>
@@ -14389,7 +14411,7 @@
         <v>20</v>
       </c>
       <c r="CT33" s="24">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:98">
@@ -14417,7 +14439,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K34" s="18">
         <v>1</v>
@@ -14453,7 +14475,7 @@
         <v>1</v>
       </c>
       <c r="X34" s="16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Y34" s="18">
         <v>0</v>
@@ -14465,9 +14487,9 @@
         <v>1</v>
       </c>
       <c r="AB34" s="16">
-        <v>24</v>
-      </c>
-      <c r="AC34" s="22">
+        <v>26</v>
+      </c>
+      <c r="AC34" s="21">
         <v>0</v>
       </c>
       <c r="AD34" s="14">
@@ -14494,7 +14516,7 @@
         <v>1</v>
       </c>
       <c r="AM34" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AN34" s="17">
         <v>3</v>
@@ -14559,7 +14581,7 @@
       <c r="BL34" s="15">
         <v>1</v>
       </c>
-      <c r="BM34" s="21">
+      <c r="BM34" s="22">
         <v>0</v>
       </c>
       <c r="BN34" s="18">
@@ -14572,7 +14594,7 @@
         <v>1</v>
       </c>
       <c r="BQ34" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BR34" s="18">
         <v>1</v>
@@ -14604,7 +14626,7 @@
         <v>3</v>
       </c>
       <c r="CC34" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CD34" s="18">
         <v>1</v>
@@ -14633,7 +14655,7 @@
         <v>1</v>
       </c>
       <c r="CN34" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CO34" s="17">
         <v>2</v>
@@ -14642,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="CQ34" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CR34" s="23">
         <v>38</v>
@@ -14651,7 +14673,7 @@
         <v>11</v>
       </c>
       <c r="CT34" s="24">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:98">
@@ -14672,16 +14694,16 @@
         <v>2</v>
       </c>
       <c r="G35" s="16">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H35" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I35" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J35" s="16">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K35" s="32">
         <v>9</v>
@@ -14711,66 +14733,66 @@
       </c>
       <c r="U35" s="16"/>
       <c r="V35" s="31">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="W35" s="30">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="X35" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35" s="32">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Z35" s="29">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AA35" s="30">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="AB35" s="20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC35" s="32">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD35" s="29">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE35" s="30">
         <v>11</v>
       </c>
       <c r="AF35" s="16">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="AG35" s="32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH35" s="29">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AI35" s="30">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AJ35" s="16">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AK35" s="31">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AL35" s="30">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="AM35" s="20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN35" s="31">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AO35" s="30">
-        <v>74</v>
-      </c>
-      <c r="AP35" s="16">
+        <v>81</v>
+      </c>
+      <c r="AP35" s="20">
         <v>10</v>
       </c>
       <c r="AQ35" s="32">
@@ -14780,7 +14802,7 @@
         <v>62</v>
       </c>
       <c r="AS35" s="30">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT35" s="16">
         <v>31</v>
@@ -14789,16 +14811,16 @@
         <v>10</v>
       </c>
       <c r="AV35" s="29">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AW35" s="30">
         <v>30</v>
       </c>
       <c r="AX35" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY35" s="32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ35" s="29">
         <v>1</v>
@@ -14808,16 +14830,16 @@
       </c>
       <c r="BB35" s="16"/>
       <c r="BC35" s="31">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BD35" s="30">
         <v>31</v>
       </c>
       <c r="BE35" s="16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BF35" s="32">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BG35" s="29">
         <v>0</v>
@@ -14825,29 +14847,29 @@
       <c r="BH35" s="30">
         <v>2</v>
       </c>
-      <c r="BI35" s="21">
+      <c r="BI35" s="22">
         <v>0</v>
       </c>
       <c r="BJ35" s="32">
         <v>1</v>
       </c>
       <c r="BK35" s="29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BL35" s="30">
-        <v>21</v>
-      </c>
-      <c r="BM35" s="21">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="BM35" s="22">
+        <v>3</v>
       </c>
       <c r="BN35" s="32">
         <v>14</v>
       </c>
       <c r="BO35" s="29">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BP35" s="30">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BQ35" s="16">
         <v>33</v>
@@ -14862,79 +14884,79 @@
         <v>5</v>
       </c>
       <c r="BU35" s="16">
+        <v>23</v>
+      </c>
+      <c r="BV35" s="32">
+        <v>3</v>
+      </c>
+      <c r="BW35" s="29">
+        <v>66</v>
+      </c>
+      <c r="BX35" s="30">
+        <v>40</v>
+      </c>
+      <c r="BY35" s="16">
         <v>22</v>
       </c>
-      <c r="BV35" s="32">
-        <v>3</v>
-      </c>
-      <c r="BW35" s="29">
-        <v>59</v>
-      </c>
-      <c r="BX35" s="30">
-        <v>39</v>
-      </c>
-      <c r="BY35" s="16">
-        <v>18</v>
-      </c>
       <c r="BZ35" s="32">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA35" s="29">
         <v>146</v>
       </c>
       <c r="CB35" s="30">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="CC35" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CD35" s="32">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="CE35" s="29">
+        <v>134</v>
+      </c>
+      <c r="CF35" s="30">
         <v>130</v>
-      </c>
-      <c r="CF35" s="30">
-        <v>122</v>
       </c>
       <c r="CG35" s="16">
         <v>13</v>
       </c>
       <c r="CH35" s="32">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="CI35" s="29">
         <v>68</v>
       </c>
       <c r="CJ35" s="30">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="CK35" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CL35" s="31">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="CM35" s="30">
         <v>18</v>
       </c>
       <c r="CN35" s="16">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="CO35" s="31">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="CP35" s="30">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="CQ35" s="20">
         <v>6</v>
       </c>
       <c r="CR35" s="23">
-        <v>1370</v>
+        <v>1391</v>
       </c>
       <c r="CS35" s="24">
-        <v>1301</v>
+        <v>1369</v>
       </c>
       <c r="CT35" s="24">
         <v>13</v>

--- a/source/stock_data.xlsx
+++ b/source/stock_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32740" windowHeight="14840" activeTab="1"/>
+    <workbookView windowWidth="32740" windowHeight="13100" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="STOCK IQOO" sheetId="3" r:id="rId1"/>
@@ -1834,10 +1834,10 @@
             <v>0</v>
           </cell>
           <cell r="W9">
-            <v>12</v>
+            <v>11</v>
           </cell>
           <cell r="X9">
-            <v>15</v>
+            <v>16</v>
           </cell>
           <cell r="Y9">
             <v>15</v>
@@ -1852,28 +1852,28 @@
             <v>19</v>
           </cell>
           <cell r="AC9">
-            <v>25</v>
+            <v>27</v>
           </cell>
           <cell r="AD9">
             <v>21</v>
           </cell>
           <cell r="AE9">
-            <v>24</v>
+            <v>23</v>
           </cell>
           <cell r="AF9">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="AG9">
-            <v>31</v>
+            <v>30</v>
           </cell>
           <cell r="AH9">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="AI9">
-            <v>158</v>
+            <v>157</v>
           </cell>
           <cell r="AJ9">
-            <v>98</v>
+            <v>101</v>
           </cell>
         </row>
         <row r="10">
@@ -2060,10 +2060,10 @@
             <v>2</v>
           </cell>
           <cell r="AE11">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AF11">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="AG11">
             <v>1</v>
@@ -2072,10 +2072,10 @@
             <v>0</v>
           </cell>
           <cell r="AI11">
+            <v>3</v>
+          </cell>
+          <cell r="AJ11">
             <v>4</v>
-          </cell>
-          <cell r="AJ11">
-            <v>3</v>
           </cell>
         </row>
         <row r="12">
@@ -2940,16 +2940,16 @@
         </row>
         <row r="21">
           <cell r="AG21">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AH21">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AI21">
+            <v>3</v>
+          </cell>
+          <cell r="AJ21">
             <v>4</v>
-          </cell>
-          <cell r="AJ21">
-            <v>3</v>
           </cell>
         </row>
         <row r="22">
@@ -3313,7 +3313,7 @@
             <v>0</v>
           </cell>
           <cell r="AC26">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="AD26">
             <v>2</v>
@@ -3331,7 +3331,7 @@
             <v>0</v>
           </cell>
           <cell r="AI26">
-            <v>8</v>
+            <v>10</v>
           </cell>
           <cell r="AJ26">
             <v>3</v>
@@ -3910,10 +3910,10 @@
             <v>0</v>
           </cell>
           <cell r="W33">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="X33">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y33">
             <v>1</v>
@@ -3946,10 +3946,10 @@
             <v>0</v>
           </cell>
           <cell r="AI33">
-            <v>10</v>
+            <v>9</v>
           </cell>
           <cell r="AJ33">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="34">
@@ -4489,10 +4489,10 @@
             <v>0</v>
           </cell>
           <cell r="W42">
-            <v>12</v>
+            <v>11</v>
           </cell>
           <cell r="X42">
-            <v>15</v>
+            <v>16</v>
           </cell>
           <cell r="Y42">
             <v>15</v>
@@ -4507,28 +4507,28 @@
             <v>19</v>
           </cell>
           <cell r="AC42">
-            <v>25</v>
+            <v>27</v>
           </cell>
           <cell r="AD42">
             <v>21</v>
           </cell>
           <cell r="AE42">
-            <v>24</v>
+            <v>23</v>
           </cell>
           <cell r="AF42">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="AG42">
-            <v>31</v>
+            <v>30</v>
           </cell>
           <cell r="AH42">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="AI42">
-            <v>158</v>
+            <v>157</v>
           </cell>
           <cell r="AJ42">
-            <v>98</v>
+            <v>101</v>
           </cell>
         </row>
       </sheetData>
@@ -5150,28 +5150,28 @@
             <v>0</v>
           </cell>
           <cell r="T9">
+            <v>12</v>
+          </cell>
+          <cell r="U9">
+            <v>8</v>
+          </cell>
+          <cell r="V9">
+            <v>12</v>
+          </cell>
+          <cell r="W9">
+            <v>21</v>
+          </cell>
+          <cell r="X9">
+            <v>4</v>
+          </cell>
+          <cell r="Y9">
+            <v>18</v>
+          </cell>
+          <cell r="Z9">
+            <v>4</v>
+          </cell>
+          <cell r="AA9">
             <v>13</v>
-          </cell>
-          <cell r="U9">
-            <v>7</v>
-          </cell>
-          <cell r="V9">
-            <v>13</v>
-          </cell>
-          <cell r="W9">
-            <v>20</v>
-          </cell>
-          <cell r="X9">
-            <v>6</v>
-          </cell>
-          <cell r="Y9">
-            <v>16</v>
-          </cell>
-          <cell r="Z9">
-            <v>3</v>
-          </cell>
-          <cell r="AA9">
-            <v>12</v>
           </cell>
           <cell r="AB9">
             <v>2</v>
@@ -5204,10 +5204,10 @@
             <v>0</v>
           </cell>
           <cell r="AL9">
-            <v>2</v>
+            <v>5</v>
           </cell>
           <cell r="AM9">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="AN9">
             <v>0</v>
@@ -5230,13 +5230,13 @@
         </row>
         <row r="9">
           <cell r="AV9">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AW9">
-            <v>13</v>
+            <v>14</v>
           </cell>
           <cell r="AX9">
-            <v>1</v>
+            <v>5</v>
           </cell>
           <cell r="AY9">
             <v>8</v>
@@ -5278,10 +5278,10 @@
             <v>1</v>
           </cell>
           <cell r="BL9">
+            <v>3</v>
+          </cell>
+          <cell r="BM9">
             <v>4</v>
-          </cell>
-          <cell r="BM9">
-            <v>3</v>
           </cell>
           <cell r="BN9">
             <v>25</v>
@@ -5290,10 +5290,10 @@
             <v>30</v>
           </cell>
           <cell r="BP9">
-            <v>82</v>
+            <v>84</v>
           </cell>
           <cell r="BQ9">
-            <v>149</v>
+            <v>157</v>
           </cell>
         </row>
         <row r="10">
@@ -5331,10 +5331,10 @@
             <v>0</v>
           </cell>
           <cell r="L10">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M10">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="N10">
             <v>0</v>
@@ -5369,16 +5369,16 @@
             <v>22</v>
           </cell>
           <cell r="Z10">
+            <v>5</v>
+          </cell>
+          <cell r="AA10">
+            <v>13</v>
+          </cell>
+          <cell r="AB10">
+            <v>0</v>
+          </cell>
+          <cell r="AC10">
             <v>3</v>
-          </cell>
-          <cell r="AA10">
-            <v>12</v>
-          </cell>
-          <cell r="AB10">
-            <v>1</v>
-          </cell>
-          <cell r="AC10">
-            <v>2</v>
           </cell>
           <cell r="AD10">
             <v>0</v>
@@ -5441,7 +5441,7 @@
             <v>14</v>
           </cell>
           <cell r="AX10">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="AY10">
             <v>7</v>
@@ -5485,16 +5485,16 @@
             <v>1</v>
           </cell>
           <cell r="BN10">
-            <v>19</v>
+            <v>15</v>
           </cell>
           <cell r="BO10">
-            <v>65</v>
+            <v>69</v>
           </cell>
           <cell r="BP10">
-            <v>88</v>
+            <v>86</v>
           </cell>
           <cell r="BQ10">
-            <v>166</v>
+            <v>173</v>
           </cell>
         </row>
         <row r="11">
@@ -5562,16 +5562,16 @@
             <v>22</v>
           </cell>
           <cell r="V11">
-            <v>14</v>
+            <v>13</v>
           </cell>
           <cell r="W11">
+            <v>38</v>
+          </cell>
+          <cell r="X11">
+            <v>11</v>
+          </cell>
+          <cell r="Y11">
             <v>37</v>
-          </cell>
-          <cell r="X11">
-            <v>12</v>
-          </cell>
-          <cell r="Y11">
-            <v>35</v>
           </cell>
           <cell r="Z11">
             <v>9</v>
@@ -5610,10 +5610,10 @@
             <v>0</v>
           </cell>
           <cell r="AL11">
-            <v>6</v>
+            <v>10</v>
           </cell>
           <cell r="AM11">
-            <v>20</v>
+            <v>22</v>
           </cell>
           <cell r="AN11">
             <v>5</v>
@@ -5636,10 +5636,10 @@
         </row>
         <row r="11">
           <cell r="AV11">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="AW11">
-            <v>13</v>
+            <v>15</v>
           </cell>
           <cell r="AX11">
             <v>4</v>
@@ -5690,16 +5690,16 @@
             <v>2</v>
           </cell>
           <cell r="BN11">
-            <v>16</v>
+            <v>13</v>
           </cell>
           <cell r="BO11">
-            <v>201</v>
+            <v>205</v>
           </cell>
           <cell r="BP11">
-            <v>97</v>
+            <v>94</v>
           </cell>
           <cell r="BQ11">
-            <v>405</v>
+            <v>416</v>
           </cell>
         </row>
         <row r="12">
@@ -5757,7 +5757,7 @@
             <v>0</v>
           </cell>
           <cell r="T12">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="U12">
             <v>9</v>
@@ -5769,16 +5769,16 @@
             <v>1</v>
           </cell>
           <cell r="X12">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="Y12">
             <v>5</v>
           </cell>
           <cell r="Z12">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="AA12">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AB12">
             <v>2</v>
@@ -5853,10 +5853,10 @@
             <v>0</v>
           </cell>
           <cell r="AZ12">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="BA12">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BB12">
             <v>4</v>
@@ -5901,10 +5901,10 @@
             <v>7</v>
           </cell>
           <cell r="BP12">
-            <v>57</v>
+            <v>59</v>
           </cell>
           <cell r="BQ12">
-            <v>42</v>
+            <v>44</v>
           </cell>
         </row>
         <row r="13">
@@ -6119,7 +6119,7 @@
             <v>0</v>
           </cell>
           <cell r="D14">
-            <v>1</v>
+            <v>3</v>
           </cell>
           <cell r="E14">
             <v>5</v>
@@ -6157,16 +6157,16 @@
         </row>
         <row r="14">
           <cell r="T14">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="U14">
             <v>11</v>
           </cell>
           <cell r="V14">
-            <v>6</v>
+            <v>5</v>
           </cell>
           <cell r="W14">
-            <v>10</v>
+            <v>11</v>
           </cell>
           <cell r="X14">
             <v>3</v>
@@ -6175,10 +6175,10 @@
             <v>10</v>
           </cell>
           <cell r="Z14">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="AA14">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="14">
@@ -6207,7 +6207,7 @@
             <v>0</v>
           </cell>
           <cell r="AL14">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AM14">
             <v>8</v>
@@ -6265,7 +6265,7 @@
         </row>
         <row r="14">
           <cell r="BJ14">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BK14">
             <v>1</v>
@@ -6283,10 +6283,10 @@
             <v>12</v>
           </cell>
           <cell r="BP14">
-            <v>28</v>
+            <v>32</v>
           </cell>
           <cell r="BQ14">
-            <v>80</v>
+            <v>82</v>
           </cell>
         </row>
         <row r="15">
@@ -6296,7 +6296,7 @@
         </row>
         <row r="15">
           <cell r="D15">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="E15">
             <v>3</v>
@@ -6356,13 +6356,13 @@
             <v>6</v>
           </cell>
           <cell r="X15">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="Y15">
             <v>4</v>
           </cell>
           <cell r="Z15">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="AA15">
             <v>7</v>
@@ -6446,7 +6446,7 @@
             <v>1</v>
           </cell>
           <cell r="BB15">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="BC15">
             <v>5</v>
@@ -6464,13 +6464,13 @@
             <v>1</v>
           </cell>
           <cell r="BH15">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="BI15">
             <v>4</v>
           </cell>
           <cell r="BJ15">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BK15">
             <v>2</v>
@@ -6488,7 +6488,7 @@
             <v>4</v>
           </cell>
           <cell r="BP15">
-            <v>47</v>
+            <v>55</v>
           </cell>
           <cell r="BQ15">
             <v>50</v>
@@ -6545,13 +6545,13 @@
             <v>0</v>
           </cell>
           <cell r="T16">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="U16">
             <v>3</v>
           </cell>
           <cell r="V16">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="W16">
             <v>1</v>
@@ -6563,7 +6563,7 @@
             <v>1</v>
           </cell>
           <cell r="Z16">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AA16">
             <v>2</v>
@@ -6651,10 +6651,10 @@
             <v>1</v>
           </cell>
           <cell r="BF16">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="BG16">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="16">
@@ -6677,10 +6677,10 @@
             <v>7</v>
           </cell>
           <cell r="BP16">
-            <v>23</v>
+            <v>25</v>
           </cell>
           <cell r="BQ16">
-            <v>21</v>
+            <v>22</v>
           </cell>
         </row>
         <row r="17">
@@ -6696,10 +6696,10 @@
             <v>0</v>
           </cell>
           <cell r="F17">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="G17">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="H17">
             <v>0</v>
@@ -6804,10 +6804,10 @@
         </row>
         <row r="17">
           <cell r="AV17">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="AW17">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="AX17">
             <v>2</v>
@@ -6860,10 +6860,10 @@
             <v>1</v>
           </cell>
           <cell r="BP17">
-            <v>33</v>
+            <v>31</v>
           </cell>
           <cell r="BQ17">
-            <v>16</v>
+            <v>18</v>
           </cell>
         </row>
         <row r="18">
@@ -7181,10 +7181,10 @@
             <v>1</v>
           </cell>
           <cell r="L20">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M20">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="N20">
             <v>0</v>
@@ -7217,7 +7217,7 @@
             <v>2</v>
           </cell>
           <cell r="X20">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="Y20">
             <v>10</v>
@@ -7255,7 +7255,7 @@
             <v>0</v>
           </cell>
           <cell r="AL20">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AM20">
             <v>1</v>
@@ -7291,7 +7291,7 @@
             <v>5</v>
           </cell>
           <cell r="AX20">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AY20">
             <v>1</v>
@@ -7323,7 +7323,7 @@
             <v>3</v>
           </cell>
           <cell r="BL20">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BM20">
             <v>3</v>
@@ -7335,10 +7335,10 @@
             <v>5</v>
           </cell>
           <cell r="BP20">
-            <v>35</v>
+            <v>38</v>
           </cell>
           <cell r="BQ20">
-            <v>59</v>
+            <v>60</v>
           </cell>
         </row>
         <row r="21">
@@ -7631,10 +7631,10 @@
             <v>1</v>
           </cell>
           <cell r="AN22">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AO22">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AP22">
             <v>0</v>
@@ -7701,16 +7701,16 @@
             <v>1</v>
           </cell>
           <cell r="BN22">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="BO22">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="BP22">
+            <v>26</v>
+          </cell>
+          <cell r="BQ22">
             <v>28</v>
-          </cell>
-          <cell r="BQ22">
-            <v>26</v>
           </cell>
         </row>
         <row r="23">
@@ -7771,7 +7771,7 @@
         </row>
         <row r="24">
           <cell r="D24">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="E24">
             <v>1</v>
@@ -7815,13 +7815,13 @@
             <v>0</v>
           </cell>
           <cell r="T24">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="U24">
             <v>1</v>
           </cell>
           <cell r="V24">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="W24">
             <v>1</v>
@@ -7959,7 +7959,7 @@
             <v>5</v>
           </cell>
           <cell r="BP24">
-            <v>49</v>
+            <v>54</v>
           </cell>
           <cell r="BQ24">
             <v>24</v>
@@ -8010,22 +8010,22 @@
             <v>0</v>
           </cell>
           <cell r="T25">
+            <v>3</v>
+          </cell>
+          <cell r="U25">
+            <v>1</v>
+          </cell>
+          <cell r="V25">
             <v>2</v>
           </cell>
-          <cell r="U25">
-            <v>1</v>
-          </cell>
-          <cell r="V25">
-            <v>1</v>
-          </cell>
           <cell r="W25">
             <v>1</v>
           </cell>
           <cell r="X25">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="Y25">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="Z25">
             <v>2</v>
@@ -8112,10 +8112,10 @@
             <v>1</v>
           </cell>
           <cell r="BP25">
-            <v>46</v>
+            <v>47</v>
           </cell>
           <cell r="BQ25">
-            <v>10</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="26">
@@ -8354,10 +8354,10 @@
             <v>0</v>
           </cell>
           <cell r="T27">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="U27">
-            <v>12</v>
+            <v>13</v>
           </cell>
           <cell r="V27">
             <v>7</v>
@@ -8366,16 +8366,16 @@
             <v>8</v>
           </cell>
           <cell r="X27">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="Y27">
-            <v>22</v>
+            <v>23</v>
           </cell>
           <cell r="Z27">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="AA27">
-            <v>13</v>
+            <v>14</v>
           </cell>
           <cell r="AB27">
             <v>3</v>
@@ -8444,7 +8444,7 @@
             <v>3</v>
           </cell>
           <cell r="AX27">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AY27">
             <v>5</v>
@@ -8488,16 +8488,16 @@
             <v>0</v>
           </cell>
           <cell r="BN27">
-            <v>7</v>
+            <v>5</v>
           </cell>
           <cell r="BO27">
-            <v>17</v>
+            <v>19</v>
           </cell>
           <cell r="BP27">
             <v>59</v>
           </cell>
           <cell r="BQ27">
-            <v>106</v>
+            <v>111</v>
           </cell>
         </row>
         <row r="28">
@@ -8511,7 +8511,7 @@
             <v>0</v>
           </cell>
           <cell r="D28">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="E28">
             <v>6</v>
@@ -8565,19 +8565,19 @@
             <v>4</v>
           </cell>
           <cell r="V28">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="W28">
             <v>4</v>
           </cell>
           <cell r="X28">
-            <v>1</v>
+            <v>3</v>
           </cell>
           <cell r="Y28">
             <v>8</v>
           </cell>
           <cell r="Z28">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AA28">
             <v>4</v>
@@ -8616,7 +8616,7 @@
             <v>2</v>
           </cell>
           <cell r="AM28">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AN28">
             <v>0</v>
@@ -8645,7 +8645,7 @@
             <v>3</v>
           </cell>
           <cell r="AX28">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AY28">
             <v>1</v>
@@ -8657,7 +8657,7 @@
             <v>1</v>
           </cell>
           <cell r="BB28">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="BC28">
             <v>5</v>
@@ -8699,10 +8699,10 @@
             <v>16</v>
           </cell>
           <cell r="BP28">
-            <v>28</v>
+            <v>37</v>
           </cell>
           <cell r="BQ28">
-            <v>61</v>
+            <v>62</v>
           </cell>
         </row>
         <row r="29">
@@ -8921,13 +8921,13 @@
             <v>7</v>
           </cell>
           <cell r="X30">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="Y30">
-            <v>17</v>
+            <v>19</v>
           </cell>
           <cell r="Z30">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="AA30">
             <v>16</v>
@@ -8999,13 +8999,13 @@
             <v>6</v>
           </cell>
           <cell r="AX30">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="AY30">
             <v>2</v>
           </cell>
           <cell r="AZ30">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="BA30">
             <v>4</v>
@@ -9043,16 +9043,16 @@
             <v>0</v>
           </cell>
           <cell r="BN30">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="BO30">
-            <v>15</v>
+            <v>16</v>
           </cell>
           <cell r="BP30">
-            <v>58</v>
+            <v>65</v>
           </cell>
           <cell r="BQ30">
-            <v>113</v>
+            <v>116</v>
           </cell>
         </row>
         <row r="31">
@@ -9062,10 +9062,10 @@
         </row>
         <row r="31">
           <cell r="D31">
-            <v>6</v>
+            <v>5</v>
           </cell>
           <cell r="E31">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="F31">
             <v>0</v>
@@ -9086,7 +9086,7 @@
             <v>0</v>
           </cell>
           <cell r="L31">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="M31">
             <v>5</v>
@@ -9106,22 +9106,22 @@
             <v>0</v>
           </cell>
           <cell r="T31">
-            <v>9</v>
+            <v>8</v>
           </cell>
           <cell r="U31">
-            <v>12</v>
+            <v>13</v>
           </cell>
           <cell r="V31">
-            <v>7</v>
+            <v>3</v>
           </cell>
           <cell r="W31">
-            <v>13</v>
+            <v>17</v>
           </cell>
           <cell r="X31">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="Y31">
-            <v>21</v>
+            <v>23</v>
           </cell>
           <cell r="Z31">
             <v>9</v>
@@ -9160,7 +9160,7 @@
             <v>0</v>
           </cell>
           <cell r="AL31">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="AM31">
             <v>3</v>
@@ -9198,7 +9198,7 @@
             <v>1</v>
           </cell>
           <cell r="AZ31">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="BA31">
             <v>9</v>
@@ -9218,10 +9218,10 @@
         </row>
         <row r="31">
           <cell r="BH31">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="BI31">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BJ31">
             <v>2</v>
@@ -9230,22 +9230,22 @@
             <v>2</v>
           </cell>
           <cell r="BL31">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BM31">
             <v>1</v>
           </cell>
           <cell r="BN31">
-            <v>7</v>
+            <v>6</v>
           </cell>
           <cell r="BO31">
-            <v>33</v>
+            <v>34</v>
           </cell>
           <cell r="BP31">
             <v>69</v>
           </cell>
           <cell r="BQ31">
-            <v>138</v>
+            <v>148</v>
           </cell>
         </row>
         <row r="32">
@@ -9259,10 +9259,10 @@
             <v>0</v>
           </cell>
           <cell r="D32">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="E32">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="F32">
             <v>0</v>
@@ -9303,7 +9303,7 @@
             <v>1</v>
           </cell>
           <cell r="V32">
-            <v>1</v>
+            <v>5</v>
           </cell>
           <cell r="W32">
             <v>12</v>
@@ -9433,10 +9433,10 @@
             <v>3</v>
           </cell>
           <cell r="BP32">
+            <v>49</v>
+          </cell>
+          <cell r="BQ32">
             <v>46</v>
-          </cell>
-          <cell r="BQ32">
-            <v>45</v>
           </cell>
         </row>
         <row r="33">
@@ -9494,22 +9494,22 @@
             <v>0</v>
           </cell>
           <cell r="T33">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="U33">
-            <v>18</v>
+            <v>19</v>
           </cell>
           <cell r="V33">
-            <v>4</v>
+            <v>6</v>
           </cell>
           <cell r="W33">
             <v>17</v>
           </cell>
           <cell r="X33">
-            <v>6</v>
+            <v>8</v>
           </cell>
           <cell r="Y33">
-            <v>40</v>
+            <v>41</v>
           </cell>
           <cell r="Z33">
             <v>10</v>
@@ -9580,7 +9580,7 @@
             <v>9</v>
           </cell>
           <cell r="AX33">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AY33">
             <v>4</v>
@@ -9592,10 +9592,10 @@
             <v>3</v>
           </cell>
           <cell r="BB33">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="BC33">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="BD33">
             <v>0</v>
@@ -9628,16 +9628,16 @@
             <v>2</v>
           </cell>
           <cell r="BN33">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="BO33">
-            <v>20</v>
+            <v>21</v>
           </cell>
           <cell r="BP33">
-            <v>62</v>
+            <v>64</v>
           </cell>
           <cell r="BQ33">
-            <v>164</v>
+            <v>168</v>
           </cell>
         </row>
         <row r="34">
@@ -9707,10 +9707,10 @@
             <v>0</v>
           </cell>
           <cell r="X34">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="Y34">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="Z34">
             <v>2</v>
@@ -9831,10 +9831,10 @@
             <v>1</v>
           </cell>
           <cell r="BP34">
-            <v>32</v>
+            <v>31</v>
           </cell>
           <cell r="BQ34">
-            <v>20</v>
+            <v>21</v>
           </cell>
         </row>
         <row r="35">
@@ -9942,16 +9942,16 @@
             <v>0</v>
           </cell>
           <cell r="AL35">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AM35">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AN35">
             <v>2</v>
           </cell>
           <cell r="AO35">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AP35">
             <v>0</v>
@@ -10028,10 +10028,10 @@
             <v>5</v>
           </cell>
           <cell r="BP35">
-            <v>30</v>
+            <v>29</v>
           </cell>
           <cell r="BQ35">
-            <v>35</v>
+            <v>37</v>
           </cell>
         </row>
         <row r="36">
@@ -10072,6 +10072,12 @@
             <v>0</v>
           </cell>
           <cell r="AM36">
+            <v>2</v>
+          </cell>
+          <cell r="AN36">
+            <v>0</v>
+          </cell>
+          <cell r="AO36">
             <v>1</v>
           </cell>
         </row>
@@ -10122,7 +10128,7 @@
             <v>0</v>
           </cell>
           <cell r="BQ36">
-            <v>18</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="37">
@@ -10543,11 +10549,17 @@
           </cell>
         </row>
         <row r="41">
+          <cell r="V41">
+            <v>0</v>
+          </cell>
+          <cell r="W41">
+            <v>2</v>
+          </cell>
           <cell r="X41">
             <v>0</v>
           </cell>
           <cell r="Y41">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="Z41">
             <v>0</v>
@@ -10577,7 +10589,7 @@
             <v>0</v>
           </cell>
           <cell r="BQ41">
-            <v>6</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="42">
@@ -10629,10 +10641,10 @@
         </row>
         <row r="42">
           <cell r="AL42">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="AM42">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="AN42">
             <v>4</v>
@@ -10699,10 +10711,10 @@
             <v>1</v>
           </cell>
           <cell r="BP42">
-            <v>53</v>
+            <v>52</v>
           </cell>
           <cell r="BQ42">
-            <v>25</v>
+            <v>26</v>
           </cell>
         </row>
         <row r="43">
@@ -10716,16 +10728,16 @@
             <v>0</v>
           </cell>
           <cell r="D43">
-            <v>61</v>
+            <v>66</v>
           </cell>
           <cell r="E43">
-            <v>57</v>
+            <v>59</v>
           </cell>
           <cell r="F43">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="G43">
-            <v>11</v>
+            <v>12</v>
           </cell>
           <cell r="H43">
             <v>1</v>
@@ -10740,10 +10752,10 @@
             <v>2</v>
           </cell>
           <cell r="L43">
-            <v>43</v>
+            <v>42</v>
           </cell>
           <cell r="M43">
-            <v>45</v>
+            <v>47</v>
           </cell>
           <cell r="N43">
             <v>0</v>
@@ -10764,70 +10776,70 @@
             <v>0</v>
           </cell>
           <cell r="T43">
-            <v>139</v>
+            <v>142</v>
           </cell>
           <cell r="U43">
-            <v>149</v>
+            <v>153</v>
           </cell>
           <cell r="V43">
-            <v>143</v>
+            <v>147</v>
           </cell>
           <cell r="W43">
-            <v>173</v>
+            <v>182</v>
           </cell>
           <cell r="X43">
-            <v>96</v>
+            <v>105</v>
           </cell>
           <cell r="Y43">
-            <v>269</v>
+            <v>283</v>
           </cell>
           <cell r="Z43">
+            <v>102</v>
+          </cell>
+          <cell r="AA43">
+            <v>170</v>
+          </cell>
+          <cell r="AB43">
+            <v>36</v>
+          </cell>
+          <cell r="AC43">
+            <v>20</v>
+          </cell>
+          <cell r="AD43">
+            <v>0</v>
+          </cell>
+          <cell r="AE43">
+            <v>0</v>
+          </cell>
+          <cell r="AF43">
+            <v>0</v>
+          </cell>
+          <cell r="AG43">
+            <v>0</v>
+          </cell>
+          <cell r="AH43">
+            <v>0</v>
+          </cell>
+          <cell r="AI43">
+            <v>0</v>
+          </cell>
+          <cell r="AJ43">
+            <v>0</v>
+          </cell>
+          <cell r="AK43">
+            <v>0</v>
+          </cell>
+          <cell r="AL43">
             <v>97</v>
           </cell>
-          <cell r="AA43">
-            <v>165</v>
-          </cell>
-          <cell r="AB43">
-            <v>37</v>
-          </cell>
-          <cell r="AC43">
-            <v>19</v>
-          </cell>
-          <cell r="AD43">
-            <v>0</v>
-          </cell>
-          <cell r="AE43">
-            <v>0</v>
-          </cell>
-          <cell r="AF43">
-            <v>0</v>
-          </cell>
-          <cell r="AG43">
-            <v>0</v>
-          </cell>
-          <cell r="AH43">
-            <v>0</v>
-          </cell>
-          <cell r="AI43">
-            <v>0</v>
-          </cell>
-          <cell r="AJ43">
-            <v>0</v>
-          </cell>
-          <cell r="AK43">
-            <v>0</v>
-          </cell>
-          <cell r="AL43">
-            <v>87</v>
-          </cell>
           <cell r="AM43">
-            <v>59</v>
+            <v>66</v>
           </cell>
           <cell r="AN43">
-            <v>41</v>
+            <v>40</v>
           </cell>
           <cell r="AO43">
-            <v>116</v>
+            <v>119</v>
           </cell>
           <cell r="AP43">
             <v>0</v>
@@ -10848,28 +10860,28 @@
             <v>0</v>
           </cell>
           <cell r="AV43">
-            <v>35</v>
+            <v>31</v>
           </cell>
           <cell r="AW43">
-            <v>123</v>
+            <v>127</v>
           </cell>
           <cell r="AX43">
-            <v>57</v>
+            <v>68</v>
           </cell>
           <cell r="AY43">
             <v>43</v>
           </cell>
           <cell r="AZ43">
-            <v>40</v>
+            <v>45</v>
           </cell>
           <cell r="BA43">
-            <v>49</v>
+            <v>50</v>
           </cell>
           <cell r="BB43">
-            <v>78</v>
+            <v>81</v>
           </cell>
           <cell r="BC43">
-            <v>54</v>
+            <v>55</v>
           </cell>
           <cell r="BD43">
             <v>4</v>
@@ -10878,40 +10890,40 @@
             <v>26</v>
           </cell>
           <cell r="BF43">
-            <v>19</v>
+            <v>18</v>
           </cell>
           <cell r="BG43">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="BH43">
             <v>29</v>
           </cell>
           <cell r="BI43">
-            <v>13</v>
+            <v>14</v>
           </cell>
           <cell r="BJ43">
-            <v>69</v>
+            <v>71</v>
           </cell>
           <cell r="BK43">
             <v>44</v>
           </cell>
           <cell r="BL43">
-            <v>60</v>
+            <v>61</v>
           </cell>
           <cell r="BM43">
-            <v>28</v>
+            <v>29</v>
           </cell>
           <cell r="BN43">
-            <v>157</v>
+            <v>144</v>
           </cell>
           <cell r="BO43">
-            <v>461</v>
+            <v>475</v>
           </cell>
           <cell r="BP43">
-            <v>1298</v>
+            <v>1334</v>
           </cell>
           <cell r="BQ43">
-            <v>1908</v>
+            <v>1979</v>
           </cell>
         </row>
         <row r="45">
@@ -12208,7 +12220,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -12273,7 +12285,7 @@
       </c>
       <c r="B3" s="31">
         <f>B1-B2</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
@@ -12754,7 +12766,7 @@
       </c>
       <c r="S8" s="24">
         <f t="shared" ref="S8:S36" si="5">IF(OR(R8="",R8=0),"",ROUND(Q8/R8*$B$2,1))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T8" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A8,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -12858,7 +12870,7 @@
       </c>
       <c r="AS8" s="24">
         <f t="shared" ref="AS8:AS36" si="17">IF(OR(AR8="",AR8=0),"",ROUND(AQ8/AR8*$B$2,1))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT8" s="25">
         <f t="shared" ref="AT8:AT35" si="18">SUM(B8,E8,H8,K8,N8,Q8,T8,X8,AB8,AF8,AJ8,AN8,AQ8)</f>
@@ -12870,7 +12882,7 @@
       </c>
       <c r="AV8" s="25">
         <f t="shared" ref="AV8:AV36" si="20">IFERROR(AT8/(AU8/$B$2),1000)</f>
-        <v>12.75</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="9" spans="1:48">
@@ -12947,7 +12959,7 @@
       </c>
       <c r="S9" s="24">
         <f t="shared" si="5"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="T9" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A9,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13031,15 +13043,15 @@
       </c>
       <c r="AN9" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A9,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="47">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A9,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP9" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="AP9" s="24">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ9" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A9,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13055,15 +13067,15 @@
       </c>
       <c r="AT9" s="25">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU9" s="25">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV9" s="25">
         <f t="shared" si="20"/>
-        <v>22.6666666666667</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="10" spans="1:48">
@@ -13116,7 +13128,7 @@
       </c>
       <c r="M10" s="24">
         <f t="shared" si="3"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N10" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13128,7 +13140,7 @@
       </c>
       <c r="P10" s="24">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q10" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13140,7 +13152,7 @@
       </c>
       <c r="S10" s="24">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T10" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13256,7 +13268,7 @@
       </c>
       <c r="AV10" s="25">
         <f t="shared" si="20"/>
-        <v>11.3333333333333</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:48">
@@ -13425,7 +13437,7 @@
       </c>
       <c r="AP11" s="24">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ11" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A11,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13449,7 +13461,7 @@
       </c>
       <c r="AV11" s="25">
         <f t="shared" si="20"/>
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:48">
@@ -13526,7 +13538,7 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T12" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A12,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13642,7 +13654,7 @@
       </c>
       <c r="AV12" s="25">
         <f t="shared" si="20"/>
-        <v>5.66666666666667</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:48">
@@ -13707,7 +13719,7 @@
       </c>
       <c r="P13" s="24">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q13" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A13,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13719,7 +13731,7 @@
       </c>
       <c r="S13" s="24">
         <f t="shared" si="5"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="T13" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A13,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13795,11 +13807,11 @@
       </c>
       <c r="AL13" s="24">
         <f t="shared" si="14"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AM13" s="47">
         <f t="shared" si="15"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AN13" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A13,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13835,7 +13847,7 @@
       </c>
       <c r="AV13" s="25">
         <f t="shared" si="20"/>
-        <v>27.2</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="14" spans="1:48">
@@ -13888,7 +13900,7 @@
       </c>
       <c r="M14" s="24">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N14" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13912,7 +13924,7 @@
       </c>
       <c r="S14" s="24">
         <f t="shared" si="5"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T14" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14028,7 +14040,7 @@
       </c>
       <c r="AV14" s="25">
         <f t="shared" si="20"/>
-        <v>27.2</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="15" spans="1:48">
@@ -14081,7 +14093,7 @@
       </c>
       <c r="M15" s="24">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N15" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A15,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14201,27 +14213,27 @@
       </c>
       <c r="AQ15" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A15,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR15" s="47">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A15,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS15" s="24">
         <f t="shared" si="17"/>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AT15" s="25">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU15" s="25">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV15" s="25">
         <f t="shared" si="20"/>
-        <v>22.6666666666667</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="16" spans="1:48">
@@ -14358,11 +14370,11 @@
       </c>
       <c r="AH16" s="24">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI16" s="47">
         <f t="shared" si="13"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AJ16" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A16,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14414,7 +14426,7 @@
       </c>
       <c r="AV16" s="25">
         <f t="shared" si="20"/>
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:48">
@@ -14571,7 +14583,7 @@
       </c>
       <c r="AM17" s="47">
         <f t="shared" si="15"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AN17" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A17,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14607,7 +14619,7 @@
       </c>
       <c r="AV17" s="25">
         <f t="shared" si="20"/>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:48">
@@ -14993,7 +15005,7 @@
       </c>
       <c r="AV19" s="25">
         <f t="shared" si="20"/>
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="20" spans="1:48">
@@ -15263,7 +15275,7 @@
       </c>
       <c r="S21" s="24">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T21" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A21,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15323,11 +15335,11 @@
       </c>
       <c r="AH21" s="24">
         <f t="shared" si="12"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI21" s="47">
         <f t="shared" si="13"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AJ21" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A21,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15379,7 +15391,7 @@
       </c>
       <c r="AV21" s="25">
         <f t="shared" si="20"/>
-        <v>24.2857142857143</v>
+        <v>25.7142857142857</v>
       </c>
     </row>
     <row r="22" spans="1:48">
@@ -15412,15 +15424,15 @@
       </c>
       <c r="H22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11X|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="47">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11X|8+256|BLACK|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="J22" s="24">
         <f t="shared" si="2"/>
-        <v/>
+        <v>18</v>
       </c>
       <c r="K22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11X|8+256|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15432,7 +15444,7 @@
       </c>
       <c r="M22" s="24">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15516,11 +15528,11 @@
       </c>
       <c r="AH22" s="24">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI22" s="47">
         <f t="shared" si="13"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AJ22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15548,7 +15560,7 @@
       </c>
       <c r="AP22" s="24">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15564,15 +15576,15 @@
       </c>
       <c r="AT22" s="25">
         <f t="shared" si="18"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU22" s="25">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV22" s="25">
         <f t="shared" si="20"/>
-        <v>56.6666666666667</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="23" spans="1:48">
@@ -15637,7 +15649,7 @@
       </c>
       <c r="P23" s="24">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q23" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A23,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15741,7 +15753,7 @@
       </c>
       <c r="AP23" s="24">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ23" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A23,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15765,7 +15777,7 @@
       </c>
       <c r="AV23" s="25">
         <f t="shared" si="20"/>
-        <v>39.6666666666667</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:48">
@@ -15818,7 +15830,7 @@
       </c>
       <c r="M24" s="24">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N24" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A24,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15906,7 +15918,7 @@
       </c>
       <c r="AI24" s="47">
         <f t="shared" si="13"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AJ24" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A24,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15922,7 +15934,7 @@
       </c>
       <c r="AM24" s="47">
         <f t="shared" si="15"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AN24" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A24,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15958,7 +15970,7 @@
       </c>
       <c r="AV24" s="25">
         <f t="shared" si="20"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:48">
@@ -16151,7 +16163,7 @@
       </c>
       <c r="AV25" s="25">
         <f t="shared" si="20"/>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:48">
@@ -16192,7 +16204,7 @@
       </c>
       <c r="J26" s="24">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K26" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11X|8+256|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16228,7 +16240,7 @@
       </c>
       <c r="S26" s="24">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T26" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16292,7 +16304,7 @@
       </c>
       <c r="AI26" s="47">
         <f t="shared" si="13"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AJ26" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16332,7 +16344,7 @@
       </c>
       <c r="AS26" s="24">
         <f t="shared" si="17"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT26" s="25">
         <f t="shared" si="18"/>
@@ -16344,7 +16356,7 @@
       </c>
       <c r="AV26" s="25">
         <f t="shared" si="20"/>
-        <v>27.2</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="27" spans="1:48">
@@ -16537,7 +16549,7 @@
       </c>
       <c r="AV27" s="25">
         <f t="shared" si="20"/>
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:48">
@@ -16730,7 +16742,7 @@
       </c>
       <c r="AV28" s="25">
         <f t="shared" si="20"/>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:48">
@@ -16795,7 +16807,7 @@
       </c>
       <c r="P29" s="24">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q29" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A29,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16807,7 +16819,7 @@
       </c>
       <c r="S29" s="24">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T29" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A29,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16871,7 +16883,7 @@
       </c>
       <c r="AI29" s="47">
         <f t="shared" si="13"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AJ29" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A29,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16911,7 +16923,7 @@
       </c>
       <c r="AS29" s="24">
         <f t="shared" si="17"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT29" s="25">
         <f t="shared" si="18"/>
@@ -16923,7 +16935,7 @@
       </c>
       <c r="AV29" s="25">
         <f t="shared" si="20"/>
-        <v>21.25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="30" spans="1:48">
@@ -16988,7 +17000,7 @@
       </c>
       <c r="P30" s="24">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q30" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A30,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17000,7 +17012,7 @@
       </c>
       <c r="S30" s="24">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T30" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A30,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17116,7 +17128,7 @@
       </c>
       <c r="AV30" s="25">
         <f t="shared" si="20"/>
-        <v>28.3333333333333</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:48">
@@ -17378,7 +17390,7 @@
       </c>
       <c r="Q32" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A32,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R32" s="47">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A32,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17386,7 +17398,7 @@
       </c>
       <c r="S32" s="24">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T32" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A32,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17446,11 +17458,11 @@
       </c>
       <c r="AH32" s="24">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI32" s="47">
         <f t="shared" si="13"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AJ32" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A32,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17494,7 +17506,7 @@
       </c>
       <c r="AT32" s="25">
         <f t="shared" si="18"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AU32" s="25">
         <f t="shared" si="19"/>
@@ -17502,7 +17514,7 @@
       </c>
       <c r="AV32" s="25">
         <f t="shared" si="20"/>
-        <v>45.3333333333333</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:48">
@@ -17627,7 +17639,7 @@
       </c>
       <c r="AE33" s="47">
         <f t="shared" si="11"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AF33" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17639,11 +17651,11 @@
       </c>
       <c r="AH33" s="24">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI33" s="47">
         <f t="shared" si="13"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AJ33" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17671,7 +17683,7 @@
       </c>
       <c r="AP33" s="24">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ33" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17683,7 +17695,7 @@
       </c>
       <c r="AS33" s="24">
         <f t="shared" si="17"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT33" s="25">
         <f t="shared" si="18"/>
@@ -17695,7 +17707,7 @@
       </c>
       <c r="AV33" s="25">
         <f t="shared" si="20"/>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:48">
@@ -17772,7 +17784,7 @@
       </c>
       <c r="S34" s="24">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T34" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A34,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17888,7 +17900,7 @@
       </c>
       <c r="AV34" s="25">
         <f t="shared" si="20"/>
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:48">
@@ -17953,7 +17965,7 @@
       </c>
       <c r="P35" s="24">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q35" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A35,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -18081,7 +18093,7 @@
       </c>
       <c r="AV35" s="25">
         <f t="shared" si="20"/>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:48">
@@ -18114,15 +18126,15 @@
       </c>
       <c r="H36" s="27">
         <f t="shared" ref="H36:L36" si="22">SUM(H8:H35)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I36" s="50">
         <f t="shared" si="22"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J36" s="24">
         <f t="shared" si="2"/>
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="K36" s="27">
         <f t="shared" si="22"/>
@@ -18134,7 +18146,7 @@
       </c>
       <c r="M36" s="24">
         <f t="shared" si="3"/>
-        <v>21.3</v>
+        <v>22.5</v>
       </c>
       <c r="N36" s="27">
         <f t="shared" ref="N36:R36" si="23">SUM(N8:N35)</f>
@@ -18146,11 +18158,11 @@
       </c>
       <c r="P36" s="24">
         <f t="shared" si="4"/>
-        <v>24.2</v>
+        <v>25.6</v>
       </c>
       <c r="Q36" s="27">
         <f t="shared" si="23"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R36" s="50">
         <f t="shared" si="23"/>
@@ -18158,7 +18170,7 @@
       </c>
       <c r="S36" s="24">
         <f t="shared" si="5"/>
-        <v>20.2</v>
+        <v>23.1</v>
       </c>
       <c r="T36" s="27">
         <f t="shared" ref="T36:Y36" si="24">SUM(T8:T35)</f>
@@ -18206,7 +18218,7 @@
       </c>
       <c r="AE36" s="50">
         <f t="shared" ref="AE36:AG36" si="26">SUM(AE8:AE35)</f>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AF36" s="27">
         <f t="shared" si="26"/>
@@ -18218,11 +18230,11 @@
       </c>
       <c r="AH36" s="24">
         <f t="shared" si="12"/>
-        <v>28.9</v>
+        <v>30.6</v>
       </c>
       <c r="AI36" s="50">
         <f t="shared" ref="AI36:AK36" si="27">SUM(AI8:AI35)</f>
-        <v>5.88235294117647</v>
+        <v>5.55555555555556</v>
       </c>
       <c r="AJ36" s="27">
         <f t="shared" si="27"/>
@@ -18234,47 +18246,47 @@
       </c>
       <c r="AL36" s="24">
         <f t="shared" si="14"/>
-        <v>23.8</v>
+        <v>25.2</v>
       </c>
       <c r="AM36" s="50">
         <f t="shared" ref="AM36:AO36" si="28">SUM(AM8:AM35)</f>
-        <v>2.94117647058824</v>
+        <v>2.77777777777778</v>
       </c>
       <c r="AN36" s="27">
         <f t="shared" si="28"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO36" s="50">
         <f t="shared" si="28"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP36" s="24">
         <f t="shared" si="16"/>
-        <v>81.6</v>
+        <v>69</v>
       </c>
       <c r="AQ36" s="27">
         <f t="shared" ref="AQ36:AU36" si="29">SUM(AQ8:AQ35)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AR36" s="50">
         <f t="shared" si="29"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS36" s="24">
         <f t="shared" si="17"/>
-        <v>75.3</v>
+        <v>67.5</v>
       </c>
       <c r="AT36" s="25">
         <f t="shared" si="29"/>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AU36" s="25">
         <f t="shared" si="29"/>
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AV36" s="25">
         <f t="shared" si="20"/>
-        <v>28.5744680851064</v>
+        <v>29.1340206185567</v>
       </c>
     </row>
   </sheetData>
@@ -18695,7 +18707,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -18830,7 +18842,7 @@
       </c>
       <c r="B3" s="3">
         <f>B1-B2</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -19575,11 +19587,11 @@
       </c>
       <c r="J7" s="24">
         <f t="shared" ref="J7:J35" si="2">IF(OR(I7="",I7=0),"",ROUND(H7/I7*$B$2,1))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7" s="23">
         <f t="shared" ref="K7:K34" si="3">(I7/$B$2)*10</f>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="L7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19623,35 +19635,35 @@
       </c>
       <c r="V7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X7" s="24">
         <f t="shared" ref="X7:X35" si="8">IF(OR(W7="",W7=0),"",ROUND(V7/W7*$B$2,1))</f>
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="Y7" s="23">
         <f t="shared" ref="Y7:Y34" si="9">(W7/$B$2)*5</f>
-        <v>4.70588235294118</v>
+        <v>5</v>
       </c>
       <c r="Z7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB7" s="24">
         <f t="shared" ref="AB7:AB35" si="10">IF(OR(AA7="",AA7=0),"",ROUND(Z7/AA7*$B$2,1))</f>
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AC7" s="23">
         <f t="shared" ref="AC7:AC34" si="11">(AA7/$B$2)*5</f>
-        <v>3.52941176470588</v>
+        <v>3.61111111111111</v>
       </c>
       <c r="AD7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19663,23 +19675,23 @@
       </c>
       <c r="AF7" s="24">
         <f t="shared" ref="AF7:AF35" si="12">IF(OR(AE7="",AE7=0),"",ROUND(AD7/AE7*$B$2,1))</f>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="AG7" s="23">
         <f t="shared" ref="AG7:AG34" si="13">(AE7/$B$2)*5</f>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AH7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AI7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ7" s="24">
         <f t="shared" ref="AJ7:AJ35" si="14">IF(OR(AI7="",AI7=0),"",ROUND(AH7/AI7*$B$2,1))</f>
-        <v>4.9</v>
+        <v>11.3</v>
       </c>
       <c r="AK7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19695,23 +19707,23 @@
       </c>
       <c r="AN7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP7" s="24">
         <f t="shared" ref="AP7:AP35" si="16">IF(OR(AO7="",AO7=0),"",ROUND(AN7/AO7*$B$2,1))</f>
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ7" s="23">
         <f t="shared" ref="AQ7:AQ34" si="17">(AO7/$B$2)*5</f>
-        <v>3.82352941176471</v>
+        <v>3.88888888888889</v>
       </c>
       <c r="AR7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AS7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -19719,11 +19731,11 @@
       </c>
       <c r="AT7" s="24">
         <f t="shared" ref="AT7:AT35" si="18">IF(OR(AS7="",AS7=0),"",ROUND(AR7/AS7*$B$2,1))</f>
-        <v>2.1</v>
+        <v>11.3</v>
       </c>
       <c r="AU7" s="23">
         <f t="shared" ref="AU7:AU34" si="19">(AS7/$B$2)*5</f>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="AV7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19735,11 +19747,11 @@
       </c>
       <c r="AX7" s="24">
         <f t="shared" ref="AX7:AX35" si="20">IF(OR(AW7="",AW7=0),"",ROUND(AV7/AW7*$B$2,1))</f>
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AY7" s="23">
         <f t="shared" ref="AY7:AY34" si="21">(AW7/$B$2)*5</f>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="AZ7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19767,7 +19779,7 @@
       </c>
       <c r="BF7" s="23">
         <f t="shared" ref="BF7:BF34" si="24">(BD7/$B$2)*8</f>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19811,11 +19823,11 @@
       </c>
       <c r="BQ7" s="24">
         <f t="shared" ref="BQ7:BQ35" si="29">IF(OR(BP7="",BP7=0),"",ROUND(BO7/BP7*$B$2,1))</f>
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BR7" s="23">
         <f t="shared" ref="BR7:BR34" si="30">(BP7/$B$2)*8</f>
-        <v>3.29411764705882</v>
+        <v>3.11111111111111</v>
       </c>
       <c r="BS7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19843,43 +19855,43 @@
       </c>
       <c r="BY7" s="24">
         <f t="shared" ref="BY7:BY35" si="33">IF(OR(BX7="",BX7=0),"",ROUND(BW7/BX7*$B$2,1))</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BZ7" s="23">
         <f t="shared" ref="BZ7:BZ34" si="34">(BX7/$B$2)*8</f>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="CA7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CB7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CC7" s="24">
         <f t="shared" ref="CC7:CC35" si="35">IF(OR(CB7="",CB7=0),"",ROUND(CA7/CB7*$B$2,1))</f>
-        <v>31.6</v>
+        <v>27</v>
       </c>
       <c r="CD7" s="23">
         <f t="shared" ref="CD7:CD34" si="36">(CB7/$B$2)*5</f>
-        <v>2.05882352941176</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="CE7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CF7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CG7" s="24">
         <f t="shared" ref="CG7:CG35" si="37">IF(OR(CF7="",CF7=0),"",ROUND(CE7/CF7*$B$2,1))</f>
-        <v>11.1</v>
+        <v>10.3</v>
       </c>
       <c r="CH7" s="23">
         <f t="shared" ref="CH7:CH34" si="38">(CF7/$B$2)*7</f>
-        <v>8.23529411764706</v>
+        <v>8.16666666666667</v>
       </c>
       <c r="CI7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19891,19 +19903,19 @@
       </c>
       <c r="CK7" s="24">
         <f t="shared" ref="CK7:CK35" si="39">IF(OR(CJ7="",CJ7=0),"",ROUND(CI7/CJ7*$B$2,1))</f>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="CL7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN7" s="24">
         <f t="shared" ref="CN7:CN35" si="40">IF(OR(CM7="",CM7=0),"",ROUND(CL7/CM7*$B$2,1))</f>
-        <v>22.7</v>
+        <v>13.5</v>
       </c>
       <c r="CO7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19915,19 +19927,19 @@
       </c>
       <c r="CQ7" s="24">
         <f t="shared" ref="CQ7:CQ35" si="41">IF(OR(CP7="",CP7=0),"",ROUND(CO7/CP7*$B$2,1))</f>
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="CR7" s="25">
         <f t="shared" ref="CR7:CR34" si="42">SUM(B7,L7,P7,S7,AZ7,BK7,BO7,BS7,BW7,CA7,CE7,BC7,AN7,AR7,AV7,BG7,V7,E7,H7,AD7,Z7,AH7,AK7,CI7,CL7,CO7)</f>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="CS7" s="25">
         <f t="shared" ref="CS7:CS34" si="43">SUM(C7,M7,Q7,T7,BL7,BP7,BT7,BX7,CB7,CF7,BA7,BD7,AO7,AS7,AW7,BH7,W7,F7,I7,AE7,AA7,AI7,AL7,CJ7,CM7,CP7)</f>
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="CT7" s="25">
         <f t="shared" ref="CT7:CT34" si="44">IFERROR(CR7/(CS7/$B$2),1000)</f>
-        <v>9.35570469798658</v>
+        <v>9.63057324840764</v>
       </c>
     </row>
     <row r="8" spans="1:98">
@@ -20024,43 +20036,43 @@
       </c>
       <c r="X8" s="24">
         <f t="shared" si="8"/>
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" s="23">
         <f t="shared" si="9"/>
-        <v>6.47058823529412</v>
+        <v>6.11111111111111</v>
       </c>
       <c r="Z8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB8" s="24">
         <f t="shared" si="10"/>
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="AC8" s="23">
         <f t="shared" si="11"/>
-        <v>3.52941176470588</v>
+        <v>3.61111111111111</v>
       </c>
       <c r="AD8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF8" s="24">
         <f t="shared" si="12"/>
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="23">
         <f t="shared" si="13"/>
-        <v>0.588235294117647</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AH8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20100,11 +20112,11 @@
       </c>
       <c r="AQ8" s="23">
         <f t="shared" si="17"/>
-        <v>4.11764705882353</v>
+        <v>3.88888888888889</v>
       </c>
       <c r="AR8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -20112,11 +20124,11 @@
       </c>
       <c r="AT8" s="24">
         <f t="shared" si="18"/>
-        <v>4.9</v>
+        <v>10.3</v>
       </c>
       <c r="AU8" s="23">
         <f t="shared" si="19"/>
-        <v>2.05882352941176</v>
+        <v>1.94444444444444</v>
       </c>
       <c r="AV8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20128,11 +20140,11 @@
       </c>
       <c r="AX8" s="24">
         <f t="shared" si="20"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY8" s="23">
         <f t="shared" si="21"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AZ8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20148,19 +20160,19 @@
       </c>
       <c r="BC8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE8" s="24">
         <f t="shared" si="23"/>
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="BF8" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>1.33333333333333</v>
       </c>
       <c r="BG8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20204,11 +20216,11 @@
       </c>
       <c r="BQ8" s="24">
         <f t="shared" si="29"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="BR8" s="23">
         <f t="shared" si="30"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BS8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20236,11 +20248,11 @@
       </c>
       <c r="BY8" s="24">
         <f t="shared" si="33"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BZ8" s="23">
         <f t="shared" si="34"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="CA8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20252,11 +20264,11 @@
       </c>
       <c r="CC8" s="24">
         <f t="shared" si="35"/>
-        <v>22.7</v>
+        <v>24</v>
       </c>
       <c r="CD8" s="23">
         <f t="shared" si="36"/>
-        <v>2.64705882352941</v>
+        <v>2.5</v>
       </c>
       <c r="CE8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20268,11 +20280,11 @@
       </c>
       <c r="CG8" s="24">
         <f t="shared" si="37"/>
-        <v>15.2</v>
+        <v>16.1</v>
       </c>
       <c r="CH8" s="23">
         <f t="shared" si="38"/>
-        <v>7.82352941176471</v>
+        <v>7.38888888888889</v>
       </c>
       <c r="CI8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20284,7 +20296,7 @@
       </c>
       <c r="CK8" s="24">
         <f t="shared" si="39"/>
-        <v>22.7</v>
+        <v>24</v>
       </c>
       <c r="CL8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20296,31 +20308,31 @@
       </c>
       <c r="CN8" s="24">
         <f t="shared" si="40"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="CO8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CP8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="CQ8" s="24">
         <f t="shared" si="41"/>
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="CR8" s="25">
         <f t="shared" si="42"/>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="CS8" s="25">
         <f t="shared" si="43"/>
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="CT8" s="25">
         <f t="shared" si="44"/>
-        <v>9.01204819277108</v>
+        <v>8.94797687861272</v>
       </c>
     </row>
     <row r="9" spans="1:98">
@@ -20409,19 +20421,19 @@
       </c>
       <c r="V9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="X9" s="24">
         <f t="shared" si="8"/>
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Y9" s="23">
         <f t="shared" si="9"/>
-        <v>10.2941176470588</v>
+        <v>10.2777777777778</v>
       </c>
       <c r="Z9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20433,11 +20445,11 @@
       </c>
       <c r="AB9" s="24">
         <f t="shared" si="10"/>
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AC9" s="23">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>9.44444444444444</v>
       </c>
       <c r="AD9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20449,23 +20461,23 @@
       </c>
       <c r="AF9" s="24">
         <f t="shared" si="12"/>
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AG9" s="23">
         <f t="shared" si="13"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AH9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ9" s="24">
         <f t="shared" si="14"/>
-        <v>5.1</v>
+        <v>8.2</v>
       </c>
       <c r="AK9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20477,23 +20489,23 @@
       </c>
       <c r="AM9" s="24">
         <f t="shared" si="15"/>
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="AN9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP9" s="24">
         <f t="shared" si="16"/>
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ9" s="23">
         <f t="shared" si="17"/>
-        <v>3.82352941176471</v>
+        <v>4.16666666666667</v>
       </c>
       <c r="AR9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20505,11 +20517,11 @@
       </c>
       <c r="AT9" s="24">
         <f t="shared" si="18"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU9" s="23">
         <f t="shared" si="19"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AV9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20521,11 +20533,11 @@
       </c>
       <c r="AX9" s="24">
         <f t="shared" si="20"/>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="AY9" s="23">
         <f t="shared" si="21"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AZ9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20553,7 +20565,7 @@
       </c>
       <c r="BF9" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20585,7 +20597,7 @@
       </c>
       <c r="BN9" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20597,11 +20609,11 @@
       </c>
       <c r="BQ9" s="24">
         <f t="shared" si="29"/>
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="BR9" s="23">
         <f t="shared" si="30"/>
-        <v>1.88235294117647</v>
+        <v>1.77777777777778</v>
       </c>
       <c r="BS9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20629,11 +20641,11 @@
       </c>
       <c r="BY9" s="24">
         <f t="shared" si="33"/>
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BZ9" s="23">
         <f t="shared" si="34"/>
-        <v>2.82352941176471</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="CA9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20645,27 +20657,27 @@
       </c>
       <c r="CC9" s="24">
         <f t="shared" si="35"/>
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="CD9" s="23">
         <f t="shared" si="36"/>
-        <v>6.47058823529412</v>
+        <v>6.11111111111111</v>
       </c>
       <c r="CE9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CF9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CG9" s="24">
         <f t="shared" si="37"/>
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CH9" s="23">
         <f t="shared" si="38"/>
-        <v>15.2352941176471</v>
+        <v>14.7777777777778</v>
       </c>
       <c r="CI9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20677,7 +20689,7 @@
       </c>
       <c r="CK9" s="24">
         <f t="shared" si="39"/>
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="CL9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20689,31 +20701,31 @@
       </c>
       <c r="CN9" s="24">
         <f t="shared" si="40"/>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="CO9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CP9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="CQ9" s="24">
         <f t="shared" si="41"/>
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="CR9" s="25">
         <f t="shared" si="42"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="CS9" s="25">
         <f t="shared" si="43"/>
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="CT9" s="25">
         <f t="shared" si="44"/>
-        <v>4.07160493827161</v>
+        <v>4.06730769230769</v>
       </c>
     </row>
     <row r="10" spans="1:98">
@@ -20802,7 +20814,7 @@
       </c>
       <c r="V10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W10" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -20810,27 +20822,27 @@
       </c>
       <c r="X10" s="24">
         <f t="shared" si="8"/>
-        <v>3.4</v>
+        <v>14.4</v>
       </c>
       <c r="Y10" s="23">
         <f t="shared" si="9"/>
-        <v>1.47058823529412</v>
+        <v>1.38888888888889</v>
       </c>
       <c r="Z10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA10" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB10" s="24">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AC10" s="23">
         <f t="shared" si="11"/>
-        <v>0.588235294117647</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AD10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20882,11 +20894,11 @@
       </c>
       <c r="AP10" s="24">
         <f t="shared" si="16"/>
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ10" s="23">
         <f t="shared" si="17"/>
-        <v>1.47058823529412</v>
+        <v>1.38888888888889</v>
       </c>
       <c r="AR10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20906,19 +20918,19 @@
       </c>
       <c r="AV10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW10" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX10" s="24">
         <f t="shared" si="20"/>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AY10" s="23">
         <f t="shared" si="21"/>
-        <v>0.294117647058824</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AZ10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20942,11 +20954,11 @@
       </c>
       <c r="BE10" s="24">
         <f t="shared" si="23"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BF10" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20990,11 +21002,11 @@
       </c>
       <c r="BQ10" s="24">
         <f t="shared" si="29"/>
-        <v>22.7</v>
+        <v>24</v>
       </c>
       <c r="BR10" s="23">
         <f t="shared" si="30"/>
-        <v>1.41176470588235</v>
+        <v>1.33333333333333</v>
       </c>
       <c r="BS10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21010,7 +21022,7 @@
       </c>
       <c r="BV10" s="23">
         <f t="shared" si="32"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BW10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21022,15 +21034,15 @@
       </c>
       <c r="BY10" s="24">
         <f t="shared" si="33"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BZ10" s="23">
         <f t="shared" si="34"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="CA10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CB10" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21038,11 +21050,11 @@
       </c>
       <c r="CC10" s="24">
         <f t="shared" si="35"/>
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="CD10" s="23">
         <f t="shared" si="36"/>
-        <v>2.64705882352941</v>
+        <v>2.5</v>
       </c>
       <c r="CE10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21054,11 +21066,11 @@
       </c>
       <c r="CG10" s="24">
         <f t="shared" si="37"/>
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="CH10" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21070,7 +21082,7 @@
       </c>
       <c r="CK10" s="24">
         <f t="shared" si="39"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CL10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21094,19 +21106,19 @@
       </c>
       <c r="CQ10" s="24">
         <f t="shared" si="41"/>
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="CR10" s="25">
         <f t="shared" si="42"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="CS10" s="25">
         <f t="shared" si="43"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CT10" s="25">
         <f t="shared" si="44"/>
-        <v>23.0714285714286</v>
+        <v>24.1363636363636</v>
       </c>
     </row>
     <row r="11" spans="1:98">
@@ -21203,27 +21215,27 @@
       </c>
       <c r="X11" s="24">
         <f t="shared" si="8"/>
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="Y11" s="23">
         <f t="shared" si="9"/>
-        <v>2.94117647058824</v>
+        <v>2.77777777777778</v>
       </c>
       <c r="Z11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB11" s="24">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AC11" s="23">
         <f t="shared" si="11"/>
-        <v>0.588235294117647</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AD11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21243,7 +21255,7 @@
       </c>
       <c r="AH11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21251,7 +21263,7 @@
       </c>
       <c r="AJ11" s="24">
         <f t="shared" si="14"/>
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AK11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21263,7 +21275,7 @@
       </c>
       <c r="AM11" s="24">
         <f t="shared" si="15"/>
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AN11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21279,7 +21291,7 @@
       </c>
       <c r="AQ11" s="23">
         <f t="shared" si="17"/>
-        <v>2.05882352941176</v>
+        <v>1.94444444444444</v>
       </c>
       <c r="AR11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21291,11 +21303,11 @@
       </c>
       <c r="AT11" s="24">
         <f t="shared" si="18"/>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="AU11" s="23">
         <f t="shared" si="19"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AV11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21311,7 +21323,7 @@
       </c>
       <c r="AY11" s="23">
         <f t="shared" si="21"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AZ11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21371,7 +21383,7 @@
       </c>
       <c r="BN11" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21383,11 +21395,11 @@
       </c>
       <c r="BQ11" s="24">
         <f t="shared" si="29"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BR11" s="23">
         <f t="shared" si="30"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BS11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21403,11 +21415,11 @@
       </c>
       <c r="BV11" s="23">
         <f t="shared" si="32"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BW11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BX11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21415,15 +21427,15 @@
       </c>
       <c r="BY11" s="24">
         <f t="shared" si="33"/>
-        <v>3.4</v>
+        <v>10.8</v>
       </c>
       <c r="BZ11" s="23">
         <f t="shared" si="34"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="CA11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CB11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21431,31 +21443,31 @@
       </c>
       <c r="CC11" s="24">
         <f t="shared" si="35"/>
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="CD11" s="23">
         <f t="shared" si="36"/>
-        <v>3.23529411764706</v>
+        <v>3.05555555555556</v>
       </c>
       <c r="CE11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CF11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CG11" s="24">
         <f t="shared" si="37"/>
-        <v>10.2</v>
+        <v>8.2</v>
       </c>
       <c r="CH11" s="23">
         <f t="shared" si="38"/>
-        <v>4.11764705882353</v>
+        <v>4.27777777777778</v>
       </c>
       <c r="CI11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21463,7 +21475,7 @@
       </c>
       <c r="CK11" s="24">
         <f t="shared" si="39"/>
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="CL11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21487,19 +21499,19 @@
       </c>
       <c r="CQ11" s="24">
         <f t="shared" si="41"/>
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="CR11" s="25">
         <f t="shared" si="42"/>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="CS11" s="25">
         <f t="shared" si="43"/>
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="CT11" s="25">
         <f t="shared" si="44"/>
-        <v>5.95</v>
+        <v>7.02439024390244</v>
       </c>
     </row>
     <row r="12" spans="1:98">
@@ -21528,11 +21540,11 @@
       </c>
       <c r="G12" s="24">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21540,11 +21552,11 @@
       </c>
       <c r="J12" s="24">
         <f t="shared" si="2"/>
-        <v>12.8</v>
+        <v>18</v>
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="L12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21588,7 +21600,7 @@
       </c>
       <c r="V12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W12" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21596,15 +21608,15 @@
       </c>
       <c r="X12" s="24">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>22.5</v>
       </c>
       <c r="Y12" s="23">
         <f t="shared" si="9"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="Z12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA12" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21612,11 +21624,11 @@
       </c>
       <c r="AB12" s="24">
         <f t="shared" si="10"/>
-        <v>9.7</v>
+        <v>12.9</v>
       </c>
       <c r="AC12" s="23">
         <f t="shared" si="11"/>
-        <v>2.05882352941176</v>
+        <v>1.94444444444444</v>
       </c>
       <c r="AD12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21644,7 +21656,7 @@
       </c>
       <c r="AJ12" s="24">
         <f t="shared" si="14"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AK12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21656,7 +21668,7 @@
       </c>
       <c r="AM12" s="24">
         <f t="shared" si="15"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21668,11 +21680,11 @@
       </c>
       <c r="AP12" s="24">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ12" s="23">
         <f t="shared" si="17"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AR12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21684,11 +21696,11 @@
       </c>
       <c r="AT12" s="24">
         <f t="shared" si="18"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU12" s="23">
         <f t="shared" si="19"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AV12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21700,11 +21712,11 @@
       </c>
       <c r="AX12" s="24">
         <f t="shared" si="20"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY12" s="23">
         <f t="shared" si="21"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AZ12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21732,7 +21744,7 @@
       </c>
       <c r="BF12" s="23">
         <f t="shared" si="24"/>
-        <v>1.88235294117647</v>
+        <v>1.77777777777778</v>
       </c>
       <c r="BG12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21764,11 +21776,11 @@
       </c>
       <c r="BN12" s="23">
         <f t="shared" si="28"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BO12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BP12" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21776,11 +21788,11 @@
       </c>
       <c r="BQ12" s="24">
         <f t="shared" si="29"/>
-        <v>6.8</v>
+        <v>14.4</v>
       </c>
       <c r="BR12" s="23">
         <f t="shared" si="30"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="BS12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21800,7 +21812,7 @@
       </c>
       <c r="BW12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BX12" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21808,11 +21820,11 @@
       </c>
       <c r="BY12" s="24">
         <f t="shared" si="33"/>
-        <v>11.3</v>
+        <v>24</v>
       </c>
       <c r="BZ12" s="23">
         <f t="shared" si="34"/>
-        <v>1.41176470588235</v>
+        <v>1.33333333333333</v>
       </c>
       <c r="CA12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21824,11 +21836,11 @@
       </c>
       <c r="CC12" s="24">
         <f t="shared" si="35"/>
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="CD12" s="23">
         <f t="shared" si="36"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="CE12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21840,15 +21852,15 @@
       </c>
       <c r="CG12" s="24">
         <f t="shared" si="37"/>
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="CH12" s="23">
         <f t="shared" si="38"/>
-        <v>2.47058823529412</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="CI12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ12" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21856,7 +21868,7 @@
       </c>
       <c r="CK12" s="24">
         <f t="shared" si="39"/>
-        <v>8.5</v>
+        <v>18</v>
       </c>
       <c r="CL12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21880,11 +21892,11 @@
       </c>
       <c r="CQ12" s="24">
         <f t="shared" si="41"/>
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="CR12" s="25">
         <f t="shared" si="42"/>
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="CS12" s="25">
         <f t="shared" si="43"/>
@@ -21892,7 +21904,7 @@
       </c>
       <c r="CT12" s="25">
         <f t="shared" si="44"/>
-        <v>15.98</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="13" spans="1:98">
@@ -21989,11 +22001,11 @@
       </c>
       <c r="X13" s="24">
         <f t="shared" si="8"/>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="Y13" s="23">
         <f t="shared" si="9"/>
-        <v>1.76470588235294</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="Z13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22037,7 +22049,7 @@
       </c>
       <c r="AJ13" s="24">
         <f t="shared" si="14"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AK13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22061,11 +22073,11 @@
       </c>
       <c r="AP13" s="24">
         <f t="shared" si="16"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AQ13" s="23">
         <f t="shared" si="17"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AR13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22093,11 +22105,11 @@
       </c>
       <c r="AX13" s="24">
         <f t="shared" si="20"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY13" s="23">
         <f t="shared" si="21"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AZ13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22121,11 +22133,11 @@
       </c>
       <c r="BE13" s="24">
         <f t="shared" si="23"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BF13" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22157,7 +22169,7 @@
       </c>
       <c r="BN13" s="23">
         <f t="shared" si="28"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BO13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22201,11 +22213,11 @@
       </c>
       <c r="BY13" s="24">
         <f t="shared" si="33"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BZ13" s="23">
         <f t="shared" si="34"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="CA13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22217,11 +22229,11 @@
       </c>
       <c r="CC13" s="24">
         <f t="shared" si="35"/>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="CD13" s="23">
         <f t="shared" si="36"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="CE13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22233,11 +22245,11 @@
       </c>
       <c r="CG13" s="24">
         <f t="shared" si="37"/>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="CH13" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22273,7 +22285,7 @@
       </c>
       <c r="CQ13" s="24">
         <f t="shared" si="41"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="CR13" s="25">
         <f t="shared" si="42"/>
@@ -22285,7 +22297,7 @@
       </c>
       <c r="CT13" s="25">
         <f t="shared" si="44"/>
-        <v>48.1666666666667</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:98">
@@ -22382,11 +22394,11 @@
       </c>
       <c r="X14" s="24">
         <f t="shared" si="8"/>
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="Y14" s="23">
         <f t="shared" si="9"/>
-        <v>2.05882352941176</v>
+        <v>1.94444444444444</v>
       </c>
       <c r="Z14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22398,11 +22410,11 @@
       </c>
       <c r="AB14" s="24">
         <f t="shared" si="10"/>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="AC14" s="23">
         <f t="shared" si="11"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AD14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22418,7 +22430,7 @@
       </c>
       <c r="AG14" s="23">
         <f t="shared" si="13"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AH14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22442,7 +22454,7 @@
       </c>
       <c r="AM14" s="24">
         <f t="shared" si="15"/>
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AN14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22458,7 +22470,7 @@
       </c>
       <c r="AQ14" s="23">
         <f t="shared" si="17"/>
-        <v>1.76470588235294</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="AR14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22470,11 +22482,11 @@
       </c>
       <c r="AT14" s="24">
         <f t="shared" si="18"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AU14" s="23">
         <f t="shared" si="19"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AV14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22486,11 +22498,11 @@
       </c>
       <c r="AX14" s="24">
         <f t="shared" si="20"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY14" s="23">
         <f t="shared" si="21"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AZ14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22514,11 +22526,11 @@
       </c>
       <c r="BE14" s="24">
         <f t="shared" si="23"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BF14" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22582,23 +22594,23 @@
       </c>
       <c r="BV14" s="23">
         <f t="shared" si="32"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BW14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BX14" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="BY14" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="BY14" s="24">
         <f t="shared" si="33"/>
-        <v/>
+        <v>18</v>
       </c>
       <c r="BZ14" s="23">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="CA14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22610,15 +22622,15 @@
       </c>
       <c r="CC14" s="24">
         <f t="shared" si="35"/>
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="CD14" s="23">
         <f t="shared" si="36"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="CE14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CF14" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -22626,11 +22638,11 @@
       </c>
       <c r="CG14" s="24">
         <f t="shared" si="37"/>
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="CH14" s="23">
         <f t="shared" si="38"/>
-        <v>4.94117647058824</v>
+        <v>4.66666666666667</v>
       </c>
       <c r="CI14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22654,7 +22666,7 @@
       </c>
       <c r="CN14" s="24">
         <f t="shared" si="40"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CO14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22666,19 +22678,19 @@
       </c>
       <c r="CQ14" s="24">
         <f t="shared" si="41"/>
-        <v>22.7</v>
+        <v>24</v>
       </c>
       <c r="CR14" s="25">
         <f t="shared" si="42"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="CS14" s="25">
         <f t="shared" si="43"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="CT14" s="25">
         <f t="shared" si="44"/>
-        <v>17.3777777777778</v>
+        <v>19.1739130434783</v>
       </c>
     </row>
     <row r="15" spans="1:98">
@@ -22767,7 +22779,7 @@
       </c>
       <c r="V15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W15" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -22775,11 +22787,11 @@
       </c>
       <c r="X15" s="24">
         <f t="shared" si="8"/>
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y15" s="23">
         <f t="shared" si="9"/>
-        <v>2.94117647058824</v>
+        <v>2.77777777777778</v>
       </c>
       <c r="Z15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22791,11 +22803,11 @@
       </c>
       <c r="AB15" s="24">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC15" s="23">
         <f t="shared" si="11"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AD15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22815,7 +22827,7 @@
       </c>
       <c r="AH15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI15" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -22823,7 +22835,7 @@
       </c>
       <c r="AJ15" s="24">
         <f t="shared" si="14"/>
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="AK15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22851,11 +22863,11 @@
       </c>
       <c r="AQ15" s="23">
         <f t="shared" si="17"/>
-        <v>1.47058823529412</v>
+        <v>1.38888888888889</v>
       </c>
       <c r="AR15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS15" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -22863,11 +22875,11 @@
       </c>
       <c r="AT15" s="24">
         <f t="shared" si="18"/>
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="AU15" s="23">
         <f t="shared" si="19"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AV15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22879,11 +22891,11 @@
       </c>
       <c r="AX15" s="24">
         <f t="shared" si="20"/>
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AY15" s="23">
         <f t="shared" si="21"/>
-        <v>1.47058823529412</v>
+        <v>1.38888888888889</v>
       </c>
       <c r="AZ15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22899,19 +22911,19 @@
       </c>
       <c r="BC15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD15" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE15" s="24">
         <f t="shared" si="23"/>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BF15" s="23">
         <f t="shared" si="24"/>
-        <v>0.470588235294118</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22927,7 +22939,7 @@
       </c>
       <c r="BJ15" s="23">
         <f t="shared" si="26"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BK15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22943,7 +22955,7 @@
       </c>
       <c r="BN15" s="23">
         <f t="shared" si="28"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BO15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22955,11 +22967,11 @@
       </c>
       <c r="BQ15" s="24">
         <f t="shared" si="29"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BR15" s="23">
         <f t="shared" si="30"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BS15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22971,11 +22983,11 @@
       </c>
       <c r="BU15" s="24">
         <f t="shared" si="31"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BV15" s="23">
         <f t="shared" si="32"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BW15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23003,11 +23015,11 @@
       </c>
       <c r="CC15" s="24">
         <f t="shared" si="35"/>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="CD15" s="23">
         <f t="shared" si="36"/>
-        <v>1.76470588235294</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="CE15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23019,11 +23031,11 @@
       </c>
       <c r="CG15" s="24">
         <f t="shared" si="37"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CH15" s="23">
         <f t="shared" si="38"/>
-        <v>0.823529411764706</v>
+        <v>0.777777777777778</v>
       </c>
       <c r="CI15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23035,11 +23047,11 @@
       </c>
       <c r="CK15" s="24">
         <f t="shared" si="39"/>
-        <v>22.7</v>
+        <v>24</v>
       </c>
       <c r="CL15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM15" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23047,7 +23059,7 @@
       </c>
       <c r="CN15" s="24">
         <f t="shared" si="40"/>
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="CO15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23059,19 +23071,19 @@
       </c>
       <c r="CQ15" s="24">
         <f t="shared" si="41"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CR15" s="25">
         <f t="shared" si="42"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="CS15" s="25">
         <f t="shared" si="43"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="CT15" s="25">
         <f t="shared" si="44"/>
-        <v>10.0847457627119</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="16" spans="1:98">
@@ -23160,7 +23172,7 @@
       </c>
       <c r="V16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W16" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23168,15 +23180,15 @@
       </c>
       <c r="X16" s="24">
         <f t="shared" si="8"/>
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="Y16" s="23">
         <f t="shared" si="9"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="Z16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA16" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23184,11 +23196,11 @@
       </c>
       <c r="AB16" s="24">
         <f t="shared" si="10"/>
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="AC16" s="23">
         <f t="shared" si="11"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AD16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23212,11 +23224,11 @@
       </c>
       <c r="AI16" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ16" s="24">
         <f t="shared" si="14"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AK16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23244,11 +23256,11 @@
       </c>
       <c r="AQ16" s="23">
         <f t="shared" si="17"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AR16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS16" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23256,11 +23268,11 @@
       </c>
       <c r="AT16" s="24">
         <f t="shared" si="18"/>
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="AU16" s="23">
         <f t="shared" si="19"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AV16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23272,11 +23284,11 @@
       </c>
       <c r="AX16" s="24">
         <f t="shared" si="20"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY16" s="23">
         <f t="shared" si="21"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AZ16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23304,7 +23316,7 @@
       </c>
       <c r="BF16" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23340,7 +23352,7 @@
       </c>
       <c r="BO16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP16" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23348,11 +23360,11 @@
       </c>
       <c r="BQ16" s="24">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" s="23">
         <f t="shared" si="30"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="BS16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23372,7 +23384,7 @@
       </c>
       <c r="BW16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BX16" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23380,11 +23392,11 @@
       </c>
       <c r="BY16" s="24">
         <f t="shared" si="33"/>
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="BZ16" s="23">
         <f t="shared" si="34"/>
-        <v>2.82352941176471</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="CA16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23396,15 +23408,15 @@
       </c>
       <c r="CC16" s="24">
         <f t="shared" si="35"/>
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="CD16" s="23">
         <f t="shared" si="36"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="CE16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CF16" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23412,11 +23424,11 @@
       </c>
       <c r="CG16" s="24">
         <f t="shared" si="37"/>
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="CH16" s="23">
         <f t="shared" si="38"/>
-        <v>1.64705882352941</v>
+        <v>1.55555555555556</v>
       </c>
       <c r="CI16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23428,7 +23440,7 @@
       </c>
       <c r="CK16" s="24">
         <f t="shared" si="39"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CL16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23440,7 +23452,7 @@
       </c>
       <c r="CN16" s="24">
         <f t="shared" si="40"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CO16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23452,19 +23464,19 @@
       </c>
       <c r="CQ16" s="24">
         <f t="shared" si="41"/>
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="CR16" s="25">
         <f t="shared" si="42"/>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="CS16" s="25">
         <f t="shared" si="43"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="CT16" s="25">
         <f t="shared" si="44"/>
-        <v>7.80327868852459</v>
+        <v>10.741935483871</v>
       </c>
     </row>
     <row r="17" spans="1:98">
@@ -23561,11 +23573,11 @@
       </c>
       <c r="X17" s="24">
         <f t="shared" si="8"/>
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y17" s="23">
         <f t="shared" si="9"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="Z17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23577,11 +23589,11 @@
       </c>
       <c r="AB17" s="24">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC17" s="23">
         <f t="shared" si="11"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AD17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23609,7 +23621,7 @@
       </c>
       <c r="AJ17" s="24">
         <f t="shared" si="14"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23649,11 +23661,11 @@
       </c>
       <c r="AT17" s="24">
         <f t="shared" si="18"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AU17" s="23">
         <f t="shared" si="19"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AV17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23729,7 +23741,7 @@
       </c>
       <c r="BN17" s="23">
         <f t="shared" si="28"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BO17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23745,7 +23757,7 @@
       </c>
       <c r="BR17" s="23">
         <f t="shared" si="30"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BS17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23789,11 +23801,11 @@
       </c>
       <c r="CC17" s="24">
         <f t="shared" si="35"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CD17" s="23">
         <f t="shared" si="36"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="CE17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23805,11 +23817,11 @@
       </c>
       <c r="CG17" s="24">
         <f t="shared" si="37"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CH17" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23857,7 +23869,7 @@
       </c>
       <c r="CT17" s="25">
         <f t="shared" si="44"/>
-        <v>27.4615384615385</v>
+        <v>29.0769230769231</v>
       </c>
     </row>
     <row r="18" spans="1:98">
@@ -23946,35 +23958,35 @@
       </c>
       <c r="V18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X18" s="24">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y18" s="23">
         <f t="shared" si="9"/>
-        <v>6.47058823529412</v>
+        <v>6.38888888888889</v>
       </c>
       <c r="Z18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA18" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB18" s="24">
         <f t="shared" si="10"/>
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC18" s="23">
         <f t="shared" si="11"/>
-        <v>3.82352941176471</v>
+        <v>3.88888888888889</v>
       </c>
       <c r="AD18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24030,11 +24042,11 @@
       </c>
       <c r="AQ18" s="23">
         <f t="shared" si="17"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AR18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS18" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24042,11 +24054,11 @@
       </c>
       <c r="AT18" s="24">
         <f t="shared" si="18"/>
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="AU18" s="23">
         <f t="shared" si="19"/>
-        <v>1.47058823529412</v>
+        <v>1.38888888888889</v>
       </c>
       <c r="AV18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24058,11 +24070,11 @@
       </c>
       <c r="AX18" s="24">
         <f t="shared" si="20"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AY18" s="23">
         <f t="shared" si="21"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AZ18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24090,7 +24102,7 @@
       </c>
       <c r="BF18" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24122,7 +24134,7 @@
       </c>
       <c r="BN18" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24134,11 +24146,11 @@
       </c>
       <c r="BQ18" s="24">
         <f t="shared" si="29"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BR18" s="23">
         <f t="shared" si="30"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="BS18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24166,27 +24178,27 @@
       </c>
       <c r="BY18" s="24">
         <f t="shared" si="33"/>
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="BZ18" s="23">
         <f t="shared" si="34"/>
-        <v>3.76470588235294</v>
+        <v>3.55555555555556</v>
       </c>
       <c r="CA18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CB18" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CC18" s="24">
         <f t="shared" si="35"/>
-        <v>11.3</v>
+        <v>9.7</v>
       </c>
       <c r="CD18" s="23">
         <f t="shared" si="36"/>
-        <v>3.52941176470588</v>
+        <v>3.61111111111111</v>
       </c>
       <c r="CE18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24198,11 +24210,11 @@
       </c>
       <c r="CG18" s="24">
         <f t="shared" si="37"/>
-        <v>14.9</v>
+        <v>15.8</v>
       </c>
       <c r="CH18" s="23">
         <f t="shared" si="38"/>
-        <v>3.29411764705882</v>
+        <v>3.11111111111111</v>
       </c>
       <c r="CI18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24214,7 +24226,7 @@
       </c>
       <c r="CK18" s="24">
         <f t="shared" si="39"/>
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="CL18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24230,15 +24242,15 @@
       </c>
       <c r="CO18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CP18" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CQ18" s="24">
         <f t="shared" si="41"/>
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="CR18" s="25">
         <f t="shared" si="42"/>
@@ -24246,11 +24258,11 @@
       </c>
       <c r="CS18" s="25">
         <f t="shared" si="43"/>
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="CT18" s="25">
         <f t="shared" si="44"/>
-        <v>9.4622641509434</v>
+        <v>9.56756756756757</v>
       </c>
     </row>
     <row r="19" spans="1:98">
@@ -24347,11 +24359,11 @@
       </c>
       <c r="X19" s="24">
         <f t="shared" si="8"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y19" s="23">
         <f t="shared" si="9"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="Z19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24367,7 +24379,7 @@
       </c>
       <c r="AC19" s="23">
         <f t="shared" si="11"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AD19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24383,7 +24395,7 @@
       </c>
       <c r="AG19" s="23">
         <f t="shared" si="13"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AH19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24419,11 +24431,11 @@
       </c>
       <c r="AP19" s="24">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ19" s="23">
         <f t="shared" si="17"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AR19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24483,7 +24495,7 @@
       </c>
       <c r="BF19" s="23">
         <f t="shared" si="24"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BG19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24515,7 +24527,7 @@
       </c>
       <c r="BN19" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24575,11 +24587,11 @@
       </c>
       <c r="CC19" s="24">
         <f t="shared" si="35"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CD19" s="23">
         <f t="shared" si="36"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="CE19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24591,11 +24603,11 @@
       </c>
       <c r="CG19" s="24">
         <f t="shared" si="37"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CH19" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24643,7 +24655,7 @@
       </c>
       <c r="CT19" s="25">
         <f t="shared" si="44"/>
-        <v>29.3636363636364</v>
+        <v>31.0909090909091</v>
       </c>
     </row>
     <row r="20" spans="1:98">
@@ -24684,11 +24696,11 @@
       </c>
       <c r="J20" s="24">
         <f t="shared" si="2"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="K20" s="23">
         <f t="shared" si="3"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="L20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24732,23 +24744,23 @@
       </c>
       <c r="V20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X20" s="24">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="Y20" s="23">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>5.27777777777778</v>
       </c>
       <c r="Z20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24756,11 +24768,11 @@
       </c>
       <c r="AB20" s="24">
         <f t="shared" si="10"/>
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="AC20" s="23">
         <f t="shared" si="11"/>
-        <v>4.70588235294118</v>
+        <v>4.44444444444444</v>
       </c>
       <c r="AD20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24776,7 +24788,7 @@
       </c>
       <c r="AG20" s="23">
         <f t="shared" si="13"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AH20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24812,15 +24824,15 @@
       </c>
       <c r="AP20" s="24">
         <f t="shared" si="16"/>
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ20" s="23">
         <f t="shared" si="17"/>
-        <v>1.76470588235294</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="AR20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24828,15 +24840,15 @@
       </c>
       <c r="AT20" s="24">
         <f t="shared" si="18"/>
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="AU20" s="23">
         <f t="shared" si="19"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AV20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24844,11 +24856,11 @@
       </c>
       <c r="AX20" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY20" s="23">
         <f t="shared" si="21"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AZ20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24872,11 +24884,11 @@
       </c>
       <c r="BE20" s="24">
         <f t="shared" si="23"/>
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="BF20" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24920,11 +24932,11 @@
       </c>
       <c r="BQ20" s="24">
         <f t="shared" si="29"/>
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="BR20" s="23">
         <f t="shared" si="30"/>
-        <v>1.88235294117647</v>
+        <v>1.77777777777778</v>
       </c>
       <c r="BS20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24952,11 +24964,11 @@
       </c>
       <c r="BY20" s="24">
         <f t="shared" si="33"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BZ20" s="23">
         <f t="shared" si="34"/>
-        <v>1.41176470588235</v>
+        <v>1.33333333333333</v>
       </c>
       <c r="CA20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24968,11 +24980,11 @@
       </c>
       <c r="CC20" s="24">
         <f t="shared" si="35"/>
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="CD20" s="23">
         <f t="shared" si="36"/>
-        <v>2.94117647058824</v>
+        <v>2.77777777777778</v>
       </c>
       <c r="CE20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24984,11 +24996,11 @@
       </c>
       <c r="CG20" s="24">
         <f t="shared" si="37"/>
-        <v>29.1</v>
+        <v>30.9</v>
       </c>
       <c r="CH20" s="23">
         <f t="shared" si="38"/>
-        <v>2.88235294117647</v>
+        <v>2.72222222222222</v>
       </c>
       <c r="CI20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25000,7 +25012,7 @@
       </c>
       <c r="CK20" s="24">
         <f t="shared" si="39"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="CL20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25016,27 +25028,27 @@
       </c>
       <c r="CO20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CP20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CQ20" s="24">
         <f t="shared" si="41"/>
-        <v>9.1</v>
+        <v>7.9</v>
       </c>
       <c r="CR20" s="25">
         <f t="shared" si="42"/>
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="CS20" s="25">
         <f t="shared" si="43"/>
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="CT20" s="25">
         <f t="shared" si="44"/>
-        <v>8.72566371681416</v>
+        <v>10.0862068965517</v>
       </c>
     </row>
     <row r="21" spans="1:98">
@@ -25133,11 +25145,11 @@
       </c>
       <c r="X21" s="24">
         <f t="shared" si="8"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y21" s="23">
         <f t="shared" si="9"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="Z21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25149,11 +25161,11 @@
       </c>
       <c r="AB21" s="24">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC21" s="23">
         <f t="shared" si="11"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AD21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25181,7 +25193,7 @@
       </c>
       <c r="AJ21" s="24">
         <f t="shared" si="14"/>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="AK21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25193,7 +25205,7 @@
       </c>
       <c r="AM21" s="24">
         <f t="shared" si="15"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AN21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25205,11 +25217,11 @@
       </c>
       <c r="AP21" s="24">
         <f t="shared" si="16"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ21" s="23">
         <f t="shared" si="17"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AR21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25237,11 +25249,11 @@
       </c>
       <c r="AX21" s="24">
         <f t="shared" si="20"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY21" s="23">
         <f t="shared" si="21"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AZ21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25265,11 +25277,11 @@
       </c>
       <c r="BE21" s="24">
         <f t="shared" si="23"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="BF21" s="23">
         <f t="shared" si="24"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BG21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25345,11 +25357,11 @@
       </c>
       <c r="BY21" s="24">
         <f t="shared" si="33"/>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="BZ21" s="23">
         <f t="shared" si="34"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="CA21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25417,7 +25429,7 @@
       </c>
       <c r="CQ21" s="24">
         <f t="shared" si="41"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="CR21" s="25">
         <f t="shared" si="42"/>
@@ -25429,7 +25441,7 @@
       </c>
       <c r="CT21" s="25">
         <f t="shared" si="44"/>
-        <v>53.6153846153846</v>
+        <v>56.7692307692308</v>
       </c>
     </row>
     <row r="22" spans="1:98">
@@ -25474,7 +25486,7 @@
       </c>
       <c r="K22" s="23">
         <f t="shared" si="3"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="L22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25518,19 +25530,19 @@
       </c>
       <c r="V22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W22" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X22" s="24">
         <f t="shared" si="8"/>
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y22" s="23">
         <f t="shared" si="9"/>
-        <v>11.7647058823529</v>
+        <v>11.3888888888889</v>
       </c>
       <c r="Z22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25542,11 +25554,11 @@
       </c>
       <c r="AB22" s="24">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="AC22" s="23">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>4.72222222222222</v>
       </c>
       <c r="AD22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25558,11 +25570,11 @@
       </c>
       <c r="AF22" s="24">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG22" s="23">
         <f t="shared" si="13"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AH22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25574,7 +25586,7 @@
       </c>
       <c r="AJ22" s="24">
         <f t="shared" si="14"/>
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="AK22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25602,11 +25614,11 @@
       </c>
       <c r="AQ22" s="23">
         <f t="shared" si="17"/>
-        <v>2.64705882352941</v>
+        <v>2.5</v>
       </c>
       <c r="AR22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS22" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25614,11 +25626,11 @@
       </c>
       <c r="AT22" s="24">
         <f t="shared" si="18"/>
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU22" s="23">
         <f t="shared" si="19"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AV22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25630,11 +25642,11 @@
       </c>
       <c r="AX22" s="24">
         <f t="shared" si="20"/>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="AY22" s="23">
         <f t="shared" si="21"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AZ22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25662,7 +25674,7 @@
       </c>
       <c r="BF22" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25694,23 +25706,23 @@
       </c>
       <c r="BN22" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BP22" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BQ22" s="24">
         <f t="shared" si="29"/>
-        <v>17</v>
+        <v>10.8</v>
       </c>
       <c r="BR22" s="23">
         <f t="shared" si="30"/>
-        <v>1.88235294117647</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="BS22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25738,31 +25750,31 @@
       </c>
       <c r="BY22" s="24">
         <f t="shared" si="33"/>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="BZ22" s="23">
         <f t="shared" si="34"/>
-        <v>2.82352941176471</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="CA22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CB22" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CC22" s="24">
         <f t="shared" si="35"/>
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="CD22" s="23">
         <f t="shared" si="36"/>
-        <v>5.29411764705882</v>
+        <v>5.27777777777778</v>
       </c>
       <c r="CE22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CF22" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25770,11 +25782,11 @@
       </c>
       <c r="CG22" s="24">
         <f t="shared" si="37"/>
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="CH22" s="23">
         <f t="shared" si="38"/>
-        <v>7</v>
+        <v>6.61111111111111</v>
       </c>
       <c r="CI22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25786,7 +25798,7 @@
       </c>
       <c r="CK22" s="24">
         <f t="shared" si="39"/>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="CL22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25798,31 +25810,31 @@
       </c>
       <c r="CN22" s="24">
         <f t="shared" si="40"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CO22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CP22" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CQ22" s="24">
         <f t="shared" si="41"/>
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="CR22" s="25">
         <f t="shared" si="42"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="CS22" s="25">
         <f t="shared" si="43"/>
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="CT22" s="25">
         <f t="shared" si="44"/>
-        <v>6.42682926829268</v>
+        <v>6.85714285714286</v>
       </c>
     </row>
     <row r="23" spans="1:98">
@@ -25855,19 +25867,19 @@
       </c>
       <c r="H23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="J23" s="24">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K23" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="L23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25911,19 +25923,19 @@
       </c>
       <c r="V23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="X23" s="24">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="Y23" s="23">
         <f t="shared" si="9"/>
-        <v>6.17647058823529</v>
+        <v>6.38888888888889</v>
       </c>
       <c r="Z23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25935,11 +25947,11 @@
       </c>
       <c r="AB23" s="24">
         <f t="shared" si="10"/>
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="AC23" s="23">
         <f t="shared" si="11"/>
-        <v>3.82352941176471</v>
+        <v>3.61111111111111</v>
       </c>
       <c r="AD23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25951,15 +25963,15 @@
       </c>
       <c r="AF23" s="24">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG23" s="23">
         <f t="shared" si="13"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AH23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25967,7 +25979,7 @@
       </c>
       <c r="AJ23" s="24">
         <f t="shared" si="14"/>
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="AK23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25991,11 +26003,11 @@
       </c>
       <c r="AP23" s="24">
         <f t="shared" si="16"/>
-        <v>9.7</v>
+        <v>10.3</v>
       </c>
       <c r="AQ23" s="23">
         <f t="shared" si="17"/>
-        <v>2.05882352941176</v>
+        <v>1.94444444444444</v>
       </c>
       <c r="AR23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26007,15 +26019,15 @@
       </c>
       <c r="AT23" s="24">
         <f t="shared" si="18"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AU23" s="23">
         <f t="shared" si="19"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AV23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26023,11 +26035,11 @@
       </c>
       <c r="AX23" s="24">
         <f t="shared" si="20"/>
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="AY23" s="23">
         <f t="shared" si="21"/>
-        <v>2.64705882352941</v>
+        <v>2.5</v>
       </c>
       <c r="AZ23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26043,7 +26055,7 @@
       </c>
       <c r="BC23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26051,11 +26063,11 @@
       </c>
       <c r="BE23" s="24">
         <f t="shared" si="23"/>
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF23" s="23">
         <f t="shared" si="24"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="BG23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26087,7 +26099,7 @@
       </c>
       <c r="BN23" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26099,11 +26111,11 @@
       </c>
       <c r="BQ23" s="24">
         <f t="shared" si="29"/>
-        <v>23.8</v>
+        <v>25.2</v>
       </c>
       <c r="BR23" s="23">
         <f t="shared" si="30"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="BS23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26123,51 +26135,51 @@
       </c>
       <c r="BW23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BX23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY23" s="24">
         <f t="shared" si="33"/>
-        <v>34</v>
+        <v>22.5</v>
       </c>
       <c r="BZ23" s="23">
         <f t="shared" si="34"/>
-        <v>1.41176470588235</v>
+        <v>1.77777777777778</v>
       </c>
       <c r="CA23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CB23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CC23" s="24">
         <f t="shared" si="35"/>
-        <v>12.8</v>
+        <v>11.1</v>
       </c>
       <c r="CD23" s="23">
         <f t="shared" si="36"/>
-        <v>3.52941176470588</v>
+        <v>3.61111111111111</v>
       </c>
       <c r="CE23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CF23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="CG23" s="24">
         <f t="shared" si="37"/>
-        <v>9.2</v>
+        <v>3.2</v>
       </c>
       <c r="CH23" s="23">
         <f t="shared" si="38"/>
-        <v>5.35294117647059</v>
+        <v>6.61111111111111</v>
       </c>
       <c r="CI23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26179,11 +26191,11 @@
       </c>
       <c r="CK23" s="24">
         <f t="shared" si="39"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26191,19 +26203,19 @@
       </c>
       <c r="CN23" s="24">
         <f t="shared" si="40"/>
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="CO23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CP23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CQ23" s="24">
         <f t="shared" si="41"/>
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="CR23" s="25">
         <f t="shared" si="42"/>
@@ -26211,11 +26223,11 @@
       </c>
       <c r="CS23" s="25">
         <f t="shared" si="43"/>
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="CT23" s="25">
         <f t="shared" si="44"/>
-        <v>8.5</v>
+        <v>8.39189189189189</v>
       </c>
     </row>
     <row r="24" spans="1:98">
@@ -26304,19 +26316,19 @@
       </c>
       <c r="V24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W24" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X24" s="24">
         <f t="shared" si="8"/>
-        <v>12.8</v>
+        <v>7.2</v>
       </c>
       <c r="Y24" s="23">
         <f t="shared" si="9"/>
-        <v>1.17647058823529</v>
+        <v>1.38888888888889</v>
       </c>
       <c r="Z24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26328,11 +26340,11 @@
       </c>
       <c r="AB24" s="24">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC24" s="23">
         <f t="shared" si="11"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AD24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26384,11 +26396,11 @@
       </c>
       <c r="AP24" s="24">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ24" s="23">
         <f t="shared" si="17"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AR24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26448,7 +26460,7 @@
       </c>
       <c r="BF24" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26480,7 +26492,7 @@
       </c>
       <c r="BN24" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26492,11 +26504,11 @@
       </c>
       <c r="BQ24" s="24">
         <f t="shared" si="29"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BR24" s="23">
         <f t="shared" si="30"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BS24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26540,11 +26552,11 @@
       </c>
       <c r="CC24" s="24">
         <f t="shared" si="35"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CD24" s="23">
         <f t="shared" si="36"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="CE24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26572,7 +26584,7 @@
       </c>
       <c r="CK24" s="24">
         <f t="shared" si="39"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26584,7 +26596,7 @@
       </c>
       <c r="CN24" s="24">
         <f t="shared" si="40"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CO24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26596,19 +26608,19 @@
       </c>
       <c r="CQ24" s="24">
         <f t="shared" si="41"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CR24" s="25">
         <f t="shared" si="42"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CS24" s="25">
         <f t="shared" si="43"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT24" s="25">
         <f t="shared" si="44"/>
-        <v>27.2</v>
+        <v>26.5714285714286</v>
       </c>
     </row>
     <row r="25" spans="1:98">
@@ -26629,15 +26641,15 @@
       </c>
       <c r="E25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+1T|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+1T|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="G25" s="24">
         <f t="shared" si="1"/>
-        <v/>
+        <v>18</v>
       </c>
       <c r="H25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26705,15 +26717,15 @@
       </c>
       <c r="X25" s="24">
         <f t="shared" si="8"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y25" s="23">
         <f t="shared" si="9"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="Z25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA25" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26721,11 +26733,11 @@
       </c>
       <c r="AB25" s="24">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AC25" s="23">
         <f t="shared" si="11"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AD25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26753,7 +26765,7 @@
       </c>
       <c r="AJ25" s="24">
         <f t="shared" si="14"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AK25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26777,11 +26789,11 @@
       </c>
       <c r="AP25" s="24">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ25" s="23">
         <f t="shared" si="17"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AR25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26857,7 +26869,7 @@
       </c>
       <c r="BJ25" s="23">
         <f t="shared" si="26"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BK25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26873,7 +26885,7 @@
       </c>
       <c r="BN25" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26925,7 +26937,7 @@
       </c>
       <c r="CA25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB25" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26933,15 +26945,15 @@
       </c>
       <c r="CC25" s="24">
         <f t="shared" si="35"/>
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="CD25" s="23">
         <f t="shared" si="36"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="CE25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CF25" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26949,11 +26961,11 @@
       </c>
       <c r="CG25" s="24">
         <f t="shared" si="37"/>
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="CH25" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26965,7 +26977,7 @@
       </c>
       <c r="CK25" s="24">
         <f t="shared" si="39"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CL25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26977,7 +26989,7 @@
       </c>
       <c r="CN25" s="24">
         <f t="shared" si="40"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CO25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26993,15 +27005,15 @@
       </c>
       <c r="CR25" s="25">
         <f t="shared" si="42"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CS25" s="25">
         <f t="shared" si="43"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CT25" s="25">
         <f t="shared" si="44"/>
-        <v>18.6190476190476</v>
+        <v>20.4545454545455</v>
       </c>
     </row>
     <row r="26" spans="1:98">
@@ -27098,11 +27110,11 @@
       </c>
       <c r="X26" s="24">
         <f t="shared" si="8"/>
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="Y26" s="23">
         <f t="shared" si="9"/>
-        <v>2.35294117647059</v>
+        <v>2.22222222222222</v>
       </c>
       <c r="Z26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27114,11 +27126,11 @@
       </c>
       <c r="AB26" s="24">
         <f t="shared" si="10"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AC26" s="23">
         <f t="shared" si="11"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AD26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27138,15 +27150,15 @@
       </c>
       <c r="AH26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ26" s="24">
         <f t="shared" si="14"/>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27154,11 +27166,11 @@
       </c>
       <c r="AL26" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM26" s="24">
         <f t="shared" si="15"/>
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AN26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27170,11 +27182,11 @@
       </c>
       <c r="AP26" s="24">
         <f t="shared" si="16"/>
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ26" s="23">
         <f t="shared" si="17"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AR26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27202,11 +27214,11 @@
       </c>
       <c r="AX26" s="24">
         <f t="shared" si="20"/>
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AY26" s="23">
         <f t="shared" si="21"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AZ26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27230,11 +27242,11 @@
       </c>
       <c r="BE26" s="24">
         <f t="shared" si="23"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="BF26" s="23">
         <f t="shared" si="24"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BG26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27266,7 +27278,7 @@
       </c>
       <c r="BN26" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27278,11 +27290,11 @@
       </c>
       <c r="BQ26" s="24">
         <f t="shared" si="29"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BR26" s="23">
         <f t="shared" si="30"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BS26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27294,11 +27306,11 @@
       </c>
       <c r="BU26" s="24">
         <f t="shared" si="31"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BV26" s="23">
         <f t="shared" si="32"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BW26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27314,7 +27326,7 @@
       </c>
       <c r="BZ26" s="23">
         <f t="shared" si="34"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="CA26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27326,11 +27338,11 @@
       </c>
       <c r="CC26" s="24">
         <f t="shared" si="35"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CD26" s="23">
         <f t="shared" si="36"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="CE26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27342,11 +27354,11 @@
       </c>
       <c r="CG26" s="24">
         <f t="shared" si="37"/>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="CH26" s="23">
         <f t="shared" si="38"/>
-        <v>1.23529411764706</v>
+        <v>1.16666666666667</v>
       </c>
       <c r="CI26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27370,7 +27382,7 @@
       </c>
       <c r="CN26" s="24">
         <f t="shared" si="40"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CO26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27382,19 +27394,19 @@
       </c>
       <c r="CQ26" s="24">
         <f t="shared" si="41"/>
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="CR26" s="25">
         <f t="shared" si="42"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CS26" s="25">
         <f t="shared" si="43"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="CT26" s="25">
         <f t="shared" si="44"/>
-        <v>14.5714285714286</v>
+        <v>14.1081081081081</v>
       </c>
     </row>
     <row r="27" spans="1:98">
@@ -27491,11 +27503,11 @@
       </c>
       <c r="X27" s="24">
         <f t="shared" si="8"/>
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y27" s="23">
         <f t="shared" si="9"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="Z27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27507,11 +27519,11 @@
       </c>
       <c r="AB27" s="24">
         <f t="shared" si="10"/>
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AC27" s="23">
         <f t="shared" si="11"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AD27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27539,19 +27551,19 @@
       </c>
       <c r="AJ27" s="24">
         <f t="shared" si="14"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL27" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM27" s="24">
         <f t="shared" si="15"/>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AN27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27567,7 +27579,7 @@
       </c>
       <c r="AQ27" s="23">
         <f t="shared" si="17"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AR27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27579,11 +27591,11 @@
       </c>
       <c r="AT27" s="24">
         <f t="shared" si="18"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AU27" s="23">
         <f t="shared" si="19"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AV27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27623,11 +27635,11 @@
       </c>
       <c r="BE27" s="24">
         <f t="shared" si="23"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BF27" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27659,7 +27671,7 @@
       </c>
       <c r="BN27" s="23">
         <f t="shared" si="28"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BO27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27707,7 +27719,7 @@
       </c>
       <c r="BZ27" s="23">
         <f t="shared" si="34"/>
-        <v>1.41176470588235</v>
+        <v>1.33333333333333</v>
       </c>
       <c r="CA27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27735,11 +27747,11 @@
       </c>
       <c r="CG27" s="24">
         <f t="shared" si="37"/>
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="CH27" s="23">
         <f t="shared" si="38"/>
-        <v>0.823529411764706</v>
+        <v>0.777777777777778</v>
       </c>
       <c r="CI27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27763,31 +27775,31 @@
       </c>
       <c r="CN27" s="24">
         <f t="shared" si="40"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CO27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP27" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CQ27" s="24">
         <f t="shared" si="41"/>
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="CR27" s="25">
         <f t="shared" si="42"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="CS27" s="25">
         <f t="shared" si="43"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CT27" s="25">
         <f t="shared" si="44"/>
-        <v>18.3076923076923</v>
+        <v>16.7142857142857</v>
       </c>
     </row>
     <row r="28" spans="1:98">
@@ -27828,11 +27840,11 @@
       </c>
       <c r="J28" s="24">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K28" s="23">
         <f t="shared" si="3"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="L28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27884,11 +27896,11 @@
       </c>
       <c r="X28" s="24">
         <f t="shared" si="8"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Y28" s="23">
         <f t="shared" si="9"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="Z28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27900,11 +27912,11 @@
       </c>
       <c r="AB28" s="24">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC28" s="23">
         <f t="shared" si="11"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AD28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27944,7 +27956,7 @@
       </c>
       <c r="AM28" s="24">
         <f t="shared" si="15"/>
-        <v>22.7</v>
+        <v>24</v>
       </c>
       <c r="AN28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27956,11 +27968,11 @@
       </c>
       <c r="AP28" s="24">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ28" s="23">
         <f t="shared" si="17"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AR28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28016,11 +28028,11 @@
       </c>
       <c r="BE28" s="24">
         <f t="shared" si="23"/>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="BF28" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28052,7 +28064,7 @@
       </c>
       <c r="BN28" s="23">
         <f t="shared" si="28"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BO28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28064,11 +28076,11 @@
       </c>
       <c r="BQ28" s="24">
         <f t="shared" si="29"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="BR28" s="23">
         <f t="shared" si="30"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BS28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28084,11 +28096,11 @@
       </c>
       <c r="BV28" s="23">
         <f t="shared" si="32"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BW28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BX28" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28096,15 +28108,15 @@
       </c>
       <c r="BY28" s="24">
         <f t="shared" si="33"/>
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="BZ28" s="23">
         <f t="shared" si="34"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="CA28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CB28" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28112,15 +28124,15 @@
       </c>
       <c r="CC28" s="24">
         <f t="shared" si="35"/>
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="CD28" s="23">
         <f t="shared" si="36"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="CE28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CF28" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28128,11 +28140,11 @@
       </c>
       <c r="CG28" s="24">
         <f t="shared" si="37"/>
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="CH28" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28168,11 +28180,11 @@
       </c>
       <c r="CQ28" s="24">
         <f t="shared" si="41"/>
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CR28" s="25">
         <f t="shared" si="42"/>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="CS28" s="25">
         <f t="shared" si="43"/>
@@ -28180,7 +28192,7 @@
       </c>
       <c r="CT28" s="25">
         <f t="shared" si="44"/>
-        <v>34.7083333333333</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="29" spans="1:98">
@@ -28221,11 +28233,11 @@
       </c>
       <c r="J29" s="24">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K29" s="23">
         <f t="shared" si="3"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="L29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28269,19 +28281,19 @@
       </c>
       <c r="V29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W29" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X29" s="24">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Y29" s="23">
         <f t="shared" si="9"/>
-        <v>0.588235294117647</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="Z29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28293,11 +28305,11 @@
       </c>
       <c r="AB29" s="24">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC29" s="23">
         <f t="shared" si="11"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AD29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28337,7 +28349,7 @@
       </c>
       <c r="AM29" s="24">
         <f t="shared" si="15"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AN29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28409,11 +28421,11 @@
       </c>
       <c r="BE29" s="24">
         <f t="shared" si="23"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="BF29" s="23">
         <f t="shared" si="24"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BG29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28497,7 +28509,7 @@
       </c>
       <c r="CA29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CB29" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28505,15 +28517,15 @@
       </c>
       <c r="CC29" s="24">
         <f t="shared" si="35"/>
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="CD29" s="23">
         <f t="shared" si="36"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="CE29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CF29" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28521,11 +28533,11 @@
       </c>
       <c r="CG29" s="24">
         <f t="shared" si="37"/>
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="CH29" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28549,7 +28561,7 @@
       </c>
       <c r="CN29" s="24">
         <f t="shared" si="40"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="CO29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28561,19 +28573,19 @@
       </c>
       <c r="CQ29" s="24">
         <f t="shared" si="41"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CR29" s="25">
         <f t="shared" si="42"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="CS29" s="25">
         <f t="shared" si="43"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CT29" s="25">
         <f t="shared" si="44"/>
-        <v>78.2</v>
+        <v>76.9090909090909</v>
       </c>
     </row>
     <row r="30" spans="1:98">
@@ -28718,7 +28730,7 @@
       </c>
       <c r="AJ30" s="24">
         <f t="shared" si="14"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AK30" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28746,7 +28758,7 @@
       </c>
       <c r="AQ30" s="23">
         <f t="shared" si="17"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AR30" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28898,11 +28910,11 @@
       </c>
       <c r="CC30" s="24">
         <f t="shared" si="35"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CD30" s="23">
         <f t="shared" si="36"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="CE30" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28930,7 +28942,7 @@
       </c>
       <c r="CK30" s="24">
         <f t="shared" si="39"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL30" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28966,7 +28978,7 @@
       </c>
       <c r="CT30" s="25">
         <f t="shared" si="44"/>
-        <v>97.75</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="31" spans="1:98">
@@ -29063,11 +29075,11 @@
       </c>
       <c r="X31" s="24">
         <f t="shared" si="8"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y31" s="23">
         <f t="shared" si="9"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="Z31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29079,11 +29091,11 @@
       </c>
       <c r="AB31" s="24">
         <f t="shared" si="10"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AC31" s="23">
         <f t="shared" si="11"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AD31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29095,11 +29107,11 @@
       </c>
       <c r="AF31" s="24">
         <f t="shared" si="12"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG31" s="23">
         <f t="shared" si="13"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AH31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29123,7 +29135,7 @@
       </c>
       <c r="AM31" s="24">
         <f t="shared" si="15"/>
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AN31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29139,7 +29151,7 @@
       </c>
       <c r="AQ31" s="23">
         <f t="shared" si="17"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="AR31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29231,7 +29243,7 @@
       </c>
       <c r="BN31" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29243,11 +29255,11 @@
       </c>
       <c r="BQ31" s="24">
         <f t="shared" si="29"/>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="BR31" s="23">
         <f t="shared" si="30"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BS31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29275,11 +29287,11 @@
       </c>
       <c r="BY31" s="24">
         <f t="shared" si="33"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BZ31" s="23">
         <f t="shared" si="34"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="CA31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29307,11 +29319,11 @@
       </c>
       <c r="CG31" s="24">
         <f t="shared" si="37"/>
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="CH31" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29323,7 +29335,7 @@
       </c>
       <c r="CK31" s="24">
         <f t="shared" si="39"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="CL31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29347,7 +29359,7 @@
       </c>
       <c r="CQ31" s="24">
         <f t="shared" si="41"/>
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="CR31" s="25">
         <f t="shared" si="42"/>
@@ -29359,7 +29371,7 @@
       </c>
       <c r="CT31" s="25">
         <f t="shared" si="44"/>
-        <v>40.4761904761905</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="32" spans="1:98">
@@ -29388,7 +29400,7 @@
       </c>
       <c r="G32" s="24">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29400,11 +29412,11 @@
       </c>
       <c r="J32" s="24">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K32" s="23">
         <f t="shared" si="3"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="L32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29456,11 +29468,11 @@
       </c>
       <c r="X32" s="24">
         <f t="shared" si="8"/>
-        <v>22.7</v>
+        <v>24</v>
       </c>
       <c r="Y32" s="23">
         <f t="shared" si="9"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="Z32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29472,11 +29484,11 @@
       </c>
       <c r="AB32" s="24">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC32" s="23">
         <f t="shared" si="11"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AD32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29516,7 +29528,7 @@
       </c>
       <c r="AM32" s="24">
         <f t="shared" si="15"/>
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AN32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29528,11 +29540,11 @@
       </c>
       <c r="AP32" s="24">
         <f t="shared" si="16"/>
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ32" s="23">
         <f t="shared" si="17"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AR32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29564,7 +29576,7 @@
       </c>
       <c r="AY32" s="23">
         <f t="shared" si="21"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AZ32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29588,11 +29600,11 @@
       </c>
       <c r="BE32" s="24">
         <f t="shared" si="23"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF32" s="23">
         <f t="shared" si="24"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BG32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29656,7 +29668,7 @@
       </c>
       <c r="BV32" s="23">
         <f t="shared" si="32"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BW32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29684,11 +29696,11 @@
       </c>
       <c r="CC32" s="24">
         <f t="shared" si="35"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CD32" s="23">
         <f t="shared" si="36"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="CE32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29700,11 +29712,11 @@
       </c>
       <c r="CG32" s="24">
         <f t="shared" si="37"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CH32" s="23">
         <f t="shared" si="38"/>
-        <v>0.823529411764706</v>
+        <v>0.777777777777778</v>
       </c>
       <c r="CI32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29716,7 +29728,7 @@
       </c>
       <c r="CK32" s="24">
         <f t="shared" si="39"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CL32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29728,7 +29740,7 @@
       </c>
       <c r="CN32" s="24">
         <f t="shared" si="40"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CO32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29740,7 +29752,7 @@
       </c>
       <c r="CQ32" s="24">
         <f t="shared" si="41"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CR32" s="25">
         <f t="shared" si="42"/>
@@ -29752,7 +29764,7 @@
       </c>
       <c r="CT32" s="25">
         <f t="shared" si="44"/>
-        <v>29.24</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="33" spans="1:98">
@@ -29849,11 +29861,11 @@
       </c>
       <c r="X33" s="24">
         <f t="shared" si="8"/>
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="Y33" s="23">
         <f t="shared" si="9"/>
-        <v>1.76470588235294</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="Z33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29865,11 +29877,11 @@
       </c>
       <c r="AB33" s="24">
         <f t="shared" si="10"/>
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="AC33" s="23">
         <f t="shared" si="11"/>
-        <v>0.882352941176471</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AD33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29889,15 +29901,15 @@
       </c>
       <c r="AH33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI33" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="AJ33" s="24">
         <f t="shared" si="14"/>
-        <v/>
+        <v>72</v>
       </c>
       <c r="AK33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29909,7 +29921,7 @@
       </c>
       <c r="AM33" s="24">
         <f t="shared" si="15"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AN33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29921,11 +29933,11 @@
       </c>
       <c r="AP33" s="24">
         <f t="shared" si="16"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AQ33" s="23">
         <f t="shared" si="17"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="AR33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29937,11 +29949,11 @@
       </c>
       <c r="AT33" s="24">
         <f t="shared" si="18"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU33" s="23">
         <f t="shared" si="19"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AV33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30017,7 +30029,7 @@
       </c>
       <c r="BN33" s="23">
         <f t="shared" si="28"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BO33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30077,11 +30089,11 @@
       </c>
       <c r="CC33" s="24">
         <f t="shared" si="35"/>
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="CD33" s="23">
         <f t="shared" si="36"/>
-        <v>1.47058823529412</v>
+        <v>1.38888888888889</v>
       </c>
       <c r="CE33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30093,11 +30105,11 @@
       </c>
       <c r="CG33" s="24">
         <f t="shared" si="37"/>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="CH33" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30109,7 +30121,7 @@
       </c>
       <c r="CK33" s="24">
         <f t="shared" si="39"/>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="CL33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30121,7 +30133,7 @@
       </c>
       <c r="CN33" s="24">
         <f t="shared" si="40"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="CO33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30133,19 +30145,19 @@
       </c>
       <c r="CQ33" s="24">
         <f t="shared" si="41"/>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="CR33" s="25">
         <f t="shared" si="42"/>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CS33" s="25">
         <f t="shared" si="43"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CT33" s="25">
         <f t="shared" si="44"/>
-        <v>36.04</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:98">
@@ -30186,11 +30198,11 @@
       </c>
       <c r="J34" s="24">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K34" s="23">
         <f t="shared" si="3"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="L34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30242,11 +30254,11 @@
       </c>
       <c r="X34" s="24">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y34" s="23">
         <f t="shared" si="9"/>
-        <v>0.588235294117647</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="Z34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30258,11 +30270,11 @@
       </c>
       <c r="AB34" s="24">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC34" s="23">
         <f t="shared" si="11"/>
-        <v>0.294117647058824</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AD34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30302,23 +30314,23 @@
       </c>
       <c r="AM34" s="24">
         <f t="shared" si="15"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AN34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO34" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AP34" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="AP34" s="24">
         <f t="shared" si="16"/>
-        <v/>
+        <v>36</v>
       </c>
       <c r="AQ34" s="23">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="AR34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30374,11 +30386,11 @@
       </c>
       <c r="BE34" s="24">
         <f t="shared" si="23"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BF34" s="23">
         <f t="shared" si="24"/>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BG34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30410,7 +30422,7 @@
       </c>
       <c r="BN34" s="23">
         <f t="shared" si="28"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BO34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30422,27 +30434,27 @@
       </c>
       <c r="BQ34" s="24">
         <f t="shared" si="29"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BR34" s="23">
         <f t="shared" si="30"/>
-        <v>0.470588235294118</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BS34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT34" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="BU34" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="BU34" s="24">
         <f t="shared" si="31"/>
-        <v/>
+        <v>18</v>
       </c>
       <c r="BV34" s="23">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="BW34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30470,11 +30482,11 @@
       </c>
       <c r="CC34" s="24">
         <f t="shared" si="35"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="CD34" s="23">
         <f t="shared" si="36"/>
-        <v>1.17647058823529</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="CE34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30486,11 +30498,11 @@
       </c>
       <c r="CG34" s="24">
         <f t="shared" si="37"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="CH34" s="23">
         <f t="shared" si="38"/>
-        <v>0.411764705882353</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="CI34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30514,7 +30526,7 @@
       </c>
       <c r="CN34" s="24">
         <f t="shared" si="40"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CO34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30526,19 +30538,19 @@
       </c>
       <c r="CQ34" s="24">
         <f t="shared" si="41"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CR34" s="25">
         <f t="shared" si="42"/>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="CS34" s="25">
         <f t="shared" si="43"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CT34" s="25">
         <f t="shared" si="44"/>
-        <v>35.0625</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:98">
@@ -30559,15 +30571,15 @@
       </c>
       <c r="E35" s="27">
         <f t="shared" si="45"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" s="28">
         <f t="shared" si="45"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="24">
         <f t="shared" si="1"/>
-        <v>161.5</v>
+        <v>108</v>
       </c>
       <c r="H35" s="27">
         <f t="shared" ref="H35:M35" si="46">SUM(H7:H34)</f>
@@ -30575,15 +30587,15 @@
       </c>
       <c r="I35" s="28">
         <f t="shared" si="46"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J35" s="24">
         <f t="shared" si="2"/>
-        <v>37.9</v>
+        <v>37.3</v>
       </c>
       <c r="K35" s="28">
         <f t="shared" si="46"/>
-        <v>7.64705882352941</v>
+        <v>7.77777777777778</v>
       </c>
       <c r="L35" s="27">
         <f t="shared" si="46"/>
@@ -30627,95 +30639,95 @@
       </c>
       <c r="V35" s="27">
         <f t="shared" si="48"/>
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="W35" s="28">
         <f t="shared" si="48"/>
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="X35" s="24">
         <f t="shared" si="8"/>
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="Y35" s="28">
         <f t="shared" ref="Y35:AA35" si="49">SUM(Y7:Y34)</f>
-        <v>76.764705882353</v>
+        <v>75.8333333333333</v>
       </c>
       <c r="Z35" s="27">
         <f t="shared" si="49"/>
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="AA35" s="28">
         <f t="shared" si="49"/>
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AB35" s="24">
         <f t="shared" si="10"/>
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="AC35" s="28">
         <f t="shared" ref="AC35:AE35" si="50">SUM(AC7:AC34)</f>
-        <v>47.3529411764706</v>
+        <v>46.1111111111111</v>
       </c>
       <c r="AD35" s="27">
         <f t="shared" si="50"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE35" s="28">
         <f t="shared" si="50"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF35" s="24">
         <f t="shared" si="12"/>
-        <v>34.9</v>
+        <v>34.1</v>
       </c>
       <c r="AG35" s="28">
         <f t="shared" ref="AG35:AI35" si="51">SUM(AG7:AG34)</f>
-        <v>5.29411764705882</v>
+        <v>5.27777777777778</v>
       </c>
       <c r="AH35" s="27">
         <f t="shared" si="51"/>
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AI35" s="28">
         <f t="shared" si="51"/>
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AJ35" s="24">
         <f t="shared" si="14"/>
-        <v>25.5</v>
+        <v>27.3</v>
       </c>
       <c r="AK35" s="27">
         <f t="shared" ref="AK35:AO35" si="52">SUM(AK7:AK34)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL35" s="28">
         <f t="shared" si="52"/>
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AM35" s="24">
         <f t="shared" si="15"/>
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AN35" s="27">
         <f t="shared" si="52"/>
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AO35" s="28">
         <f t="shared" si="52"/>
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AP35" s="24">
         <f t="shared" si="16"/>
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AQ35" s="28">
         <f t="shared" ref="AQ35:AS35" si="53">SUM(AQ7:AQ34)</f>
-        <v>34.4117647058824</v>
+        <v>33.6111111111111</v>
       </c>
       <c r="AR35" s="27">
         <f t="shared" si="53"/>
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="AS35" s="28">
         <f t="shared" si="53"/>
@@ -30723,27 +30735,27 @@
       </c>
       <c r="AT35" s="24">
         <f t="shared" si="18"/>
-        <v>23.1</v>
+        <v>29.1</v>
       </c>
       <c r="AU35" s="28">
         <f t="shared" ref="AU35:AW35" si="54">SUM(AU7:AU34)</f>
-        <v>12.3529411764706</v>
+        <v>11.6666666666667</v>
       </c>
       <c r="AV35" s="27">
         <f t="shared" si="54"/>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AW35" s="28">
         <f t="shared" si="54"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AX35" s="24">
         <f t="shared" si="20"/>
-        <v>14.8</v>
+        <v>17.2</v>
       </c>
       <c r="AY35" s="28">
         <f t="shared" ref="AY35:BA35" si="55">SUM(AY7:AY34)</f>
-        <v>13.5294117647059</v>
+        <v>13.0555555555556</v>
       </c>
       <c r="AZ35" s="27">
         <f t="shared" si="55"/>
@@ -30759,19 +30771,19 @@
       </c>
       <c r="BC35" s="27">
         <f t="shared" ref="BC35:BH35" si="56">SUM(BC7:BC34)</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BD35" s="28">
         <f t="shared" si="56"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="BE35" s="24">
         <f t="shared" si="23"/>
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="BF35" s="28">
         <f t="shared" si="56"/>
-        <v>20.2352941176471</v>
+        <v>20</v>
       </c>
       <c r="BG35" s="27">
         <f t="shared" si="56"/>
@@ -30787,7 +30799,7 @@
       </c>
       <c r="BJ35" s="28">
         <f t="shared" ref="BJ35:BL35" si="57">SUM(BJ7:BJ34)</f>
-        <v>0.941176470588235</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="BK35" s="27">
         <f t="shared" si="57"/>
@@ -30799,95 +30811,95 @@
       </c>
       <c r="BM35" s="24">
         <f t="shared" si="27"/>
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="BN35" s="28">
         <f t="shared" ref="BN35:BP35" si="58">SUM(BN7:BN34)</f>
-        <v>11.7647058823529</v>
+        <v>11.1111111111111</v>
       </c>
       <c r="BO35" s="27">
         <f t="shared" si="58"/>
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="BP35" s="28">
         <f t="shared" si="58"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BQ35" s="24">
         <f t="shared" si="29"/>
-        <v>24.6</v>
+        <v>26.5</v>
       </c>
       <c r="BR35" s="28">
         <f t="shared" ref="BR35:BT35" si="59">SUM(BR7:BR34)</f>
-        <v>25.4117647058823</v>
+        <v>24.4444444444444</v>
       </c>
       <c r="BS35" s="27">
         <f t="shared" si="59"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BT35" s="28">
         <f t="shared" si="59"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BU35" s="24">
         <f t="shared" si="31"/>
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV35" s="28">
         <f t="shared" ref="BV35:BX35" si="60">SUM(BV7:BV34)</f>
-        <v>4.23529411764706</v>
+        <v>4.44444444444444</v>
       </c>
       <c r="BW35" s="27">
         <f t="shared" si="60"/>
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="BX35" s="28">
         <f t="shared" si="60"/>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="BY35" s="24">
         <f t="shared" si="33"/>
-        <v>18.5</v>
+        <v>20.5</v>
       </c>
       <c r="BZ35" s="28">
         <f t="shared" ref="BZ35:CB35" si="61">SUM(BZ7:BZ34)</f>
-        <v>26.3529411764706</v>
+        <v>25.7777777777778</v>
       </c>
       <c r="CA35" s="27">
         <f t="shared" si="61"/>
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="CB35" s="28">
         <f t="shared" si="61"/>
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="CC35" s="24">
         <f t="shared" si="35"/>
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="CD35" s="28">
         <f t="shared" ref="CD35:CF35" si="62">SUM(CD7:CD34)</f>
-        <v>43.2352941176471</v>
+        <v>41.9444444444445</v>
       </c>
       <c r="CE35" s="27">
         <f t="shared" si="62"/>
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CF35" s="28">
         <f t="shared" si="62"/>
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="CG35" s="24">
         <f t="shared" si="37"/>
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="CH35" s="28">
         <f t="shared" ref="CH35:CJ35" si="63">SUM(CH7:CH34)</f>
-        <v>70.8235294117647</v>
+        <v>69.6111111111111</v>
       </c>
       <c r="CI35" s="27">
         <f t="shared" si="63"/>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="CJ35" s="28">
         <f t="shared" si="63"/>
@@ -30895,43 +30907,43 @@
       </c>
       <c r="CK35" s="24">
         <f t="shared" si="39"/>
-        <v>27.9</v>
+        <v>30.4</v>
       </c>
       <c r="CL35" s="27">
         <f t="shared" ref="CL35:CP35" si="64">SUM(CL7:CL34)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="CM35" s="28">
         <f t="shared" si="64"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CN35" s="24">
         <f t="shared" si="40"/>
-        <v>39.2</v>
+        <v>40.7</v>
       </c>
       <c r="CO35" s="27">
         <f t="shared" si="64"/>
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="CP35" s="28">
         <f t="shared" si="64"/>
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="CQ35" s="24">
         <f t="shared" si="41"/>
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="CR35" s="25">
         <f>SUM(CR7:CR34)</f>
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="CS35" s="25">
         <f>SUM(CS7:CS34)</f>
-        <v>1860</v>
+        <v>1925</v>
       </c>
       <c r="CT35" s="25">
         <f>IF(OR(CS35="",CS35=0),"",ROUND(CR35/CS35*$B$2,1))</f>
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>

--- a/source/stock_data.xlsx
+++ b/source/stock_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32740" windowHeight="13100" activeTab="1"/>
+    <workbookView windowWidth="31600" windowHeight="14840"/>
   </bookViews>
   <sheets>
     <sheet name="STOCK IQOO" sheetId="3" r:id="rId1"/>
@@ -1774,10 +1774,10 @@
         </row>
         <row r="9">
           <cell r="C9">
-            <v>17</v>
+            <v>16</v>
           </cell>
           <cell r="D9">
-            <v>11</v>
+            <v>13</v>
           </cell>
           <cell r="E9">
             <v>7</v>
@@ -1846,16 +1846,16 @@
             <v>12</v>
           </cell>
           <cell r="AA9">
-            <v>27</v>
+            <v>25</v>
           </cell>
           <cell r="AB9">
-            <v>19</v>
+            <v>21</v>
           </cell>
           <cell r="AC9">
-            <v>27</v>
+            <v>26</v>
           </cell>
           <cell r="AD9">
-            <v>21</v>
+            <v>22</v>
           </cell>
           <cell r="AE9">
             <v>23</v>
@@ -1864,16 +1864,16 @@
             <v>7</v>
           </cell>
           <cell r="AG9">
-            <v>30</v>
+            <v>29</v>
           </cell>
           <cell r="AH9">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="AI9">
-            <v>157</v>
+            <v>152</v>
           </cell>
           <cell r="AJ9">
-            <v>101</v>
+            <v>107</v>
           </cell>
         </row>
         <row r="10">
@@ -2141,10 +2141,10 @@
             <v>2</v>
           </cell>
           <cell r="AA12">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AB12">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AC12">
             <v>1</v>
@@ -2155,16 +2155,16 @@
         </row>
         <row r="12">
           <cell r="AG12">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AH12">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="AI12">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="AJ12">
-            <v>6</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
@@ -2626,10 +2626,10 @@
             <v>0</v>
           </cell>
           <cell r="AA17">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AB17">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AC17">
             <v>0</v>
@@ -2646,10 +2646,10 @@
             <v>1</v>
           </cell>
           <cell r="AI17">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="AJ17">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="18">
@@ -2808,10 +2808,10 @@
             <v>2</v>
           </cell>
           <cell r="AC19">
+            <v>1</v>
+          </cell>
+          <cell r="AD19">
             <v>2</v>
-          </cell>
-          <cell r="AD19">
-            <v>1</v>
           </cell>
           <cell r="AE19">
             <v>2</v>
@@ -2826,10 +2826,10 @@
             <v>0</v>
           </cell>
           <cell r="AI19">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="AJ19">
-            <v>5</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="20">
@@ -2840,7 +2840,7 @@
             <v>0</v>
           </cell>
           <cell r="D20">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="20">
@@ -2856,7 +2856,7 @@
             <v>0</v>
           </cell>
           <cell r="AJ20">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="21">
@@ -3854,10 +3854,10 @@
             <v>6220701-MVS MBH-VIP VIVO STORE-DD284仓库</v>
           </cell>
           <cell r="C33">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="D33">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="E33">
             <v>0</v>
@@ -3946,10 +3946,10 @@
             <v>0</v>
           </cell>
           <cell r="AI33">
-            <v>9</v>
+            <v>8</v>
           </cell>
           <cell r="AJ33">
-            <v>4</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="34">
@@ -4429,10 +4429,10 @@
         </row>
         <row r="42">
           <cell r="C42">
-            <v>17</v>
+            <v>16</v>
           </cell>
           <cell r="D42">
-            <v>11</v>
+            <v>13</v>
           </cell>
           <cell r="E42">
             <v>7</v>
@@ -4501,16 +4501,16 @@
             <v>12</v>
           </cell>
           <cell r="AA42">
-            <v>27</v>
+            <v>25</v>
           </cell>
           <cell r="AB42">
-            <v>19</v>
+            <v>21</v>
           </cell>
           <cell r="AC42">
-            <v>27</v>
+            <v>26</v>
           </cell>
           <cell r="AD42">
-            <v>21</v>
+            <v>22</v>
           </cell>
           <cell r="AE42">
             <v>23</v>
@@ -4519,16 +4519,16 @@
             <v>7</v>
           </cell>
           <cell r="AG42">
-            <v>30</v>
+            <v>29</v>
           </cell>
           <cell r="AH42">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="AI42">
-            <v>157</v>
+            <v>152</v>
           </cell>
           <cell r="AJ42">
-            <v>101</v>
+            <v>107</v>
           </cell>
         </row>
       </sheetData>
@@ -5150,25 +5150,25 @@
             <v>0</v>
           </cell>
           <cell r="T9">
-            <v>12</v>
+            <v>13</v>
           </cell>
           <cell r="U9">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="V9">
-            <v>12</v>
+            <v>16</v>
           </cell>
           <cell r="W9">
             <v>21</v>
           </cell>
           <cell r="X9">
-            <v>4</v>
+            <v>7</v>
           </cell>
           <cell r="Y9">
             <v>18</v>
           </cell>
           <cell r="Z9">
-            <v>4</v>
+            <v>6</v>
           </cell>
           <cell r="AA9">
             <v>13</v>
@@ -5204,7 +5204,7 @@
             <v>0</v>
           </cell>
           <cell r="AL9">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="AM9">
             <v>8</v>
@@ -5236,7 +5236,7 @@
             <v>14</v>
           </cell>
           <cell r="AX9">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="AY9">
             <v>8</v>
@@ -5278,22 +5278,22 @@
             <v>1</v>
           </cell>
           <cell r="BL9">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="BM9">
             <v>4</v>
           </cell>
           <cell r="BN9">
-            <v>25</v>
+            <v>23</v>
           </cell>
           <cell r="BO9">
-            <v>30</v>
+            <v>32</v>
           </cell>
           <cell r="BP9">
-            <v>84</v>
+            <v>96</v>
           </cell>
           <cell r="BQ9">
-            <v>157</v>
+            <v>160</v>
           </cell>
         </row>
         <row r="10">
@@ -5351,25 +5351,25 @@
             <v>0</v>
           </cell>
           <cell r="T10">
-            <v>12</v>
+            <v>13</v>
           </cell>
           <cell r="U10">
-            <v>9</v>
+            <v>11</v>
           </cell>
           <cell r="V10">
-            <v>17</v>
+            <v>21</v>
           </cell>
           <cell r="W10">
             <v>19</v>
           </cell>
           <cell r="X10">
+            <v>7</v>
+          </cell>
+          <cell r="Y10">
+            <v>24</v>
+          </cell>
+          <cell r="Z10">
             <v>6</v>
-          </cell>
-          <cell r="Y10">
-            <v>22</v>
-          </cell>
-          <cell r="Z10">
-            <v>5</v>
           </cell>
           <cell r="AA10">
             <v>13</v>
@@ -5441,16 +5441,16 @@
             <v>14</v>
           </cell>
           <cell r="AX10">
-            <v>4</v>
+            <v>6</v>
           </cell>
           <cell r="AY10">
             <v>7</v>
           </cell>
           <cell r="AZ10">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="BA10">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="BB10">
             <v>4</v>
@@ -5485,16 +5485,16 @@
             <v>1</v>
           </cell>
           <cell r="BN10">
-            <v>15</v>
+            <v>22</v>
           </cell>
           <cell r="BO10">
             <v>69</v>
           </cell>
           <cell r="BP10">
-            <v>86</v>
+            <v>101</v>
           </cell>
           <cell r="BQ10">
-            <v>173</v>
+            <v>178</v>
           </cell>
         </row>
         <row r="11">
@@ -5508,7 +5508,7 @@
             <v>0</v>
           </cell>
           <cell r="D11">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="E11">
             <v>6</v>
@@ -5556,28 +5556,28 @@
             <v>0</v>
           </cell>
           <cell r="T11">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="U11">
-            <v>22</v>
+            <v>23</v>
           </cell>
           <cell r="V11">
-            <v>13</v>
+            <v>12</v>
           </cell>
           <cell r="W11">
-            <v>38</v>
+            <v>39</v>
           </cell>
           <cell r="X11">
+            <v>9</v>
+          </cell>
+          <cell r="Y11">
+            <v>39</v>
+          </cell>
+          <cell r="Z11">
             <v>11</v>
           </cell>
-          <cell r="Y11">
-            <v>37</v>
-          </cell>
-          <cell r="Z11">
-            <v>9</v>
-          </cell>
           <cell r="AA11">
-            <v>34</v>
+            <v>35</v>
           </cell>
           <cell r="AB11">
             <v>1</v>
@@ -5610,16 +5610,16 @@
             <v>0</v>
           </cell>
           <cell r="AL11">
-            <v>10</v>
+            <v>8</v>
           </cell>
           <cell r="AM11">
-            <v>22</v>
+            <v>24</v>
           </cell>
           <cell r="AN11">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="AO11">
-            <v>13</v>
+            <v>14</v>
           </cell>
           <cell r="AP11">
             <v>0</v>
@@ -5636,10 +5636,10 @@
         </row>
         <row r="11">
           <cell r="AV11">
-            <v>3</v>
+            <v>1</v>
           </cell>
           <cell r="AW11">
-            <v>15</v>
+            <v>17</v>
           </cell>
           <cell r="AX11">
             <v>4</v>
@@ -5654,7 +5654,7 @@
             <v>2</v>
           </cell>
           <cell r="BB11">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="BC11">
             <v>4</v>
@@ -5690,16 +5690,16 @@
             <v>2</v>
           </cell>
           <cell r="BN11">
-            <v>13</v>
+            <v>51</v>
           </cell>
           <cell r="BO11">
-            <v>205</v>
+            <v>207</v>
           </cell>
           <cell r="BP11">
-            <v>94</v>
+            <v>128</v>
           </cell>
           <cell r="BQ11">
-            <v>416</v>
+            <v>428</v>
           </cell>
         </row>
         <row r="12">
@@ -5709,7 +5709,7 @@
         </row>
         <row r="12">
           <cell r="D12">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="E12">
             <v>5</v>
@@ -5775,7 +5775,7 @@
             <v>5</v>
           </cell>
           <cell r="Z12">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="AA12">
             <v>3</v>
@@ -5877,10 +5877,10 @@
             <v>0</v>
           </cell>
           <cell r="BH12">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="BI12">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BJ12">
             <v>2</v>
@@ -5895,16 +5895,16 @@
             <v>0</v>
           </cell>
           <cell r="BN12">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="BO12">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="BP12">
-            <v>59</v>
+            <v>60</v>
           </cell>
           <cell r="BQ12">
-            <v>44</v>
+            <v>46</v>
           </cell>
         </row>
         <row r="13">
@@ -6016,16 +6016,16 @@
             <v>0</v>
           </cell>
           <cell r="AL13">
+            <v>3</v>
+          </cell>
+          <cell r="AM13">
+            <v>1</v>
+          </cell>
+          <cell r="AN13">
+            <v>0</v>
+          </cell>
+          <cell r="AO13">
             <v>4</v>
-          </cell>
-          <cell r="AM13">
-            <v>0</v>
-          </cell>
-          <cell r="AN13">
-            <v>1</v>
-          </cell>
-          <cell r="AO13">
-            <v>3</v>
           </cell>
           <cell r="AP13">
             <v>0</v>
@@ -6102,10 +6102,10 @@
             <v>2</v>
           </cell>
           <cell r="BP13">
-            <v>43</v>
+            <v>41</v>
           </cell>
           <cell r="BQ13">
-            <v>25</v>
+            <v>27</v>
           </cell>
         </row>
         <row r="14">
@@ -6119,10 +6119,10 @@
             <v>0</v>
           </cell>
           <cell r="D14">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="E14">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="F14">
             <v>0</v>
@@ -6163,16 +6163,16 @@
             <v>11</v>
           </cell>
           <cell r="V14">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="W14">
-            <v>11</v>
+            <v>12</v>
           </cell>
           <cell r="X14">
-            <v>3</v>
+            <v>1</v>
           </cell>
           <cell r="Y14">
-            <v>10</v>
+            <v>12</v>
           </cell>
           <cell r="Z14">
             <v>1</v>
@@ -6239,10 +6239,10 @@
             <v>7</v>
           </cell>
           <cell r="AX14">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="AY14">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="AZ14">
             <v>0</v>
@@ -6277,16 +6277,16 @@
             <v>2</v>
           </cell>
           <cell r="BN14">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="BO14">
-            <v>12</v>
+            <v>13</v>
           </cell>
           <cell r="BP14">
-            <v>32</v>
+            <v>26</v>
           </cell>
           <cell r="BQ14">
-            <v>82</v>
+            <v>88</v>
           </cell>
         </row>
         <row r="15">
@@ -6350,10 +6350,10 @@
             <v>1</v>
           </cell>
           <cell r="V15">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="W15">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="X15">
             <v>5</v>
@@ -6488,10 +6488,10 @@
             <v>4</v>
           </cell>
           <cell r="BP15">
-            <v>55</v>
+            <v>54</v>
           </cell>
           <cell r="BQ15">
-            <v>50</v>
+            <v>51</v>
           </cell>
         </row>
         <row r="16">
@@ -6501,7 +6501,7 @@
         </row>
         <row r="16">
           <cell r="D16">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="E16">
             <v>0</v>
@@ -6599,7 +6599,7 @@
             <v>0</v>
           </cell>
           <cell r="AL16">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AM16">
             <v>2</v>
@@ -6671,13 +6671,13 @@
             <v>1</v>
           </cell>
           <cell r="BN16">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="BO16">
             <v>7</v>
           </cell>
           <cell r="BP16">
-            <v>25</v>
+            <v>29</v>
           </cell>
           <cell r="BQ16">
             <v>22</v>
@@ -6901,10 +6901,10 @@
             <v>0</v>
           </cell>
           <cell r="L18">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="M18">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="N18">
             <v>0</v>
@@ -7051,10 +7051,10 @@
             <v>1</v>
           </cell>
           <cell r="BP18">
-            <v>51</v>
+            <v>50</v>
           </cell>
           <cell r="BQ18">
-            <v>18</v>
+            <v>19</v>
           </cell>
         </row>
         <row r="19">
@@ -7117,7 +7117,7 @@
             <v>0</v>
           </cell>
           <cell r="AY19">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AZ19">
             <v>0</v>
@@ -7143,7 +7143,7 @@
             <v>0</v>
           </cell>
           <cell r="BQ19">
-            <v>15</v>
+            <v>16</v>
           </cell>
         </row>
         <row r="20">
@@ -7217,10 +7217,10 @@
             <v>2</v>
           </cell>
           <cell r="X20">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="Y20">
-            <v>10</v>
+            <v>11</v>
           </cell>
           <cell r="Z20">
             <v>4</v>
@@ -7303,10 +7303,10 @@
             <v>5</v>
           </cell>
           <cell r="BB20">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="BC20">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="BD20">
             <v>0</v>
@@ -7329,16 +7329,16 @@
             <v>3</v>
           </cell>
           <cell r="BN20">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="BO20">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="BP20">
-            <v>38</v>
+            <v>35</v>
           </cell>
           <cell r="BQ20">
-            <v>60</v>
+            <v>63</v>
           </cell>
         </row>
         <row r="21">
@@ -7541,7 +7541,7 @@
         </row>
         <row r="22">
           <cell r="D22">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="E22">
             <v>3</v>
@@ -7583,13 +7583,13 @@
             <v>2</v>
           </cell>
           <cell r="X22">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="Y22">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="Z22">
-            <v>1</v>
+            <v>5</v>
           </cell>
           <cell r="AA22">
             <v>4</v>
@@ -7631,7 +7631,7 @@
             <v>1</v>
           </cell>
           <cell r="AN22">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="AO22">
             <v>2</v>
@@ -7651,7 +7651,7 @@
         </row>
         <row r="22">
           <cell r="AV22">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="AW22">
             <v>3</v>
@@ -7701,16 +7701,16 @@
             <v>1</v>
           </cell>
           <cell r="BN22">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="BO22">
             <v>3</v>
           </cell>
           <cell r="BP22">
-            <v>26</v>
+            <v>43</v>
           </cell>
           <cell r="BQ22">
-            <v>28</v>
+            <v>29</v>
           </cell>
         </row>
         <row r="23">
@@ -7911,10 +7911,10 @@
             <v>0</v>
           </cell>
           <cell r="AZ24">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="BA24">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BB24">
             <v>3</v>
@@ -7959,10 +7959,10 @@
             <v>5</v>
           </cell>
           <cell r="BP24">
-            <v>54</v>
+            <v>53</v>
           </cell>
           <cell r="BQ24">
-            <v>24</v>
+            <v>25</v>
           </cell>
         </row>
         <row r="25">
@@ -8283,16 +8283,16 @@
             <v>0</v>
           </cell>
           <cell r="BN26">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="BO26">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BP26">
-            <v>19</v>
+            <v>18</v>
           </cell>
           <cell r="BQ26">
-            <v>11</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="27">
@@ -8360,10 +8360,10 @@
             <v>13</v>
           </cell>
           <cell r="V27">
-            <v>7</v>
+            <v>6</v>
           </cell>
           <cell r="W27">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="X27">
             <v>3</v>
@@ -8372,10 +8372,10 @@
             <v>23</v>
           </cell>
           <cell r="Z27">
-            <v>7</v>
+            <v>6</v>
           </cell>
           <cell r="AA27">
-            <v>14</v>
+            <v>15</v>
           </cell>
           <cell r="AB27">
             <v>3</v>
@@ -8408,10 +8408,10 @@
             <v>0</v>
           </cell>
           <cell r="AL27">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="AM27">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="AN27">
             <v>0</v>
@@ -8488,16 +8488,16 @@
             <v>0</v>
           </cell>
           <cell r="BN27">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="BO27">
-            <v>19</v>
+            <v>20</v>
           </cell>
           <cell r="BP27">
-            <v>59</v>
+            <v>55</v>
           </cell>
           <cell r="BQ27">
-            <v>111</v>
+            <v>115</v>
           </cell>
         </row>
         <row r="28">
@@ -8577,10 +8577,10 @@
             <v>8</v>
           </cell>
           <cell r="Z28">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="AA28">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="AB28">
             <v>2</v>
@@ -8651,10 +8651,10 @@
             <v>1</v>
           </cell>
           <cell r="AZ28">
+            <v>1</v>
+          </cell>
+          <cell r="BA28">
             <v>2</v>
-          </cell>
-          <cell r="BA28">
-            <v>1</v>
           </cell>
           <cell r="BB28">
             <v>2</v>
@@ -8699,10 +8699,10 @@
             <v>16</v>
           </cell>
           <cell r="BP28">
-            <v>37</v>
+            <v>35</v>
           </cell>
           <cell r="BQ28">
-            <v>62</v>
+            <v>64</v>
           </cell>
         </row>
         <row r="29">
@@ -8909,28 +8909,28 @@
             <v>0</v>
           </cell>
           <cell r="T30">
-            <v>6</v>
+            <v>5</v>
           </cell>
           <cell r="U30">
-            <v>10</v>
+            <v>11</v>
           </cell>
           <cell r="V30">
-            <v>12</v>
+            <v>11</v>
           </cell>
           <cell r="W30">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="X30">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="Y30">
-            <v>19</v>
+            <v>21</v>
           </cell>
           <cell r="Z30">
-            <v>7</v>
+            <v>5</v>
           </cell>
           <cell r="AA30">
-            <v>16</v>
+            <v>18</v>
           </cell>
           <cell r="AB30">
             <v>0</v>
@@ -8993,22 +8993,22 @@
             <v>0</v>
           </cell>
           <cell r="AV30">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="AW30">
-            <v>6</v>
+            <v>8</v>
           </cell>
           <cell r="AX30">
+            <v>4</v>
+          </cell>
+          <cell r="AY30">
+            <v>3</v>
+          </cell>
+          <cell r="AZ30">
+            <v>3</v>
+          </cell>
+          <cell r="BA30">
             <v>5</v>
-          </cell>
-          <cell r="AY30">
-            <v>2</v>
-          </cell>
-          <cell r="AZ30">
-            <v>4</v>
-          </cell>
-          <cell r="BA30">
-            <v>4</v>
           </cell>
           <cell r="BB30">
             <v>3</v>
@@ -9049,10 +9049,10 @@
             <v>16</v>
           </cell>
           <cell r="BP30">
-            <v>65</v>
+            <v>55</v>
           </cell>
           <cell r="BQ30">
-            <v>116</v>
+            <v>126</v>
           </cell>
         </row>
         <row r="31">
@@ -9062,11 +9062,11 @@
         </row>
         <row r="31">
           <cell r="D31">
+            <v>4</v>
+          </cell>
+          <cell r="E31">
             <v>5</v>
           </cell>
-          <cell r="E31">
-            <v>4</v>
-          </cell>
           <cell r="F31">
             <v>0</v>
           </cell>
@@ -9086,10 +9086,10 @@
             <v>0</v>
           </cell>
           <cell r="L31">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="M31">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="N31">
             <v>0</v>
@@ -9106,10 +9106,10 @@
             <v>0</v>
           </cell>
           <cell r="T31">
-            <v>8</v>
+            <v>6</v>
           </cell>
           <cell r="U31">
-            <v>13</v>
+            <v>15</v>
           </cell>
           <cell r="V31">
             <v>3</v>
@@ -9124,10 +9124,10 @@
             <v>23</v>
           </cell>
           <cell r="Z31">
-            <v>9</v>
+            <v>8</v>
           </cell>
           <cell r="AA31">
-            <v>13</v>
+            <v>14</v>
           </cell>
           <cell r="AB31">
             <v>1</v>
@@ -9242,10 +9242,10 @@
             <v>34</v>
           </cell>
           <cell r="BP31">
-            <v>69</v>
+            <v>64</v>
           </cell>
           <cell r="BQ31">
-            <v>148</v>
+            <v>153</v>
           </cell>
         </row>
         <row r="32">
@@ -9309,10 +9309,10 @@
             <v>12</v>
           </cell>
           <cell r="X32">
-            <v>6</v>
+            <v>5</v>
           </cell>
           <cell r="Y32">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="Z32">
             <v>2</v>
@@ -9383,10 +9383,10 @@
             <v>6</v>
           </cell>
           <cell r="AX32">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="AY32">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AZ32">
             <v>2</v>
@@ -9433,10 +9433,10 @@
             <v>3</v>
           </cell>
           <cell r="BP32">
-            <v>49</v>
+            <v>47</v>
           </cell>
           <cell r="BQ32">
-            <v>46</v>
+            <v>48</v>
           </cell>
         </row>
         <row r="33">
@@ -9500,10 +9500,10 @@
             <v>19</v>
           </cell>
           <cell r="V33">
-            <v>6</v>
+            <v>5</v>
           </cell>
           <cell r="W33">
-            <v>17</v>
+            <v>18</v>
           </cell>
           <cell r="X33">
             <v>8</v>
@@ -9548,10 +9548,10 @@
             <v>0</v>
           </cell>
           <cell r="AL33">
+            <v>5</v>
+          </cell>
+          <cell r="AM33">
             <v>6</v>
-          </cell>
-          <cell r="AM33">
-            <v>5</v>
           </cell>
           <cell r="AN33">
             <v>0</v>
@@ -9634,10 +9634,10 @@
             <v>21</v>
           </cell>
           <cell r="BP33">
-            <v>64</v>
+            <v>62</v>
           </cell>
           <cell r="BQ33">
-            <v>168</v>
+            <v>170</v>
           </cell>
         </row>
         <row r="34">
@@ -9844,7 +9844,7 @@
         </row>
         <row r="35">
           <cell r="D35">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="E35">
             <v>1</v>
@@ -9868,10 +9868,10 @@
             <v>0</v>
           </cell>
           <cell r="L35">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="M35">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="N35">
             <v>0</v>
@@ -9894,7 +9894,7 @@
             <v>2</v>
           </cell>
           <cell r="V35">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="W35">
             <v>3</v>
@@ -9942,7 +9942,7 @@
             <v>0</v>
           </cell>
           <cell r="AL35">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="AM35">
             <v>2</v>
@@ -9980,10 +9980,10 @@
             <v>0</v>
           </cell>
           <cell r="AZ35">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="BA35">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="BB35">
             <v>2</v>
@@ -10010,7 +10010,7 @@
             <v>0</v>
           </cell>
           <cell r="BJ35">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BK35">
             <v>1</v>
@@ -10022,16 +10022,16 @@
             <v>1</v>
           </cell>
           <cell r="BN35">
-            <v>1</v>
+            <v>3</v>
           </cell>
           <cell r="BO35">
             <v>5</v>
           </cell>
           <cell r="BP35">
-            <v>29</v>
+            <v>33</v>
           </cell>
           <cell r="BQ35">
-            <v>37</v>
+            <v>39</v>
           </cell>
         </row>
         <row r="36">
@@ -10048,6 +10048,14 @@
           </cell>
         </row>
         <row r="36">
+          <cell r="L36">
+            <v>0</v>
+          </cell>
+          <cell r="M36">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="36">
           <cell r="T36">
             <v>0</v>
           </cell>
@@ -10094,7 +10102,7 @@
             <v>0</v>
           </cell>
           <cell r="BA36">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="36">
@@ -10128,7 +10136,7 @@
             <v>0</v>
           </cell>
           <cell r="BQ36">
-            <v>20</v>
+            <v>22</v>
           </cell>
         </row>
         <row r="37">
@@ -10627,10 +10635,10 @@
             <v>1</v>
           </cell>
           <cell r="X42">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="Y42">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="Z42">
             <v>2</v>
@@ -10655,10 +10663,10 @@
         </row>
         <row r="42">
           <cell r="AV42">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AW42">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AX42">
             <v>1</v>
@@ -10705,16 +10713,16 @@
             <v>1</v>
           </cell>
           <cell r="BN42">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="BO42">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BP42">
-            <v>52</v>
+            <v>49</v>
           </cell>
           <cell r="BQ42">
-            <v>26</v>
+            <v>29</v>
           </cell>
         </row>
         <row r="43">
@@ -10728,10 +10736,10 @@
             <v>0</v>
           </cell>
           <cell r="D43">
-            <v>66</v>
+            <v>70</v>
           </cell>
           <cell r="E43">
-            <v>59</v>
+            <v>61</v>
           </cell>
           <cell r="F43">
             <v>4</v>
@@ -10752,10 +10760,10 @@
             <v>2</v>
           </cell>
           <cell r="L43">
-            <v>42</v>
+            <v>39</v>
           </cell>
           <cell r="M43">
-            <v>47</v>
+            <v>51</v>
           </cell>
           <cell r="N43">
             <v>0</v>
@@ -10776,28 +10784,28 @@
             <v>0</v>
           </cell>
           <cell r="T43">
-            <v>142</v>
+            <v>140</v>
           </cell>
           <cell r="U43">
-            <v>153</v>
+            <v>160</v>
           </cell>
           <cell r="V43">
-            <v>147</v>
+            <v>150</v>
           </cell>
           <cell r="W43">
-            <v>182</v>
+            <v>188</v>
           </cell>
           <cell r="X43">
-            <v>105</v>
+            <v>101</v>
           </cell>
           <cell r="Y43">
-            <v>283</v>
+            <v>295</v>
           </cell>
           <cell r="Z43">
-            <v>102</v>
+            <v>108</v>
           </cell>
           <cell r="AA43">
-            <v>170</v>
+            <v>176</v>
           </cell>
           <cell r="AB43">
             <v>36</v>
@@ -10830,16 +10838,16 @@
             <v>0</v>
           </cell>
           <cell r="AL43">
-            <v>97</v>
+            <v>96</v>
           </cell>
           <cell r="AM43">
-            <v>66</v>
+            <v>71</v>
           </cell>
           <cell r="AN43">
             <v>40</v>
           </cell>
           <cell r="AO43">
-            <v>119</v>
+            <v>121</v>
           </cell>
           <cell r="AP43">
             <v>0</v>
@@ -10860,28 +10868,28 @@
             <v>0</v>
           </cell>
           <cell r="AV43">
-            <v>31</v>
+            <v>30</v>
           </cell>
           <cell r="AW43">
-            <v>127</v>
+            <v>132</v>
           </cell>
           <cell r="AX43">
             <v>68</v>
           </cell>
           <cell r="AY43">
-            <v>43</v>
+            <v>47</v>
           </cell>
           <cell r="AZ43">
-            <v>45</v>
+            <v>40</v>
           </cell>
           <cell r="BA43">
-            <v>50</v>
+            <v>56</v>
           </cell>
           <cell r="BB43">
-            <v>81</v>
+            <v>82</v>
           </cell>
           <cell r="BC43">
-            <v>55</v>
+            <v>56</v>
           </cell>
           <cell r="BD43">
             <v>4</v>
@@ -10896,34 +10904,34 @@
             <v>3</v>
           </cell>
           <cell r="BH43">
-            <v>29</v>
+            <v>28</v>
           </cell>
           <cell r="BI43">
-            <v>14</v>
+            <v>15</v>
           </cell>
           <cell r="BJ43">
-            <v>71</v>
+            <v>72</v>
           </cell>
           <cell r="BK43">
             <v>44</v>
           </cell>
           <cell r="BL43">
-            <v>61</v>
+            <v>62</v>
           </cell>
           <cell r="BM43">
             <v>29</v>
           </cell>
           <cell r="BN43">
-            <v>144</v>
+            <v>189</v>
           </cell>
           <cell r="BO43">
-            <v>475</v>
+            <v>485</v>
           </cell>
           <cell r="BP43">
-            <v>1334</v>
+            <v>1378</v>
           </cell>
           <cell r="BQ43">
-            <v>1979</v>
+            <v>2050</v>
           </cell>
         </row>
         <row r="45">
@@ -12220,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -12285,7 +12293,7 @@
       </c>
       <c r="B3" s="31">
         <f>B1-B2</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
@@ -12766,7 +12774,7 @@
       </c>
       <c r="S8" s="24">
         <f t="shared" ref="S8:S36" si="5">IF(OR(R8="",R8=0),"",ROUND(Q8/R8*$B$2,1))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T8" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A8,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -12870,7 +12878,7 @@
       </c>
       <c r="AS8" s="24">
         <f t="shared" ref="AS8:AS36" si="17">IF(OR(AR8="",AR8=0),"",ROUND(AQ8/AR8*$B$2,1))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT8" s="25">
         <f t="shared" ref="AT8:AT35" si="18">SUM(B8,E8,H8,K8,N8,Q8,T8,X8,AB8,AF8,AJ8,AN8,AQ8)</f>
@@ -12882,7 +12890,7 @@
       </c>
       <c r="AV8" s="25">
         <f t="shared" ref="AV8:AV36" si="20">IFERROR(AT8/(AU8/$B$2),1000)</f>
-        <v>13.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="9" spans="1:48">
@@ -12959,7 +12967,7 @@
       </c>
       <c r="S9" s="24">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="T9" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A9,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13075,7 +13083,7 @@
       </c>
       <c r="AV9" s="25">
         <f t="shared" si="20"/>
-        <v>13.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="10" spans="1:48">
@@ -13128,19 +13136,19 @@
       </c>
       <c r="M10" s="24">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="N10" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="47">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" s="24">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13152,7 +13160,7 @@
       </c>
       <c r="S10" s="24">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T10" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13248,27 +13256,27 @@
       </c>
       <c r="AQ10" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR10" s="47">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS10" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="24">
         <f t="shared" si="17"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT10" s="25">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU10" s="25">
         <f t="shared" si="19"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV10" s="25">
         <f t="shared" si="20"/>
-        <v>12</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="11" spans="1:48">
@@ -13437,7 +13445,7 @@
       </c>
       <c r="AP11" s="24">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A11,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13461,7 +13469,7 @@
       </c>
       <c r="AV11" s="25">
         <f t="shared" si="20"/>
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:48">
@@ -13538,7 +13546,7 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T12" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A12,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13654,7 +13662,7 @@
       </c>
       <c r="AV12" s="25">
         <f t="shared" si="20"/>
-        <v>6</v>
+        <v>6.33333333333333</v>
       </c>
     </row>
     <row r="13" spans="1:48">
@@ -13719,7 +13727,7 @@
       </c>
       <c r="P13" s="24">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q13" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A13,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13731,7 +13739,7 @@
       </c>
       <c r="S13" s="24">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="T13" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A13,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13807,11 +13815,11 @@
       </c>
       <c r="AL13" s="24">
         <f t="shared" si="14"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AM13" s="47">
         <f t="shared" si="15"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AN13" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A13,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13847,7 +13855,7 @@
       </c>
       <c r="AV13" s="25">
         <f t="shared" si="20"/>
-        <v>28.8</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="14" spans="1:48">
@@ -13900,7 +13908,7 @@
       </c>
       <c r="M14" s="24">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N14" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -13916,15 +13924,15 @@
       </c>
       <c r="Q14" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" s="47">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" s="24">
         <f t="shared" si="5"/>
-        <v>36</v>
+        <v>9.5</v>
       </c>
       <c r="T14" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14032,15 +14040,15 @@
       </c>
       <c r="AT14" s="25">
         <f t="shared" si="18"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU14" s="25">
         <f t="shared" si="19"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV14" s="25">
         <f t="shared" si="20"/>
-        <v>28.8</v>
+        <v>22.1666666666667</v>
       </c>
     </row>
     <row r="15" spans="1:48">
@@ -14093,7 +14101,7 @@
       </c>
       <c r="M15" s="24">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N15" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A15,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14233,7 +14241,7 @@
       </c>
       <c r="AV15" s="25">
         <f t="shared" si="20"/>
-        <v>13.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="16" spans="1:48">
@@ -14370,11 +14378,11 @@
       </c>
       <c r="AH16" s="24">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI16" s="47">
         <f t="shared" si="13"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AJ16" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A16,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14426,7 +14434,7 @@
       </c>
       <c r="AV16" s="25">
         <f t="shared" si="20"/>
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:48">
@@ -14583,7 +14591,7 @@
       </c>
       <c r="AM17" s="47">
         <f t="shared" si="15"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AN17" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A17,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14619,7 +14627,7 @@
       </c>
       <c r="AV17" s="25">
         <f t="shared" si="20"/>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:48">
@@ -15005,7 +15013,7 @@
       </c>
       <c r="AV19" s="25">
         <f t="shared" si="20"/>
-        <v>21.6</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="20" spans="1:48">
@@ -15275,7 +15283,7 @@
       </c>
       <c r="S21" s="24">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T21" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A21,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15335,11 +15343,11 @@
       </c>
       <c r="AH21" s="24">
         <f t="shared" si="12"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI21" s="47">
         <f t="shared" si="13"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AJ21" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A21,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15391,7 +15399,7 @@
       </c>
       <c r="AV21" s="25">
         <f t="shared" si="20"/>
-        <v>25.7142857142857</v>
+        <v>27.1428571428571</v>
       </c>
     </row>
     <row r="22" spans="1:48">
@@ -15432,7 +15440,7 @@
       </c>
       <c r="J22" s="24">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11X|8+256|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15444,7 +15452,7 @@
       </c>
       <c r="M22" s="24">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15520,19 +15528,19 @@
       </c>
       <c r="AF22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" s="47">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|BLACK|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22" s="24">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="47">
         <f t="shared" si="13"/>
-        <v>0.555555555555556</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AJ22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15560,7 +15568,7 @@
       </c>
       <c r="AP22" s="24">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ22" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15576,15 +15584,15 @@
       </c>
       <c r="AT22" s="25">
         <f t="shared" si="18"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU22" s="25">
         <f t="shared" si="19"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV22" s="25">
         <f t="shared" si="20"/>
-        <v>40.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="23" spans="1:48">
@@ -15649,7 +15657,7 @@
       </c>
       <c r="P23" s="24">
         <f t="shared" si="4"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q23" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A23,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15753,7 +15761,7 @@
       </c>
       <c r="AP23" s="24">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ23" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A23,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15777,7 +15785,7 @@
       </c>
       <c r="AV23" s="25">
         <f t="shared" si="20"/>
-        <v>42</v>
+        <v>44.3333333333333</v>
       </c>
     </row>
     <row r="24" spans="1:48">
@@ -15830,7 +15838,7 @@
       </c>
       <c r="M24" s="24">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N24" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A24,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15918,7 +15926,7 @@
       </c>
       <c r="AI24" s="47">
         <f t="shared" si="13"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AJ24" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A24,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15934,7 +15942,7 @@
       </c>
       <c r="AM24" s="47">
         <f t="shared" si="15"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AN24" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A24,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15970,7 +15978,7 @@
       </c>
       <c r="AV24" s="25">
         <f t="shared" si="20"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="25" spans="1:48">
@@ -16163,7 +16171,7 @@
       </c>
       <c r="AV25" s="25">
         <f t="shared" si="20"/>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:48">
@@ -16204,7 +16212,7 @@
       </c>
       <c r="J26" s="24">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K26" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11X|8+256|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16240,7 +16248,7 @@
       </c>
       <c r="S26" s="24">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T26" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16304,7 +16312,7 @@
       </c>
       <c r="AI26" s="47">
         <f t="shared" si="13"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AJ26" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16344,7 +16352,7 @@
       </c>
       <c r="AS26" s="24">
         <f t="shared" si="17"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT26" s="25">
         <f t="shared" si="18"/>
@@ -16356,7 +16364,7 @@
       </c>
       <c r="AV26" s="25">
         <f t="shared" si="20"/>
-        <v>28.8</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="27" spans="1:48">
@@ -16549,7 +16557,7 @@
       </c>
       <c r="AV27" s="25">
         <f t="shared" si="20"/>
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:48">
@@ -16742,7 +16750,7 @@
       </c>
       <c r="AV28" s="25">
         <f t="shared" si="20"/>
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:48">
@@ -16807,7 +16815,7 @@
       </c>
       <c r="P29" s="24">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q29" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A29,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16819,7 +16827,7 @@
       </c>
       <c r="S29" s="24">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T29" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A29,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16883,7 +16891,7 @@
       </c>
       <c r="AI29" s="47">
         <f t="shared" si="13"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AJ29" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A29,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16923,7 +16931,7 @@
       </c>
       <c r="AS29" s="24">
         <f t="shared" si="17"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT29" s="25">
         <f t="shared" si="18"/>
@@ -16935,7 +16943,7 @@
       </c>
       <c r="AV29" s="25">
         <f t="shared" si="20"/>
-        <v>22.5</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="30" spans="1:48">
@@ -17000,7 +17008,7 @@
       </c>
       <c r="P30" s="24">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q30" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A30,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17012,7 +17020,7 @@
       </c>
       <c r="S30" s="24">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T30" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A30,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17128,7 +17136,7 @@
       </c>
       <c r="AV30" s="25">
         <f t="shared" si="20"/>
-        <v>30</v>
+        <v>31.6666666666667</v>
       </c>
     </row>
     <row r="31" spans="1:48">
@@ -17398,7 +17406,7 @@
       </c>
       <c r="S32" s="24">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T32" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A32,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17458,11 +17466,11 @@
       </c>
       <c r="AH32" s="24">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI32" s="47">
         <f t="shared" si="13"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AJ32" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A32,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17514,7 +17522,7 @@
       </c>
       <c r="AV32" s="25">
         <f t="shared" si="20"/>
-        <v>60</v>
+        <v>63.3333333333333</v>
       </c>
     </row>
     <row r="33" spans="1:48">
@@ -17639,7 +17647,7 @@
       </c>
       <c r="AE33" s="47">
         <f t="shared" si="11"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AF33" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17651,11 +17659,11 @@
       </c>
       <c r="AH33" s="24">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI33" s="47">
         <f t="shared" si="13"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AJ33" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17683,7 +17691,7 @@
       </c>
       <c r="AP33" s="24">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ33" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17695,7 +17703,7 @@
       </c>
       <c r="AS33" s="24">
         <f t="shared" si="17"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT33" s="25">
         <f t="shared" si="18"/>
@@ -17707,7 +17715,7 @@
       </c>
       <c r="AV33" s="25">
         <f t="shared" si="20"/>
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:48">
@@ -17784,7 +17792,7 @@
       </c>
       <c r="S34" s="24">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T34" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A34,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17900,7 +17908,7 @@
       </c>
       <c r="AV34" s="25">
         <f t="shared" si="20"/>
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:48">
@@ -17957,15 +17965,15 @@
       </c>
       <c r="N35" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A35,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="47">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A35,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35" s="24">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="22">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A35,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -18085,15 +18093,15 @@
       </c>
       <c r="AT35" s="25">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU35" s="25">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV35" s="25">
         <f t="shared" si="20"/>
-        <v>18</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="36" spans="1:48">
@@ -18134,7 +18142,7 @@
       </c>
       <c r="J36" s="24">
         <f t="shared" si="2"/>
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="K36" s="27">
         <f t="shared" si="22"/>
@@ -18146,31 +18154,31 @@
       </c>
       <c r="M36" s="24">
         <f t="shared" si="3"/>
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
       <c r="N36" s="27">
         <f t="shared" ref="N36:R36" si="23">SUM(N8:N35)</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O36" s="50">
         <f t="shared" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P36" s="24">
         <f t="shared" si="4"/>
-        <v>25.6</v>
+        <v>22.6</v>
       </c>
       <c r="Q36" s="27">
         <f t="shared" si="23"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R36" s="50">
         <f t="shared" si="23"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S36" s="24">
         <f t="shared" si="5"/>
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="T36" s="27">
         <f t="shared" ref="T36:Y36" si="24">SUM(T8:T35)</f>
@@ -18218,23 +18226,23 @@
       </c>
       <c r="AE36" s="50">
         <f t="shared" ref="AE36:AG36" si="26">SUM(AE8:AE35)</f>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AF36" s="27">
         <f t="shared" si="26"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG36" s="50">
         <f t="shared" si="26"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH36" s="24">
         <f t="shared" si="12"/>
-        <v>30.6</v>
+        <v>27.6</v>
       </c>
       <c r="AI36" s="50">
         <f t="shared" ref="AI36:AK36" si="27">SUM(AI8:AI35)</f>
-        <v>5.55555555555556</v>
+        <v>5.78947368421053</v>
       </c>
       <c r="AJ36" s="27">
         <f t="shared" si="27"/>
@@ -18246,11 +18254,11 @@
       </c>
       <c r="AL36" s="24">
         <f t="shared" si="14"/>
-        <v>25.2</v>
+        <v>26.6</v>
       </c>
       <c r="AM36" s="50">
         <f t="shared" ref="AM36:AO36" si="28">SUM(AM8:AM35)</f>
-        <v>2.77777777777778</v>
+        <v>2.63157894736842</v>
       </c>
       <c r="AN36" s="27">
         <f t="shared" si="28"/>
@@ -18262,31 +18270,31 @@
       </c>
       <c r="AP36" s="24">
         <f t="shared" si="16"/>
-        <v>69</v>
+        <v>72.8</v>
       </c>
       <c r="AQ36" s="27">
         <f t="shared" ref="AQ36:AU36" si="29">SUM(AQ8:AQ35)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR36" s="50">
         <f t="shared" si="29"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS36" s="24">
         <f t="shared" si="17"/>
-        <v>67.5</v>
+        <v>61.2</v>
       </c>
       <c r="AT36" s="25">
         <f t="shared" si="29"/>
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AU36" s="25">
         <f t="shared" si="29"/>
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="AV36" s="25">
         <f t="shared" si="20"/>
-        <v>29.1340206185567</v>
+        <v>28.3137254901961</v>
       </c>
     </row>
   </sheetData>
@@ -18707,7 +18715,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -18842,7 +18850,7 @@
       </c>
       <c r="B3" s="3">
         <f>B1-B2</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -19587,11 +19595,11 @@
       </c>
       <c r="J7" s="24">
         <f t="shared" ref="J7:J35" si="2">IF(OR(I7="",I7=0),"",ROUND(H7/I7*$B$2,1))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7" s="23">
         <f t="shared" ref="K7:K34" si="3">(I7/$B$2)*10</f>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="L7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19635,7 +19643,7 @@
       </c>
       <c r="V7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -19643,15 +19651,15 @@
       </c>
       <c r="X7" s="24">
         <f t="shared" ref="X7:X35" si="8">IF(OR(W7="",W7=0),"",ROUND(V7/W7*$B$2,1))</f>
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="Y7" s="23">
         <f t="shared" ref="Y7:Y34" si="9">(W7/$B$2)*5</f>
-        <v>5</v>
+        <v>4.73684210526316</v>
       </c>
       <c r="Z7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -19659,11 +19667,11 @@
       </c>
       <c r="AB7" s="24">
         <f t="shared" ref="AB7:AB35" si="10">IF(OR(AA7="",AA7=0),"",ROUND(Z7/AA7*$B$2,1))</f>
-        <v>5.5</v>
+        <v>8.8</v>
       </c>
       <c r="AC7" s="23">
         <f t="shared" ref="AC7:AC34" si="11">(AA7/$B$2)*5</f>
-        <v>3.61111111111111</v>
+        <v>3.42105263157895</v>
       </c>
       <c r="AD7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19675,15 +19683,15 @@
       </c>
       <c r="AF7" s="24">
         <f t="shared" ref="AF7:AF35" si="12">IF(OR(AE7="",AE7=0),"",ROUND(AD7/AE7*$B$2,1))</f>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="AG7" s="23">
         <f t="shared" ref="AG7:AG34" si="13">(AE7/$B$2)*5</f>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AH7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -19691,7 +19699,7 @@
       </c>
       <c r="AJ7" s="24">
         <f t="shared" ref="AJ7:AJ35" si="14">IF(OR(AI7="",AI7=0),"",ROUND(AH7/AI7*$B$2,1))</f>
-        <v>11.3</v>
+        <v>16.6</v>
       </c>
       <c r="AK7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19719,11 +19727,11 @@
       </c>
       <c r="AQ7" s="23">
         <f t="shared" ref="AQ7:AQ34" si="17">(AO7/$B$2)*5</f>
-        <v>3.88888888888889</v>
+        <v>3.68421052631579</v>
       </c>
       <c r="AR7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -19731,11 +19739,11 @@
       </c>
       <c r="AT7" s="24">
         <f t="shared" ref="AT7:AT35" si="18">IF(OR(AS7="",AS7=0),"",ROUND(AR7/AS7*$B$2,1))</f>
-        <v>11.3</v>
+        <v>14.3</v>
       </c>
       <c r="AU7" s="23">
         <f t="shared" ref="AU7:AU34" si="19">(AS7/$B$2)*5</f>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="AV7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19747,11 +19755,11 @@
       </c>
       <c r="AX7" s="24">
         <f t="shared" ref="AX7:AX35" si="20">IF(OR(AW7="",AW7=0),"",ROUND(AV7/AW7*$B$2,1))</f>
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AY7" s="23">
         <f t="shared" ref="AY7:AY34" si="21">(AW7/$B$2)*5</f>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="AZ7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19779,7 +19787,7 @@
       </c>
       <c r="BF7" s="23">
         <f t="shared" ref="BF7:BF34" si="24">(BD7/$B$2)*8</f>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19823,11 +19831,11 @@
       </c>
       <c r="BQ7" s="24">
         <f t="shared" ref="BQ7:BQ35" si="29">IF(OR(BP7="",BP7=0),"",ROUND(BO7/BP7*$B$2,1))</f>
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BR7" s="23">
         <f t="shared" ref="BR7:BR34" si="30">(BP7/$B$2)*8</f>
-        <v>3.11111111111111</v>
+        <v>2.94736842105263</v>
       </c>
       <c r="BS7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19855,31 +19863,31 @@
       </c>
       <c r="BY7" s="24">
         <f t="shared" ref="BY7:BY35" si="33">IF(OR(BX7="",BX7=0),"",ROUND(BW7/BX7*$B$2,1))</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BZ7" s="23">
         <f t="shared" ref="BZ7:BZ34" si="34">(BX7/$B$2)*8</f>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="CA7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CC7" s="24">
         <f t="shared" ref="CC7:CC35" si="35">IF(OR(CB7="",CB7=0),"",ROUND(CA7/CB7*$B$2,1))</f>
-        <v>27</v>
+        <v>27.4</v>
       </c>
       <c r="CD7" s="23">
         <f t="shared" ref="CD7:CD34" si="36">(CB7/$B$2)*5</f>
-        <v>2.22222222222222</v>
+        <v>2.36842105263158</v>
       </c>
       <c r="CE7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CF7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -19887,11 +19895,11 @@
       </c>
       <c r="CG7" s="24">
         <f t="shared" ref="CG7:CG35" si="37">IF(OR(CF7="",CF7=0),"",ROUND(CE7/CF7*$B$2,1))</f>
-        <v>10.3</v>
+        <v>14.5</v>
       </c>
       <c r="CH7" s="23">
         <f t="shared" ref="CH7:CH34" si="38">(CF7/$B$2)*7</f>
-        <v>8.16666666666667</v>
+        <v>7.73684210526316</v>
       </c>
       <c r="CI7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -19903,11 +19911,11 @@
       </c>
       <c r="CK7" s="24">
         <f t="shared" ref="CK7:CK35" si="39">IF(OR(CJ7="",CJ7=0),"",ROUND(CI7/CJ7*$B$2,1))</f>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="CL7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -19915,31 +19923,31 @@
       </c>
       <c r="CN7" s="24">
         <f t="shared" ref="CN7:CN35" si="40">IF(OR(CM7="",CM7=0),"",ROUND(CL7/CM7*$B$2,1))</f>
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="CO7" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CP7" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CQ7" s="24">
         <f t="shared" ref="CQ7:CQ35" si="41">IF(OR(CP7="",CP7=0),"",ROUND(CO7/CP7*$B$2,1))</f>
-        <v>15</v>
+        <v>13.7</v>
       </c>
       <c r="CR7" s="25">
         <f t="shared" ref="CR7:CR34" si="42">SUM(B7,L7,P7,S7,AZ7,BK7,BO7,BS7,BW7,CA7,CE7,BC7,AN7,AR7,AV7,BG7,V7,E7,H7,AD7,Z7,AH7,AK7,CI7,CL7,CO7)</f>
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="CS7" s="25">
         <f t="shared" ref="CS7:CS34" si="43">SUM(C7,M7,Q7,T7,BL7,BP7,BT7,BX7,CB7,CF7,BA7,BD7,AO7,AS7,AW7,BH7,W7,F7,I7,AE7,AA7,AI7,AL7,CJ7,CM7,CP7)</f>
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="CT7" s="25">
         <f t="shared" ref="CT7:CT34" si="44">IFERROR(CR7/(CS7/$B$2),1000)</f>
-        <v>9.63057324840764</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="8" spans="1:98">
@@ -20028,23 +20036,23 @@
       </c>
       <c r="V8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="X8" s="24">
         <f t="shared" si="8"/>
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y8" s="23">
         <f t="shared" si="9"/>
-        <v>6.11111111111111</v>
+        <v>6.31578947368421</v>
       </c>
       <c r="Z8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -20052,11 +20060,11 @@
       </c>
       <c r="AB8" s="24">
         <f t="shared" si="10"/>
-        <v>6.9</v>
+        <v>8.8</v>
       </c>
       <c r="AC8" s="23">
         <f t="shared" si="11"/>
-        <v>3.61111111111111</v>
+        <v>3.42105263157895</v>
       </c>
       <c r="AD8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20072,7 +20080,7 @@
       </c>
       <c r="AG8" s="23">
         <f t="shared" si="13"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AH8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20112,11 +20120,11 @@
       </c>
       <c r="AQ8" s="23">
         <f t="shared" si="17"/>
-        <v>3.88888888888889</v>
+        <v>3.68421052631579</v>
       </c>
       <c r="AR8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -20124,27 +20132,27 @@
       </c>
       <c r="AT8" s="24">
         <f t="shared" si="18"/>
-        <v>10.3</v>
+        <v>16.3</v>
       </c>
       <c r="AU8" s="23">
         <f t="shared" si="19"/>
-        <v>1.94444444444444</v>
+        <v>1.84210526315789</v>
       </c>
       <c r="AV8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX8" s="24">
         <f t="shared" si="20"/>
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AY8" s="23">
         <f t="shared" si="21"/>
-        <v>0.555555555555556</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AZ8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20172,7 +20180,7 @@
       </c>
       <c r="BF8" s="23">
         <f t="shared" si="24"/>
-        <v>1.33333333333333</v>
+        <v>1.26315789473684</v>
       </c>
       <c r="BG8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20216,11 +20224,11 @@
       </c>
       <c r="BQ8" s="24">
         <f t="shared" si="29"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="BR8" s="23">
         <f t="shared" si="30"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BS8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20248,31 +20256,31 @@
       </c>
       <c r="BY8" s="24">
         <f t="shared" si="33"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BZ8" s="23">
         <f t="shared" si="34"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="CA8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CC8" s="24">
         <f t="shared" si="35"/>
-        <v>24</v>
+        <v>22.5</v>
       </c>
       <c r="CD8" s="23">
         <f t="shared" si="36"/>
-        <v>2.5</v>
+        <v>2.89473684210526</v>
       </c>
       <c r="CE8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CF8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -20280,11 +20288,11 @@
       </c>
       <c r="CG8" s="24">
         <f t="shared" si="37"/>
-        <v>16.1</v>
+        <v>21</v>
       </c>
       <c r="CH8" s="23">
         <f t="shared" si="38"/>
-        <v>7.38888888888889</v>
+        <v>7</v>
       </c>
       <c r="CI8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20296,7 +20304,7 @@
       </c>
       <c r="CK8" s="24">
         <f t="shared" si="39"/>
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="CL8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20308,11 +20316,11 @@
       </c>
       <c r="CN8" s="24">
         <f t="shared" si="40"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="CO8" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="CP8" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -20320,19 +20328,19 @@
       </c>
       <c r="CQ8" s="24">
         <f t="shared" si="41"/>
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="CR8" s="25">
         <f t="shared" si="42"/>
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="CS8" s="25">
         <f t="shared" si="43"/>
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="CT8" s="25">
         <f t="shared" si="44"/>
-        <v>8.94797687861272</v>
+        <v>10.7808988764045</v>
       </c>
     </row>
     <row r="9" spans="1:98">
@@ -20421,35 +20429,35 @@
       </c>
       <c r="V9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X9" s="24">
         <f t="shared" si="8"/>
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="Y9" s="23">
         <f t="shared" si="9"/>
-        <v>10.2777777777778</v>
+        <v>10.2631578947368</v>
       </c>
       <c r="Z9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AB9" s="24">
         <f t="shared" si="10"/>
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AC9" s="23">
         <f t="shared" si="11"/>
-        <v>9.44444444444444</v>
+        <v>9.21052631578947</v>
       </c>
       <c r="AD9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20461,51 +20469,51 @@
       </c>
       <c r="AF9" s="24">
         <f t="shared" si="12"/>
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AG9" s="23">
         <f t="shared" si="13"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AH9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ9" s="24">
         <f t="shared" si="14"/>
-        <v>8.2</v>
+        <v>6.3</v>
       </c>
       <c r="AK9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM9" s="24">
         <f t="shared" si="15"/>
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="AN9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP9" s="24">
         <f t="shared" si="16"/>
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="AQ9" s="23">
         <f t="shared" si="17"/>
-        <v>4.16666666666667</v>
+        <v>4.47368421052632</v>
       </c>
       <c r="AR9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20517,11 +20525,11 @@
       </c>
       <c r="AT9" s="24">
         <f t="shared" si="18"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU9" s="23">
         <f t="shared" si="19"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AV9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20533,11 +20541,11 @@
       </c>
       <c r="AX9" s="24">
         <f t="shared" si="20"/>
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="AY9" s="23">
         <f t="shared" si="21"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AZ9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20565,7 +20573,7 @@
       </c>
       <c r="BF9" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20597,11 +20605,11 @@
       </c>
       <c r="BN9" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BP9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -20609,11 +20617,11 @@
       </c>
       <c r="BQ9" s="24">
         <f t="shared" si="29"/>
-        <v>13.5</v>
+        <v>23.8</v>
       </c>
       <c r="BR9" s="23">
         <f t="shared" si="30"/>
-        <v>1.77777777777778</v>
+        <v>1.68421052631579</v>
       </c>
       <c r="BS9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20633,7 +20641,7 @@
       </c>
       <c r="BW9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BX9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -20641,43 +20649,43 @@
       </c>
       <c r="BY9" s="24">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="BZ9" s="23">
         <f t="shared" si="34"/>
-        <v>2.66666666666667</v>
+        <v>2.52631578947368</v>
       </c>
       <c r="CA9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CB9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CC9" s="24">
         <f t="shared" si="35"/>
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="CD9" s="23">
         <f t="shared" si="36"/>
-        <v>6.11111111111111</v>
+        <v>6.05263157894737</v>
       </c>
       <c r="CE9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CF9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CG9" s="24">
         <f t="shared" si="37"/>
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="CH9" s="23">
         <f t="shared" si="38"/>
-        <v>14.7777777777778</v>
+        <v>14.3684210526316</v>
       </c>
       <c r="CI9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20689,7 +20697,7 @@
       </c>
       <c r="CK9" s="24">
         <f t="shared" si="39"/>
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="CL9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20701,31 +20709,31 @@
       </c>
       <c r="CN9" s="24">
         <f t="shared" si="40"/>
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="CO9" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="CP9" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="CQ9" s="24">
         <f t="shared" si="41"/>
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="CR9" s="25">
         <f t="shared" si="42"/>
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="CS9" s="25">
         <f t="shared" si="43"/>
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="CT9" s="25">
         <f t="shared" si="44"/>
-        <v>4.06730769230769</v>
+        <v>5.68224299065421</v>
       </c>
     </row>
     <row r="10" spans="1:98">
@@ -20758,19 +20766,19 @@
       </c>
       <c r="H10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="J10" s="24">
         <f t="shared" si="2"/>
-        <v/>
+        <v>57</v>
       </c>
       <c r="K10" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="L10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20822,15 +20830,15 @@
       </c>
       <c r="X10" s="24">
         <f t="shared" si="8"/>
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="Y10" s="23">
         <f t="shared" si="9"/>
-        <v>1.38888888888889</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="Z10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA10" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -20838,11 +20846,11 @@
       </c>
       <c r="AB10" s="24">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>31.7</v>
       </c>
       <c r="AC10" s="23">
         <f t="shared" si="11"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AD10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20894,11 +20902,11 @@
       </c>
       <c r="AP10" s="24">
         <f t="shared" si="16"/>
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ10" s="23">
         <f t="shared" si="17"/>
-        <v>1.38888888888889</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="AR10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20930,7 +20938,7 @@
       </c>
       <c r="AY10" s="23">
         <f t="shared" si="21"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AZ10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -20954,11 +20962,11 @@
       </c>
       <c r="BE10" s="24">
         <f t="shared" si="23"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BF10" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21002,11 +21010,11 @@
       </c>
       <c r="BQ10" s="24">
         <f t="shared" si="29"/>
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="BR10" s="23">
         <f t="shared" si="30"/>
-        <v>1.33333333333333</v>
+        <v>1.26315789473684</v>
       </c>
       <c r="BS10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21022,11 +21030,11 @@
       </c>
       <c r="BV10" s="23">
         <f t="shared" si="32"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BW10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BX10" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21034,11 +21042,11 @@
       </c>
       <c r="BY10" s="24">
         <f t="shared" si="33"/>
-        <v>18</v>
+        <v>22.8</v>
       </c>
       <c r="BZ10" s="23">
         <f t="shared" si="34"/>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="CA10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21050,11 +21058,11 @@
       </c>
       <c r="CC10" s="24">
         <f t="shared" si="35"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="CD10" s="23">
         <f t="shared" si="36"/>
-        <v>2.5</v>
+        <v>2.36842105263158</v>
       </c>
       <c r="CE10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21066,11 +21074,11 @@
       </c>
       <c r="CG10" s="24">
         <f t="shared" si="37"/>
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="CH10" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21082,7 +21090,7 @@
       </c>
       <c r="CK10" s="24">
         <f t="shared" si="39"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CL10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21098,27 +21106,27 @@
       </c>
       <c r="CO10" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP10" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CQ10" s="24">
         <f t="shared" si="41"/>
-        <v>12.9</v>
+        <v>9.5</v>
       </c>
       <c r="CR10" s="25">
         <f t="shared" si="42"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="CS10" s="25">
         <f t="shared" si="43"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CT10" s="25">
         <f t="shared" si="44"/>
-        <v>24.1363636363636</v>
+        <v>24.7826086956522</v>
       </c>
     </row>
     <row r="11" spans="1:98">
@@ -21207,19 +21215,19 @@
       </c>
       <c r="V11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X11" s="24">
         <f t="shared" si="8"/>
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="Y11" s="23">
         <f t="shared" si="9"/>
-        <v>2.77777777777778</v>
+        <v>3.15789473684211</v>
       </c>
       <c r="Z11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21231,11 +21239,11 @@
       </c>
       <c r="AB11" s="24">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AC11" s="23">
         <f t="shared" si="11"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AD11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21263,7 +21271,7 @@
       </c>
       <c r="AJ11" s="24">
         <f t="shared" si="14"/>
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="AK11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21275,7 +21283,7 @@
       </c>
       <c r="AM11" s="24">
         <f t="shared" si="15"/>
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AN11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21291,23 +21299,23 @@
       </c>
       <c r="AQ11" s="23">
         <f t="shared" si="17"/>
-        <v>1.94444444444444</v>
+        <v>1.84210526315789</v>
       </c>
       <c r="AR11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT11" s="24">
         <f t="shared" si="18"/>
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="AU11" s="23">
         <f t="shared" si="19"/>
-        <v>0.833333333333333</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AV11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21323,7 +21331,7 @@
       </c>
       <c r="AY11" s="23">
         <f t="shared" si="21"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AZ11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21383,7 +21391,7 @@
       </c>
       <c r="BN11" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21395,11 +21403,11 @@
       </c>
       <c r="BQ11" s="24">
         <f t="shared" si="29"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BR11" s="23">
         <f t="shared" si="30"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BS11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21415,23 +21423,23 @@
       </c>
       <c r="BV11" s="23">
         <f t="shared" si="32"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BW11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BX11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BY11" s="24">
         <f t="shared" si="33"/>
-        <v>10.8</v>
+        <v>6.3</v>
       </c>
       <c r="BZ11" s="23">
         <f t="shared" si="34"/>
-        <v>2.22222222222222</v>
+        <v>2.52631578947368</v>
       </c>
       <c r="CA11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21443,27 +21451,27 @@
       </c>
       <c r="CC11" s="24">
         <f t="shared" si="35"/>
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="CD11" s="23">
         <f t="shared" si="36"/>
-        <v>3.05555555555556</v>
+        <v>2.89473684210526</v>
       </c>
       <c r="CE11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CF11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CG11" s="24">
         <f t="shared" si="37"/>
-        <v>8.2</v>
+        <v>6.3</v>
       </c>
       <c r="CH11" s="23">
         <f t="shared" si="38"/>
-        <v>4.27777777777778</v>
+        <v>4.42105263157895</v>
       </c>
       <c r="CI11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21475,7 +21483,7 @@
       </c>
       <c r="CK11" s="24">
         <f t="shared" si="39"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CL11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21491,27 +21499,27 @@
       </c>
       <c r="CO11" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP11" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CQ11" s="24">
         <f t="shared" si="41"/>
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="CR11" s="25">
         <f t="shared" si="42"/>
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="CS11" s="25">
         <f t="shared" si="43"/>
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="CT11" s="25">
         <f t="shared" si="44"/>
-        <v>7.02439024390244</v>
+        <v>5.61363636363636</v>
       </c>
     </row>
     <row r="12" spans="1:98">
@@ -21540,7 +21548,7 @@
       </c>
       <c r="G12" s="24">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21552,11 +21560,11 @@
       </c>
       <c r="J12" s="24">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="L12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21608,11 +21616,11 @@
       </c>
       <c r="X12" s="24">
         <f t="shared" si="8"/>
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
       <c r="Y12" s="23">
         <f t="shared" si="9"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="Z12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21624,11 +21632,11 @@
       </c>
       <c r="AB12" s="24">
         <f t="shared" si="10"/>
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="AC12" s="23">
         <f t="shared" si="11"/>
-        <v>1.94444444444444</v>
+        <v>1.84210526315789</v>
       </c>
       <c r="AD12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21656,7 +21664,7 @@
       </c>
       <c r="AJ12" s="24">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AK12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21668,7 +21676,7 @@
       </c>
       <c r="AM12" s="24">
         <f t="shared" si="15"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21680,11 +21688,11 @@
       </c>
       <c r="AP12" s="24">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ12" s="23">
         <f t="shared" si="17"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AR12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21696,11 +21704,11 @@
       </c>
       <c r="AT12" s="24">
         <f t="shared" si="18"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU12" s="23">
         <f t="shared" si="19"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AV12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21712,11 +21720,11 @@
       </c>
       <c r="AX12" s="24">
         <f t="shared" si="20"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY12" s="23">
         <f t="shared" si="21"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AZ12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21744,7 +21752,7 @@
       </c>
       <c r="BF12" s="23">
         <f t="shared" si="24"/>
-        <v>1.77777777777778</v>
+        <v>1.68421052631579</v>
       </c>
       <c r="BG12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21776,7 +21784,7 @@
       </c>
       <c r="BN12" s="23">
         <f t="shared" si="28"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BO12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21788,11 +21796,11 @@
       </c>
       <c r="BQ12" s="24">
         <f t="shared" si="29"/>
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="BR12" s="23">
         <f t="shared" si="30"/>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="BS12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21820,11 +21828,11 @@
       </c>
       <c r="BY12" s="24">
         <f t="shared" si="33"/>
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="BZ12" s="23">
         <f t="shared" si="34"/>
-        <v>1.33333333333333</v>
+        <v>1.26315789473684</v>
       </c>
       <c r="CA12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21836,27 +21844,27 @@
       </c>
       <c r="CC12" s="24">
         <f t="shared" si="35"/>
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="CD12" s="23">
         <f t="shared" si="36"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="CE12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CF12" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CG12" s="24">
         <f t="shared" si="37"/>
-        <v>15</v>
+        <v>10.9</v>
       </c>
       <c r="CH12" s="23">
         <f t="shared" si="38"/>
-        <v>2.33333333333333</v>
+        <v>2.57894736842105</v>
       </c>
       <c r="CI12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21868,7 +21876,7 @@
       </c>
       <c r="CK12" s="24">
         <f t="shared" si="39"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CL12" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21892,19 +21900,19 @@
       </c>
       <c r="CQ12" s="24">
         <f t="shared" si="41"/>
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="CR12" s="25">
         <f t="shared" si="42"/>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="CS12" s="25">
         <f t="shared" si="43"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="CT12" s="25">
         <f t="shared" si="44"/>
-        <v>19.8</v>
+        <v>20.1176470588235</v>
       </c>
     </row>
     <row r="13" spans="1:98">
@@ -22001,11 +22009,11 @@
       </c>
       <c r="X13" s="24">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="Y13" s="23">
         <f t="shared" si="9"/>
-        <v>1.66666666666667</v>
+        <v>1.57894736842105</v>
       </c>
       <c r="Z13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22049,7 +22057,7 @@
       </c>
       <c r="AJ13" s="24">
         <f t="shared" si="14"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AK13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22073,11 +22081,11 @@
       </c>
       <c r="AP13" s="24">
         <f t="shared" si="16"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AQ13" s="23">
         <f t="shared" si="17"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AR13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22105,11 +22113,11 @@
       </c>
       <c r="AX13" s="24">
         <f t="shared" si="20"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY13" s="23">
         <f t="shared" si="21"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AZ13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22125,19 +22133,19 @@
       </c>
       <c r="BC13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD13" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE13" s="24">
         <f t="shared" si="23"/>
-        <v>18</v>
+        <v>6.3</v>
       </c>
       <c r="BF13" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>1.26315789473684</v>
       </c>
       <c r="BG13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22169,7 +22177,7 @@
       </c>
       <c r="BN13" s="23">
         <f t="shared" si="28"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BO13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22213,11 +22221,11 @@
       </c>
       <c r="BY13" s="24">
         <f t="shared" si="33"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BZ13" s="23">
         <f t="shared" si="34"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="CA13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22229,11 +22237,11 @@
       </c>
       <c r="CC13" s="24">
         <f t="shared" si="35"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="CD13" s="23">
         <f t="shared" si="36"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="CE13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22245,11 +22253,11 @@
       </c>
       <c r="CG13" s="24">
         <f t="shared" si="37"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="CH13" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI13" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22285,19 +22293,19 @@
       </c>
       <c r="CQ13" s="24">
         <f t="shared" si="41"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="CR13" s="25">
         <f t="shared" si="42"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="CS13" s="25">
         <f t="shared" si="43"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT13" s="25">
         <f t="shared" si="44"/>
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:98">
@@ -22386,19 +22394,19 @@
       </c>
       <c r="V14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14" s="24">
         <f t="shared" si="8"/>
-        <v>15.4</v>
+        <v>11.9</v>
       </c>
       <c r="Y14" s="23">
         <f t="shared" si="9"/>
-        <v>1.94444444444444</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="Z14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22410,11 +22418,11 @@
       </c>
       <c r="AB14" s="24">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="AC14" s="23">
         <f t="shared" si="11"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AD14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22430,7 +22438,7 @@
       </c>
       <c r="AG14" s="23">
         <f t="shared" si="13"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AH14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22454,7 +22462,7 @@
       </c>
       <c r="AM14" s="24">
         <f t="shared" si="15"/>
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AN14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22470,23 +22478,23 @@
       </c>
       <c r="AQ14" s="23">
         <f t="shared" si="17"/>
-        <v>1.66666666666667</v>
+        <v>1.57894736842105</v>
       </c>
       <c r="AR14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS14" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT14" s="24">
         <f t="shared" si="18"/>
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="AU14" s="23">
         <f t="shared" si="19"/>
-        <v>0.277777777777778</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AV14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22498,11 +22506,11 @@
       </c>
       <c r="AX14" s="24">
         <f t="shared" si="20"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY14" s="23">
         <f t="shared" si="21"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AZ14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22526,11 +22534,11 @@
       </c>
       <c r="BE14" s="24">
         <f t="shared" si="23"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BF14" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22594,7 +22602,7 @@
       </c>
       <c r="BV14" s="23">
         <f t="shared" si="32"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BW14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22606,11 +22614,11 @@
       </c>
       <c r="BY14" s="24">
         <f t="shared" si="33"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BZ14" s="23">
         <f t="shared" si="34"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="CA14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22622,11 +22630,11 @@
       </c>
       <c r="CC14" s="24">
         <f t="shared" si="35"/>
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="CD14" s="23">
         <f t="shared" si="36"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="CE14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22638,11 +22646,11 @@
       </c>
       <c r="CG14" s="24">
         <f t="shared" si="37"/>
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="CH14" s="23">
         <f t="shared" si="38"/>
-        <v>4.66666666666667</v>
+        <v>4.42105263157895</v>
       </c>
       <c r="CI14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22666,7 +22674,7 @@
       </c>
       <c r="CN14" s="24">
         <f t="shared" si="40"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CO14" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22678,19 +22686,19 @@
       </c>
       <c r="CQ14" s="24">
         <f t="shared" si="41"/>
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="CR14" s="25">
         <f t="shared" si="42"/>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="CS14" s="25">
         <f t="shared" si="43"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="CT14" s="25">
         <f t="shared" si="44"/>
-        <v>19.1739130434783</v>
+        <v>18.6041666666667</v>
       </c>
     </row>
     <row r="15" spans="1:98">
@@ -22779,19 +22787,19 @@
       </c>
       <c r="V15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W15" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X15" s="24">
         <f t="shared" si="8"/>
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" s="23">
         <f t="shared" si="9"/>
-        <v>2.77777777777778</v>
+        <v>2.89473684210526</v>
       </c>
       <c r="Z15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22803,11 +22811,11 @@
       </c>
       <c r="AB15" s="24">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC15" s="23">
         <f t="shared" si="11"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AD15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22835,7 +22843,7 @@
       </c>
       <c r="AJ15" s="24">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AK15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22863,7 +22871,7 @@
       </c>
       <c r="AQ15" s="23">
         <f t="shared" si="17"/>
-        <v>1.38888888888889</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="AR15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22875,11 +22883,11 @@
       </c>
       <c r="AT15" s="24">
         <f t="shared" si="18"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AU15" s="23">
         <f t="shared" si="19"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AV15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22891,11 +22899,11 @@
       </c>
       <c r="AX15" s="24">
         <f t="shared" si="20"/>
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AY15" s="23">
         <f t="shared" si="21"/>
-        <v>1.38888888888889</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="AZ15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22923,7 +22931,7 @@
       </c>
       <c r="BF15" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22939,7 +22947,7 @@
       </c>
       <c r="BJ15" s="23">
         <f t="shared" si="26"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BK15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22955,23 +22963,23 @@
       </c>
       <c r="BN15" s="23">
         <f t="shared" si="28"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BO15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP15" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ15" s="24">
         <f t="shared" si="29"/>
-        <v>18</v>
+        <v>6.3</v>
       </c>
       <c r="BR15" s="23">
         <f t="shared" si="30"/>
-        <v>0.888888888888889</v>
+        <v>1.26315789473684</v>
       </c>
       <c r="BS15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22983,11 +22991,11 @@
       </c>
       <c r="BU15" s="24">
         <f t="shared" si="31"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BV15" s="23">
         <f t="shared" si="32"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BW15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23015,11 +23023,11 @@
       </c>
       <c r="CC15" s="24">
         <f t="shared" si="35"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="CD15" s="23">
         <f t="shared" si="36"/>
-        <v>1.66666666666667</v>
+        <v>1.57894736842105</v>
       </c>
       <c r="CE15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23031,11 +23039,11 @@
       </c>
       <c r="CG15" s="24">
         <f t="shared" si="37"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CH15" s="23">
         <f t="shared" si="38"/>
-        <v>0.777777777777778</v>
+        <v>0.736842105263158</v>
       </c>
       <c r="CI15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23047,7 +23055,7 @@
       </c>
       <c r="CK15" s="24">
         <f t="shared" si="39"/>
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="CL15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23059,31 +23067,31 @@
       </c>
       <c r="CN15" s="24">
         <f t="shared" si="40"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="CO15" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP15" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CQ15" s="24">
         <f t="shared" si="41"/>
-        <v>18</v>
+        <v>12.7</v>
       </c>
       <c r="CR15" s="25">
         <f t="shared" si="42"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="CS15" s="25">
         <f t="shared" si="43"/>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="CT15" s="25">
         <f t="shared" si="44"/>
-        <v>11.4</v>
+        <v>10.5555555555556</v>
       </c>
     </row>
     <row r="16" spans="1:98">
@@ -23180,27 +23188,27 @@
       </c>
       <c r="X16" s="24">
         <f t="shared" si="8"/>
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="Y16" s="23">
         <f t="shared" si="9"/>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="Z16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA16" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB16" s="24">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="AC16" s="23">
         <f t="shared" si="11"/>
-        <v>1.11111111111111</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="AD16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23228,7 +23236,7 @@
       </c>
       <c r="AJ16" s="24">
         <f t="shared" si="14"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="AK16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23256,7 +23264,7 @@
       </c>
       <c r="AQ16" s="23">
         <f t="shared" si="17"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AR16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23268,27 +23276,27 @@
       </c>
       <c r="AT16" s="24">
         <f t="shared" si="18"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AU16" s="23">
         <f t="shared" si="19"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AV16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW16" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX16" s="24">
         <f t="shared" si="20"/>
-        <v>36</v>
+        <v>9.5</v>
       </c>
       <c r="AY16" s="23">
         <f t="shared" si="21"/>
-        <v>0.277777777777778</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AZ16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23316,7 +23324,7 @@
       </c>
       <c r="BF16" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23360,11 +23368,11 @@
       </c>
       <c r="BQ16" s="24">
         <f t="shared" si="29"/>
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR16" s="23">
         <f t="shared" si="30"/>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="BS16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23392,11 +23400,11 @@
       </c>
       <c r="BY16" s="24">
         <f t="shared" si="33"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="BZ16" s="23">
         <f t="shared" si="34"/>
-        <v>2.66666666666667</v>
+        <v>2.52631578947368</v>
       </c>
       <c r="CA16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23408,11 +23416,11 @@
       </c>
       <c r="CC16" s="24">
         <f t="shared" si="35"/>
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="CD16" s="23">
         <f t="shared" si="36"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="CE16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23424,11 +23432,11 @@
       </c>
       <c r="CG16" s="24">
         <f t="shared" si="37"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="CH16" s="23">
         <f t="shared" si="38"/>
-        <v>1.55555555555556</v>
+        <v>1.47368421052632</v>
       </c>
       <c r="CI16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23440,7 +23448,7 @@
       </c>
       <c r="CK16" s="24">
         <f t="shared" si="39"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CL16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23452,7 +23460,7 @@
       </c>
       <c r="CN16" s="24">
         <f t="shared" si="40"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CO16" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23464,19 +23472,19 @@
       </c>
       <c r="CQ16" s="24">
         <f t="shared" si="41"/>
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CR16" s="25">
         <f t="shared" si="42"/>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="CS16" s="25">
         <f t="shared" si="43"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="CT16" s="25">
         <f t="shared" si="44"/>
-        <v>10.741935483871</v>
+        <v>10.390625</v>
       </c>
     </row>
     <row r="17" spans="1:98">
@@ -23573,11 +23581,11 @@
       </c>
       <c r="X17" s="24">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="Y17" s="23">
         <f t="shared" si="9"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="Z17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23589,11 +23597,11 @@
       </c>
       <c r="AB17" s="24">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC17" s="23">
         <f t="shared" si="11"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AD17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23621,7 +23629,7 @@
       </c>
       <c r="AJ17" s="24">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23661,11 +23669,11 @@
       </c>
       <c r="AT17" s="24">
         <f t="shared" si="18"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AU17" s="23">
         <f t="shared" si="19"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AV17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23741,7 +23749,7 @@
       </c>
       <c r="BN17" s="23">
         <f t="shared" si="28"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BO17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23757,7 +23765,7 @@
       </c>
       <c r="BR17" s="23">
         <f t="shared" si="30"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BS17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23801,11 +23809,11 @@
       </c>
       <c r="CC17" s="24">
         <f t="shared" si="35"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CD17" s="23">
         <f t="shared" si="36"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="CE17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23817,11 +23825,11 @@
       </c>
       <c r="CG17" s="24">
         <f t="shared" si="37"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CH17" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI17" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23869,7 +23877,7 @@
       </c>
       <c r="CT17" s="25">
         <f t="shared" si="44"/>
-        <v>29.0769230769231</v>
+        <v>30.6923076923077</v>
       </c>
     </row>
     <row r="18" spans="1:98">
@@ -23966,27 +23974,27 @@
       </c>
       <c r="X18" s="24">
         <f t="shared" si="8"/>
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" s="23">
         <f t="shared" si="9"/>
-        <v>6.38888888888889</v>
+        <v>6.05263157894737</v>
       </c>
       <c r="Z18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA18" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB18" s="24">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AC18" s="23">
         <f t="shared" si="11"/>
-        <v>3.88888888888889</v>
+        <v>3.94736842105263</v>
       </c>
       <c r="AD18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24006,15 +24014,15 @@
       </c>
       <c r="AH18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI18" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="24">
         <f t="shared" si="14"/>
-        <v/>
+        <v>76</v>
       </c>
       <c r="AK18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24042,7 +24050,7 @@
       </c>
       <c r="AQ18" s="23">
         <f t="shared" si="17"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AR18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24054,11 +24062,11 @@
       </c>
       <c r="AT18" s="24">
         <f t="shared" si="18"/>
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="AU18" s="23">
         <f t="shared" si="19"/>
-        <v>1.38888888888889</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="AV18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24070,11 +24078,11 @@
       </c>
       <c r="AX18" s="24">
         <f t="shared" si="20"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AY18" s="23">
         <f t="shared" si="21"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AZ18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24102,7 +24110,7 @@
       </c>
       <c r="BF18" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24134,7 +24142,7 @@
       </c>
       <c r="BN18" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24146,11 +24154,11 @@
       </c>
       <c r="BQ18" s="24">
         <f t="shared" si="29"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BR18" s="23">
         <f t="shared" si="30"/>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="BS18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24178,11 +24186,11 @@
       </c>
       <c r="BY18" s="24">
         <f t="shared" si="33"/>
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="BZ18" s="23">
         <f t="shared" si="34"/>
-        <v>3.55555555555556</v>
+        <v>3.36842105263158</v>
       </c>
       <c r="CA18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24194,27 +24202,27 @@
       </c>
       <c r="CC18" s="24">
         <f t="shared" si="35"/>
-        <v>9.7</v>
+        <v>10.2</v>
       </c>
       <c r="CD18" s="23">
         <f t="shared" si="36"/>
-        <v>3.61111111111111</v>
+        <v>3.42105263157895</v>
       </c>
       <c r="CE18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CF18" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CG18" s="24">
         <f t="shared" si="37"/>
-        <v>15.8</v>
+        <v>12.7</v>
       </c>
       <c r="CH18" s="23">
         <f t="shared" si="38"/>
-        <v>3.11111111111111</v>
+        <v>3.31578947368421</v>
       </c>
       <c r="CI18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24226,7 +24234,7 @@
       </c>
       <c r="CK18" s="24">
         <f t="shared" si="39"/>
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="CL18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24242,27 +24250,27 @@
       </c>
       <c r="CO18" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP18" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CQ18" s="24">
         <f t="shared" si="41"/>
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="CR18" s="25">
         <f t="shared" si="42"/>
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="CS18" s="25">
         <f t="shared" si="43"/>
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="CT18" s="25">
         <f t="shared" si="44"/>
-        <v>9.56756756756757</v>
+        <v>9.08695652173913</v>
       </c>
     </row>
     <row r="19" spans="1:98">
@@ -24359,11 +24367,11 @@
       </c>
       <c r="X19" s="24">
         <f t="shared" si="8"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y19" s="23">
         <f t="shared" si="9"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="Z19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24379,7 +24387,7 @@
       </c>
       <c r="AC19" s="23">
         <f t="shared" si="11"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AD19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24395,7 +24403,7 @@
       </c>
       <c r="AG19" s="23">
         <f t="shared" si="13"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AH19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24431,11 +24439,11 @@
       </c>
       <c r="AP19" s="24">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ19" s="23">
         <f t="shared" si="17"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AR19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24495,7 +24503,7 @@
       </c>
       <c r="BF19" s="23">
         <f t="shared" si="24"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BG19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24527,7 +24535,7 @@
       </c>
       <c r="BN19" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24587,11 +24595,11 @@
       </c>
       <c r="CC19" s="24">
         <f t="shared" si="35"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CD19" s="23">
         <f t="shared" si="36"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="CE19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24603,11 +24611,11 @@
       </c>
       <c r="CG19" s="24">
         <f t="shared" si="37"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CH19" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24635,27 +24643,27 @@
       </c>
       <c r="CO19" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP19" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="CQ19" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="CQ19" s="24">
         <f t="shared" si="41"/>
-        <v/>
+        <v>19</v>
       </c>
       <c r="CR19" s="25">
         <f t="shared" si="42"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CS19" s="25">
         <f t="shared" si="43"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CT19" s="25">
         <f t="shared" si="44"/>
-        <v>31.0909090909091</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="20" spans="1:98">
@@ -24696,11 +24704,11 @@
       </c>
       <c r="J20" s="24">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="K20" s="23">
         <f t="shared" si="3"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="L20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24744,35 +24752,35 @@
       </c>
       <c r="V20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X20" s="24">
         <f t="shared" si="8"/>
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y20" s="23">
         <f t="shared" si="9"/>
-        <v>5.27777777777778</v>
+        <v>5.52631578947368</v>
       </c>
       <c r="Z20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB20" s="24">
         <f t="shared" si="10"/>
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="AC20" s="23">
         <f t="shared" si="11"/>
-        <v>4.44444444444444</v>
+        <v>4.73684210526316</v>
       </c>
       <c r="AD20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24788,7 +24796,7 @@
       </c>
       <c r="AG20" s="23">
         <f t="shared" si="13"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AH20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24816,51 +24824,51 @@
       </c>
       <c r="AN20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP20" s="24">
         <f t="shared" si="16"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AQ20" s="23">
         <f t="shared" si="17"/>
-        <v>1.66666666666667</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="AR20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT20" s="24">
         <f t="shared" si="18"/>
-        <v>45</v>
+        <v>25.3</v>
       </c>
       <c r="AU20" s="23">
         <f t="shared" si="19"/>
-        <v>0.555555555555556</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AV20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX20" s="24">
         <f t="shared" si="20"/>
-        <v>18</v>
+        <v>11.4</v>
       </c>
       <c r="AY20" s="23">
         <f t="shared" si="21"/>
-        <v>1.11111111111111</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="AZ20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24884,11 +24892,11 @@
       </c>
       <c r="BE20" s="24">
         <f t="shared" si="23"/>
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="BF20" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24932,11 +24940,11 @@
       </c>
       <c r="BQ20" s="24">
         <f t="shared" si="29"/>
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="BR20" s="23">
         <f t="shared" si="30"/>
-        <v>1.77777777777778</v>
+        <v>1.68421052631579</v>
       </c>
       <c r="BS20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24964,43 +24972,43 @@
       </c>
       <c r="BY20" s="24">
         <f t="shared" si="33"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BZ20" s="23">
         <f t="shared" si="34"/>
-        <v>1.33333333333333</v>
+        <v>1.26315789473684</v>
       </c>
       <c r="CA20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CB20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CC20" s="24">
         <f t="shared" si="35"/>
-        <v>10.8</v>
+        <v>8.6</v>
       </c>
       <c r="CD20" s="23">
         <f t="shared" si="36"/>
-        <v>2.77777777777778</v>
+        <v>2.89473684210526</v>
       </c>
       <c r="CE20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CF20" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CG20" s="24">
         <f t="shared" si="37"/>
-        <v>30.9</v>
+        <v>26.1</v>
       </c>
       <c r="CH20" s="23">
         <f t="shared" si="38"/>
-        <v>2.72222222222222</v>
+        <v>2.94736842105263</v>
       </c>
       <c r="CI20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25012,7 +25020,7 @@
       </c>
       <c r="CK20" s="24">
         <f t="shared" si="39"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="CL20" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25036,19 +25044,19 @@
       </c>
       <c r="CQ20" s="24">
         <f t="shared" si="41"/>
-        <v>7.9</v>
+        <v>8.3</v>
       </c>
       <c r="CR20" s="25">
         <f t="shared" si="42"/>
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="CS20" s="25">
         <f t="shared" si="43"/>
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="CT20" s="25">
         <f t="shared" si="44"/>
-        <v>10.0862068965517</v>
+        <v>8.29365079365079</v>
       </c>
     </row>
     <row r="21" spans="1:98">
@@ -25145,11 +25153,11 @@
       </c>
       <c r="X21" s="24">
         <f t="shared" si="8"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y21" s="23">
         <f t="shared" si="9"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="Z21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25161,11 +25169,11 @@
       </c>
       <c r="AB21" s="24">
         <f t="shared" si="10"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC21" s="23">
         <f t="shared" si="11"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25193,7 +25201,7 @@
       </c>
       <c r="AJ21" s="24">
         <f t="shared" si="14"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="AK21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25205,7 +25213,7 @@
       </c>
       <c r="AM21" s="24">
         <f t="shared" si="15"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AN21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25217,11 +25225,11 @@
       </c>
       <c r="AP21" s="24">
         <f t="shared" si="16"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ21" s="23">
         <f t="shared" si="17"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AR21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25249,11 +25257,11 @@
       </c>
       <c r="AX21" s="24">
         <f t="shared" si="20"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY21" s="23">
         <f t="shared" si="21"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AZ21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25277,11 +25285,11 @@
       </c>
       <c r="BE21" s="24">
         <f t="shared" si="23"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="BF21" s="23">
         <f t="shared" si="24"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BG21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25357,11 +25365,11 @@
       </c>
       <c r="BY21" s="24">
         <f t="shared" si="33"/>
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="BZ21" s="23">
         <f t="shared" si="34"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="CA21" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25429,7 +25437,7 @@
       </c>
       <c r="CQ21" s="24">
         <f t="shared" si="41"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="CR21" s="25">
         <f t="shared" si="42"/>
@@ -25441,7 +25449,7 @@
       </c>
       <c r="CT21" s="25">
         <f t="shared" si="44"/>
-        <v>56.7692307692308</v>
+        <v>59.9230769230769</v>
       </c>
     </row>
     <row r="22" spans="1:98">
@@ -25486,7 +25494,7 @@
       </c>
       <c r="K22" s="23">
         <f t="shared" si="3"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="L22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25538,11 +25546,11 @@
       </c>
       <c r="X22" s="24">
         <f t="shared" si="8"/>
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" s="23">
         <f t="shared" si="9"/>
-        <v>11.3888888888889</v>
+        <v>10.7894736842105</v>
       </c>
       <c r="Z22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25554,11 +25562,11 @@
       </c>
       <c r="AB22" s="24">
         <f t="shared" si="10"/>
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="AC22" s="23">
         <f t="shared" si="11"/>
-        <v>4.72222222222222</v>
+        <v>4.47368421052632</v>
       </c>
       <c r="AD22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25570,23 +25578,23 @@
       </c>
       <c r="AF22" s="24">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG22" s="23">
         <f t="shared" si="13"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AH22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI22" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ22" s="24">
         <f t="shared" si="14"/>
-        <v>21.6</v>
+        <v>15.8</v>
       </c>
       <c r="AK22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25614,7 +25622,7 @@
       </c>
       <c r="AQ22" s="23">
         <f t="shared" si="17"/>
-        <v>2.5</v>
+        <v>2.36842105263158</v>
       </c>
       <c r="AR22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25626,11 +25634,11 @@
       </c>
       <c r="AT22" s="24">
         <f t="shared" si="18"/>
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="AU22" s="23">
         <f t="shared" si="19"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AV22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25642,11 +25650,11 @@
       </c>
       <c r="AX22" s="24">
         <f t="shared" si="20"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="AY22" s="23">
         <f t="shared" si="21"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AZ22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25674,7 +25682,7 @@
       </c>
       <c r="BF22" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25706,7 +25714,7 @@
       </c>
       <c r="BN22" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25718,11 +25726,11 @@
       </c>
       <c r="BQ22" s="24">
         <f t="shared" si="29"/>
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="BR22" s="23">
         <f t="shared" si="30"/>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="BS22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25750,11 +25758,11 @@
       </c>
       <c r="BY22" s="24">
         <f t="shared" si="33"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="BZ22" s="23">
         <f t="shared" si="34"/>
-        <v>2.66666666666667</v>
+        <v>2.52631578947368</v>
       </c>
       <c r="CA22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25766,27 +25774,27 @@
       </c>
       <c r="CC22" s="24">
         <f t="shared" si="35"/>
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CD22" s="23">
         <f t="shared" si="36"/>
-        <v>5.27777777777778</v>
+        <v>5</v>
       </c>
       <c r="CE22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CF22" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CG22" s="24">
         <f t="shared" si="37"/>
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="CH22" s="23">
         <f t="shared" si="38"/>
-        <v>6.61111111111111</v>
+        <v>6.63157894736842</v>
       </c>
       <c r="CI22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25798,7 +25806,7 @@
       </c>
       <c r="CK22" s="24">
         <f t="shared" si="39"/>
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="CL22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25810,7 +25818,7 @@
       </c>
       <c r="CN22" s="24">
         <f t="shared" si="40"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CO22" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25822,19 +25830,19 @@
       </c>
       <c r="CQ22" s="24">
         <f t="shared" si="41"/>
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="CR22" s="25">
         <f t="shared" si="42"/>
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="CS22" s="25">
         <f t="shared" si="43"/>
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="CT22" s="25">
         <f t="shared" si="44"/>
-        <v>6.85714285714286</v>
+        <v>6.92941176470588</v>
       </c>
     </row>
     <row r="23" spans="1:98">
@@ -25879,7 +25887,7 @@
       </c>
       <c r="K23" s="23">
         <f t="shared" si="3"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="L23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25931,27 +25939,27 @@
       </c>
       <c r="X23" s="24">
         <f t="shared" si="8"/>
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Y23" s="23">
         <f t="shared" si="9"/>
-        <v>6.38888888888889</v>
+        <v>6.05263157894737</v>
       </c>
       <c r="Z23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB23" s="24">
         <f t="shared" si="10"/>
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
       <c r="AC23" s="23">
         <f t="shared" si="11"/>
-        <v>3.61111111111111</v>
+        <v>3.68421052631579</v>
       </c>
       <c r="AD23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25963,11 +25971,11 @@
       </c>
       <c r="AF23" s="24">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG23" s="23">
         <f t="shared" si="13"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AH23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25979,7 +25987,7 @@
       </c>
       <c r="AJ23" s="24">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26003,11 +26011,11 @@
       </c>
       <c r="AP23" s="24">
         <f t="shared" si="16"/>
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="AQ23" s="23">
         <f t="shared" si="17"/>
-        <v>1.94444444444444</v>
+        <v>1.84210526315789</v>
       </c>
       <c r="AR23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26019,11 +26027,11 @@
       </c>
       <c r="AT23" s="24">
         <f t="shared" si="18"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AU23" s="23">
         <f t="shared" si="19"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AV23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26035,11 +26043,11 @@
       </c>
       <c r="AX23" s="24">
         <f t="shared" si="20"/>
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY23" s="23">
         <f t="shared" si="21"/>
-        <v>2.5</v>
+        <v>2.36842105263158</v>
       </c>
       <c r="AZ23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26055,19 +26063,19 @@
       </c>
       <c r="BC23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE23" s="24">
         <f t="shared" si="23"/>
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="BF23" s="23">
         <f t="shared" si="24"/>
-        <v>2.22222222222222</v>
+        <v>2.52631578947368</v>
       </c>
       <c r="BG23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26099,7 +26107,7 @@
       </c>
       <c r="BN23" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26111,11 +26119,11 @@
       </c>
       <c r="BQ23" s="24">
         <f t="shared" si="29"/>
-        <v>25.2</v>
+        <v>26.6</v>
       </c>
       <c r="BR23" s="23">
         <f t="shared" si="30"/>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="BS23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26135,35 +26143,35 @@
       </c>
       <c r="BW23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BX23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BY23" s="24">
         <f t="shared" si="33"/>
-        <v>22.5</v>
+        <v>15.2</v>
       </c>
       <c r="BZ23" s="23">
         <f t="shared" si="34"/>
-        <v>1.77777777777778</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="CA23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CB23" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CC23" s="24">
         <f t="shared" si="35"/>
-        <v>11.1</v>
+        <v>7.6</v>
       </c>
       <c r="CD23" s="23">
         <f t="shared" si="36"/>
-        <v>3.61111111111111</v>
+        <v>3.94736842105263</v>
       </c>
       <c r="CE23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26175,11 +26183,11 @@
       </c>
       <c r="CG23" s="24">
         <f t="shared" si="37"/>
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="CH23" s="23">
         <f t="shared" si="38"/>
-        <v>6.61111111111111</v>
+        <v>6.26315789473684</v>
       </c>
       <c r="CI23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26191,7 +26199,7 @@
       </c>
       <c r="CK23" s="24">
         <f t="shared" si="39"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CL23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26203,7 +26211,7 @@
       </c>
       <c r="CN23" s="24">
         <f t="shared" si="40"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CO23" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26215,19 +26223,19 @@
       </c>
       <c r="CQ23" s="24">
         <f t="shared" si="41"/>
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="CR23" s="25">
         <f t="shared" si="42"/>
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="CS23" s="25">
         <f t="shared" si="43"/>
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="CT23" s="25">
         <f t="shared" si="44"/>
-        <v>8.39189189189189</v>
+        <v>7.94771241830065</v>
       </c>
     </row>
     <row r="24" spans="1:98">
@@ -26324,11 +26332,11 @@
       </c>
       <c r="X24" s="24">
         <f t="shared" si="8"/>
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Y24" s="23">
         <f t="shared" si="9"/>
-        <v>1.38888888888889</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="Z24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26340,11 +26348,11 @@
       </c>
       <c r="AB24" s="24">
         <f t="shared" si="10"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC24" s="23">
         <f t="shared" si="11"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26396,11 +26404,11 @@
       </c>
       <c r="AP24" s="24">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ24" s="23">
         <f t="shared" si="17"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AR24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26460,7 +26468,7 @@
       </c>
       <c r="BF24" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26492,7 +26500,7 @@
       </c>
       <c r="BN24" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26504,11 +26512,11 @@
       </c>
       <c r="BQ24" s="24">
         <f t="shared" si="29"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BR24" s="23">
         <f t="shared" si="30"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BS24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26552,11 +26560,11 @@
       </c>
       <c r="CC24" s="24">
         <f t="shared" si="35"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CD24" s="23">
         <f t="shared" si="36"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="CE24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26584,7 +26592,7 @@
       </c>
       <c r="CK24" s="24">
         <f t="shared" si="39"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CL24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26596,7 +26604,7 @@
       </c>
       <c r="CN24" s="24">
         <f t="shared" si="40"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CO24" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26608,7 +26616,7 @@
       </c>
       <c r="CQ24" s="24">
         <f t="shared" si="41"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CR24" s="25">
         <f t="shared" si="42"/>
@@ -26620,7 +26628,7 @@
       </c>
       <c r="CT24" s="25">
         <f t="shared" si="44"/>
-        <v>26.5714285714286</v>
+        <v>28.047619047619</v>
       </c>
     </row>
     <row r="25" spans="1:98">
@@ -26649,7 +26657,7 @@
       </c>
       <c r="G25" s="24">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26717,11 +26725,11 @@
       </c>
       <c r="X25" s="24">
         <f t="shared" si="8"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y25" s="23">
         <f t="shared" si="9"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="Z25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26733,11 +26741,11 @@
       </c>
       <c r="AB25" s="24">
         <f t="shared" si="10"/>
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="AC25" s="23">
         <f t="shared" si="11"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AD25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26757,7 +26765,7 @@
       </c>
       <c r="AH25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI25" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26765,7 +26773,7 @@
       </c>
       <c r="AJ25" s="24">
         <f t="shared" si="14"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AK25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26789,11 +26797,11 @@
       </c>
       <c r="AP25" s="24">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ25" s="23">
         <f t="shared" si="17"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AR25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26869,7 +26877,7 @@
       </c>
       <c r="BJ25" s="23">
         <f t="shared" si="26"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BK25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26885,7 +26893,7 @@
       </c>
       <c r="BN25" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26921,7 +26929,7 @@
       </c>
       <c r="BW25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX25" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26945,11 +26953,11 @@
       </c>
       <c r="CC25" s="24">
         <f t="shared" si="35"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="CD25" s="23">
         <f t="shared" si="36"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="CE25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26961,11 +26969,11 @@
       </c>
       <c r="CG25" s="24">
         <f t="shared" si="37"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="CH25" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26977,7 +26985,7 @@
       </c>
       <c r="CK25" s="24">
         <f t="shared" si="39"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CL25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26989,11 +26997,11 @@
       </c>
       <c r="CN25" s="24">
         <f t="shared" si="40"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CO25" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CP25" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27001,11 +27009,11 @@
       </c>
       <c r="CQ25" s="24">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="CR25" s="25">
         <f t="shared" si="42"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="CS25" s="25">
         <f t="shared" si="43"/>
@@ -27013,7 +27021,7 @@
       </c>
       <c r="CT25" s="25">
         <f t="shared" si="44"/>
-        <v>20.4545454545455</v>
+        <v>25.0454545454545</v>
       </c>
     </row>
     <row r="26" spans="1:98">
@@ -27110,11 +27118,11 @@
       </c>
       <c r="X26" s="24">
         <f t="shared" si="8"/>
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="Y26" s="23">
         <f t="shared" si="9"/>
-        <v>2.22222222222222</v>
+        <v>2.10526315789474</v>
       </c>
       <c r="Z26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27126,11 +27134,11 @@
       </c>
       <c r="AB26" s="24">
         <f t="shared" si="10"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AC26" s="23">
         <f t="shared" si="11"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27150,7 +27158,7 @@
       </c>
       <c r="AH26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27158,7 +27166,7 @@
       </c>
       <c r="AJ26" s="24">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AK26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27170,7 +27178,7 @@
       </c>
       <c r="AM26" s="24">
         <f t="shared" si="15"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27182,11 +27190,11 @@
       </c>
       <c r="AP26" s="24">
         <f t="shared" si="16"/>
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AQ26" s="23">
         <f t="shared" si="17"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AR26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27206,19 +27214,19 @@
       </c>
       <c r="AV26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW26" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX26" s="24">
         <f t="shared" si="20"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY26" s="23">
         <f t="shared" si="21"/>
-        <v>0.833333333333333</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AZ26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27234,19 +27242,19 @@
       </c>
       <c r="BC26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD26" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE26" s="24">
         <f t="shared" si="23"/>
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="BF26" s="23">
         <f t="shared" si="24"/>
-        <v>0.444444444444444</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27278,7 +27286,7 @@
       </c>
       <c r="BN26" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27290,11 +27298,11 @@
       </c>
       <c r="BQ26" s="24">
         <f t="shared" si="29"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BR26" s="23">
         <f t="shared" si="30"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BS26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27306,15 +27314,15 @@
       </c>
       <c r="BU26" s="24">
         <f t="shared" si="31"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BV26" s="23">
         <f t="shared" si="32"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BW26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX26" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27322,11 +27330,11 @@
       </c>
       <c r="BY26" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BZ26" s="23">
         <f t="shared" si="34"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="CA26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27338,15 +27346,15 @@
       </c>
       <c r="CC26" s="24">
         <f t="shared" si="35"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CD26" s="23">
         <f t="shared" si="36"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="CE26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CF26" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27354,15 +27362,15 @@
       </c>
       <c r="CG26" s="24">
         <f t="shared" si="37"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CH26" s="23">
         <f t="shared" si="38"/>
-        <v>1.16666666666667</v>
+        <v>1.10526315789474</v>
       </c>
       <c r="CI26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ26" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27370,7 +27378,7 @@
       </c>
       <c r="CK26" s="24">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CL26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27382,11 +27390,11 @@
       </c>
       <c r="CN26" s="24">
         <f t="shared" si="40"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CO26" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CP26" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27394,19 +27402,19 @@
       </c>
       <c r="CQ26" s="24">
         <f t="shared" si="41"/>
-        <v>3.6</v>
+        <v>11.4</v>
       </c>
       <c r="CR26" s="25">
         <f t="shared" si="42"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="CS26" s="25">
         <f t="shared" si="43"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="CT26" s="25">
         <f t="shared" si="44"/>
-        <v>14.1081081081081</v>
+        <v>16.0769230769231</v>
       </c>
     </row>
     <row r="27" spans="1:98">
@@ -27495,23 +27503,23 @@
       </c>
       <c r="V27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X27" s="24">
         <f t="shared" si="8"/>
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y27" s="23">
         <f t="shared" si="9"/>
-        <v>1.11111111111111</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="Z27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA27" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27519,11 +27527,11 @@
       </c>
       <c r="AB27" s="24">
         <f t="shared" si="10"/>
-        <v>4.5</v>
+        <v>23.8</v>
       </c>
       <c r="AC27" s="23">
         <f t="shared" si="11"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AD27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27551,11 +27559,11 @@
       </c>
       <c r="AJ27" s="24">
         <f t="shared" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL27" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27563,11 +27571,11 @@
       </c>
       <c r="AM27" s="24">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AN27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO27" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27575,11 +27583,11 @@
       </c>
       <c r="AP27" s="24">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="AQ27" s="23">
         <f t="shared" si="17"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AR27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27591,11 +27599,11 @@
       </c>
       <c r="AT27" s="24">
         <f t="shared" si="18"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AU27" s="23">
         <f t="shared" si="19"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AV27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27635,11 +27643,11 @@
       </c>
       <c r="BE27" s="24">
         <f t="shared" si="23"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BF27" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27671,7 +27679,7 @@
       </c>
       <c r="BN27" s="23">
         <f t="shared" si="28"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BO27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27707,7 +27715,7 @@
       </c>
       <c r="BW27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BX27" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27715,11 +27723,11 @@
       </c>
       <c r="BY27" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="BZ27" s="23">
         <f t="shared" si="34"/>
-        <v>1.33333333333333</v>
+        <v>1.26315789473684</v>
       </c>
       <c r="CA27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27747,11 +27755,11 @@
       </c>
       <c r="CG27" s="24">
         <f t="shared" si="37"/>
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="CH27" s="23">
         <f t="shared" si="38"/>
-        <v>0.777777777777778</v>
+        <v>0.736842105263158</v>
       </c>
       <c r="CI27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27775,11 +27783,11 @@
       </c>
       <c r="CN27" s="24">
         <f t="shared" si="40"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CO27" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CP27" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27787,19 +27795,19 @@
       </c>
       <c r="CQ27" s="24">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="CR27" s="25">
         <f t="shared" si="42"/>
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="CS27" s="25">
         <f t="shared" si="43"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CT27" s="25">
         <f t="shared" si="44"/>
-        <v>16.7142857142857</v>
+        <v>28.1724137931034</v>
       </c>
     </row>
     <row r="28" spans="1:98">
@@ -27840,11 +27848,11 @@
       </c>
       <c r="J28" s="24">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K28" s="23">
         <f t="shared" si="3"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="L28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27896,11 +27904,11 @@
       </c>
       <c r="X28" s="24">
         <f t="shared" si="8"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="Y28" s="23">
         <f t="shared" si="9"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="Z28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27912,11 +27920,11 @@
       </c>
       <c r="AB28" s="24">
         <f t="shared" si="10"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC28" s="23">
         <f t="shared" si="11"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="AD28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27956,7 +27964,7 @@
       </c>
       <c r="AM28" s="24">
         <f t="shared" si="15"/>
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="AN28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27968,11 +27976,11 @@
       </c>
       <c r="AP28" s="24">
         <f t="shared" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ28" s="23">
         <f t="shared" si="17"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AR28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27992,19 +28000,19 @@
       </c>
       <c r="AV28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW28" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AX28" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX28" s="24">
         <f t="shared" si="20"/>
-        <v/>
+        <v>19</v>
       </c>
       <c r="AY28" s="23">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AZ28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28028,11 +28036,11 @@
       </c>
       <c r="BE28" s="24">
         <f t="shared" si="23"/>
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="BF28" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28064,7 +28072,7 @@
       </c>
       <c r="BN28" s="23">
         <f t="shared" si="28"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BO28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28076,11 +28084,11 @@
       </c>
       <c r="BQ28" s="24">
         <f t="shared" si="29"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="BR28" s="23">
         <f t="shared" si="30"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BS28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28096,7 +28104,7 @@
       </c>
       <c r="BV28" s="23">
         <f t="shared" si="32"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BW28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28108,11 +28116,11 @@
       </c>
       <c r="BY28" s="24">
         <f t="shared" si="33"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="BZ28" s="23">
         <f t="shared" si="34"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="CA28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28124,11 +28132,11 @@
       </c>
       <c r="CC28" s="24">
         <f t="shared" si="35"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="CD28" s="23">
         <f t="shared" si="36"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="CE28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28140,11 +28148,11 @@
       </c>
       <c r="CG28" s="24">
         <f t="shared" si="37"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="CH28" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI28" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28180,19 +28188,19 @@
       </c>
       <c r="CQ28" s="24">
         <f t="shared" si="41"/>
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CR28" s="25">
         <f t="shared" si="42"/>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CS28" s="25">
         <f t="shared" si="43"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CT28" s="25">
         <f t="shared" si="44"/>
-        <v>40.5</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="29" spans="1:98">
@@ -28233,11 +28241,11 @@
       </c>
       <c r="J29" s="24">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K29" s="23">
         <f t="shared" si="3"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="L29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28289,11 +28297,11 @@
       </c>
       <c r="X29" s="24">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="Y29" s="23">
         <f t="shared" si="9"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="Z29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28305,11 +28313,11 @@
       </c>
       <c r="AB29" s="24">
         <f t="shared" si="10"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC29" s="23">
         <f t="shared" si="11"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28349,7 +28357,7 @@
       </c>
       <c r="AM29" s="24">
         <f t="shared" si="15"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AN29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28421,11 +28429,11 @@
       </c>
       <c r="BE29" s="24">
         <f t="shared" si="23"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="BF29" s="23">
         <f t="shared" si="24"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BG29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28517,11 +28525,11 @@
       </c>
       <c r="CC29" s="24">
         <f t="shared" si="35"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="CD29" s="23">
         <f t="shared" si="36"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="CE29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28533,11 +28541,11 @@
       </c>
       <c r="CG29" s="24">
         <f t="shared" si="37"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CH29" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28561,7 +28569,7 @@
       </c>
       <c r="CN29" s="24">
         <f t="shared" si="40"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="CO29" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28573,7 +28581,7 @@
       </c>
       <c r="CQ29" s="24">
         <f t="shared" si="41"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CR29" s="25">
         <f t="shared" si="42"/>
@@ -28585,7 +28593,7 @@
       </c>
       <c r="CT29" s="25">
         <f t="shared" si="44"/>
-        <v>76.9090909090909</v>
+        <v>81.1818181818182</v>
       </c>
     </row>
     <row r="30" spans="1:98">
@@ -28730,7 +28738,7 @@
       </c>
       <c r="AJ30" s="24">
         <f t="shared" si="14"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AK30" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28758,7 +28766,7 @@
       </c>
       <c r="AQ30" s="23">
         <f t="shared" si="17"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AR30" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28910,11 +28918,11 @@
       </c>
       <c r="CC30" s="24">
         <f t="shared" si="35"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CD30" s="23">
         <f t="shared" si="36"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="CE30" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28942,7 +28950,7 @@
       </c>
       <c r="CK30" s="24">
         <f t="shared" si="39"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CL30" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28978,7 +28986,7 @@
       </c>
       <c r="CT30" s="25">
         <f t="shared" si="44"/>
-        <v>103.5</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="31" spans="1:98">
@@ -29075,11 +29083,11 @@
       </c>
       <c r="X31" s="24">
         <f t="shared" si="8"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y31" s="23">
         <f t="shared" si="9"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="Z31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29091,11 +29099,11 @@
       </c>
       <c r="AB31" s="24">
         <f t="shared" si="10"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AC31" s="23">
         <f t="shared" si="11"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29107,11 +29115,11 @@
       </c>
       <c r="AF31" s="24">
         <f t="shared" si="12"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG31" s="23">
         <f t="shared" si="13"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AH31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29135,7 +29143,7 @@
       </c>
       <c r="AM31" s="24">
         <f t="shared" si="15"/>
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AN31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29151,7 +29159,7 @@
       </c>
       <c r="AQ31" s="23">
         <f t="shared" si="17"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="AR31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29243,7 +29251,7 @@
       </c>
       <c r="BN31" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29255,11 +29263,11 @@
       </c>
       <c r="BQ31" s="24">
         <f t="shared" si="29"/>
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="BR31" s="23">
         <f t="shared" si="30"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BS31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29287,11 +29295,11 @@
       </c>
       <c r="BY31" s="24">
         <f t="shared" si="33"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BZ31" s="23">
         <f t="shared" si="34"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="CA31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29319,11 +29327,11 @@
       </c>
       <c r="CG31" s="24">
         <f t="shared" si="37"/>
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="CH31" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29335,7 +29343,7 @@
       </c>
       <c r="CK31" s="24">
         <f t="shared" si="39"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="CL31" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29359,7 +29367,7 @@
       </c>
       <c r="CQ31" s="24">
         <f t="shared" si="41"/>
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="CR31" s="25">
         <f t="shared" si="42"/>
@@ -29371,7 +29379,7 @@
       </c>
       <c r="CT31" s="25">
         <f t="shared" si="44"/>
-        <v>42.8571428571429</v>
+        <v>45.2380952380952</v>
       </c>
     </row>
     <row r="32" spans="1:98">
@@ -29400,7 +29408,7 @@
       </c>
       <c r="G32" s="24">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29412,11 +29420,11 @@
       </c>
       <c r="J32" s="24">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K32" s="23">
         <f t="shared" si="3"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="L32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29468,11 +29476,11 @@
       </c>
       <c r="X32" s="24">
         <f t="shared" si="8"/>
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="Y32" s="23">
         <f t="shared" si="9"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="Z32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29484,11 +29492,11 @@
       </c>
       <c r="AB32" s="24">
         <f t="shared" si="10"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC32" s="23">
         <f t="shared" si="11"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29508,27 +29516,27 @@
       </c>
       <c r="AH32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI32" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="24" t="str">
+        <v>1</v>
+      </c>
+      <c r="AJ32" s="24">
         <f t="shared" si="14"/>
-        <v/>
+        <v>57</v>
       </c>
       <c r="AK32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL32" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM32" s="24">
         <f t="shared" si="15"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29540,11 +29548,11 @@
       </c>
       <c r="AP32" s="24">
         <f t="shared" si="16"/>
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AQ32" s="23">
         <f t="shared" si="17"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AR32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29576,7 +29584,7 @@
       </c>
       <c r="AY32" s="23">
         <f t="shared" si="21"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AZ32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29600,11 +29608,11 @@
       </c>
       <c r="BE32" s="24">
         <f t="shared" si="23"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF32" s="23">
         <f t="shared" si="24"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BG32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29668,7 +29676,7 @@
       </c>
       <c r="BV32" s="23">
         <f t="shared" si="32"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BW32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29696,11 +29704,11 @@
       </c>
       <c r="CC32" s="24">
         <f t="shared" si="35"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CD32" s="23">
         <f t="shared" si="36"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="CE32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29712,11 +29720,11 @@
       </c>
       <c r="CG32" s="24">
         <f t="shared" si="37"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CH32" s="23">
         <f t="shared" si="38"/>
-        <v>0.777777777777778</v>
+        <v>0.736842105263158</v>
       </c>
       <c r="CI32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29728,7 +29736,7 @@
       </c>
       <c r="CK32" s="24">
         <f t="shared" si="39"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CL32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29740,7 +29748,7 @@
       </c>
       <c r="CN32" s="24">
         <f t="shared" si="40"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CO32" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29752,19 +29760,19 @@
       </c>
       <c r="CQ32" s="24">
         <f t="shared" si="41"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CR32" s="25">
         <f t="shared" si="42"/>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="CS32" s="25">
         <f t="shared" si="43"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="CT32" s="25">
         <f t="shared" si="44"/>
-        <v>30.96</v>
+        <v>28.8518518518519</v>
       </c>
     </row>
     <row r="33" spans="1:98">
@@ -29853,19 +29861,19 @@
       </c>
       <c r="V33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W33" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33" s="24">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>10.9</v>
       </c>
       <c r="Y33" s="23">
         <f t="shared" si="9"/>
-        <v>1.66666666666667</v>
+        <v>1.84210526315789</v>
       </c>
       <c r="Z33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29877,11 +29885,11 @@
       </c>
       <c r="AB33" s="24">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="AC33" s="23">
         <f t="shared" si="11"/>
-        <v>0.833333333333333</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AD33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29909,7 +29917,7 @@
       </c>
       <c r="AJ33" s="24">
         <f t="shared" si="14"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AK33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29921,23 +29929,23 @@
       </c>
       <c r="AM33" s="24">
         <f t="shared" si="15"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AN33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP33" s="24">
         <f t="shared" si="16"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ33" s="23">
         <f t="shared" si="17"/>
-        <v>0.555555555555556</v>
+        <v>0.789473684210526</v>
       </c>
       <c r="AR33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29949,11 +29957,11 @@
       </c>
       <c r="AT33" s="24">
         <f t="shared" si="18"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU33" s="23">
         <f t="shared" si="19"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AV33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30029,7 +30037,7 @@
       </c>
       <c r="BN33" s="23">
         <f t="shared" si="28"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BO33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30089,11 +30097,11 @@
       </c>
       <c r="CC33" s="24">
         <f t="shared" si="35"/>
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="CD33" s="23">
         <f t="shared" si="36"/>
-        <v>1.38888888888889</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="CE33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30105,11 +30113,11 @@
       </c>
       <c r="CG33" s="24">
         <f t="shared" si="37"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="CH33" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30121,7 +30129,7 @@
       </c>
       <c r="CK33" s="24">
         <f t="shared" si="39"/>
-        <v>27</v>
+        <v>28.5</v>
       </c>
       <c r="CL33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30133,31 +30141,31 @@
       </c>
       <c r="CN33" s="24">
         <f t="shared" si="40"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="CO33" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP33" s="23">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CQ33" s="24">
         <f t="shared" si="41"/>
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="CR33" s="25">
         <f t="shared" si="42"/>
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="CS33" s="25">
         <f t="shared" si="43"/>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="CT33" s="25">
         <f t="shared" si="44"/>
-        <v>36</v>
+        <v>32.1034482758621</v>
       </c>
     </row>
     <row r="34" spans="1:98">
@@ -30198,11 +30206,11 @@
       </c>
       <c r="J34" s="24">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K34" s="23">
         <f t="shared" si="3"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="L34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30254,11 +30262,11 @@
       </c>
       <c r="X34" s="24">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y34" s="23">
         <f t="shared" si="9"/>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
       <c r="Z34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30270,11 +30278,11 @@
       </c>
       <c r="AB34" s="24">
         <f t="shared" si="10"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC34" s="23">
         <f t="shared" si="11"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30314,7 +30322,7 @@
       </c>
       <c r="AM34" s="24">
         <f t="shared" si="15"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AN34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30326,11 +30334,11 @@
       </c>
       <c r="AP34" s="24">
         <f t="shared" si="16"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ34" s="23">
         <f t="shared" si="17"/>
-        <v>0.277777777777778</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AR34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30386,11 +30394,11 @@
       </c>
       <c r="BE34" s="24">
         <f t="shared" si="23"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BF34" s="23">
         <f t="shared" si="24"/>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BG34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30422,7 +30430,7 @@
       </c>
       <c r="BN34" s="23">
         <f t="shared" si="28"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BO34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30434,11 +30442,11 @@
       </c>
       <c r="BQ34" s="24">
         <f t="shared" si="29"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BR34" s="23">
         <f t="shared" si="30"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BS34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30450,11 +30458,11 @@
       </c>
       <c r="BU34" s="24">
         <f t="shared" si="31"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV34" s="23">
         <f t="shared" si="32"/>
-        <v>0.444444444444444</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="BW34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30482,11 +30490,11 @@
       </c>
       <c r="CC34" s="24">
         <f t="shared" si="35"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="CD34" s="23">
         <f t="shared" si="36"/>
-        <v>1.11111111111111</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="CE34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30498,11 +30506,11 @@
       </c>
       <c r="CG34" s="24">
         <f t="shared" si="37"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="CH34" s="23">
         <f t="shared" si="38"/>
-        <v>0.388888888888889</v>
+        <v>0.368421052631579</v>
       </c>
       <c r="CI34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30526,7 +30534,7 @@
       </c>
       <c r="CN34" s="24">
         <f t="shared" si="40"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CO34" s="22">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30538,7 +30546,7 @@
       </c>
       <c r="CQ34" s="24">
         <f t="shared" si="41"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CR34" s="25">
         <f t="shared" si="42"/>
@@ -30550,7 +30558,7 @@
       </c>
       <c r="CT34" s="25">
         <f t="shared" si="44"/>
-        <v>31</v>
+        <v>32.7222222222222</v>
       </c>
     </row>
     <row r="35" spans="1:98">
@@ -30579,23 +30587,23 @@
       </c>
       <c r="G35" s="24">
         <f t="shared" si="1"/>
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H35" s="27">
         <f t="shared" ref="H35:M35" si="46">SUM(H7:H34)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I35" s="28">
         <f t="shared" si="46"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J35" s="24">
         <f t="shared" si="2"/>
-        <v>37.3</v>
+        <v>35.5</v>
       </c>
       <c r="K35" s="28">
         <f t="shared" si="46"/>
-        <v>7.77777777777778</v>
+        <v>7.89473684210526</v>
       </c>
       <c r="L35" s="27">
         <f t="shared" si="46"/>
@@ -30639,35 +30647,35 @@
       </c>
       <c r="V35" s="27">
         <f t="shared" si="48"/>
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="W35" s="28">
         <f t="shared" si="48"/>
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="X35" s="24">
         <f t="shared" si="8"/>
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="Y35" s="28">
         <f t="shared" ref="Y35:AA35" si="49">SUM(Y7:Y34)</f>
-        <v>75.8333333333333</v>
+        <v>75</v>
       </c>
       <c r="Z35" s="27">
         <f t="shared" si="49"/>
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AA35" s="28">
         <f t="shared" si="49"/>
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AB35" s="24">
         <f t="shared" si="10"/>
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="AC35" s="28">
         <f t="shared" ref="AC35:AE35" si="50">SUM(AC7:AC34)</f>
-        <v>46.1111111111111</v>
+        <v>45.2631578947368</v>
       </c>
       <c r="AD35" s="27">
         <f t="shared" si="50"/>
@@ -30679,23 +30687,23 @@
       </c>
       <c r="AF35" s="24">
         <f t="shared" si="12"/>
-        <v>34.1</v>
+        <v>36</v>
       </c>
       <c r="AG35" s="28">
         <f t="shared" ref="AG35:AI35" si="51">SUM(AG7:AG34)</f>
-        <v>5.27777777777778</v>
+        <v>5</v>
       </c>
       <c r="AH35" s="27">
         <f t="shared" si="51"/>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AI35" s="28">
         <f t="shared" si="51"/>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="AJ35" s="24">
         <f t="shared" si="14"/>
-        <v>27.3</v>
+        <v>26.4</v>
       </c>
       <c r="AK35" s="27">
         <f t="shared" ref="AK35:AO35" si="52">SUM(AK7:AK34)</f>
@@ -30703,27 +30711,27 @@
       </c>
       <c r="AL35" s="28">
         <f t="shared" si="52"/>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AM35" s="24">
         <f t="shared" si="15"/>
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="AN35" s="27">
         <f t="shared" si="52"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AO35" s="28">
         <f t="shared" si="52"/>
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="AP35" s="24">
         <f t="shared" si="16"/>
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ35" s="28">
         <f t="shared" ref="AQ35:AS35" si="53">SUM(AQ7:AQ34)</f>
-        <v>33.6111111111111</v>
+        <v>33.1578947368421</v>
       </c>
       <c r="AR35" s="27">
         <f t="shared" si="53"/>
@@ -30731,31 +30739,31 @@
       </c>
       <c r="AS35" s="28">
         <f t="shared" si="53"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AT35" s="24">
         <f t="shared" si="18"/>
-        <v>29.1</v>
+        <v>28.7</v>
       </c>
       <c r="AU35" s="28">
         <f t="shared" ref="AU35:AW35" si="54">SUM(AU7:AU34)</f>
-        <v>11.6666666666667</v>
+        <v>11.8421052631579</v>
       </c>
       <c r="AV35" s="27">
         <f t="shared" si="54"/>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AW35" s="28">
         <f t="shared" si="54"/>
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AX35" s="24">
         <f t="shared" si="20"/>
-        <v>17.2</v>
+        <v>14.6</v>
       </c>
       <c r="AY35" s="28">
         <f t="shared" ref="AY35:BA35" si="55">SUM(AY7:AY34)</f>
-        <v>13.0555555555556</v>
+        <v>13.6842105263158</v>
       </c>
       <c r="AZ35" s="27">
         <f t="shared" si="55"/>
@@ -30771,19 +30779,19 @@
       </c>
       <c r="BC35" s="27">
         <f t="shared" ref="BC35:BH35" si="56">SUM(BC7:BC34)</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BD35" s="28">
         <f t="shared" si="56"/>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="BE35" s="24">
         <f t="shared" si="23"/>
-        <v>16.8</v>
+        <v>15.4</v>
       </c>
       <c r="BF35" s="28">
         <f t="shared" si="56"/>
-        <v>20</v>
+        <v>20.2105263157895</v>
       </c>
       <c r="BG35" s="27">
         <f t="shared" si="56"/>
@@ -30799,7 +30807,7 @@
       </c>
       <c r="BJ35" s="28">
         <f t="shared" ref="BJ35:BL35" si="57">SUM(BJ7:BJ34)</f>
-        <v>0.888888888888889</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="BK35" s="27">
         <f t="shared" si="57"/>
@@ -30811,27 +30819,27 @@
       </c>
       <c r="BM35" s="24">
         <f t="shared" si="27"/>
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BN35" s="28">
         <f t="shared" ref="BN35:BP35" si="58">SUM(BN7:BN34)</f>
-        <v>11.1111111111111</v>
+        <v>10.5263157894737</v>
       </c>
       <c r="BO35" s="27">
         <f t="shared" si="58"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BP35" s="28">
         <f t="shared" si="58"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BQ35" s="24">
         <f t="shared" si="29"/>
-        <v>26.5</v>
+        <v>27.8</v>
       </c>
       <c r="BR35" s="28">
         <f t="shared" ref="BR35:BT35" si="59">SUM(BR7:BR34)</f>
-        <v>24.4444444444444</v>
+        <v>23.5789473684211</v>
       </c>
       <c r="BS35" s="27">
         <f t="shared" si="59"/>
@@ -30843,63 +30851,63 @@
       </c>
       <c r="BU35" s="24">
         <f t="shared" si="31"/>
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BV35" s="28">
         <f t="shared" ref="BV35:BX35" si="60">SUM(BV7:BV34)</f>
-        <v>4.44444444444444</v>
+        <v>4.21052631578947</v>
       </c>
       <c r="BW35" s="27">
         <f t="shared" si="60"/>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="BX35" s="28">
         <f t="shared" si="60"/>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="BY35" s="24">
         <f t="shared" si="33"/>
-        <v>20.5</v>
+        <v>22.2</v>
       </c>
       <c r="BZ35" s="28">
         <f t="shared" ref="BZ35:CB35" si="61">SUM(BZ7:BZ34)</f>
-        <v>25.7777777777778</v>
+        <v>25.2631578947368</v>
       </c>
       <c r="CA35" s="27">
         <f t="shared" si="61"/>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="CB35" s="28">
         <f t="shared" si="61"/>
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="CC35" s="24">
         <f t="shared" si="35"/>
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="CD35" s="28">
         <f t="shared" ref="CD35:CF35" si="62">SUM(CD7:CD34)</f>
-        <v>41.9444444444445</v>
+        <v>41.5789473684211</v>
       </c>
       <c r="CE35" s="27">
         <f t="shared" si="62"/>
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="CF35" s="28">
         <f t="shared" si="62"/>
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="CG35" s="24">
         <f t="shared" si="37"/>
-        <v>14.8</v>
+        <v>15.4</v>
       </c>
       <c r="CH35" s="28">
         <f t="shared" ref="CH35:CJ35" si="63">SUM(CH7:CH34)</f>
-        <v>69.6111111111111</v>
+        <v>68.1578947368421</v>
       </c>
       <c r="CI35" s="27">
         <f t="shared" si="63"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="CJ35" s="28">
         <f t="shared" si="63"/>
@@ -30907,11 +30915,11 @@
       </c>
       <c r="CK35" s="24">
         <f t="shared" si="39"/>
-        <v>30.4</v>
+        <v>32.6</v>
       </c>
       <c r="CL35" s="27">
         <f t="shared" ref="CL35:CP35" si="64">SUM(CL7:CL34)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="CM35" s="28">
         <f t="shared" si="64"/>
@@ -30919,31 +30927,31 @@
       </c>
       <c r="CN35" s="24">
         <f t="shared" si="40"/>
-        <v>40.7</v>
+        <v>43.6</v>
       </c>
       <c r="CO35" s="27">
         <f t="shared" si="64"/>
-        <v>144</v>
+        <v>189</v>
       </c>
       <c r="CP35" s="28">
         <f t="shared" si="64"/>
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="CQ35" s="24">
         <f t="shared" si="41"/>
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="CR35" s="25">
         <f>SUM(CR7:CR34)</f>
-        <v>1334</v>
+        <v>1378</v>
       </c>
       <c r="CS35" s="25">
         <f>SUM(CS7:CS34)</f>
-        <v>1925</v>
+        <v>1993</v>
       </c>
       <c r="CT35" s="25">
         <f>IF(OR(CS35="",CS35=0),"",ROUND(CR35/CS35*$B$2,1))</f>
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
     </row>
   </sheetData>

--- a/source/stock_data.xlsx
+++ b/source/stock_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michael/Desktop/02 Stock &amp; DOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA54A57-89BA-1145-913B-0B8F958FFFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3A2366-E820-1B4A-87F7-0EF8A5AE6DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="32740" windowHeight="14840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -633,29 +633,11 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -667,13 +649,40 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -685,22 +694,13 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3848,10 +3848,10 @@
             <v>18</v>
           </cell>
           <cell r="E9">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="F9">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="G9">
             <v>0</v>
@@ -3920,28 +3920,28 @@
             <v>27</v>
           </cell>
           <cell r="AC9">
-            <v>30</v>
+            <v>29</v>
           </cell>
           <cell r="AD9">
+            <v>28</v>
+          </cell>
+          <cell r="AE9">
+            <v>21</v>
+          </cell>
+          <cell r="AF9">
+            <v>10</v>
+          </cell>
+          <cell r="AG9">
             <v>27</v>
           </cell>
-          <cell r="AE9">
-            <v>22</v>
-          </cell>
-          <cell r="AF9">
-            <v>9</v>
-          </cell>
-          <cell r="AG9">
-            <v>28</v>
-          </cell>
           <cell r="AH9">
-            <v>11</v>
+            <v>12</v>
           </cell>
           <cell r="AI9">
-            <v>146</v>
+            <v>142</v>
           </cell>
           <cell r="AJ9">
-            <v>130</v>
+            <v>134</v>
           </cell>
         </row>
         <row r="10">
@@ -5272,16 +5272,16 @@
             <v>1</v>
           </cell>
           <cell r="AG25">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="AH25">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="AI25">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="AJ25">
-            <v>10</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="26">
@@ -5526,10 +5526,10 @@
             <v>0</v>
           </cell>
           <cell r="E29">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="F29">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G29">
             <v>0</v>
@@ -5610,10 +5610,10 @@
             <v>0</v>
           </cell>
           <cell r="AI29">
-            <v>7</v>
+            <v>6</v>
           </cell>
           <cell r="AJ29">
-            <v>5</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="30">
@@ -5722,10 +5722,10 @@
             <v>1</v>
           </cell>
           <cell r="AE31">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="AF31">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="AG31">
             <v>3</v>
@@ -5734,10 +5734,10 @@
             <v>0</v>
           </cell>
           <cell r="AI31">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="AJ31">
-            <v>9</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="32">
@@ -6354,10 +6354,10 @@
             <v>0</v>
           </cell>
           <cell r="AC41">
+            <v>1</v>
+          </cell>
+          <cell r="AD41">
             <v>2</v>
-          </cell>
-          <cell r="AD41">
-            <v>1</v>
           </cell>
           <cell r="AE41">
             <v>1</v>
@@ -6372,10 +6372,10 @@
             <v>0</v>
           </cell>
           <cell r="AI41">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="AJ41">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="42">
@@ -6389,10 +6389,10 @@
             <v>18</v>
           </cell>
           <cell r="E42">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="F42">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="G42">
             <v>0</v>
@@ -6461,28 +6461,28 @@
             <v>27</v>
           </cell>
           <cell r="AC42">
-            <v>30</v>
+            <v>29</v>
           </cell>
           <cell r="AD42">
+            <v>28</v>
+          </cell>
+          <cell r="AE42">
+            <v>21</v>
+          </cell>
+          <cell r="AF42">
+            <v>10</v>
+          </cell>
+          <cell r="AG42">
             <v>27</v>
           </cell>
-          <cell r="AE42">
-            <v>22</v>
-          </cell>
-          <cell r="AF42">
-            <v>9</v>
-          </cell>
-          <cell r="AG42">
-            <v>28</v>
-          </cell>
           <cell r="AH42">
-            <v>11</v>
+            <v>12</v>
           </cell>
           <cell r="AI42">
-            <v>146</v>
+            <v>142</v>
           </cell>
           <cell r="AJ42">
-            <v>130</v>
+            <v>134</v>
           </cell>
         </row>
       </sheetData>
@@ -7004,28 +7004,28 @@
             <v>0</v>
           </cell>
           <cell r="T9">
-            <v>11</v>
+            <v>10</v>
           </cell>
           <cell r="U9">
-            <v>17</v>
+            <v>18</v>
           </cell>
           <cell r="V9">
-            <v>16</v>
+            <v>15</v>
           </cell>
           <cell r="W9">
-            <v>25</v>
+            <v>26</v>
           </cell>
           <cell r="X9">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y9">
-            <v>29</v>
+            <v>30</v>
           </cell>
           <cell r="Z9">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="AA9">
-            <v>17</v>
+            <v>18</v>
           </cell>
           <cell r="AB9">
             <v>0</v>
@@ -7100,10 +7100,10 @@
             <v>13</v>
           </cell>
           <cell r="BB9">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="BC9">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="BD9">
             <v>0</v>
@@ -7142,10 +7142,10 @@
             <v>39</v>
           </cell>
           <cell r="BP9">
-            <v>80</v>
+            <v>81</v>
           </cell>
           <cell r="BQ9">
-            <v>216</v>
+            <v>221</v>
           </cell>
         </row>
         <row r="10">
@@ -7207,13 +7207,13 @@
             <v>19</v>
           </cell>
           <cell r="V10">
-            <v>16</v>
+            <v>13</v>
           </cell>
           <cell r="W10">
-            <v>24</v>
+            <v>27</v>
           </cell>
           <cell r="X10">
-            <v>2</v>
+            <v>5</v>
           </cell>
           <cell r="Y10">
             <v>33</v>
@@ -7285,7 +7285,7 @@
             <v>0</v>
           </cell>
           <cell r="AV10">
-            <v>2</v>
+            <v>5</v>
           </cell>
           <cell r="AW10">
             <v>23</v>
@@ -7303,10 +7303,10 @@
             <v>4</v>
           </cell>
           <cell r="BB10">
+            <v>2</v>
+          </cell>
+          <cell r="BC10">
             <v>3</v>
-          </cell>
-          <cell r="BC10">
-            <v>2</v>
           </cell>
           <cell r="BD10">
             <v>0</v>
@@ -7333,16 +7333,16 @@
             <v>1</v>
           </cell>
           <cell r="BN10">
-            <v>11</v>
+            <v>9</v>
           </cell>
           <cell r="BO10">
-            <v>93</v>
+            <v>95</v>
           </cell>
           <cell r="BP10">
             <v>77</v>
           </cell>
           <cell r="BQ10">
-            <v>240</v>
+            <v>246</v>
           </cell>
         </row>
         <row r="11">
@@ -7356,10 +7356,10 @@
             <v>0</v>
           </cell>
           <cell r="D11">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="E11">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="F11">
             <v>0</v>
@@ -7404,22 +7404,22 @@
             <v>0</v>
           </cell>
           <cell r="T11">
-            <v>9</v>
+            <v>8</v>
           </cell>
           <cell r="U11">
-            <v>29</v>
+            <v>30</v>
           </cell>
           <cell r="V11">
-            <v>10</v>
+            <v>8</v>
           </cell>
           <cell r="W11">
-            <v>52</v>
+            <v>54</v>
           </cell>
           <cell r="X11">
-            <v>9</v>
+            <v>8</v>
           </cell>
           <cell r="Y11">
-            <v>49</v>
+            <v>50</v>
           </cell>
           <cell r="Z11">
             <v>9</v>
@@ -7485,7 +7485,7 @@
             <v>6</v>
           </cell>
           <cell r="AW11">
-            <v>22</v>
+            <v>23</v>
           </cell>
           <cell r="AX11">
             <v>4</v>
@@ -7494,10 +7494,10 @@
             <v>4</v>
           </cell>
           <cell r="AZ11">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="BA11">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="BB11">
             <v>5</v>
@@ -7536,16 +7536,16 @@
             <v>3</v>
           </cell>
           <cell r="BN11">
-            <v>56</v>
+            <v>49</v>
           </cell>
           <cell r="BO11">
-            <v>237</v>
+            <v>244</v>
           </cell>
           <cell r="BP11">
-            <v>132</v>
+            <v>119</v>
           </cell>
           <cell r="BQ11">
-            <v>520</v>
+            <v>534</v>
           </cell>
         </row>
         <row r="12">
@@ -7816,13 +7816,13 @@
             <v>4</v>
           </cell>
           <cell r="X13">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="Y13">
             <v>5</v>
           </cell>
           <cell r="Z13">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AA13">
             <v>4</v>
@@ -7882,10 +7882,10 @@
             <v>0</v>
           </cell>
           <cell r="AV13">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="AW13">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="AX13">
             <v>3</v>
@@ -7918,7 +7918,7 @@
             <v>1</v>
           </cell>
           <cell r="BH13">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BI13">
             <v>3</v>
@@ -7936,16 +7936,16 @@
             <v>2</v>
           </cell>
           <cell r="BN13">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="BO13">
             <v>3</v>
           </cell>
           <cell r="BP13">
-            <v>44</v>
+            <v>47</v>
           </cell>
           <cell r="BQ13">
-            <v>39</v>
+            <v>40</v>
           </cell>
         </row>
         <row r="14">
@@ -7959,7 +7959,7 @@
             <v>0</v>
           </cell>
           <cell r="D14">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="E14">
             <v>10</v>
@@ -8001,13 +8001,13 @@
             <v>13</v>
           </cell>
           <cell r="V14">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="W14">
-            <v>19</v>
+            <v>20</v>
           </cell>
           <cell r="X14">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="Y14">
             <v>17</v>
@@ -8043,10 +8043,10 @@
             <v>0</v>
           </cell>
           <cell r="AL14">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="AM14">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="AN14">
             <v>1</v>
@@ -8067,7 +8067,7 @@
             <v>0</v>
           </cell>
           <cell r="AV14">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="AW14">
             <v>8</v>
@@ -8079,7 +8079,7 @@
             <v>5</v>
           </cell>
           <cell r="AZ14">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BA14">
             <v>3</v>
@@ -8097,28 +8097,28 @@
             <v>1</v>
           </cell>
           <cell r="BJ14">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BK14">
             <v>2</v>
           </cell>
           <cell r="BL14">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BM14">
             <v>2</v>
           </cell>
           <cell r="BN14">
-            <v>2</v>
+            <v>10</v>
           </cell>
           <cell r="BO14">
             <v>26</v>
           </cell>
           <cell r="BP14">
-            <v>22</v>
+            <v>42</v>
           </cell>
           <cell r="BQ14">
-            <v>124</v>
+            <v>126</v>
           </cell>
         </row>
         <row r="15">
@@ -8377,19 +8377,19 @@
             <v>4</v>
           </cell>
           <cell r="V16">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="W16">
             <v>2</v>
           </cell>
           <cell r="X16">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="Y16">
             <v>3</v>
           </cell>
           <cell r="Z16">
-            <v>1</v>
+            <v>3</v>
           </cell>
           <cell r="AA16">
             <v>4</v>
@@ -8443,7 +8443,7 @@
             <v>0</v>
           </cell>
           <cell r="AV16">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AW16">
             <v>1</v>
@@ -8455,7 +8455,7 @@
             <v>0</v>
           </cell>
           <cell r="AZ16">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BA16">
             <v>0</v>
@@ -8497,7 +8497,7 @@
             <v>7</v>
           </cell>
           <cell r="BP16">
-            <v>24</v>
+            <v>31</v>
           </cell>
           <cell r="BQ16">
             <v>30</v>
@@ -8556,13 +8556,13 @@
             <v>1</v>
           </cell>
           <cell r="X17">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="Y17">
             <v>4</v>
           </cell>
           <cell r="Z17">
-            <v>1</v>
+            <v>3</v>
           </cell>
           <cell r="AA17">
             <v>2</v>
@@ -8664,13 +8664,13 @@
             <v>1</v>
           </cell>
           <cell r="BN17">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="BO17">
             <v>3</v>
           </cell>
           <cell r="BP17">
-            <v>28</v>
+            <v>34</v>
           </cell>
           <cell r="BQ17">
             <v>25</v>
@@ -8843,19 +8843,19 @@
             <v>0</v>
           </cell>
           <cell r="BL18">
+            <v>3</v>
+          </cell>
+          <cell r="BM18">
+            <v>1</v>
+          </cell>
+          <cell r="BN18">
             <v>2</v>
-          </cell>
-          <cell r="BM18">
-            <v>1</v>
-          </cell>
-          <cell r="BN18">
-            <v>0</v>
           </cell>
           <cell r="BO18">
             <v>5</v>
           </cell>
           <cell r="BP18">
-            <v>45</v>
+            <v>48</v>
           </cell>
           <cell r="BQ18">
             <v>29</v>
@@ -9009,19 +9009,19 @@
             <v>7</v>
           </cell>
           <cell r="V20">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="W20">
             <v>5</v>
           </cell>
           <cell r="X20">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="Y20">
             <v>16</v>
           </cell>
           <cell r="Z20">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="AA20">
             <v>6</v>
@@ -9051,10 +9051,10 @@
             <v>0</v>
           </cell>
           <cell r="AL20">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="AM20">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AN20">
             <v>0</v>
@@ -9081,7 +9081,7 @@
             <v>0</v>
           </cell>
           <cell r="AV20">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="AW20">
             <v>5</v>
@@ -9093,7 +9093,7 @@
             <v>1</v>
           </cell>
           <cell r="AZ20">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BA20">
             <v>7</v>
@@ -9117,22 +9117,22 @@
             <v>3</v>
           </cell>
           <cell r="BL20">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BM20">
             <v>4</v>
           </cell>
           <cell r="BN20">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="BO20">
             <v>7</v>
           </cell>
           <cell r="BP20">
-            <v>31</v>
+            <v>39</v>
           </cell>
           <cell r="BQ20">
-            <v>79</v>
+            <v>80</v>
           </cell>
         </row>
         <row r="21">
@@ -9533,10 +9533,10 @@
             <v>6140705-QUEENCITY 2F027仓库</v>
           </cell>
           <cell r="D24">
+            <v>2</v>
+          </cell>
+          <cell r="E24">
             <v>3</v>
-          </cell>
-          <cell r="E24">
-            <v>2</v>
           </cell>
           <cell r="F24">
             <v>0</v>
@@ -9665,7 +9665,7 @@
             <v>3</v>
           </cell>
           <cell r="AX24">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AY24">
             <v>1</v>
@@ -9713,16 +9713,16 @@
             <v>0</v>
           </cell>
           <cell r="BN24">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="BO24">
             <v>5</v>
           </cell>
           <cell r="BP24">
-            <v>54</v>
+            <v>56</v>
           </cell>
           <cell r="BQ24">
-            <v>28</v>
+            <v>29</v>
           </cell>
         </row>
         <row r="25">
@@ -9778,7 +9778,7 @@
             <v>1</v>
           </cell>
           <cell r="V25">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="W25">
             <v>2</v>
@@ -9790,7 +9790,7 @@
             <v>3</v>
           </cell>
           <cell r="Z25">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AA25">
             <v>2</v>
@@ -9862,13 +9862,13 @@
             <v>2</v>
           </cell>
           <cell r="BN25">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="BO25">
             <v>3</v>
           </cell>
           <cell r="BP25">
-            <v>43</v>
+            <v>47</v>
           </cell>
           <cell r="BQ25">
             <v>19</v>
@@ -9921,10 +9921,10 @@
             <v>2</v>
           </cell>
           <cell r="X26">
+            <v>1</v>
+          </cell>
+          <cell r="Y26">
             <v>2</v>
-          </cell>
-          <cell r="Y26">
-            <v>1</v>
           </cell>
           <cell r="Z26">
             <v>2</v>
@@ -10035,10 +10035,10 @@
             <v>1</v>
           </cell>
           <cell r="BP26">
-            <v>23</v>
+            <v>22</v>
           </cell>
           <cell r="BQ26">
-            <v>13</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="27">
@@ -10052,10 +10052,10 @@
             <v>0</v>
           </cell>
           <cell r="D27">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="E27">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="F27">
             <v>0</v>
@@ -10100,22 +10100,22 @@
             <v>0</v>
           </cell>
           <cell r="T27">
-            <v>4</v>
+            <v>6</v>
           </cell>
           <cell r="U27">
             <v>19</v>
           </cell>
           <cell r="V27">
-            <v>6</v>
+            <v>5</v>
           </cell>
           <cell r="W27">
-            <v>15</v>
+            <v>16</v>
           </cell>
           <cell r="X27">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="Y27">
-            <v>31</v>
+            <v>32</v>
           </cell>
           <cell r="Z27">
             <v>8</v>
@@ -10154,10 +10154,10 @@
             <v>0</v>
           </cell>
           <cell r="AL27">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="AM27">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="AN27">
             <v>0</v>
@@ -10187,7 +10187,7 @@
             <v>3</v>
           </cell>
           <cell r="AW27">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="AX27">
             <v>4</v>
@@ -10202,10 +10202,10 @@
             <v>2</v>
           </cell>
           <cell r="BB27">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="BC27">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="BD27">
             <v>0</v>
@@ -10232,16 +10232,16 @@
             <v>0</v>
           </cell>
           <cell r="BN27">
-            <v>1</v>
+            <v>6</v>
           </cell>
           <cell r="BO27">
             <v>29</v>
           </cell>
           <cell r="BP27">
-            <v>51</v>
+            <v>53</v>
           </cell>
           <cell r="BQ27">
-            <v>156</v>
+            <v>162</v>
           </cell>
         </row>
         <row r="28">
@@ -10255,7 +10255,7 @@
             <v>0</v>
           </cell>
           <cell r="D28">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="E28">
             <v>9</v>
@@ -10306,25 +10306,25 @@
             <v>2</v>
           </cell>
           <cell r="U28">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="V28">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="W28">
             <v>6</v>
           </cell>
           <cell r="X28">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="Y28">
             <v>12</v>
           </cell>
           <cell r="Z28">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="AA28">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="AB28">
             <v>2</v>
@@ -10381,7 +10381,7 @@
             <v>0</v>
           </cell>
           <cell r="AV28">
-            <v>1</v>
+            <v>3</v>
           </cell>
           <cell r="AW28">
             <v>6</v>
@@ -10435,16 +10435,16 @@
             <v>1</v>
           </cell>
           <cell r="BN28">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="BO28">
-            <v>17</v>
+            <v>18</v>
           </cell>
           <cell r="BP28">
-            <v>29</v>
+            <v>33</v>
           </cell>
           <cell r="BQ28">
-            <v>87</v>
+            <v>90</v>
           </cell>
         </row>
         <row r="29">
@@ -10494,7 +10494,7 @@
             <v>3</v>
           </cell>
           <cell r="Z29">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AA29">
             <v>3</v>
@@ -10560,11 +10560,17 @@
             <v>2</v>
           </cell>
           <cell r="BJ29">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="BK29">
             <v>2</v>
           </cell>
+          <cell r="BL29">
+            <v>1</v>
+          </cell>
+          <cell r="BM29">
+            <v>0</v>
+          </cell>
           <cell r="BN29">
             <v>3</v>
           </cell>
@@ -10572,7 +10578,7 @@
             <v>0</v>
           </cell>
           <cell r="BP29">
-            <v>17</v>
+            <v>20</v>
           </cell>
           <cell r="BQ29">
             <v>20</v>
@@ -10631,25 +10637,25 @@
             <v>0</v>
           </cell>
           <cell r="T30">
+            <v>5</v>
+          </cell>
+          <cell r="U30">
+            <v>14</v>
+          </cell>
+          <cell r="V30">
+            <v>4</v>
+          </cell>
+          <cell r="W30">
+            <v>15</v>
+          </cell>
+          <cell r="X30">
             <v>6</v>
-          </cell>
-          <cell r="U30">
-            <v>13</v>
-          </cell>
-          <cell r="V30">
-            <v>5</v>
-          </cell>
-          <cell r="W30">
-            <v>14</v>
-          </cell>
-          <cell r="X30">
-            <v>2</v>
           </cell>
           <cell r="Y30">
             <v>28</v>
           </cell>
           <cell r="Z30">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="AA30">
             <v>26</v>
@@ -10733,10 +10739,10 @@
             <v>8</v>
           </cell>
           <cell r="BB30">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="BC30">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="BD30">
             <v>0</v>
@@ -10763,16 +10769,16 @@
             <v>1</v>
           </cell>
           <cell r="BN30">
-            <v>2</v>
+            <v>11</v>
           </cell>
           <cell r="BO30">
-            <v>21</v>
+            <v>22</v>
           </cell>
           <cell r="BP30">
-            <v>45</v>
+            <v>58</v>
           </cell>
           <cell r="BQ30">
-            <v>166</v>
+            <v>170</v>
           </cell>
         </row>
         <row r="31">
@@ -10834,16 +10840,16 @@
             <v>20</v>
           </cell>
           <cell r="X31">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="Y31">
-            <v>31</v>
+            <v>32</v>
           </cell>
           <cell r="Z31">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="AA31">
-            <v>22</v>
+            <v>24</v>
           </cell>
           <cell r="AB31">
             <v>1</v>
@@ -10900,19 +10906,19 @@
             <v>0</v>
           </cell>
           <cell r="AV31">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="AW31">
-            <v>12</v>
+            <v>13</v>
           </cell>
           <cell r="AX31">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="AY31">
             <v>2</v>
           </cell>
           <cell r="AZ31">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="BA31">
             <v>13</v>
@@ -10948,16 +10954,16 @@
             <v>1</v>
           </cell>
           <cell r="BN31">
-            <v>3</v>
+            <v>14</v>
           </cell>
           <cell r="BO31">
             <v>37</v>
           </cell>
           <cell r="BP31">
-            <v>50</v>
+            <v>72</v>
           </cell>
           <cell r="BQ31">
-            <v>194</v>
+            <v>198</v>
           </cell>
         </row>
         <row r="32">
@@ -11010,7 +11016,7 @@
             <v>5</v>
           </cell>
           <cell r="U32">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="V32">
             <v>6</v>
@@ -11019,13 +11025,13 @@
             <v>12</v>
           </cell>
           <cell r="X32">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="Y32">
             <v>14</v>
           </cell>
           <cell r="Z32">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="AA32">
             <v>4</v>
@@ -11061,10 +11067,10 @@
             <v>0</v>
           </cell>
           <cell r="AL32">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="AM32">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="AN32">
             <v>1</v>
@@ -11091,7 +11097,7 @@
             <v>6</v>
           </cell>
           <cell r="AX32">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AY32">
             <v>3</v>
@@ -11133,16 +11139,16 @@
             <v>2</v>
           </cell>
           <cell r="BN32">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="BO32">
             <v>5</v>
           </cell>
           <cell r="BP32">
-            <v>44</v>
+            <v>51</v>
           </cell>
           <cell r="BQ32">
-            <v>66</v>
+            <v>68</v>
           </cell>
         </row>
         <row r="33">
@@ -11204,10 +11210,10 @@
             <v>23</v>
           </cell>
           <cell r="V33">
-            <v>9</v>
+            <v>8</v>
           </cell>
           <cell r="W33">
-            <v>22</v>
+            <v>23</v>
           </cell>
           <cell r="X33">
             <v>3</v>
@@ -11219,7 +11225,7 @@
             <v>6</v>
           </cell>
           <cell r="AA33">
-            <v>22</v>
+            <v>23</v>
           </cell>
           <cell r="AB33">
             <v>1</v>
@@ -11276,10 +11282,10 @@
             <v>0</v>
           </cell>
           <cell r="AV33">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="AW33">
-            <v>13</v>
+            <v>15</v>
           </cell>
           <cell r="AX33">
             <v>2</v>
@@ -11330,16 +11336,16 @@
             <v>3</v>
           </cell>
           <cell r="BN33">
-            <v>2</v>
+            <v>13</v>
           </cell>
           <cell r="BO33">
-            <v>26</v>
+            <v>27</v>
           </cell>
           <cell r="BP33">
-            <v>51</v>
+            <v>59</v>
           </cell>
           <cell r="BQ33">
-            <v>217</v>
+            <v>222</v>
           </cell>
         </row>
         <row r="34">
@@ -11353,7 +11359,7 @@
             <v>0</v>
           </cell>
           <cell r="D34">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="E34">
             <v>1</v>
@@ -11407,7 +11413,7 @@
             <v>0</v>
           </cell>
           <cell r="X34">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="Y34">
             <v>5</v>
@@ -11473,10 +11479,10 @@
             <v>0</v>
           </cell>
           <cell r="AV34">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="AW34">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AX34">
             <v>2</v>
@@ -11515,22 +11521,22 @@
             <v>3</v>
           </cell>
           <cell r="BL34">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BM34">
             <v>1</v>
           </cell>
           <cell r="BN34">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="BO34">
             <v>2</v>
           </cell>
           <cell r="BP34">
-            <v>24</v>
+            <v>31</v>
           </cell>
           <cell r="BQ34">
-            <v>28</v>
+            <v>29</v>
           </cell>
         </row>
         <row r="35">
@@ -11640,10 +11646,10 @@
             <v>2</v>
           </cell>
           <cell r="AN35">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="AO35">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="AP35">
             <v>0</v>
@@ -11676,10 +11682,10 @@
             <v>5</v>
           </cell>
           <cell r="BB35">
+            <v>1</v>
+          </cell>
+          <cell r="BC35">
             <v>2</v>
-          </cell>
-          <cell r="BC35">
-            <v>1</v>
           </cell>
           <cell r="BD35">
             <v>0</v>
@@ -11718,10 +11724,10 @@
             <v>6</v>
           </cell>
           <cell r="BP35">
-            <v>34</v>
+            <v>32</v>
           </cell>
           <cell r="BQ35">
-            <v>44</v>
+            <v>46</v>
           </cell>
         </row>
         <row r="36">
@@ -11788,6 +11794,12 @@
           <cell r="BA36">
             <v>4</v>
           </cell>
+          <cell r="BB36">
+            <v>0</v>
+          </cell>
+          <cell r="BC36">
+            <v>1</v>
+          </cell>
           <cell r="BD36">
             <v>0</v>
           </cell>
@@ -11816,7 +11828,7 @@
             <v>0</v>
           </cell>
           <cell r="BQ36">
-            <v>26</v>
+            <v>27</v>
           </cell>
         </row>
         <row r="37">
@@ -11878,10 +11890,10 @@
             <v>1</v>
           </cell>
           <cell r="X37">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="Y37">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="Z37">
             <v>3</v>
@@ -11950,7 +11962,7 @@
             <v>0</v>
           </cell>
           <cell r="AZ37">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="BA37">
             <v>1</v>
@@ -11986,16 +11998,16 @@
             <v>0</v>
           </cell>
           <cell r="BN37">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="BO37">
             <v>9</v>
           </cell>
           <cell r="BP37">
-            <v>36</v>
+            <v>39</v>
           </cell>
           <cell r="BQ37">
-            <v>42</v>
+            <v>43</v>
           </cell>
         </row>
         <row r="38">
@@ -12219,7 +12231,7 @@
             <v>0</v>
           </cell>
           <cell r="Y41">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="Z41">
             <v>0</v>
@@ -12249,7 +12261,7 @@
             <v>0</v>
           </cell>
           <cell r="BQ41">
-            <v>14</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="42">
@@ -12281,10 +12293,10 @@
             <v>1</v>
           </cell>
           <cell r="X42">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="Y42">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="Z42">
             <v>2</v>
@@ -12359,10 +12371,10 @@
             <v>3</v>
           </cell>
           <cell r="BP42">
-            <v>55</v>
+            <v>54</v>
           </cell>
           <cell r="BQ42">
-            <v>32</v>
+            <v>33</v>
           </cell>
         </row>
         <row r="43">
@@ -12376,10 +12388,10 @@
             <v>0</v>
           </cell>
           <cell r="D43">
-            <v>64</v>
+            <v>66</v>
           </cell>
           <cell r="E43">
-            <v>83</v>
+            <v>86</v>
           </cell>
           <cell r="F43">
             <v>4</v>
@@ -12424,28 +12436,28 @@
             <v>0</v>
           </cell>
           <cell r="T43">
-            <v>129</v>
+            <v>128</v>
           </cell>
           <cell r="U43">
-            <v>214</v>
+            <v>219</v>
           </cell>
           <cell r="V43">
-            <v>135</v>
+            <v>134</v>
           </cell>
           <cell r="W43">
-            <v>249</v>
+            <v>259</v>
           </cell>
           <cell r="X43">
-            <v>91</v>
+            <v>110</v>
           </cell>
           <cell r="Y43">
-            <v>400</v>
+            <v>408</v>
           </cell>
           <cell r="Z43">
-            <v>85</v>
+            <v>102</v>
           </cell>
           <cell r="AA43">
-            <v>238</v>
+            <v>243</v>
           </cell>
           <cell r="AB43">
             <v>33</v>
@@ -12481,13 +12493,13 @@
             <v>79</v>
           </cell>
           <cell r="AM43">
-            <v>118</v>
+            <v>122</v>
           </cell>
           <cell r="AN43">
-            <v>35</v>
+            <v>34</v>
           </cell>
           <cell r="AO43">
-            <v>126</v>
+            <v>127</v>
           </cell>
           <cell r="AP43">
             <v>0</v>
@@ -12508,28 +12520,28 @@
             <v>0</v>
           </cell>
           <cell r="AV43">
-            <v>82</v>
+            <v>91</v>
           </cell>
           <cell r="AW43">
-            <v>173</v>
+            <v>180</v>
           </cell>
           <cell r="AX43">
-            <v>63</v>
+            <v>66</v>
           </cell>
           <cell r="AY43">
             <v>63</v>
           </cell>
           <cell r="AZ43">
-            <v>37</v>
+            <v>42</v>
           </cell>
           <cell r="BA43">
-            <v>80</v>
+            <v>81</v>
           </cell>
           <cell r="BB43">
-            <v>74</v>
+            <v>69</v>
           </cell>
           <cell r="BC43">
-            <v>78</v>
+            <v>84</v>
           </cell>
           <cell r="BD43">
             <v>3</v>
@@ -12544,34 +12556,34 @@
             <v>4</v>
           </cell>
           <cell r="BH43">
-            <v>27</v>
+            <v>28</v>
           </cell>
           <cell r="BI43">
             <v>18</v>
           </cell>
           <cell r="BJ43">
-            <v>68</v>
+            <v>70</v>
           </cell>
           <cell r="BK43">
             <v>53</v>
           </cell>
           <cell r="BL43">
-            <v>57</v>
+            <v>62</v>
           </cell>
           <cell r="BM43">
             <v>37</v>
           </cell>
           <cell r="BN43">
-            <v>138</v>
+            <v>189</v>
           </cell>
           <cell r="BO43">
-            <v>615</v>
+            <v>627</v>
           </cell>
           <cell r="BP43">
-            <v>1258</v>
+            <v>1364</v>
           </cell>
           <cell r="BQ43">
-            <v>2676</v>
+            <v>2738</v>
           </cell>
         </row>
         <row r="45">
@@ -13868,7 +13880,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -13933,7 +13945,7 @@
       </c>
       <c r="B3" s="19">
         <f>B1-B2</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -13993,217 +14005,217 @@
       <c r="AV3" s="20"/>
     </row>
     <row r="4" spans="1:48" ht="16.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="42" t="s">
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="42" t="s">
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="42" t="s">
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="43"/>
-      <c r="AA4" s="43"/>
-      <c r="AB4" s="43"/>
-      <c r="AC4" s="43"/>
-      <c r="AD4" s="43"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="42" t="s">
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="47"/>
+      <c r="AF4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="AG4" s="43"/>
-      <c r="AH4" s="43"/>
-      <c r="AI4" s="43"/>
-      <c r="AJ4" s="43"/>
-      <c r="AK4" s="43"/>
-      <c r="AL4" s="43"/>
-      <c r="AM4" s="44"/>
-      <c r="AN4" s="42" t="s">
+      <c r="AG4" s="46"/>
+      <c r="AH4" s="46"/>
+      <c r="AI4" s="46"/>
+      <c r="AJ4" s="46"/>
+      <c r="AK4" s="46"/>
+      <c r="AL4" s="46"/>
+      <c r="AM4" s="47"/>
+      <c r="AN4" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="AO4" s="43"/>
-      <c r="AP4" s="43"/>
-      <c r="AQ4" s="43"/>
-      <c r="AR4" s="43"/>
-      <c r="AS4" s="44"/>
-      <c r="AT4" s="36" t="s">
+      <c r="AO4" s="46"/>
+      <c r="AP4" s="46"/>
+      <c r="AQ4" s="46"/>
+      <c r="AR4" s="46"/>
+      <c r="AS4" s="47"/>
+      <c r="AT4" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="AU4" s="36" t="s">
+      <c r="AU4" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="AV4" s="36" t="s">
+      <c r="AV4" s="30" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:48" ht="16.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="46"/>
-      <c r="B5" s="39" t="s">
+      <c r="A5" s="43"/>
+      <c r="B5" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39" t="s">
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="39" t="s">
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="39" t="s">
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="U5" s="40"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="41"/>
-      <c r="AB5" s="39" t="s">
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="50"/>
+      <c r="AB5" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AC5" s="40"/>
-      <c r="AD5" s="40"/>
-      <c r="AE5" s="41"/>
-      <c r="AF5" s="39" t="s">
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="49"/>
+      <c r="AE5" s="50"/>
+      <c r="AF5" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="AG5" s="40"/>
-      <c r="AH5" s="40"/>
-      <c r="AI5" s="40"/>
-      <c r="AJ5" s="40"/>
-      <c r="AK5" s="40"/>
-      <c r="AL5" s="40"/>
-      <c r="AM5" s="41"/>
-      <c r="AN5" s="39" t="s">
+      <c r="AG5" s="49"/>
+      <c r="AH5" s="49"/>
+      <c r="AI5" s="49"/>
+      <c r="AJ5" s="49"/>
+      <c r="AK5" s="49"/>
+      <c r="AL5" s="49"/>
+      <c r="AM5" s="50"/>
+      <c r="AN5" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="AO5" s="40"/>
-      <c r="AP5" s="40"/>
-      <c r="AQ5" s="40"/>
-      <c r="AR5" s="40"/>
-      <c r="AS5" s="41"/>
-      <c r="AT5" s="37"/>
-      <c r="AU5" s="37"/>
-      <c r="AV5" s="37"/>
+      <c r="AO5" s="49"/>
+      <c r="AP5" s="49"/>
+      <c r="AQ5" s="49"/>
+      <c r="AR5" s="49"/>
+      <c r="AS5" s="50"/>
+      <c r="AT5" s="31"/>
+      <c r="AU5" s="31"/>
+      <c r="AV5" s="31"/>
     </row>
     <row r="6" spans="1:48" ht="16.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46"/>
-      <c r="B6" s="48" t="s">
+      <c r="A6" s="43"/>
+      <c r="B6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="48" t="s">
+      <c r="C6" s="40"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="48" t="s">
+      <c r="F6" s="40"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="49"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="48" t="s">
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="49"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="48" t="s">
+      <c r="L6" s="40"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="49"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="48" t="s">
+      <c r="O6" s="40"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="49"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="48" t="s">
+      <c r="R6" s="40"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="U6" s="49"/>
-      <c r="V6" s="49"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="48" t="s">
+      <c r="U6" s="40"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="49"/>
-      <c r="AA6" s="50"/>
-      <c r="AB6" s="48" t="s">
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="40"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AC6" s="49"/>
-      <c r="AD6" s="49"/>
-      <c r="AE6" s="50"/>
-      <c r="AF6" s="48" t="s">
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="40"/>
+      <c r="AE6" s="41"/>
+      <c r="AF6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="AG6" s="49"/>
-      <c r="AH6" s="49"/>
-      <c r="AI6" s="50"/>
-      <c r="AJ6" s="48" t="s">
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="40"/>
+      <c r="AI6" s="41"/>
+      <c r="AJ6" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="AK6" s="49"/>
-      <c r="AL6" s="49"/>
-      <c r="AM6" s="50"/>
-      <c r="AN6" s="48" t="s">
+      <c r="AK6" s="40"/>
+      <c r="AL6" s="40"/>
+      <c r="AM6" s="41"/>
+      <c r="AN6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="AO6" s="49"/>
-      <c r="AP6" s="50"/>
-      <c r="AQ6" s="48" t="s">
+      <c r="AO6" s="40"/>
+      <c r="AP6" s="41"/>
+      <c r="AQ6" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AR6" s="49"/>
-      <c r="AS6" s="50"/>
-      <c r="AT6" s="37"/>
-      <c r="AU6" s="37"/>
-      <c r="AV6" s="37"/>
+      <c r="AR6" s="40"/>
+      <c r="AS6" s="41"/>
+      <c r="AT6" s="31"/>
+      <c r="AU6" s="31"/>
+      <c r="AV6" s="31"/>
     </row>
     <row r="7" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A7" s="47"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="21" t="s">
         <v>22</v>
       </c>
@@ -14336,9 +14348,9 @@
       <c r="AS7" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="AT7" s="38"/>
-      <c r="AU7" s="38"/>
-      <c r="AV7" s="38"/>
+      <c r="AT7" s="32"/>
+      <c r="AU7" s="32"/>
+      <c r="AV7" s="32"/>
     </row>
     <row r="8" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A8" s="22" t="s">
@@ -14414,7 +14426,7 @@
       </c>
       <c r="S8" s="13">
         <f t="shared" ref="S8:S36" si="5">IF(OR(R8="",R8=0),"",ROUND(Q8/R8*$B$2,1))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T8" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A8,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14518,7 +14530,7 @@
       </c>
       <c r="AS8" s="13">
         <f t="shared" ref="AS8:AS36" si="17">IF(OR(AR8="",AR8=0),"",ROUND(AQ8/AR8*$B$2,1))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" ref="AT8:AU35" si="18">SUM(B8,E8,H8,K8,N8,Q8,T8,X8,AB8,AF8,AJ8,AN8,AQ8)</f>
@@ -14530,7 +14542,7 @@
       </c>
       <c r="AV8" s="14">
         <f t="shared" ref="AV8:AV36" si="19">IFERROR(AT8/(AU8/$B$2),1000)</f>
-        <v>12.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.2">
@@ -14607,7 +14619,7 @@
       </c>
       <c r="S9" s="13">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="T9" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A9,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14723,7 +14735,7 @@
       </c>
       <c r="AV9" s="14">
         <f t="shared" si="19"/>
-        <v>18.75</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.2">
@@ -14776,7 +14788,7 @@
       </c>
       <c r="M10" s="13">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="N10" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14788,7 +14800,7 @@
       </c>
       <c r="P10" s="13">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q10" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14800,7 +14812,7 @@
       </c>
       <c r="S10" s="13">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T10" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A10,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -14916,7 +14928,7 @@
       </c>
       <c r="AV10" s="14">
         <f t="shared" si="19"/>
-        <v>11.111111111111111</v>
+        <v>11.555555555555555</v>
       </c>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.2">
@@ -15085,7 +15097,7 @@
       </c>
       <c r="AP11" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ11" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A11,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15109,7 +15121,7 @@
       </c>
       <c r="AV11" s="14">
         <f t="shared" si="19"/>
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.2">
@@ -15367,7 +15379,7 @@
       </c>
       <c r="P13" s="13">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q13" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A13,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15379,7 +15391,7 @@
       </c>
       <c r="S13" s="13">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T13" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A13,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15459,7 +15471,7 @@
       </c>
       <c r="AM13" s="23">
         <f t="shared" si="15"/>
-        <v>1.2</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AN13" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A13,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15495,7 +15507,7 @@
       </c>
       <c r="AV13" s="14">
         <f t="shared" si="19"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.2">
@@ -15548,7 +15560,7 @@
       </c>
       <c r="M14" s="13">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N14" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15560,7 +15572,7 @@
       </c>
       <c r="P14" s="13">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q14" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15572,7 +15584,7 @@
       </c>
       <c r="S14" s="13">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="T14" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15636,7 +15648,7 @@
       </c>
       <c r="AI14" s="23">
         <f t="shared" si="13"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AJ14" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15652,7 +15664,7 @@
       </c>
       <c r="AM14" s="23">
         <f t="shared" si="15"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AN14" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A14,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15688,7 +15700,7 @@
       </c>
       <c r="AV14" s="14">
         <f t="shared" si="19"/>
-        <v>18.75</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.2">
@@ -15741,7 +15753,7 @@
       </c>
       <c r="M15" s="13">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N15" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A15,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15765,7 +15777,7 @@
       </c>
       <c r="S15" s="13">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T15" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A15,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -15881,7 +15893,7 @@
       </c>
       <c r="AV15" s="14">
         <f t="shared" si="19"/>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.2">
@@ -15946,7 +15958,7 @@
       </c>
       <c r="P16" s="13">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q16" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A16,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16018,11 +16030,11 @@
       </c>
       <c r="AH16" s="13">
         <f t="shared" si="12"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI16" s="23">
         <f t="shared" si="13"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AJ16" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A16,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16074,7 +16086,7 @@
       </c>
       <c r="AV16" s="14">
         <f t="shared" si="19"/>
-        <v>87.5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:48" x14ac:dyDescent="0.2">
@@ -16231,7 +16243,7 @@
       </c>
       <c r="AM17" s="23">
         <f t="shared" si="15"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AN17" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A17,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16267,7 +16279,7 @@
       </c>
       <c r="AV17" s="14">
         <f t="shared" si="19"/>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:48" x14ac:dyDescent="0.2">
@@ -16408,7 +16420,7 @@
       </c>
       <c r="AI18" s="23">
         <f t="shared" si="13"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AJ18" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A18,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16460,7 +16472,7 @@
       </c>
       <c r="AV18" s="14">
         <f t="shared" si="19"/>
-        <v>16.666666666666668</v>
+        <v>17.333333333333332</v>
       </c>
     </row>
     <row r="19" spans="1:48" x14ac:dyDescent="0.2">
@@ -16537,7 +16549,7 @@
       </c>
       <c r="S19" s="13">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="T19" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A19,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16605,19 +16617,19 @@
       </c>
       <c r="AJ19" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A19,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="23">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A19,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL19" s="13" t="str">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="13">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM19" s="23">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AN19" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A19,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16645,15 +16657,15 @@
       </c>
       <c r="AT19" s="14">
         <f t="shared" si="18"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU19" s="14">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV19" s="14">
         <f t="shared" si="19"/>
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:48" x14ac:dyDescent="0.2">
@@ -16923,7 +16935,7 @@
       </c>
       <c r="S21" s="13">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T21" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A21,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -16983,11 +16995,11 @@
       </c>
       <c r="AH21" s="13">
         <f t="shared" si="12"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AI21" s="23">
         <f t="shared" si="13"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AJ21" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A21,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17007,15 +17019,15 @@
       </c>
       <c r="AN21" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A21,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO21" s="23">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A21,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP21" s="13" t="str">
+        <v>1</v>
+      </c>
+      <c r="AP21" s="13">
         <f t="shared" si="16"/>
-        <v/>
+        <v>52</v>
       </c>
       <c r="AQ21" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A21,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17031,15 +17043,15 @@
       </c>
       <c r="AT21" s="14">
         <f t="shared" si="18"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU21" s="14">
         <f t="shared" si="18"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV21" s="14">
         <f t="shared" si="19"/>
-        <v>22.222222222222221</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="22" spans="1:48" x14ac:dyDescent="0.2">
@@ -17080,7 +17092,7 @@
       </c>
       <c r="J22" s="13">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K22" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11X|8+256|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17092,7 +17104,7 @@
       </c>
       <c r="M22" s="13">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N22" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17180,7 +17192,7 @@
       </c>
       <c r="AI22" s="23">
         <f t="shared" si="13"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AJ22" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17208,7 +17220,7 @@
       </c>
       <c r="AP22" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ22" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A22,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17220,7 +17232,7 @@
       </c>
       <c r="AS22" s="13">
         <f t="shared" si="17"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT22" s="14">
         <f t="shared" si="18"/>
@@ -17232,7 +17244,7 @@
       </c>
       <c r="AV22" s="14">
         <f t="shared" si="19"/>
-        <v>29.166666666666668</v>
+        <v>30.333333333333332</v>
       </c>
     </row>
     <row r="23" spans="1:48" x14ac:dyDescent="0.2">
@@ -17297,7 +17309,7 @@
       </c>
       <c r="P23" s="13">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q23" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A23,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17373,7 +17385,7 @@
       </c>
       <c r="AI23" s="23">
         <f t="shared" si="13"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AJ23" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A23,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17425,7 +17437,7 @@
       </c>
       <c r="AV23" s="14">
         <f t="shared" si="19"/>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:48" x14ac:dyDescent="0.2">
@@ -17478,7 +17490,7 @@
       </c>
       <c r="M24" s="13">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N24" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A24,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17566,7 +17578,7 @@
       </c>
       <c r="AI24" s="23">
         <f t="shared" si="13"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AJ24" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A24,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17582,7 +17594,7 @@
       </c>
       <c r="AM24" s="23">
         <f t="shared" si="15"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AN24" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A24,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17618,7 +17630,7 @@
       </c>
       <c r="AV24" s="14">
         <f t="shared" si="19"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:48" x14ac:dyDescent="0.2">
@@ -17811,7 +17823,7 @@
       </c>
       <c r="AV25" s="14">
         <f t="shared" si="19"/>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:48" x14ac:dyDescent="0.2">
@@ -17852,7 +17864,7 @@
       </c>
       <c r="J26" s="13">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K26" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11X|8+256|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17876,7 +17888,7 @@
       </c>
       <c r="P26" s="13">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q26" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17888,7 +17900,7 @@
       </c>
       <c r="S26" s="13">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T26" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17952,7 +17964,7 @@
       </c>
       <c r="AI26" s="23">
         <f t="shared" si="13"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AJ26" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A26,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -17992,7 +18004,7 @@
       </c>
       <c r="AS26" s="13">
         <f t="shared" si="17"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT26" s="14">
         <f t="shared" si="18"/>
@@ -18004,7 +18016,7 @@
       </c>
       <c r="AV26" s="14">
         <f t="shared" si="19"/>
-        <v>29.166666666666668</v>
+        <v>30.333333333333332</v>
       </c>
     </row>
     <row r="27" spans="1:48" x14ac:dyDescent="0.2">
@@ -18197,7 +18209,7 @@
       </c>
       <c r="AV27" s="14">
         <f t="shared" si="19"/>
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:48" x14ac:dyDescent="0.2">
@@ -18390,7 +18402,7 @@
       </c>
       <c r="AV28" s="14">
         <f t="shared" si="19"/>
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:48" x14ac:dyDescent="0.2">
@@ -18455,7 +18467,7 @@
       </c>
       <c r="P29" s="13">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q29" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A29,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -18467,7 +18479,7 @@
       </c>
       <c r="S29" s="13">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T29" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A29,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -18531,7 +18543,7 @@
       </c>
       <c r="AI29" s="23">
         <f t="shared" si="13"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AJ29" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A29,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -18571,7 +18583,7 @@
       </c>
       <c r="AS29" s="13">
         <f t="shared" si="17"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT29" s="14">
         <f t="shared" si="18"/>
@@ -18583,7 +18595,7 @@
       </c>
       <c r="AV29" s="14">
         <f t="shared" si="19"/>
-        <v>31.25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="30" spans="1:48" x14ac:dyDescent="0.2">
@@ -18648,7 +18660,7 @@
       </c>
       <c r="P30" s="13">
         <f t="shared" si="4"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="Q30" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A30,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -18660,7 +18672,7 @@
       </c>
       <c r="S30" s="13">
         <f t="shared" si="5"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="T30" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A30,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -18720,11 +18732,11 @@
       </c>
       <c r="AH30" s="13">
         <f t="shared" si="12"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AI30" s="23">
         <f t="shared" si="13"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AJ30" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A30,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -18752,31 +18764,31 @@
       </c>
       <c r="AP30" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ30" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A30,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR30" s="23">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A30,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS30" s="13" t="str">
+        <v>1</v>
+      </c>
+      <c r="AS30" s="13">
         <f t="shared" si="17"/>
-        <v/>
+        <v>26</v>
       </c>
       <c r="AT30" s="14">
         <f t="shared" si="18"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU30" s="14">
         <f t="shared" si="18"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV30" s="14">
         <f t="shared" si="19"/>
-        <v>20</v>
+        <v>16.545454545454547</v>
       </c>
     </row>
     <row r="31" spans="1:48" x14ac:dyDescent="0.2">
@@ -19034,7 +19046,7 @@
       </c>
       <c r="P32" s="13">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q32" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A32,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19046,7 +19058,7 @@
       </c>
       <c r="S32" s="13">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T32" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A32,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19106,11 +19118,11 @@
       </c>
       <c r="AH32" s="13">
         <f t="shared" si="12"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI32" s="23">
         <f t="shared" si="13"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AJ32" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A32,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19162,7 +19174,7 @@
       </c>
       <c r="AV32" s="14">
         <f t="shared" si="19"/>
-        <v>40</v>
+        <v>41.599999999999994</v>
       </c>
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.2">
@@ -19239,7 +19251,7 @@
       </c>
       <c r="S33" s="13">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T33" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19287,7 +19299,7 @@
       </c>
       <c r="AE33" s="23">
         <f t="shared" si="11"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AF33" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|BLACK|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19299,11 +19311,11 @@
       </c>
       <c r="AH33" s="13">
         <f t="shared" si="12"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI33" s="23">
         <f t="shared" si="13"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AJ33" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15R|12+512|SILVER|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19331,7 +19343,7 @@
       </c>
       <c r="AP33" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ33" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A33,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|12+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19343,7 +19355,7 @@
       </c>
       <c r="AS33" s="13">
         <f t="shared" si="17"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT33" s="14">
         <f t="shared" si="18"/>
@@ -19355,7 +19367,7 @@
       </c>
       <c r="AV33" s="14">
         <f t="shared" si="19"/>
-        <v>35</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.2">
@@ -19424,15 +19436,15 @@
       </c>
       <c r="Q34" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A34,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34" s="23">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A34,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|SALES",[1]PVKEYIQOO!$1:$1,0)),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S34" s="13">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T34" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A34,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19540,15 +19552,15 @@
       </c>
       <c r="AT34" s="14">
         <f t="shared" si="18"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU34" s="14">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV34" s="14">
         <f t="shared" si="19"/>
-        <v>200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.2">
@@ -19613,7 +19625,7 @@
       </c>
       <c r="P35" s="13">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q35" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A35,[1]PV.iQOO!$B:$B,0),MATCH("IQOOZ11|8+256|BLUE|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19625,7 +19637,7 @@
       </c>
       <c r="S35" s="13">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T35" s="11">
         <f>IFERROR(INDEX([1]PV.iQOO!$A:$BL,MATCH($A35,[1]PV.iQOO!$B:$B,0),MATCH("IQOO15|16+512|ALPHA|STOCK",[1]PVKEYIQOO!$1:$1,0)),0)</f>
@@ -19741,7 +19753,7 @@
       </c>
       <c r="AV35" s="14">
         <f t="shared" si="19"/>
-        <v>31.25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.2">
@@ -19782,7 +19794,7 @@
       </c>
       <c r="J36" s="13">
         <f t="shared" si="2"/>
-        <v>15.6</v>
+        <v>16.3</v>
       </c>
       <c r="K36" s="16">
         <f>SUM(K8:K35)</f>
@@ -19794,7 +19806,7 @@
       </c>
       <c r="M36" s="13">
         <f t="shared" si="3"/>
-        <v>26.9</v>
+        <v>28</v>
       </c>
       <c r="N36" s="16">
         <f>SUM(N8:N35)</f>
@@ -19806,19 +19818,19 @@
       </c>
       <c r="P36" s="13">
         <f t="shared" si="4"/>
-        <v>24.1</v>
+        <v>25</v>
       </c>
       <c r="Q36" s="16">
         <f>SUM(Q8:Q35)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R36" s="26">
         <f>SUM(R8:R35)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S36" s="13">
         <f t="shared" si="5"/>
-        <v>27.8</v>
+        <v>26.9</v>
       </c>
       <c r="T36" s="16">
         <f>SUM(T8:T35)</f>
@@ -19866,7 +19878,7 @@
       </c>
       <c r="AE36" s="26">
         <f>SUM(AE8:AE35)</f>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AF36" s="16">
         <f>SUM(AF8:AF35)</f>
@@ -19878,72 +19890,76 @@
       </c>
       <c r="AH36" s="13">
         <f t="shared" si="12"/>
-        <v>17.2</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="AI36" s="26">
         <f>SUM(AI8:AI35)</f>
-        <v>6.4000000000000012</v>
+        <v>6.153846153846156</v>
       </c>
       <c r="AJ36" s="16">
         <f>SUM(AJ8:AJ35)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK36" s="26">
         <f>SUM(AK8:AK35)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL36" s="13">
         <f t="shared" si="14"/>
-        <v>17.899999999999999</v>
+        <v>13</v>
       </c>
       <c r="AM36" s="26">
         <f>SUM(AM8:AM35)</f>
-        <v>2.8</v>
+        <v>3.0769230769230771</v>
       </c>
       <c r="AN36" s="16">
         <f>SUM(AN8:AN35)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO36" s="26">
         <f>SUM(AO8:AO35)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP36" s="13">
         <f t="shared" si="16"/>
-        <v>68.8</v>
+        <v>60.7</v>
       </c>
       <c r="AQ36" s="16">
         <f>SUM(AQ8:AQ35)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR36" s="26">
         <f>SUM(AR8:AR35)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS36" s="13">
         <f t="shared" si="17"/>
-        <v>70</v>
+        <v>63.8</v>
       </c>
       <c r="AT36" s="14">
         <f>SUM(AT8:AT35)</f>
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU36" s="14">
         <f>SUM(AU8:AU35)</f>
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AV36" s="14">
         <f t="shared" si="19"/>
-        <v>29.2</v>
+        <v>28.620155038759687</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AU4:AU7"/>
-    <mergeCell ref="AV4:AV7"/>
-    <mergeCell ref="AJ6:AM6"/>
-    <mergeCell ref="AN6:AP6"/>
-    <mergeCell ref="AQ6:AS6"/>
+    <mergeCell ref="T5:AA5"/>
+    <mergeCell ref="AB5:AE5"/>
+    <mergeCell ref="AF5:AM5"/>
+    <mergeCell ref="AN5:AS5"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="T4:AE4"/>
+    <mergeCell ref="AF4:AM4"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="AT4:AT7"/>
     <mergeCell ref="Q6:S6"/>
@@ -19960,15 +19976,11 @@
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="H5:M5"/>
     <mergeCell ref="N5:S5"/>
-    <mergeCell ref="T5:AA5"/>
-    <mergeCell ref="AB5:AE5"/>
-    <mergeCell ref="AF5:AM5"/>
-    <mergeCell ref="AN5:AS5"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="T4:AE4"/>
-    <mergeCell ref="AF4:AM4"/>
+    <mergeCell ref="AU4:AU7"/>
+    <mergeCell ref="AV4:AV7"/>
+    <mergeCell ref="AJ6:AM6"/>
+    <mergeCell ref="AN6:AP6"/>
+    <mergeCell ref="AQ6:AS6"/>
   </mergeCells>
   <conditionalFormatting sqref="D8:D36">
     <cfRule type="cellIs" dxfId="133" priority="41" operator="lessThan">
@@ -20353,7 +20365,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -20488,7 +20500,7 @@
       </c>
       <c r="B3" s="4">
         <f>B1-B2</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -20618,15 +20630,15 @@
       <c r="CT3" s="6"/>
     </row>
     <row r="4" spans="1:98" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="29" t="s">
         <v>55</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="29" t="s">
         <v>56</v>
       </c>
       <c r="F4" s="28"/>
@@ -20635,13 +20647,13 @@
       <c r="I4" s="28"/>
       <c r="J4" s="28"/>
       <c r="K4" s="28"/>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="29" t="s">
         <v>57</v>
       </c>
       <c r="M4" s="28"/>
       <c r="N4" s="28"/>
       <c r="O4" s="28"/>
-      <c r="P4" s="27" t="s">
+      <c r="P4" s="29" t="s">
         <v>58</v>
       </c>
       <c r="Q4" s="28"/>
@@ -20649,7 +20661,7 @@
       <c r="S4" s="28"/>
       <c r="T4" s="28"/>
       <c r="U4" s="28"/>
-      <c r="V4" s="27" t="s">
+      <c r="V4" s="29" t="s">
         <v>59</v>
       </c>
       <c r="W4" s="28"/>
@@ -20663,29 +20675,29 @@
       <c r="AE4" s="28"/>
       <c r="AF4" s="28"/>
       <c r="AG4" s="28"/>
-      <c r="AH4" s="29" t="s">
+      <c r="AH4" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="AI4" s="30"/>
-      <c r="AJ4" s="31"/>
-      <c r="AK4" s="30" t="s">
+      <c r="AI4" s="37"/>
+      <c r="AJ4" s="38"/>
+      <c r="AK4" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="AL4" s="30"/>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="30"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="30"/>
-      <c r="AT4" s="30"/>
-      <c r="AU4" s="30"/>
-      <c r="AV4" s="30"/>
-      <c r="AW4" s="30"/>
-      <c r="AX4" s="30"/>
-      <c r="AY4" s="31"/>
-      <c r="AZ4" s="27" t="s">
+      <c r="AL4" s="37"/>
+      <c r="AM4" s="37"/>
+      <c r="AN4" s="37"/>
+      <c r="AO4" s="37"/>
+      <c r="AP4" s="37"/>
+      <c r="AQ4" s="37"/>
+      <c r="AR4" s="37"/>
+      <c r="AS4" s="37"/>
+      <c r="AT4" s="37"/>
+      <c r="AU4" s="37"/>
+      <c r="AV4" s="37"/>
+      <c r="AW4" s="37"/>
+      <c r="AX4" s="37"/>
+      <c r="AY4" s="38"/>
+      <c r="AZ4" s="29" t="s">
         <v>62</v>
       </c>
       <c r="BA4" s="28"/>
@@ -20698,7 +20710,7 @@
       <c r="BH4" s="28"/>
       <c r="BI4" s="28"/>
       <c r="BJ4" s="28"/>
-      <c r="BK4" s="27" t="s">
+      <c r="BK4" s="29" t="s">
         <v>63</v>
       </c>
       <c r="BL4" s="28"/>
@@ -20708,19 +20720,19 @@
       <c r="BP4" s="28"/>
       <c r="BQ4" s="28"/>
       <c r="BR4" s="28"/>
-      <c r="BS4" s="27" t="s">
+      <c r="BS4" s="29" t="s">
         <v>64</v>
       </c>
       <c r="BT4" s="28"/>
       <c r="BU4" s="28"/>
       <c r="BV4" s="28"/>
-      <c r="BW4" s="27" t="s">
+      <c r="BW4" s="29" t="s">
         <v>65</v>
       </c>
       <c r="BX4" s="28"/>
       <c r="BY4" s="28"/>
       <c r="BZ4" s="28"/>
-      <c r="CA4" s="27" t="s">
+      <c r="CA4" s="29" t="s">
         <v>66</v>
       </c>
       <c r="CB4" s="28"/>
@@ -20730,182 +20742,182 @@
       <c r="CF4" s="28"/>
       <c r="CG4" s="28"/>
       <c r="CH4" s="28"/>
-      <c r="CI4" s="27" t="s">
+      <c r="CI4" s="29" t="s">
         <v>67</v>
       </c>
       <c r="CJ4" s="28"/>
       <c r="CK4" s="28"/>
-      <c r="CL4" s="27" t="s">
+      <c r="CL4" s="29" t="s">
         <v>67</v>
       </c>
       <c r="CM4" s="28"/>
       <c r="CN4" s="28"/>
-      <c r="CO4" s="27" t="s">
+      <c r="CO4" s="29" t="s">
         <v>68</v>
       </c>
       <c r="CP4" s="28"/>
       <c r="CQ4" s="28"/>
-      <c r="CR4" s="36" t="s">
+      <c r="CR4" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="CS4" s="36" t="s">
+      <c r="CS4" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="CT4" s="36" t="s">
+      <c r="CT4" s="30" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:98" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="28"/>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="27" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" s="28"/>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="27" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="28"/>
       <c r="J5" s="28"/>
       <c r="K5" s="28"/>
-      <c r="L5" s="32" t="s">
+      <c r="L5" s="27" t="s">
         <v>12</v>
       </c>
       <c r="M5" s="28"/>
       <c r="N5" s="28"/>
       <c r="O5" s="28"/>
-      <c r="P5" s="32" t="s">
+      <c r="P5" s="27" t="s">
         <v>15</v>
       </c>
       <c r="Q5" s="28"/>
       <c r="R5" s="28"/>
-      <c r="S5" s="32" t="s">
+      <c r="S5" s="27" t="s">
         <v>12</v>
       </c>
       <c r="T5" s="28"/>
       <c r="U5" s="28"/>
-      <c r="V5" s="32" t="s">
+      <c r="V5" s="27" t="s">
         <v>72</v>
       </c>
       <c r="W5" s="28"/>
       <c r="X5" s="28"/>
       <c r="Y5" s="28"/>
-      <c r="Z5" s="33" t="s">
+      <c r="Z5" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="AA5" s="34"/>
-      <c r="AB5" s="34"/>
-      <c r="AC5" s="35"/>
-      <c r="AD5" s="32" t="s">
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="34"/>
+      <c r="AD5" s="27" t="s">
         <v>74</v>
       </c>
       <c r="AE5" s="28"/>
       <c r="AF5" s="28"/>
       <c r="AG5" s="28"/>
-      <c r="AH5" s="33" t="s">
+      <c r="AH5" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="AI5" s="34"/>
-      <c r="AJ5" s="35"/>
-      <c r="AK5" s="34" t="s">
+      <c r="AI5" s="33"/>
+      <c r="AJ5" s="34"/>
+      <c r="AK5" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="AL5" s="34"/>
-      <c r="AM5" s="35"/>
-      <c r="AN5" s="32" t="s">
+      <c r="AL5" s="33"/>
+      <c r="AM5" s="34"/>
+      <c r="AN5" s="27" t="s">
         <v>74</v>
       </c>
       <c r="AO5" s="28"/>
       <c r="AP5" s="28"/>
       <c r="AQ5" s="28"/>
-      <c r="AR5" s="32" t="s">
+      <c r="AR5" s="27" t="s">
         <v>75</v>
       </c>
       <c r="AS5" s="28"/>
       <c r="AT5" s="28"/>
       <c r="AU5" s="28"/>
-      <c r="AV5" s="32" t="s">
+      <c r="AV5" s="27" t="s">
         <v>11</v>
       </c>
       <c r="AW5" s="28"/>
       <c r="AX5" s="28"/>
       <c r="AY5" s="28"/>
-      <c r="AZ5" s="32" t="s">
+      <c r="AZ5" s="27" t="s">
         <v>15</v>
       </c>
       <c r="BA5" s="28"/>
       <c r="BB5" s="28"/>
-      <c r="BC5" s="32" t="s">
+      <c r="BC5" s="27" t="s">
         <v>11</v>
       </c>
       <c r="BD5" s="28"/>
       <c r="BE5" s="28"/>
       <c r="BF5" s="28"/>
-      <c r="BG5" s="32" t="s">
+      <c r="BG5" s="27" t="s">
         <v>76</v>
       </c>
       <c r="BH5" s="28"/>
       <c r="BI5" s="28"/>
       <c r="BJ5" s="28"/>
-      <c r="BK5" s="32" t="s">
+      <c r="BK5" s="27" t="s">
         <v>11</v>
       </c>
       <c r="BL5" s="28"/>
       <c r="BM5" s="28"/>
       <c r="BN5" s="28"/>
-      <c r="BO5" s="32" t="s">
+      <c r="BO5" s="27" t="s">
         <v>15</v>
       </c>
       <c r="BP5" s="28"/>
       <c r="BQ5" s="28"/>
       <c r="BR5" s="28"/>
-      <c r="BS5" s="32" t="s">
+      <c r="BS5" s="27" t="s">
         <v>11</v>
       </c>
       <c r="BT5" s="28"/>
       <c r="BU5" s="28"/>
       <c r="BV5" s="28"/>
-      <c r="BW5" s="32" t="s">
+      <c r="BW5" s="27" t="s">
         <v>11</v>
       </c>
       <c r="BX5" s="28"/>
       <c r="BY5" s="28"/>
       <c r="BZ5" s="28"/>
-      <c r="CA5" s="32" t="s">
+      <c r="CA5" s="27" t="s">
         <v>72</v>
       </c>
       <c r="CB5" s="28"/>
       <c r="CC5" s="28"/>
       <c r="CD5" s="28"/>
-      <c r="CE5" s="32" t="s">
+      <c r="CE5" s="27" t="s">
         <v>73</v>
       </c>
       <c r="CF5" s="28"/>
       <c r="CG5" s="28"/>
       <c r="CH5" s="28"/>
-      <c r="CI5" s="32" t="s">
+      <c r="CI5" s="27" t="s">
         <v>74</v>
       </c>
       <c r="CJ5" s="28"/>
       <c r="CK5" s="28"/>
-      <c r="CL5" s="32" t="s">
+      <c r="CL5" s="27" t="s">
         <v>77</v>
       </c>
       <c r="CM5" s="28"/>
       <c r="CN5" s="28"/>
-      <c r="CO5" s="32" t="s">
+      <c r="CO5" s="27" t="s">
         <v>73</v>
       </c>
       <c r="CP5" s="28"/>
       <c r="CQ5" s="28"/>
-      <c r="CR5" s="37"/>
-      <c r="CS5" s="37"/>
-      <c r="CT5" s="37"/>
+      <c r="CR5" s="31"/>
+      <c r="CS5" s="31"/>
+      <c r="CT5" s="31"/>
     </row>
     <row r="6" spans="1:98" ht="24" x14ac:dyDescent="0.15">
       <c r="A6" s="28"/>
@@ -21191,9 +21203,9 @@
       <c r="CQ6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="CR6" s="38"/>
-      <c r="CS6" s="38"/>
-      <c r="CT6" s="38"/>
+      <c r="CR6" s="32"/>
+      <c r="CS6" s="32"/>
+      <c r="CT6" s="32"/>
     </row>
     <row r="7" spans="1:98" x14ac:dyDescent="0.15">
       <c r="A7" s="10" t="s">
@@ -21233,11 +21245,11 @@
       </c>
       <c r="J7" s="13">
         <f t="shared" ref="J7:J35" si="2">IF(OR(I7="",I7=0),"",ROUND(H7/I7*$B$2,1))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" ref="K7:K34" si="3">(I7/$B$2)*10</f>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="L7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21281,35 +21293,35 @@
       </c>
       <c r="V7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W7" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X7" s="13">
         <f t="shared" ref="X7:X35" si="8">IF(OR(W7="",W7=0),"",ROUND(V7/W7*$B$2,1))</f>
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="Y7" s="12">
         <f t="shared" ref="Y7:Y34" si="9">(W7/$B$2)*5</f>
-        <v>5.8</v>
+        <v>5.7692307692307683</v>
       </c>
       <c r="Z7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA7" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB7" s="13">
         <f t="shared" ref="AB7:AB35" si="10">IF(OR(AA7="",AA7=0),"",ROUND(Z7/AA7*$B$2,1))</f>
-        <v>4.4000000000000004</v>
+        <v>7.2</v>
       </c>
       <c r="AC7" s="12">
         <f t="shared" ref="AC7:AC34" si="11">(AA7/$B$2)*5</f>
-        <v>3.4000000000000004</v>
+        <v>3.4615384615384617</v>
       </c>
       <c r="AD7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21325,7 +21337,7 @@
       </c>
       <c r="AG7" s="12">
         <f t="shared" ref="AG7:AG34" si="13">(AE7/$B$2)*5</f>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AH7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21361,11 +21373,11 @@
       </c>
       <c r="AP7" s="13">
         <f t="shared" ref="AP7:AP35" si="16">IF(OR(AO7="",AO7=0),"",ROUND(AN7/AO7*$B$2,1))</f>
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="AQ7" s="12">
         <f t="shared" ref="AQ7:AQ34" si="17">(AO7/$B$2)*5</f>
-        <v>2.8000000000000003</v>
+        <v>2.6923076923076921</v>
       </c>
       <c r="AR7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21377,11 +21389,11 @@
       </c>
       <c r="AT7" s="13">
         <f t="shared" ref="AT7:AT35" si="18">IF(OR(AS7="",AS7=0),"",ROUND(AR7/AS7*$B$2,1))</f>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="AU7" s="12">
         <f t="shared" ref="AU7:AU34" si="19">(AS7/$B$2)*5</f>
-        <v>1.7999999999999998</v>
+        <v>1.7307692307692308</v>
       </c>
       <c r="AV7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21393,11 +21405,11 @@
       </c>
       <c r="AX7" s="13">
         <f t="shared" ref="AX7:AX35" si="20">IF(OR(AW7="",AW7=0),"",ROUND(AV7/AW7*$B$2,1))</f>
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AY7" s="12">
         <f t="shared" ref="AY7:AY34" si="21">(AW7/$B$2)*5</f>
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AZ7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21425,7 +21437,7 @@
       </c>
       <c r="BF7" s="12">
         <f t="shared" ref="BF7:BF34" si="24">(BD7/$B$2)*8</f>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21461,19 +21473,19 @@
       </c>
       <c r="BO7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP7" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BQ7" s="13">
         <f t="shared" ref="BQ7:BQ35" si="29">IF(OR(BP7="",BP7=0),"",ROUND(BO7/BP7*$B$2,1))</f>
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BR7" s="12">
         <f t="shared" ref="BR7:BR34" si="30">(BP7/$B$2)*8</f>
-        <v>2.56</v>
+        <v>2.7692307692307692</v>
       </c>
       <c r="BS7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21501,39 +21513,39 @@
       </c>
       <c r="BY7" s="13">
         <f t="shared" ref="BY7:BY35" si="33">IF(OR(BX7="",BX7=0),"",ROUND(BW7/BX7*$B$2,1))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BZ7" s="12">
         <f t="shared" ref="BZ7:BZ34" si="34">(BX7/$B$2)*8</f>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="CA7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB7" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CC7" s="13">
         <f t="shared" ref="CC7:CC35" si="35">IF(OR(CB7="",CB7=0),"",ROUND(CA7/CB7*$B$2,1))</f>
-        <v>16.2</v>
+        <v>14.4</v>
       </c>
       <c r="CD7" s="12">
         <f t="shared" ref="CD7:CD34" si="36">(CB7/$B$2)*5</f>
-        <v>3.4000000000000004</v>
+        <v>3.4615384615384617</v>
       </c>
       <c r="CE7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CF7" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CG7" s="13">
         <f t="shared" ref="CG7:CG35" si="37">IF(OR(CF7="",CF7=0),"",ROUND(CE7/CF7*$B$2,1))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CH7" s="12">
         <f t="shared" ref="CH7:CH34" si="38">(CF7/$B$2)*7</f>
@@ -21549,7 +21561,7 @@
       </c>
       <c r="CK7" s="13">
         <f t="shared" ref="CK7:CK35" si="39">IF(OR(CJ7="",CJ7=0),"",ROUND(CI7/CJ7*$B$2,1))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21561,7 +21573,7 @@
       </c>
       <c r="CN7" s="13">
         <f t="shared" ref="CN7:CN35" si="40">IF(OR(CM7="",CM7=0),"",ROUND(CL7/CM7*$B$2,1))</f>
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="CO7" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A7,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21573,19 +21585,19 @@
       </c>
       <c r="CQ7" s="13">
         <f t="shared" ref="CQ7:CQ35" si="41">IF(OR(CP7="",CP7=0),"",ROUND(CO7/CP7*$B$2,1))</f>
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="CR7" s="14">
         <f t="shared" ref="CR7:CR34" si="42">SUM(B7,L7,P7,S7,AZ7,BK7,BO7,BS7,BW7,CA7,CE7,BC7,AN7,AR7,AV7,BG7,V7,E7,H7,AD7,Z7,AH7,AK7,CI7,CL7,CO7)</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CS7" s="14">
         <f t="shared" ref="CS7:CS34" si="43">SUM(C7,M7,Q7,T7,BL7,BP7,BT7,BX7,CB7,CF7,BA7,BD7,AO7,AS7,AW7,BH7,W7,F7,I7,AE7,AA7,AI7,AL7,CJ7,CM7,CP7)</f>
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="CT7" s="14">
         <f t="shared" ref="CT7:CT34" si="44">IFERROR(CR7/(CS7/$B$2),1000)</f>
-        <v>9.2592592592592595</v>
+        <v>9.5294117647058822</v>
       </c>
     </row>
     <row r="8" spans="1:98" x14ac:dyDescent="0.15">
@@ -21674,7 +21686,7 @@
       </c>
       <c r="V8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W8" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21682,11 +21694,11 @@
       </c>
       <c r="X8" s="13">
         <f t="shared" si="8"/>
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="Y8" s="12">
         <f t="shared" si="9"/>
-        <v>6.6000000000000005</v>
+        <v>6.3461538461538458</v>
       </c>
       <c r="Z8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21698,11 +21710,11 @@
       </c>
       <c r="AB8" s="13">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AC8" s="12">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>2.8846153846153841</v>
       </c>
       <c r="AD8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21718,7 +21730,7 @@
       </c>
       <c r="AG8" s="12">
         <f t="shared" si="13"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AH8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21730,7 +21742,7 @@
       </c>
       <c r="AJ8" s="13">
         <f t="shared" si="14"/>
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AK8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21746,7 +21758,7 @@
       </c>
       <c r="AN8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO8" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -21754,11 +21766,11 @@
       </c>
       <c r="AP8" s="13">
         <f t="shared" si="16"/>
-        <v>2.2000000000000002</v>
+        <v>5.7</v>
       </c>
       <c r="AQ8" s="12">
         <f t="shared" si="17"/>
-        <v>4.6000000000000005</v>
+        <v>4.4230769230769234</v>
       </c>
       <c r="AR8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21770,11 +21782,11 @@
       </c>
       <c r="AT8" s="13">
         <f t="shared" si="18"/>
-        <v>15.6</v>
+        <v>16.3</v>
       </c>
       <c r="AU8" s="12">
         <f t="shared" si="19"/>
-        <v>1.6</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="AV8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21786,11 +21798,11 @@
       </c>
       <c r="AX8" s="13">
         <f t="shared" si="20"/>
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
       <c r="AY8" s="12">
         <f t="shared" si="21"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AZ8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21818,7 +21830,7 @@
       </c>
       <c r="BF8" s="12">
         <f t="shared" si="24"/>
-        <v>0.96</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="BG8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21854,19 +21866,19 @@
       </c>
       <c r="BO8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BP8" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ8" s="13">
         <f t="shared" si="29"/>
-        <v>37.5</v>
+        <v>17.3</v>
       </c>
       <c r="BR8" s="12">
         <f t="shared" si="30"/>
-        <v>0.64</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="BS8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21894,11 +21906,11 @@
       </c>
       <c r="BY8" s="13">
         <f t="shared" si="33"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BZ8" s="12">
         <f t="shared" si="34"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="CA8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21910,27 +21922,27 @@
       </c>
       <c r="CC8" s="13">
         <f t="shared" si="35"/>
-        <v>15.8</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="CD8" s="12">
         <f t="shared" si="36"/>
-        <v>3.8</v>
+        <v>3.6538461538461537</v>
       </c>
       <c r="CE8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CF8" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CG8" s="13">
         <f t="shared" si="37"/>
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="CH8" s="12">
         <f t="shared" si="38"/>
-        <v>6.72</v>
+        <v>7.2692307692307701</v>
       </c>
       <c r="CI8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21942,7 +21954,7 @@
       </c>
       <c r="CK8" s="13">
         <f t="shared" si="39"/>
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
       <c r="CL8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -21954,19 +21966,19 @@
       </c>
       <c r="CN8" s="13">
         <f t="shared" si="40"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="CO8" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CP8" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A8,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="CQ8" s="13">
         <f t="shared" si="41"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="CR8" s="14">
         <f t="shared" si="42"/>
@@ -21974,11 +21986,11 @@
       </c>
       <c r="CS8" s="14">
         <f t="shared" si="43"/>
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="CT8" s="14">
         <f t="shared" si="44"/>
-        <v>8.0208333333333339</v>
+        <v>8.1382113821138216</v>
       </c>
     </row>
     <row r="9" spans="1:98" x14ac:dyDescent="0.15">
@@ -22067,19 +22079,19 @@
       </c>
       <c r="V9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X9" s="13">
         <f t="shared" si="8"/>
-        <v>4.5999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="Y9" s="12">
         <f t="shared" si="9"/>
-        <v>9.8000000000000007</v>
+        <v>9.615384615384615</v>
       </c>
       <c r="Z9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22091,11 +22103,11 @@
       </c>
       <c r="AB9" s="13">
         <f t="shared" si="10"/>
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AC9" s="12">
         <f t="shared" si="11"/>
-        <v>9.3999999999999986</v>
+        <v>9.0384615384615383</v>
       </c>
       <c r="AD9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22107,11 +22119,11 @@
       </c>
       <c r="AF9" s="13">
         <f t="shared" si="12"/>
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AG9" s="12">
         <f t="shared" si="13"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AH9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22123,7 +22135,7 @@
       </c>
       <c r="AJ9" s="13">
         <f t="shared" si="14"/>
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AK9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22135,7 +22147,7 @@
       </c>
       <c r="AM9" s="13">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AN9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22143,7 +22155,7 @@
       </c>
       <c r="AO9" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP9" s="13">
         <f t="shared" si="16"/>
@@ -22151,7 +22163,7 @@
       </c>
       <c r="AQ9" s="12">
         <f t="shared" si="17"/>
-        <v>4.4000000000000004</v>
+        <v>4.4230769230769234</v>
       </c>
       <c r="AR9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22163,27 +22175,27 @@
       </c>
       <c r="AT9" s="13">
         <f t="shared" si="18"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU9" s="12">
         <f t="shared" si="19"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AV9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW9" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX9" s="13">
         <f t="shared" si="20"/>
-        <v>16.7</v>
+        <v>6.5</v>
       </c>
       <c r="AY9" s="12">
         <f t="shared" si="21"/>
-        <v>0.6</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AZ9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22211,7 +22223,7 @@
       </c>
       <c r="BF9" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22243,7 +22255,7 @@
       </c>
       <c r="BN9" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22255,11 +22267,11 @@
       </c>
       <c r="BQ9" s="13">
         <f t="shared" si="29"/>
-        <v>17.899999999999999</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="BR9" s="12">
         <f t="shared" si="30"/>
-        <v>2.2400000000000002</v>
+        <v>2.1538461538461537</v>
       </c>
       <c r="BS9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22279,51 +22291,51 @@
       </c>
       <c r="BW9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BX9" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BY9" s="13">
         <f t="shared" si="33"/>
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="BZ9" s="12">
         <f t="shared" si="34"/>
-        <v>2.56</v>
+        <v>2.7692307692307692</v>
       </c>
       <c r="CA9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CB9" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CC9" s="13">
         <f t="shared" si="35"/>
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="CD9" s="12">
         <f t="shared" si="36"/>
-        <v>5.8</v>
+        <v>5.7692307692307683</v>
       </c>
       <c r="CE9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CF9" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="CG9" s="13">
         <f t="shared" si="37"/>
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="CH9" s="12">
         <f t="shared" si="38"/>
-        <v>14.56</v>
+        <v>14.53846153846154</v>
       </c>
       <c r="CI9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22335,7 +22347,7 @@
       </c>
       <c r="CK9" s="13">
         <f t="shared" si="39"/>
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="CL9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22347,31 +22359,31 @@
       </c>
       <c r="CN9" s="13">
         <f t="shared" si="40"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="CO9" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="CP9" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A9,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="CQ9" s="13">
         <f t="shared" si="41"/>
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="CR9" s="14">
         <f t="shared" si="42"/>
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="CS9" s="14">
         <f t="shared" si="43"/>
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="CT9" s="14">
         <f t="shared" si="44"/>
-        <v>6.3461538461538458</v>
+        <v>5.7940074906367034</v>
       </c>
     </row>
     <row r="10" spans="1:98" x14ac:dyDescent="0.15">
@@ -22412,11 +22424,11 @@
       </c>
       <c r="J10" s="13">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="L10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22468,11 +22480,11 @@
       </c>
       <c r="X10" s="13">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="Y10" s="12">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="Z10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22484,11 +22496,11 @@
       </c>
       <c r="AB10" s="13">
         <f t="shared" si="10"/>
-        <v>41.7</v>
+        <v>43.3</v>
       </c>
       <c r="AC10" s="12">
         <f t="shared" si="11"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AD10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22516,7 +22528,7 @@
       </c>
       <c r="AJ10" s="13">
         <f t="shared" si="14"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AK10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22528,7 +22540,7 @@
       </c>
       <c r="AM10" s="13">
         <f t="shared" si="15"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AN10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22540,11 +22552,11 @@
       </c>
       <c r="AP10" s="13">
         <f t="shared" si="16"/>
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AQ10" s="12">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AR10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22556,11 +22568,11 @@
       </c>
       <c r="AT10" s="13">
         <f t="shared" si="18"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU10" s="12">
         <f t="shared" si="19"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AV10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22572,11 +22584,11 @@
       </c>
       <c r="AX10" s="13">
         <f t="shared" si="20"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY10" s="12">
         <f t="shared" si="21"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AZ10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22600,11 +22612,11 @@
       </c>
       <c r="BE10" s="13">
         <f t="shared" si="23"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF10" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22648,11 +22660,11 @@
       </c>
       <c r="BQ10" s="13">
         <f t="shared" si="29"/>
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR10" s="12">
         <f t="shared" si="30"/>
-        <v>1.92</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="BS10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22668,7 +22680,7 @@
       </c>
       <c r="BV10" s="12">
         <f t="shared" si="32"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BW10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22680,11 +22692,11 @@
       </c>
       <c r="BY10" s="13">
         <f t="shared" si="33"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BZ10" s="12">
         <f t="shared" si="34"/>
-        <v>1.92</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="CA10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22696,11 +22708,11 @@
       </c>
       <c r="CC10" s="13">
         <f t="shared" si="35"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CD10" s="12">
         <f t="shared" si="36"/>
-        <v>2</v>
+        <v>1.9230769230769231</v>
       </c>
       <c r="CE10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22712,11 +22724,11 @@
       </c>
       <c r="CG10" s="13">
         <f t="shared" si="37"/>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="CH10" s="12">
         <f t="shared" si="38"/>
-        <v>0.28000000000000003</v>
+        <v>0.26923076923076927</v>
       </c>
       <c r="CI10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22728,7 +22740,7 @@
       </c>
       <c r="CK10" s="13">
         <f t="shared" si="39"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CL10" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A10,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22752,7 +22764,7 @@
       </c>
       <c r="CQ10" s="13">
         <f t="shared" si="41"/>
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="CR10" s="14">
         <f t="shared" si="42"/>
@@ -22764,7 +22776,7 @@
       </c>
       <c r="CT10" s="14">
         <f t="shared" si="44"/>
-        <v>23.27586206896552</v>
+        <v>24.206896551724139</v>
       </c>
     </row>
     <row r="11" spans="1:98" x14ac:dyDescent="0.15">
@@ -22853,7 +22865,7 @@
       </c>
       <c r="V11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -22861,11 +22873,11 @@
       </c>
       <c r="X11" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y11" s="12">
         <f t="shared" si="9"/>
-        <v>3.4000000000000004</v>
+        <v>3.2692307692307692</v>
       </c>
       <c r="Z11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22877,11 +22889,11 @@
       </c>
       <c r="AB11" s="13">
         <f t="shared" si="10"/>
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AC11" s="12">
         <f t="shared" si="11"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AD11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22901,15 +22913,15 @@
       </c>
       <c r="AH11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI11" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ11" s="13">
         <f t="shared" si="14"/>
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="AK11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22921,11 +22933,11 @@
       </c>
       <c r="AM11" s="13">
         <f t="shared" si="15"/>
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AN11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO11" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -22933,11 +22945,11 @@
       </c>
       <c r="AP11" s="13">
         <f t="shared" si="16"/>
-        <v>6.3</v>
+        <v>13</v>
       </c>
       <c r="AQ11" s="12">
         <f t="shared" si="17"/>
-        <v>1.6</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="AR11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -22949,15 +22961,15 @@
       </c>
       <c r="AT11" s="13">
         <f t="shared" si="18"/>
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AU11" s="12">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AV11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW11" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -22965,11 +22977,11 @@
       </c>
       <c r="AX11" s="13">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AY11" s="12">
         <f t="shared" si="21"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AZ11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23029,7 +23041,7 @@
       </c>
       <c r="BN11" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23041,11 +23053,11 @@
       </c>
       <c r="BQ11" s="13">
         <f t="shared" si="29"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BR11" s="12">
         <f t="shared" si="30"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BS11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23061,11 +23073,11 @@
       </c>
       <c r="BV11" s="12">
         <f t="shared" si="32"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BW11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BX11" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23073,11 +23085,11 @@
       </c>
       <c r="BY11" s="13">
         <f t="shared" si="33"/>
-        <v>2.5</v>
+        <v>10.4</v>
       </c>
       <c r="BZ11" s="12">
         <f t="shared" si="34"/>
-        <v>3.2</v>
+        <v>3.0769230769230771</v>
       </c>
       <c r="CA11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23089,31 +23101,31 @@
       </c>
       <c r="CC11" s="13">
         <f t="shared" si="35"/>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CD11" s="12">
         <f t="shared" si="36"/>
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="CE11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF11" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CG11" s="13">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="CH11" s="12">
         <f t="shared" si="38"/>
-        <v>5.32</v>
+        <v>5.384615384615385</v>
       </c>
       <c r="CI11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ11" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23121,11 +23133,11 @@
       </c>
       <c r="CK11" s="13">
         <f t="shared" si="39"/>
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="CL11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM11" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23133,11 +23145,11 @@
       </c>
       <c r="CN11" s="13">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CO11" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="CP11" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A11,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23145,19 +23157,19 @@
       </c>
       <c r="CQ11" s="13">
         <f t="shared" si="41"/>
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="CR11" s="14">
         <f t="shared" si="42"/>
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="CS11" s="14">
         <f t="shared" si="43"/>
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="CT11" s="14">
         <f t="shared" si="44"/>
-        <v>4.435483870967742</v>
+        <v>8.6666666666666679</v>
       </c>
     </row>
     <row r="12" spans="1:98" x14ac:dyDescent="0.15">
@@ -23186,7 +23198,7 @@
       </c>
       <c r="G12" s="13">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23198,11 +23210,11 @@
       </c>
       <c r="J12" s="13">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="3"/>
-        <v>1.6</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="L12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23254,11 +23266,11 @@
       </c>
       <c r="X12" s="13">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="Y12" s="12">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="Z12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23270,11 +23282,11 @@
       </c>
       <c r="AB12" s="13">
         <f t="shared" si="10"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC12" s="12">
         <f t="shared" si="11"/>
-        <v>1.6</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="AD12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23302,7 +23314,7 @@
       </c>
       <c r="AJ12" s="13">
         <f t="shared" si="14"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AK12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23314,7 +23326,7 @@
       </c>
       <c r="AM12" s="13">
         <f t="shared" si="15"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AN12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23326,11 +23338,11 @@
       </c>
       <c r="AP12" s="13">
         <f t="shared" si="16"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="AQ12" s="12">
         <f t="shared" si="17"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AR12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23342,11 +23354,11 @@
       </c>
       <c r="AT12" s="13">
         <f t="shared" si="18"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AU12" s="12">
         <f t="shared" si="19"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AV12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23358,11 +23370,11 @@
       </c>
       <c r="AX12" s="13">
         <f t="shared" si="20"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AY12" s="12">
         <f t="shared" si="21"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AZ12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23390,7 +23402,7 @@
       </c>
       <c r="BF12" s="12">
         <f t="shared" si="24"/>
-        <v>1.28</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="BG12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23422,7 +23434,7 @@
       </c>
       <c r="BN12" s="12">
         <f t="shared" si="28"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BO12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23434,11 +23446,11 @@
       </c>
       <c r="BQ12" s="13">
         <f t="shared" si="29"/>
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="BR12" s="12">
         <f t="shared" si="30"/>
-        <v>2.56</v>
+        <v>2.4615384615384617</v>
       </c>
       <c r="BS12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23466,11 +23478,11 @@
       </c>
       <c r="BY12" s="13">
         <f t="shared" si="33"/>
-        <v>31.3</v>
+        <v>32.5</v>
       </c>
       <c r="BZ12" s="12">
         <f t="shared" si="34"/>
-        <v>1.28</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="CA12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23482,11 +23494,11 @@
       </c>
       <c r="CC12" s="13">
         <f t="shared" si="35"/>
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="CD12" s="12">
         <f t="shared" si="36"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="CE12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23498,11 +23510,11 @@
       </c>
       <c r="CG12" s="13">
         <f t="shared" si="37"/>
-        <v>9.4</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="CH12" s="12">
         <f t="shared" si="38"/>
-        <v>2.2400000000000002</v>
+        <v>2.1538461538461542</v>
       </c>
       <c r="CI12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23514,7 +23526,7 @@
       </c>
       <c r="CK12" s="13">
         <f t="shared" si="39"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL12" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A12,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23538,7 +23550,7 @@
       </c>
       <c r="CQ12" s="13">
         <f t="shared" si="41"/>
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="CR12" s="14">
         <f t="shared" si="42"/>
@@ -23550,7 +23562,7 @@
       </c>
       <c r="CT12" s="14">
         <f t="shared" si="44"/>
-        <v>22.61904761904762</v>
+        <v>23.523809523809526</v>
       </c>
     </row>
     <row r="13" spans="1:98" x14ac:dyDescent="0.15">
@@ -23647,11 +23659,11 @@
       </c>
       <c r="X13" s="13">
         <f t="shared" si="8"/>
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="Y13" s="12">
         <f t="shared" si="9"/>
-        <v>1.4000000000000001</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="Z13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23695,7 +23707,7 @@
       </c>
       <c r="AJ13" s="13">
         <f t="shared" si="14"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AK13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23707,7 +23719,7 @@
       </c>
       <c r="AM13" s="13">
         <f t="shared" si="15"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AN13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23719,11 +23731,11 @@
       </c>
       <c r="AP13" s="13">
         <f t="shared" si="16"/>
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="AQ13" s="12">
         <f t="shared" si="17"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AR13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23735,11 +23747,11 @@
       </c>
       <c r="AT13" s="13">
         <f t="shared" si="18"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AU13" s="12">
         <f t="shared" si="19"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AV13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23751,11 +23763,11 @@
       </c>
       <c r="AX13" s="13">
         <f t="shared" si="20"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AY13" s="12">
         <f t="shared" si="21"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AZ13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23783,7 +23795,7 @@
       </c>
       <c r="BF13" s="12">
         <f t="shared" si="24"/>
-        <v>1.28</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="BG13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23815,7 +23827,7 @@
       </c>
       <c r="BN13" s="12">
         <f t="shared" si="28"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BO13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23827,11 +23839,11 @@
       </c>
       <c r="BQ13" s="13">
         <f t="shared" si="29"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="BR13" s="12">
         <f t="shared" si="30"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BS13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23859,11 +23871,11 @@
       </c>
       <c r="BY13" s="13">
         <f t="shared" si="33"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BZ13" s="12">
         <f t="shared" si="34"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="CA13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23875,11 +23887,11 @@
       </c>
       <c r="CC13" s="13">
         <f t="shared" si="35"/>
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="CD13" s="12">
         <f t="shared" si="36"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="CE13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23891,11 +23903,11 @@
       </c>
       <c r="CG13" s="13">
         <f t="shared" si="37"/>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="CH13" s="12">
         <f t="shared" si="38"/>
-        <v>0.28000000000000003</v>
+        <v>0.26923076923076927</v>
       </c>
       <c r="CI13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -23911,7 +23923,7 @@
       </c>
       <c r="CL13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM13" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23919,11 +23931,11 @@
       </c>
       <c r="CN13" s="13">
         <f t="shared" si="40"/>
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="CO13" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CP13" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A13,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -23931,11 +23943,11 @@
       </c>
       <c r="CQ13" s="13">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="CR13" s="14">
         <f t="shared" si="42"/>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CS13" s="14">
         <f t="shared" si="43"/>
@@ -23943,7 +23955,7 @@
       </c>
       <c r="CT13" s="14">
         <f t="shared" si="44"/>
-        <v>38.793103448275865</v>
+        <v>43.03448275862069</v>
       </c>
     </row>
     <row r="14" spans="1:98" x14ac:dyDescent="0.15">
@@ -24032,7 +24044,7 @@
       </c>
       <c r="V14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W14" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24040,15 +24052,15 @@
       </c>
       <c r="X14" s="13">
         <f t="shared" si="8"/>
-        <v>7.1</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="Y14" s="12">
         <f t="shared" si="9"/>
-        <v>2.8000000000000003</v>
+        <v>2.6923076923076921</v>
       </c>
       <c r="Z14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA14" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24056,11 +24068,11 @@
       </c>
       <c r="AB14" s="13">
         <f t="shared" si="10"/>
-        <v>6.3</v>
+        <v>13</v>
       </c>
       <c r="AC14" s="12">
         <f t="shared" si="11"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AD14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24076,19 +24088,19 @@
       </c>
       <c r="AG14" s="12">
         <f t="shared" si="13"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AH14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI14" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" s="13">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="AK14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24100,7 +24112,7 @@
       </c>
       <c r="AM14" s="13">
         <f t="shared" si="15"/>
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AN14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24112,15 +24124,15 @@
       </c>
       <c r="AP14" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ14" s="12">
         <f t="shared" si="17"/>
-        <v>1.2</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AR14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS14" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24128,11 +24140,11 @@
       </c>
       <c r="AT14" s="13">
         <f t="shared" si="18"/>
-        <v>16.7</v>
+        <v>26</v>
       </c>
       <c r="AU14" s="12">
         <f t="shared" si="19"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AV14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24144,11 +24156,11 @@
       </c>
       <c r="AX14" s="13">
         <f t="shared" si="20"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AY14" s="12">
         <f t="shared" si="21"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AZ14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24172,11 +24184,11 @@
       </c>
       <c r="BE14" s="13">
         <f t="shared" si="23"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="BF14" s="12">
         <f t="shared" si="24"/>
-        <v>0.96</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="BG14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24240,7 +24252,7 @@
       </c>
       <c r="BV14" s="12">
         <f t="shared" si="32"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BW14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24252,11 +24264,11 @@
       </c>
       <c r="BY14" s="13">
         <f t="shared" si="33"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BZ14" s="12">
         <f t="shared" si="34"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="CA14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24264,15 +24276,15 @@
       </c>
       <c r="CB14" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CC14" s="13">
         <f t="shared" si="35"/>
-        <v>31.3</v>
+        <v>26</v>
       </c>
       <c r="CD14" s="12">
         <f t="shared" si="36"/>
-        <v>0.8</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="CE14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24284,11 +24296,11 @@
       </c>
       <c r="CG14" s="13">
         <f t="shared" si="37"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CH14" s="12">
         <f t="shared" si="38"/>
-        <v>3.36</v>
+        <v>3.2307692307692308</v>
       </c>
       <c r="CI14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24312,11 +24324,11 @@
       </c>
       <c r="CN14" s="13">
         <f t="shared" si="40"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CO14" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP14" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A14,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24324,19 +24336,19 @@
       </c>
       <c r="CQ14" s="13">
         <f t="shared" si="41"/>
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="CR14" s="14">
         <f t="shared" si="42"/>
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="CS14" s="14">
         <f t="shared" si="43"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="CT14" s="14">
         <f t="shared" si="44"/>
-        <v>16.666666666666664</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="15" spans="1:98" x14ac:dyDescent="0.15">
@@ -24425,7 +24437,7 @@
       </c>
       <c r="V15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W15" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24433,15 +24445,15 @@
       </c>
       <c r="X15" s="13">
         <f t="shared" si="8"/>
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="Y15" s="12">
         <f t="shared" si="9"/>
-        <v>3.2</v>
+        <v>3.0769230769230771</v>
       </c>
       <c r="Z15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA15" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24449,11 +24461,11 @@
       </c>
       <c r="AB15" s="13">
         <f t="shared" si="10"/>
-        <v>8.3000000000000007</v>
+        <v>17.3</v>
       </c>
       <c r="AC15" s="12">
         <f t="shared" si="11"/>
-        <v>1.2</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AD15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24473,15 +24485,15 @@
       </c>
       <c r="AH15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ15" s="13">
         <f t="shared" si="14"/>
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="AK15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24497,7 +24509,7 @@
       </c>
       <c r="AN15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO15" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24505,11 +24517,11 @@
       </c>
       <c r="AP15" s="13">
         <f t="shared" si="16"/>
-        <v>15</v>
+        <v>20.8</v>
       </c>
       <c r="AQ15" s="12">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AR15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24521,15 +24533,15 @@
       </c>
       <c r="AT15" s="13">
         <f t="shared" si="18"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AU15" s="12">
         <f t="shared" si="19"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AV15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24537,11 +24549,11 @@
       </c>
       <c r="AX15" s="13">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AY15" s="12">
         <f t="shared" si="21"/>
-        <v>1.4000000000000001</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="AZ15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24569,7 +24581,7 @@
       </c>
       <c r="BF15" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24585,7 +24597,7 @@
       </c>
       <c r="BJ15" s="12">
         <f t="shared" si="26"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BK15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24601,7 +24613,7 @@
       </c>
       <c r="BN15" s="12">
         <f t="shared" si="28"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BO15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24613,11 +24625,11 @@
       </c>
       <c r="BQ15" s="13">
         <f t="shared" si="29"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BR15" s="12">
         <f t="shared" si="30"/>
-        <v>1.28</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="BS15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24629,11 +24641,11 @@
       </c>
       <c r="BU15" s="13">
         <f t="shared" si="31"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BV15" s="12">
         <f t="shared" si="32"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BW15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24661,15 +24673,15 @@
       </c>
       <c r="CC15" s="13">
         <f t="shared" si="35"/>
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="CD15" s="12">
         <f t="shared" si="36"/>
-        <v>1.4000000000000001</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="CE15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CF15" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24677,11 +24689,11 @@
       </c>
       <c r="CG15" s="13">
         <f t="shared" si="37"/>
-        <v>5</v>
+        <v>10.4</v>
       </c>
       <c r="CH15" s="12">
         <f t="shared" si="38"/>
-        <v>1.4000000000000001</v>
+        <v>1.3461538461538463</v>
       </c>
       <c r="CI15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24693,11 +24705,11 @@
       </c>
       <c r="CK15" s="13">
         <f t="shared" si="39"/>
-        <v>33.299999999999997</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="CL15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM15" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24705,11 +24717,11 @@
       </c>
       <c r="CN15" s="13">
         <f t="shared" si="40"/>
-        <v>6.3</v>
+        <v>13</v>
       </c>
       <c r="CO15" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP15" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A15,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24717,19 +24729,19 @@
       </c>
       <c r="CQ15" s="13">
         <f t="shared" si="41"/>
-        <v>14.3</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="CR15" s="14">
         <f t="shared" si="42"/>
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="CS15" s="14">
         <f t="shared" si="43"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="CT15" s="14">
         <f t="shared" si="44"/>
-        <v>9.81012658227848</v>
+        <v>12.674999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:98" x14ac:dyDescent="0.15">
@@ -24818,7 +24830,7 @@
       </c>
       <c r="V16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W16" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24826,27 +24838,27 @@
       </c>
       <c r="X16" s="13">
         <f t="shared" si="8"/>
-        <v>4.2</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="Y16" s="12">
         <f t="shared" si="9"/>
-        <v>2.4</v>
+        <v>2.3076923076923079</v>
       </c>
       <c r="Z16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA16" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB16" s="13">
         <f t="shared" si="10"/>
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="AC16" s="12">
         <f t="shared" si="11"/>
-        <v>1.4000000000000001</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="AD16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24874,7 +24886,7 @@
       </c>
       <c r="AJ16" s="13">
         <f t="shared" si="14"/>
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AK16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24890,7 +24902,7 @@
       </c>
       <c r="AN16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO16" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -24898,11 +24910,11 @@
       </c>
       <c r="AP16" s="13">
         <f t="shared" si="16"/>
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AQ16" s="12">
         <f t="shared" si="17"/>
-        <v>1.2</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AR16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24914,11 +24926,11 @@
       </c>
       <c r="AT16" s="13">
         <f t="shared" si="18"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AU16" s="12">
         <f t="shared" si="19"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AV16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24930,11 +24942,11 @@
       </c>
       <c r="AX16" s="13">
         <f t="shared" si="20"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AY16" s="12">
         <f t="shared" si="21"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AZ16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -24962,7 +24974,7 @@
       </c>
       <c r="BF16" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25006,11 +25018,11 @@
       </c>
       <c r="BQ16" s="13">
         <f t="shared" si="29"/>
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BR16" s="12">
         <f t="shared" si="30"/>
-        <v>2.2400000000000002</v>
+        <v>2.1538461538461537</v>
       </c>
       <c r="BS16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25030,7 +25042,7 @@
       </c>
       <c r="BW16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BX16" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25038,11 +25050,11 @@
       </c>
       <c r="BY16" s="13">
         <f t="shared" si="33"/>
-        <v>5.6</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="BZ16" s="12">
         <f t="shared" si="34"/>
-        <v>2.88</v>
+        <v>2.7692307692307692</v>
       </c>
       <c r="CA16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25050,19 +25062,19 @@
       </c>
       <c r="CB16" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC16" s="13">
         <f t="shared" si="35"/>
-        <v>8.3000000000000007</v>
+        <v>7.4</v>
       </c>
       <c r="CD16" s="12">
         <f t="shared" si="36"/>
-        <v>1.2</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="CE16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CF16" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25070,11 +25082,11 @@
       </c>
       <c r="CG16" s="13">
         <f t="shared" si="37"/>
-        <v>4.2</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="CH16" s="12">
         <f t="shared" si="38"/>
-        <v>1.68</v>
+        <v>1.6153846153846154</v>
       </c>
       <c r="CI16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25086,7 +25098,7 @@
       </c>
       <c r="CK16" s="13">
         <f t="shared" si="39"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CL16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25098,31 +25110,31 @@
       </c>
       <c r="CN16" s="13">
         <f t="shared" si="40"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CO16" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP16" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A16,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CQ16" s="13">
         <f t="shared" si="41"/>
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="CR16" s="14">
         <f t="shared" si="42"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="CS16" s="14">
         <f t="shared" si="43"/>
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="CT16" s="14">
         <f t="shared" si="44"/>
-        <v>8.3333333333333339</v>
+        <v>9.5333333333333332</v>
       </c>
     </row>
     <row r="17" spans="1:98" x14ac:dyDescent="0.15">
@@ -25219,15 +25231,15 @@
       </c>
       <c r="X17" s="13">
         <f t="shared" si="8"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="Y17" s="12">
         <f t="shared" si="9"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="Z17" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25235,11 +25247,11 @@
       </c>
       <c r="AB17" s="13">
         <f t="shared" si="10"/>
-        <v>8.3000000000000007</v>
+        <v>17.3</v>
       </c>
       <c r="AC17" s="12">
         <f t="shared" si="11"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AD17" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25307,11 +25319,11 @@
       </c>
       <c r="AT17" s="13">
         <f t="shared" si="18"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="19"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AV17" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25387,7 +25399,7 @@
       </c>
       <c r="BN17" s="12">
         <f t="shared" si="28"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BO17" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25399,11 +25411,11 @@
       </c>
       <c r="BQ17" s="13">
         <f t="shared" si="29"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BR17" s="12">
         <f t="shared" si="30"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BS17" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25435,7 +25447,7 @@
       </c>
       <c r="BZ17" s="12">
         <f t="shared" si="34"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="CA17" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25447,11 +25459,11 @@
       </c>
       <c r="CC17" s="13">
         <f t="shared" si="35"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="CD17" s="12">
         <f t="shared" si="36"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="CE17" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25463,15 +25475,15 @@
       </c>
       <c r="CG17" s="13">
         <f t="shared" si="37"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CH17" s="12">
         <f t="shared" si="38"/>
-        <v>0.28000000000000003</v>
+        <v>0.26923076923076927</v>
       </c>
       <c r="CI17" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ17" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25479,11 +25491,11 @@
       </c>
       <c r="CK17" s="13">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CL17" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM17" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A17,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25507,7 +25519,7 @@
       </c>
       <c r="CR17" s="14">
         <f t="shared" si="42"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CS17" s="14">
         <f t="shared" si="43"/>
@@ -25515,7 +25527,7 @@
       </c>
       <c r="CT17" s="14">
         <f t="shared" si="44"/>
-        <v>21.25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:98" x14ac:dyDescent="0.15">
@@ -25604,19 +25616,19 @@
       </c>
       <c r="V18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W18" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X18" s="13">
         <f t="shared" si="8"/>
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y18" s="12">
         <f t="shared" si="9"/>
-        <v>6.2</v>
+        <v>6.1538461538461542</v>
       </c>
       <c r="Z18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25628,11 +25640,11 @@
       </c>
       <c r="AB18" s="13">
         <f t="shared" si="10"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC18" s="12">
         <f t="shared" si="11"/>
-        <v>3.2</v>
+        <v>3.0769230769230771</v>
       </c>
       <c r="AD18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25652,15 +25664,15 @@
       </c>
       <c r="AH18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ18" s="13">
         <f t="shared" si="14"/>
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25680,15 +25692,15 @@
       </c>
       <c r="AO18" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP18" s="13">
         <f t="shared" si="16"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ18" s="12">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AR18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25700,11 +25712,11 @@
       </c>
       <c r="AT18" s="13">
         <f t="shared" si="18"/>
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AV18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25716,11 +25728,11 @@
       </c>
       <c r="AX18" s="13">
         <f t="shared" si="20"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY18" s="12">
         <f t="shared" si="21"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AZ18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25744,11 +25756,11 @@
       </c>
       <c r="BE18" s="13">
         <f t="shared" si="23"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="BF18" s="12">
         <f t="shared" si="24"/>
-        <v>0.96</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="BG18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25780,23 +25792,23 @@
       </c>
       <c r="BN18" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BP18" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BQ18" s="13">
         <f t="shared" si="29"/>
-        <v>10.7</v>
+        <v>6.5</v>
       </c>
       <c r="BR18" s="12">
         <f t="shared" si="30"/>
-        <v>2.2400000000000002</v>
+        <v>2.4615384615384617</v>
       </c>
       <c r="BS18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25816,23 +25828,23 @@
       </c>
       <c r="BW18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BX18" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BY18" s="13">
         <f t="shared" si="33"/>
-        <v>11.1</v>
+        <v>7.8</v>
       </c>
       <c r="BZ18" s="12">
         <f t="shared" si="34"/>
-        <v>2.88</v>
+        <v>3.0769230769230771</v>
       </c>
       <c r="CA18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CB18" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25840,27 +25852,27 @@
       </c>
       <c r="CC18" s="13">
         <f t="shared" si="35"/>
-        <v>5.3</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="CD18" s="12">
         <f t="shared" si="36"/>
-        <v>3.8</v>
+        <v>3.6538461538461537</v>
       </c>
       <c r="CE18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CF18" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CG18" s="13">
         <f t="shared" si="37"/>
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="CH18" s="12">
         <f t="shared" si="38"/>
-        <v>4.2</v>
+        <v>4.3076923076923084</v>
       </c>
       <c r="CI18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25872,7 +25884,7 @@
       </c>
       <c r="CK18" s="13">
         <f t="shared" si="39"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CL18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -25888,7 +25900,7 @@
       </c>
       <c r="CO18" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CP18" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A18,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -25896,19 +25908,19 @@
       </c>
       <c r="CQ18" s="13">
         <f t="shared" si="41"/>
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="CR18" s="14">
         <f t="shared" si="42"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="CS18" s="14">
         <f t="shared" si="43"/>
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="CT18" s="14">
         <f t="shared" si="44"/>
-        <v>8.1730769230769234</v>
+        <v>8.5061728395061724</v>
       </c>
     </row>
     <row r="19" spans="1:98" x14ac:dyDescent="0.15">
@@ -25997,19 +26009,19 @@
       </c>
       <c r="V19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W19" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X19" s="13">
         <f t="shared" si="8"/>
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="Y19" s="12">
         <f t="shared" si="9"/>
-        <v>0.2</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="Z19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26021,11 +26033,11 @@
       </c>
       <c r="AB19" s="13">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC19" s="12">
         <f t="shared" si="11"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AD19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26041,7 +26053,7 @@
       </c>
       <c r="AG19" s="12">
         <f t="shared" si="13"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AH19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26053,7 +26065,7 @@
       </c>
       <c r="AJ19" s="13">
         <f t="shared" si="14"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AK19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26077,11 +26089,11 @@
       </c>
       <c r="AP19" s="13">
         <f t="shared" si="16"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AQ19" s="12">
         <f t="shared" si="17"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AR19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26141,7 +26153,7 @@
       </c>
       <c r="BF19" s="12">
         <f t="shared" si="24"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BG19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26173,7 +26185,7 @@
       </c>
       <c r="BN19" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26233,11 +26245,11 @@
       </c>
       <c r="CC19" s="13">
         <f t="shared" si="35"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CD19" s="12">
         <f t="shared" si="36"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="CE19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26253,7 +26265,7 @@
       </c>
       <c r="CH19" s="12">
         <f t="shared" si="38"/>
-        <v>0.56000000000000005</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="CI19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26265,7 +26277,7 @@
       </c>
       <c r="CK19" s="13">
         <f t="shared" si="39"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL19" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A19,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26289,19 +26301,19 @@
       </c>
       <c r="CQ19" s="13">
         <f t="shared" si="41"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CR19" s="14">
         <f t="shared" si="42"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS19" s="14">
         <f t="shared" si="43"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CT19" s="14">
         <f t="shared" si="44"/>
-        <v>44.230769230769226</v>
+        <v>40.857142857142861</v>
       </c>
     </row>
     <row r="20" spans="1:98" x14ac:dyDescent="0.15">
@@ -26342,11 +26354,11 @@
       </c>
       <c r="J20" s="13">
         <f t="shared" si="2"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="3"/>
-        <v>1.2</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="L20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26390,7 +26402,7 @@
       </c>
       <c r="V20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W20" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26398,15 +26410,15 @@
       </c>
       <c r="X20" s="13">
         <f t="shared" si="8"/>
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="Y20" s="12">
         <f t="shared" si="9"/>
-        <v>5.6000000000000005</v>
+        <v>5.3846153846153841</v>
       </c>
       <c r="Z20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA20" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -26414,11 +26426,11 @@
       </c>
       <c r="AB20" s="13">
         <f t="shared" si="10"/>
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="AC20" s="12">
         <f t="shared" si="11"/>
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AD20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26434,7 +26446,7 @@
       </c>
       <c r="AG20" s="12">
         <f t="shared" si="13"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AH20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26470,11 +26482,11 @@
       </c>
       <c r="AP20" s="13">
         <f t="shared" si="16"/>
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="AQ20" s="12">
         <f t="shared" si="17"/>
-        <v>2.4</v>
+        <v>2.3076923076923079</v>
       </c>
       <c r="AR20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26486,11 +26498,11 @@
       </c>
       <c r="AT20" s="13">
         <f t="shared" si="18"/>
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="AU20" s="12">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AV20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26502,11 +26514,11 @@
       </c>
       <c r="AX20" s="13">
         <f t="shared" si="20"/>
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AY20" s="12">
         <f t="shared" si="21"/>
-        <v>1.6</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="AZ20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26530,11 +26542,11 @@
       </c>
       <c r="BE20" s="13">
         <f t="shared" si="23"/>
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="BF20" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26570,19 +26582,19 @@
       </c>
       <c r="BO20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BP20" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BQ20" s="13">
         <f t="shared" si="29"/>
-        <v>18.8</v>
+        <v>10.4</v>
       </c>
       <c r="BR20" s="12">
         <f t="shared" si="30"/>
-        <v>1.28</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="BS20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26610,43 +26622,43 @@
       </c>
       <c r="BY20" s="13">
         <f t="shared" si="33"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ20" s="12">
         <f t="shared" si="34"/>
-        <v>1.28</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="CA20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CB20" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CC20" s="13">
         <f t="shared" si="35"/>
-        <v>11.5</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="CD20" s="12">
         <f t="shared" si="36"/>
-        <v>2.6</v>
+        <v>2.6923076923076921</v>
       </c>
       <c r="CE20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CF20" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CG20" s="13">
         <f t="shared" si="37"/>
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="CH20" s="12">
         <f t="shared" si="38"/>
-        <v>3.9200000000000004</v>
+        <v>4.0384615384615383</v>
       </c>
       <c r="CI20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26658,7 +26670,7 @@
       </c>
       <c r="CK20" s="13">
         <f t="shared" si="39"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CL20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26670,31 +26682,31 @@
       </c>
       <c r="CN20" s="13">
         <f t="shared" si="40"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="CO20" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="CP20" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A20,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CQ20" s="13">
         <f t="shared" si="41"/>
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="CR20" s="14">
         <f t="shared" si="42"/>
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="CS20" s="14">
         <f t="shared" si="43"/>
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="CT20" s="14">
         <f t="shared" si="44"/>
-        <v>6.7771084337349397</v>
+        <v>8.8705882352941181</v>
       </c>
     </row>
     <row r="21" spans="1:98" x14ac:dyDescent="0.15">
@@ -26791,11 +26803,11 @@
       </c>
       <c r="X21" s="13">
         <f t="shared" si="8"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y21" s="12">
         <f t="shared" si="9"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="Z21" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26807,11 +26819,11 @@
       </c>
       <c r="AB21" s="13">
         <f t="shared" si="10"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="AC21" s="12">
         <f t="shared" si="11"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AD21" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26839,7 +26851,7 @@
       </c>
       <c r="AJ21" s="13">
         <f t="shared" si="14"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK21" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26851,7 +26863,7 @@
       </c>
       <c r="AM21" s="13">
         <f t="shared" si="15"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AN21" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26863,11 +26875,11 @@
       </c>
       <c r="AP21" s="13">
         <f t="shared" si="16"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ21" s="12">
         <f t="shared" si="17"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AR21" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26895,11 +26907,11 @@
       </c>
       <c r="AX21" s="13">
         <f t="shared" si="20"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY21" s="12">
         <f t="shared" si="21"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AZ21" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -26923,11 +26935,11 @@
       </c>
       <c r="BE21" s="13">
         <f t="shared" si="23"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="BF21" s="12">
         <f t="shared" si="24"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BG21" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27003,11 +27015,11 @@
       </c>
       <c r="BY21" s="13">
         <f t="shared" si="33"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="BZ21" s="12">
         <f t="shared" si="34"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="CA21" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27035,11 +27047,11 @@
       </c>
       <c r="CG21" s="13">
         <f t="shared" si="37"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CH21" s="12">
         <f t="shared" si="38"/>
-        <v>0.28000000000000003</v>
+        <v>0.26923076923076927</v>
       </c>
       <c r="CI21" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A21,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27075,7 +27087,7 @@
       </c>
       <c r="CQ21" s="13">
         <f t="shared" si="41"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CR21" s="14">
         <f t="shared" si="42"/>
@@ -27087,7 +27099,7 @@
       </c>
       <c r="CT21" s="14">
         <f t="shared" si="44"/>
-        <v>46.25</v>
+        <v>48.099999999999994</v>
       </c>
     </row>
     <row r="22" spans="1:98" x14ac:dyDescent="0.15">
@@ -27132,7 +27144,7 @@
       </c>
       <c r="K22" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="L22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27184,11 +27196,11 @@
       </c>
       <c r="X22" s="13">
         <f t="shared" si="8"/>
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Y22" s="12">
         <f t="shared" si="9"/>
-        <v>10.600000000000001</v>
+        <v>10.192307692307692</v>
       </c>
       <c r="Z22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27196,7 +27208,7 @@
       </c>
       <c r="AA22" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB22" s="13">
         <f t="shared" si="10"/>
@@ -27204,7 +27216,7 @@
       </c>
       <c r="AC22" s="12">
         <f t="shared" si="11"/>
-        <v>4.4000000000000004</v>
+        <v>4.4230769230769234</v>
       </c>
       <c r="AD22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27216,11 +27228,11 @@
       </c>
       <c r="AF22" s="13">
         <f t="shared" si="12"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG22" s="12">
         <f t="shared" si="13"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AH22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27232,7 +27244,7 @@
       </c>
       <c r="AJ22" s="13">
         <f t="shared" si="14"/>
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AK22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27248,19 +27260,19 @@
       </c>
       <c r="AN22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO22" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP22" s="13">
         <f t="shared" si="16"/>
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="AQ22" s="12">
         <f t="shared" si="17"/>
-        <v>2.6</v>
+        <v>2.8846153846153841</v>
       </c>
       <c r="AR22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27272,11 +27284,11 @@
       </c>
       <c r="AT22" s="13">
         <f t="shared" si="18"/>
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AU22" s="12">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AV22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27288,11 +27300,11 @@
       </c>
       <c r="AX22" s="13">
         <f t="shared" si="20"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY22" s="12">
         <f t="shared" si="21"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AZ22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27320,7 +27332,7 @@
       </c>
       <c r="BF22" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27352,7 +27364,7 @@
       </c>
       <c r="BN22" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27364,11 +27376,11 @@
       </c>
       <c r="BQ22" s="13">
         <f t="shared" si="29"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="BR22" s="12">
         <f t="shared" si="30"/>
-        <v>1.92</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="BS22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27396,11 +27408,11 @@
       </c>
       <c r="BY22" s="13">
         <f t="shared" si="33"/>
-        <v>9.4</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="BZ22" s="12">
         <f t="shared" si="34"/>
-        <v>2.56</v>
+        <v>2.4615384615384617</v>
       </c>
       <c r="CA22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27412,27 +27424,27 @@
       </c>
       <c r="CC22" s="13">
         <f t="shared" si="35"/>
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="CD22" s="12">
         <f t="shared" si="36"/>
-        <v>4.6000000000000005</v>
+        <v>4.4230769230769234</v>
       </c>
       <c r="CE22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CF22" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CG22" s="13">
         <f t="shared" si="37"/>
-        <v>10.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CH22" s="12">
         <f t="shared" si="38"/>
-        <v>6.16</v>
+        <v>6.1923076923076916</v>
       </c>
       <c r="CI22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27444,7 +27456,7 @@
       </c>
       <c r="CK22" s="13">
         <f t="shared" si="39"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="CL22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27456,31 +27468,31 @@
       </c>
       <c r="CN22" s="13">
         <f t="shared" si="40"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="CO22" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="CP22" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A22,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CQ22" s="13">
         <f t="shared" si="41"/>
-        <v>1.9</v>
+        <v>12.5</v>
       </c>
       <c r="CR22" s="14">
         <f t="shared" si="42"/>
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="CS22" s="14">
         <f t="shared" si="43"/>
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="CT22" s="14">
         <f t="shared" si="44"/>
-        <v>5.8755760368663594</v>
+        <v>6.9099099099099099</v>
       </c>
     </row>
     <row r="23" spans="1:98" x14ac:dyDescent="0.15">
@@ -27521,11 +27533,11 @@
       </c>
       <c r="J23" s="13">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="L23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27569,35 +27581,35 @@
       </c>
       <c r="V23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W23" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X23" s="13">
         <f t="shared" si="8"/>
-        <v>2.4</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="Y23" s="12">
         <f t="shared" si="9"/>
-        <v>6.2</v>
+        <v>6.1538461538461542</v>
       </c>
       <c r="Z23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA23" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB23" s="13">
         <f t="shared" si="10"/>
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="AC23" s="12">
         <f t="shared" si="11"/>
-        <v>4.4000000000000004</v>
+        <v>4.6153846153846159</v>
       </c>
       <c r="AD23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27609,11 +27621,11 @@
       </c>
       <c r="AF23" s="13">
         <f t="shared" si="12"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG23" s="12">
         <f t="shared" si="13"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AH23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27625,7 +27637,7 @@
       </c>
       <c r="AJ23" s="13">
         <f t="shared" si="14"/>
-        <v>31.3</v>
+        <v>32.5</v>
       </c>
       <c r="AK23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27641,23 +27653,23 @@
       </c>
       <c r="AN23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO23" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP23" s="13">
         <f t="shared" si="16"/>
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AQ23" s="12">
         <f t="shared" si="17"/>
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AR23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS23" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27665,15 +27677,15 @@
       </c>
       <c r="AT23" s="13">
         <f t="shared" si="18"/>
-        <v>37.5</v>
+        <v>52</v>
       </c>
       <c r="AU23" s="12">
         <f t="shared" si="19"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AV23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW23" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27681,11 +27693,11 @@
       </c>
       <c r="AX23" s="13">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY23" s="12">
         <f t="shared" si="21"/>
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AZ23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27709,11 +27721,11 @@
       </c>
       <c r="BE23" s="13">
         <f t="shared" si="23"/>
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF23" s="12">
         <f t="shared" si="24"/>
-        <v>1.92</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="BG23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27745,7 +27757,7 @@
       </c>
       <c r="BN23" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27757,11 +27769,11 @@
       </c>
       <c r="BQ23" s="13">
         <f t="shared" si="29"/>
-        <v>17.899999999999999</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="BR23" s="12">
         <f t="shared" si="30"/>
-        <v>2.2400000000000002</v>
+        <v>2.1538461538461537</v>
       </c>
       <c r="BS23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27789,11 +27801,11 @@
       </c>
       <c r="BY23" s="13">
         <f t="shared" si="33"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BZ23" s="12">
         <f t="shared" si="34"/>
-        <v>1.92</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="CA23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27805,11 +27817,11 @@
       </c>
       <c r="CC23" s="13">
         <f t="shared" si="35"/>
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="CD23" s="12">
         <f t="shared" si="36"/>
-        <v>4</v>
+        <v>3.8461538461538463</v>
       </c>
       <c r="CE23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27821,11 +27833,11 @@
       </c>
       <c r="CG23" s="13">
         <f t="shared" si="37"/>
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="CH23" s="12">
         <f t="shared" si="38"/>
-        <v>5.6000000000000005</v>
+        <v>5.384615384615385</v>
       </c>
       <c r="CI23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27837,7 +27849,7 @@
       </c>
       <c r="CK23" s="13">
         <f t="shared" si="39"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27849,11 +27861,11 @@
       </c>
       <c r="CN23" s="13">
         <f t="shared" si="40"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CO23" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="CP23" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A23,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27861,19 +27873,19 @@
       </c>
       <c r="CQ23" s="13">
         <f t="shared" si="41"/>
-        <v>2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="CR23" s="14">
         <f t="shared" si="42"/>
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="CS23" s="14">
         <f t="shared" si="43"/>
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="CT23" s="14">
         <f t="shared" si="44"/>
-        <v>6.4432989690721651</v>
+        <v>9.454545454545455</v>
       </c>
     </row>
     <row r="24" spans="1:98" x14ac:dyDescent="0.15">
@@ -27962,7 +27974,7 @@
       </c>
       <c r="V24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W24" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -27970,11 +27982,11 @@
       </c>
       <c r="X24" s="13">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="Y24" s="12">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="Z24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -27986,11 +27998,11 @@
       </c>
       <c r="AB24" s="13">
         <f t="shared" si="10"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC24" s="12">
         <f t="shared" si="11"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AD24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28018,7 +28030,7 @@
       </c>
       <c r="AJ24" s="13">
         <f t="shared" si="14"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28034,19 +28046,19 @@
       </c>
       <c r="AN24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO24" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP24" s="13">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AQ24" s="12">
         <f t="shared" si="17"/>
-        <v>0.4</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AR24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28106,7 +28118,7 @@
       </c>
       <c r="BF24" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28138,7 +28150,7 @@
       </c>
       <c r="BN24" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28154,7 +28166,7 @@
       </c>
       <c r="BR24" s="12">
         <f t="shared" si="30"/>
-        <v>1.28</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="BS24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28174,7 +28186,7 @@
       </c>
       <c r="BW24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BX24" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28182,11 +28194,11 @@
       </c>
       <c r="BY24" s="13">
         <f t="shared" si="33"/>
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="BZ24" s="12">
         <f t="shared" si="34"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="CA24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28198,11 +28210,11 @@
       </c>
       <c r="CC24" s="13">
         <f t="shared" si="35"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CD24" s="12">
         <f t="shared" si="36"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="CE24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28230,11 +28242,11 @@
       </c>
       <c r="CK24" s="13">
         <f t="shared" si="39"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM24" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28242,11 +28254,11 @@
       </c>
       <c r="CN24" s="13">
         <f t="shared" si="40"/>
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="CO24" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CP24" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A24,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28254,19 +28266,19 @@
       </c>
       <c r="CQ24" s="13">
         <f t="shared" si="41"/>
-        <v>12.5</v>
+        <v>52</v>
       </c>
       <c r="CR24" s="14">
         <f t="shared" si="42"/>
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="CS24" s="14">
         <f t="shared" si="43"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CT24" s="14">
         <f t="shared" si="44"/>
-        <v>21.428571428571427</v>
+        <v>27.793103448275861</v>
       </c>
     </row>
     <row r="25" spans="1:98" x14ac:dyDescent="0.15">
@@ -28295,7 +28307,7 @@
       </c>
       <c r="G25" s="13">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28355,7 +28367,7 @@
       </c>
       <c r="V25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W25" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28363,15 +28375,15 @@
       </c>
       <c r="X25" s="13">
         <f t="shared" si="8"/>
-        <v>8.3000000000000007</v>
+        <v>17.3</v>
       </c>
       <c r="Y25" s="12">
         <f t="shared" si="9"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="Z25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA25" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28379,11 +28391,11 @@
       </c>
       <c r="AB25" s="13">
         <f t="shared" si="10"/>
-        <v>6.3</v>
+        <v>19.5</v>
       </c>
       <c r="AC25" s="12">
         <f t="shared" si="11"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AD25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28399,7 +28411,7 @@
       </c>
       <c r="AG25" s="12">
         <f t="shared" si="13"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AH25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28411,7 +28423,7 @@
       </c>
       <c r="AJ25" s="13">
         <f t="shared" si="14"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28427,7 +28439,7 @@
       </c>
       <c r="AN25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO25" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28435,11 +28447,11 @@
       </c>
       <c r="AP25" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="AQ25" s="12">
         <f t="shared" si="17"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AR25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28459,7 +28471,7 @@
       </c>
       <c r="AV25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW25" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28495,11 +28507,11 @@
       </c>
       <c r="BE25" s="13">
         <f t="shared" si="23"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BF25" s="12">
         <f t="shared" si="24"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BG25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28515,7 +28527,7 @@
       </c>
       <c r="BJ25" s="12">
         <f t="shared" si="26"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BK25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28531,7 +28543,7 @@
       </c>
       <c r="BN25" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28591,15 +28603,15 @@
       </c>
       <c r="CC25" s="13">
         <f t="shared" si="35"/>
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="CD25" s="12">
         <f t="shared" si="36"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="CE25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CF25" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -28607,11 +28619,11 @@
       </c>
       <c r="CG25" s="13">
         <f t="shared" si="37"/>
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="CH25" s="12">
         <f t="shared" si="38"/>
-        <v>0.56000000000000005</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="CI25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28623,7 +28635,7 @@
       </c>
       <c r="CK25" s="13">
         <f t="shared" si="39"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CL25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28635,7 +28647,7 @@
       </c>
       <c r="CN25" s="13">
         <f t="shared" si="40"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CO25" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A25,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28647,11 +28659,11 @@
       </c>
       <c r="CQ25" s="13">
         <f t="shared" si="41"/>
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="CR25" s="14">
         <f t="shared" si="42"/>
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="CS25" s="14">
         <f t="shared" si="43"/>
@@ -28659,7 +28671,7 @@
       </c>
       <c r="CT25" s="14">
         <f t="shared" si="44"/>
-        <v>20</v>
+        <v>26.866666666666671</v>
       </c>
     </row>
     <row r="26" spans="1:98" x14ac:dyDescent="0.15">
@@ -28756,11 +28768,11 @@
       </c>
       <c r="X26" s="13">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="Y26" s="12">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1.9230769230769231</v>
       </c>
       <c r="Z26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28772,11 +28784,11 @@
       </c>
       <c r="AB26" s="13">
         <f t="shared" si="10"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AC26" s="12">
         <f t="shared" si="11"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AD26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28804,19 +28816,19 @@
       </c>
       <c r="AJ26" s="13">
         <f t="shared" si="14"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL26" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM26" s="13">
         <f t="shared" si="15"/>
-        <v>25</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AN26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28828,11 +28840,11 @@
       </c>
       <c r="AP26" s="13">
         <f t="shared" si="16"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="AQ26" s="12">
         <f t="shared" si="17"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AR26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28848,7 +28860,7 @@
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="19"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AV26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28860,11 +28872,11 @@
       </c>
       <c r="AX26" s="13">
         <f t="shared" si="20"/>
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY26" s="12">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AZ26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28888,11 +28900,11 @@
       </c>
       <c r="BE26" s="13">
         <f t="shared" si="23"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BF26" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28924,23 +28936,23 @@
       </c>
       <c r="BN26" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP26" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ26" s="13">
         <f t="shared" si="29"/>
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="BR26" s="12">
         <f t="shared" si="30"/>
-        <v>0.32</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BS26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28952,11 +28964,11 @@
       </c>
       <c r="BU26" s="13">
         <f t="shared" si="31"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BV26" s="12">
         <f t="shared" si="32"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BW26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28968,11 +28980,11 @@
       </c>
       <c r="BY26" s="13">
         <f t="shared" si="33"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BZ26" s="12">
         <f t="shared" si="34"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="CA26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -28984,11 +28996,11 @@
       </c>
       <c r="CC26" s="13">
         <f t="shared" si="35"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CD26" s="12">
         <f t="shared" si="36"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="CE26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29000,11 +29012,11 @@
       </c>
       <c r="CG26" s="13">
         <f t="shared" si="37"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CH26" s="12">
         <f t="shared" si="38"/>
-        <v>0.84</v>
+        <v>0.80769230769230771</v>
       </c>
       <c r="CI26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29016,7 +29028,7 @@
       </c>
       <c r="CK26" s="13">
         <f t="shared" si="39"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29028,7 +29040,7 @@
       </c>
       <c r="CN26" s="13">
         <f t="shared" si="40"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CO26" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A26,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29040,19 +29052,19 @@
       </c>
       <c r="CQ26" s="13">
         <f t="shared" si="41"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="CR26" s="14">
         <f t="shared" si="42"/>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CS26" s="14">
         <f t="shared" si="43"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CT26" s="14">
         <f t="shared" si="44"/>
-        <v>19.318181818181817</v>
+        <v>18.086956521739133</v>
       </c>
     </row>
     <row r="27" spans="1:98" x14ac:dyDescent="0.15">
@@ -29149,11 +29161,11 @@
       </c>
       <c r="X27" s="13">
         <f t="shared" si="8"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y27" s="12">
         <f t="shared" si="9"/>
-        <v>1.7999999999999998</v>
+        <v>1.7307692307692308</v>
       </c>
       <c r="Z27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29165,11 +29177,11 @@
       </c>
       <c r="AB27" s="13">
         <f t="shared" si="10"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="AC27" s="12">
         <f t="shared" si="11"/>
-        <v>1.2</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AD27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29197,7 +29209,7 @@
       </c>
       <c r="AJ27" s="13">
         <f t="shared" si="14"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AK27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29209,7 +29221,7 @@
       </c>
       <c r="AM27" s="13">
         <f t="shared" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29221,11 +29233,11 @@
       </c>
       <c r="AP27" s="13">
         <f t="shared" si="16"/>
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AQ27" s="12">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AR27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29237,11 +29249,11 @@
       </c>
       <c r="AT27" s="13">
         <f t="shared" si="18"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="19"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AV27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29281,11 +29293,11 @@
       </c>
       <c r="BE27" s="13">
         <f t="shared" si="23"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF27" s="12">
         <f t="shared" si="24"/>
-        <v>1.28</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="BG27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29317,7 +29329,7 @@
       </c>
       <c r="BN27" s="12">
         <f t="shared" si="28"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BO27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29361,11 +29373,11 @@
       </c>
       <c r="BY27" s="13">
         <f t="shared" si="33"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="BZ27" s="12">
         <f t="shared" si="34"/>
-        <v>0.96</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="CA27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29377,11 +29389,11 @@
       </c>
       <c r="CC27" s="13">
         <f t="shared" si="35"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="CD27" s="12">
         <f t="shared" si="36"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="CE27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29393,11 +29405,11 @@
       </c>
       <c r="CG27" s="13">
         <f t="shared" si="37"/>
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="CH27" s="12">
         <f t="shared" si="38"/>
-        <v>0.56000000000000005</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="CI27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29421,7 +29433,7 @@
       </c>
       <c r="CN27" s="13">
         <f t="shared" si="40"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CO27" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A27,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29433,7 +29445,7 @@
       </c>
       <c r="CQ27" s="13">
         <f t="shared" si="41"/>
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
       <c r="CR27" s="14">
         <f t="shared" si="42"/>
@@ -29445,7 +29457,7 @@
       </c>
       <c r="CT27" s="14">
         <f t="shared" si="44"/>
-        <v>26.785714285714288</v>
+        <v>27.857142857142858</v>
       </c>
     </row>
     <row r="28" spans="1:98" x14ac:dyDescent="0.15">
@@ -29486,11 +29498,11 @@
       </c>
       <c r="J28" s="13">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="L28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29542,11 +29554,11 @@
       </c>
       <c r="X28" s="13">
         <f t="shared" si="8"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Y28" s="12">
         <f t="shared" si="9"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="Z28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29558,11 +29570,11 @@
       </c>
       <c r="AB28" s="13">
         <f t="shared" si="10"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="11"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AD28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29602,7 +29614,7 @@
       </c>
       <c r="AM28" s="13">
         <f t="shared" si="15"/>
-        <v>33.299999999999997</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="AN28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29614,15 +29626,15 @@
       </c>
       <c r="AP28" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ28" s="12">
         <f t="shared" si="17"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AR28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS28" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -29630,11 +29642,11 @@
       </c>
       <c r="AT28" s="13">
         <f t="shared" si="18"/>
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="AU28" s="12">
         <f t="shared" si="19"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AV28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29646,11 +29658,11 @@
       </c>
       <c r="AX28" s="13">
         <f t="shared" si="20"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AY28" s="12">
         <f t="shared" si="21"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AZ28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29674,11 +29686,11 @@
       </c>
       <c r="BE28" s="13">
         <f t="shared" si="23"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="BF28" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29710,7 +29722,7 @@
       </c>
       <c r="BN28" s="12">
         <f t="shared" si="28"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BO28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29722,11 +29734,11 @@
       </c>
       <c r="BQ28" s="13">
         <f t="shared" si="29"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="BR28" s="12">
         <f t="shared" si="30"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BS28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29742,23 +29754,23 @@
       </c>
       <c r="BV28" s="12">
         <f t="shared" si="32"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BW28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BX28" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BY28" s="13">
         <f t="shared" si="33"/>
-        <v>37.5</v>
+        <v>17.3</v>
       </c>
       <c r="BZ28" s="12">
         <f t="shared" si="34"/>
-        <v>0.64</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="CA28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29770,11 +29782,11 @@
       </c>
       <c r="CC28" s="13">
         <f t="shared" si="35"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="CD28" s="12">
         <f t="shared" si="36"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="CE28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29786,11 +29798,11 @@
       </c>
       <c r="CG28" s="13">
         <f t="shared" si="37"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="CH28" s="12">
         <f t="shared" si="38"/>
-        <v>0.28000000000000003</v>
+        <v>0.26923076923076927</v>
       </c>
       <c r="CI28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29818,7 +29830,7 @@
       </c>
       <c r="CO28" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CP28" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A28,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -29826,19 +29838,19 @@
       </c>
       <c r="CQ28" s="13">
         <f t="shared" si="41"/>
-        <v>10</v>
+        <v>20.8</v>
       </c>
       <c r="CR28" s="14">
         <f t="shared" si="42"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="CS28" s="14">
         <f t="shared" si="43"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CT28" s="14">
         <f t="shared" si="44"/>
-        <v>48.214285714285708</v>
+        <v>50.206896551724135</v>
       </c>
     </row>
     <row r="29" spans="1:98" x14ac:dyDescent="0.15">
@@ -29879,11 +29891,11 @@
       </c>
       <c r="J29" s="13">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="L29" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29935,15 +29947,15 @@
       </c>
       <c r="X29" s="13">
         <f t="shared" si="8"/>
-        <v>33.299999999999997</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="Y29" s="12">
         <f t="shared" si="9"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="Z29" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA29" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -29951,11 +29963,11 @@
       </c>
       <c r="AB29" s="13">
         <f t="shared" si="10"/>
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="11"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AD29" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -29995,7 +30007,7 @@
       </c>
       <c r="AM29" s="13">
         <f t="shared" si="15"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AN29" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30067,11 +30079,11 @@
       </c>
       <c r="BE29" s="13">
         <f t="shared" si="23"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="BF29" s="12">
         <f t="shared" si="24"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BG29" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30103,7 +30115,7 @@
       </c>
       <c r="BN29" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO29" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30163,15 +30175,15 @@
       </c>
       <c r="CC29" s="13">
         <f t="shared" si="35"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="CD29" s="12">
         <f t="shared" si="36"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="CE29" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CF29" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -30179,11 +30191,11 @@
       </c>
       <c r="CG29" s="13">
         <f t="shared" si="37"/>
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="CH29" s="12">
         <f t="shared" si="38"/>
-        <v>0.56000000000000005</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="CI29" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30207,11 +30219,11 @@
       </c>
       <c r="CN29" s="13">
         <f t="shared" si="40"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CO29" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CP29" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A29,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -30219,11 +30231,11 @@
       </c>
       <c r="CQ29" s="13">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="CR29" s="14">
         <f t="shared" si="42"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="CS29" s="14">
         <f t="shared" si="43"/>
@@ -30231,7 +30243,7 @@
       </c>
       <c r="CT29" s="14">
         <f t="shared" si="44"/>
-        <v>56.578947368421055</v>
+        <v>64.31578947368422</v>
       </c>
     </row>
     <row r="30" spans="1:98" ht="16" x14ac:dyDescent="0.2">
@@ -30376,7 +30388,7 @@
       </c>
       <c r="AJ30" s="13">
         <f t="shared" si="14"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AK30" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30400,11 +30412,11 @@
       </c>
       <c r="AP30" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ30" s="12">
         <f t="shared" si="17"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AR30" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30556,11 +30568,11 @@
       </c>
       <c r="CC30" s="13">
         <f t="shared" si="35"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CD30" s="12">
         <f t="shared" si="36"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="CE30" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30588,7 +30600,7 @@
       </c>
       <c r="CK30" s="13">
         <f t="shared" si="39"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="CL30" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30600,7 +30612,7 @@
       </c>
       <c r="CN30" s="13">
         <f t="shared" si="40"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CO30" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A30,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30624,7 +30636,7 @@
       </c>
       <c r="CT30" s="14">
         <f t="shared" si="44"/>
-        <v>92.857142857142847</v>
+        <v>96.571428571428569</v>
       </c>
     </row>
     <row r="31" spans="1:98" x14ac:dyDescent="0.15">
@@ -30713,19 +30725,19 @@
       </c>
       <c r="V31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W31" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31" s="13">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="Y31" s="12">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="Z31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30737,11 +30749,11 @@
       </c>
       <c r="AB31" s="13">
         <f t="shared" si="10"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="AC31" s="12">
         <f t="shared" si="11"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AD31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30753,11 +30765,11 @@
       </c>
       <c r="AF31" s="13">
         <f t="shared" si="12"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AG31" s="12">
         <f t="shared" si="13"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AH31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30769,7 +30781,7 @@
       </c>
       <c r="AJ31" s="13">
         <f t="shared" si="14"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AK31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30793,11 +30805,11 @@
       </c>
       <c r="AP31" s="13">
         <f t="shared" si="16"/>
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AQ31" s="12">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="AR31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30817,7 +30829,7 @@
       </c>
       <c r="AV31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW31" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -30825,11 +30837,11 @@
       </c>
       <c r="AX31" s="13">
         <f t="shared" si="20"/>
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="AY31" s="12">
         <f t="shared" si="21"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AZ31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30853,11 +30865,11 @@
       </c>
       <c r="BE31" s="13">
         <f t="shared" si="23"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="BF31" s="12">
         <f t="shared" si="24"/>
-        <v>0.96</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="BG31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30889,7 +30901,7 @@
       </c>
       <c r="BN31" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30901,11 +30913,11 @@
       </c>
       <c r="BQ31" s="13">
         <f t="shared" si="29"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="BR31" s="12">
         <f t="shared" si="30"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BS31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30933,11 +30945,11 @@
       </c>
       <c r="BY31" s="13">
         <f t="shared" si="33"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ31" s="12">
         <f t="shared" si="34"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="CA31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30949,11 +30961,11 @@
       </c>
       <c r="CC31" s="13">
         <f t="shared" si="35"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="CD31" s="12">
         <f t="shared" si="36"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="CE31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30965,11 +30977,11 @@
       </c>
       <c r="CG31" s="13">
         <f t="shared" si="37"/>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="CH31" s="12">
         <f t="shared" si="38"/>
-        <v>0.28000000000000003</v>
+        <v>0.26923076923076927</v>
       </c>
       <c r="CI31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30981,7 +30993,7 @@
       </c>
       <c r="CK31" s="13">
         <f t="shared" si="39"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -30997,7 +31009,7 @@
       </c>
       <c r="CO31" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CP31" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A31,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -31005,19 +31017,19 @@
       </c>
       <c r="CQ31" s="13">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="CR31" s="14">
         <f t="shared" si="42"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="CS31" s="14">
         <f t="shared" si="43"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CT31" s="14">
         <f t="shared" si="44"/>
-        <v>21.428571428571431</v>
+        <v>23.581395348837212</v>
       </c>
     </row>
     <row r="32" spans="1:98" x14ac:dyDescent="0.15">
@@ -31046,11 +31058,11 @@
       </c>
       <c r="G32" s="13">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300ULTRA|16+512|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -31058,11 +31070,11 @@
       </c>
       <c r="J32" s="13">
         <f t="shared" si="2"/>
-        <v>8.3000000000000007</v>
+        <v>17.3</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="3"/>
-        <v>1.2</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="L32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31106,7 +31118,7 @@
       </c>
       <c r="V32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W32" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -31114,15 +31126,15 @@
       </c>
       <c r="X32" s="13">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Y32" s="12">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="Z32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA32" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -31130,11 +31142,11 @@
       </c>
       <c r="AB32" s="13">
         <f t="shared" si="10"/>
-        <v>6.3</v>
+        <v>13</v>
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="11"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AD32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31162,7 +31174,7 @@
       </c>
       <c r="AJ32" s="13">
         <f t="shared" si="14"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31178,19 +31190,19 @@
       </c>
       <c r="AN32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO32" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP32" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AQ32" s="12">
         <f t="shared" si="17"/>
-        <v>0.6</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AR32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31218,11 +31230,11 @@
       </c>
       <c r="AX32" s="13">
         <f t="shared" si="20"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY32" s="12">
         <f t="shared" si="21"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AZ32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31246,11 +31258,11 @@
       </c>
       <c r="BE32" s="13">
         <f t="shared" si="23"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BF32" s="12">
         <f t="shared" si="24"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BG32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31314,7 +31326,7 @@
       </c>
       <c r="BV32" s="12">
         <f t="shared" si="32"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BW32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31342,11 +31354,11 @@
       </c>
       <c r="CC32" s="13">
         <f t="shared" si="35"/>
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="CD32" s="12">
         <f t="shared" si="36"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="CE32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31358,11 +31370,11 @@
       </c>
       <c r="CG32" s="13">
         <f t="shared" si="37"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CH32" s="12">
         <f t="shared" si="38"/>
-        <v>1.1200000000000001</v>
+        <v>1.0769230769230771</v>
       </c>
       <c r="CI32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31374,7 +31386,7 @@
       </c>
       <c r="CK32" s="13">
         <f t="shared" si="39"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CL32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31386,11 +31398,11 @@
       </c>
       <c r="CN32" s="13">
         <f t="shared" si="40"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="CO32" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CP32" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A32,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -31398,19 +31410,19 @@
       </c>
       <c r="CQ32" s="13">
         <f t="shared" si="41"/>
-        <v>25</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="CR32" s="14">
         <f t="shared" si="42"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="CS32" s="14">
         <f t="shared" si="43"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CT32" s="14">
         <f t="shared" si="44"/>
-        <v>28.205128205128204</v>
+        <v>30.549999999999997</v>
       </c>
     </row>
     <row r="33" spans="1:98" x14ac:dyDescent="0.15">
@@ -31499,19 +31511,19 @@
       </c>
       <c r="V33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W33" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33" s="13">
         <f t="shared" si="8"/>
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="9"/>
-        <v>1.6</v>
+        <v>1.7307692307692308</v>
       </c>
       <c r="Z33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31523,11 +31535,11 @@
       </c>
       <c r="AB33" s="13">
         <f t="shared" si="10"/>
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="11"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AD33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31555,7 +31567,7 @@
       </c>
       <c r="AJ33" s="13">
         <f t="shared" si="14"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AK33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31567,7 +31579,7 @@
       </c>
       <c r="AM33" s="13">
         <f t="shared" si="15"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AN33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31579,11 +31591,11 @@
       </c>
       <c r="AP33" s="13">
         <f t="shared" si="16"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AQ33" s="12">
         <f t="shared" si="17"/>
-        <v>0.6</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="AR33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31595,11 +31607,11 @@
       </c>
       <c r="AT33" s="13">
         <f t="shared" si="18"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="19"/>
-        <v>0.2</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AV33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31675,7 +31687,7 @@
       </c>
       <c r="BN33" s="12">
         <f t="shared" si="28"/>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BO33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31735,11 +31747,11 @@
       </c>
       <c r="CC33" s="13">
         <f t="shared" si="35"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CD33" s="12">
         <f t="shared" si="36"/>
-        <v>1.2</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="CE33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31751,11 +31763,11 @@
       </c>
       <c r="CG33" s="13">
         <f t="shared" si="37"/>
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="CH33" s="12">
         <f t="shared" si="38"/>
-        <v>0.28000000000000003</v>
+        <v>0.26923076923076927</v>
       </c>
       <c r="CI33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31767,7 +31779,7 @@
       </c>
       <c r="CK33" s="13">
         <f t="shared" si="39"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="CL33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31779,7 +31791,7 @@
       </c>
       <c r="CN33" s="13">
         <f t="shared" si="40"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="CO33" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A33,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31791,19 +31803,19 @@
       </c>
       <c r="CQ33" s="13">
         <f t="shared" si="41"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CR33" s="14">
         <f t="shared" si="42"/>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="CS33" s="14">
         <f t="shared" si="43"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CT33" s="14">
         <f t="shared" si="44"/>
-        <v>42.96875</v>
+        <v>42.545454545454547</v>
       </c>
     </row>
     <row r="34" spans="1:98" x14ac:dyDescent="0.15">
@@ -31844,11 +31856,11 @@
       </c>
       <c r="J34" s="13">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="L34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("X300PRO|16+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31892,7 +31904,7 @@
       </c>
       <c r="V34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W34" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+128|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -31900,15 +31912,15 @@
       </c>
       <c r="X34" s="13">
         <f t="shared" si="8"/>
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="Y34" s="12">
         <f t="shared" si="9"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="Z34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA34" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -31916,11 +31928,11 @@
       </c>
       <c r="AB34" s="13">
         <f t="shared" si="10"/>
-        <v>12.5</v>
+        <v>39</v>
       </c>
       <c r="AC34" s="12">
         <f t="shared" si="11"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AD34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y11D|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31960,7 +31972,7 @@
       </c>
       <c r="AM34" s="13">
         <f t="shared" si="15"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AN34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -31972,11 +31984,11 @@
       </c>
       <c r="AP34" s="13">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ34" s="12">
         <f t="shared" si="17"/>
-        <v>0.4</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="AR34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y31DPRO|8+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -32032,11 +32044,11 @@
       </c>
       <c r="BE34" s="13">
         <f t="shared" si="23"/>
-        <v>8.3000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="BF34" s="12">
         <f t="shared" si="24"/>
-        <v>0.96</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="BG34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70|12+512|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -32068,7 +32080,7 @@
       </c>
       <c r="BN34" s="12">
         <f t="shared" si="28"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BO34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V70FE|12+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -32080,11 +32092,11 @@
       </c>
       <c r="BQ34" s="13">
         <f t="shared" si="29"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BR34" s="12">
         <f t="shared" si="30"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BS34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE5G|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -32096,11 +32108,11 @@
       </c>
       <c r="BU34" s="13">
         <f t="shared" si="31"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BV34" s="12">
         <f t="shared" si="32"/>
-        <v>0.32</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="BW34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("V60LITE|8+256|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -32128,11 +32140,11 @@
       </c>
       <c r="CC34" s="13">
         <f t="shared" si="35"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CD34" s="12">
         <f t="shared" si="36"/>
-        <v>0.8</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="CE34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -32144,11 +32156,11 @@
       </c>
       <c r="CG34" s="13">
         <f t="shared" si="37"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="CH34" s="12">
         <f t="shared" si="38"/>
-        <v>0.28000000000000003</v>
+        <v>0.26923076923076927</v>
       </c>
       <c r="CI34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y500|6+128|STOCK",[1]PVKEY!$1:$1,0))</f>
@@ -32172,11 +32184,11 @@
       </c>
       <c r="CN34" s="13">
         <f t="shared" si="40"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CO34" s="11">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|STOCK",[1]PVKEY!$1:$1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CP34" s="12">
         <f>INDEX('[1]PV.STOCK TIAP GUDANG'!$A:$CV,MATCH($A34,'[1]PV.STOCK TIAP GUDANG'!$A:$A,0),MATCH("Y05E|4+64|SALES",[1]PVKEY!$1:$1,0))</f>
@@ -32184,11 +32196,11 @@
       </c>
       <c r="CQ34" s="13">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="CR34" s="14">
         <f t="shared" si="42"/>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="CS34" s="14">
         <f t="shared" si="43"/>
@@ -32196,7 +32208,7 @@
       </c>
       <c r="CT34" s="14">
         <f t="shared" si="44"/>
-        <v>28</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="35" spans="1:98" x14ac:dyDescent="0.15">
@@ -32225,11 +32237,11 @@
       </c>
       <c r="G35" s="13">
         <f t="shared" si="1"/>
-        <v>106.3</v>
+        <v>110.5</v>
       </c>
       <c r="H35" s="16">
         <f>SUM(H7:H34)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I35" s="17">
         <f>SUM(I7:I34)</f>
@@ -32237,11 +32249,11 @@
       </c>
       <c r="J35" s="13">
         <f t="shared" si="2"/>
-        <v>37.5</v>
+        <v>40.4</v>
       </c>
       <c r="K35" s="17">
         <f>SUM(K7:K34)</f>
-        <v>7.200000000000002</v>
+        <v>6.923076923076926</v>
       </c>
       <c r="L35" s="16">
         <f>SUM(L7:L34)</f>
@@ -32281,39 +32293,39 @@
       </c>
       <c r="U35" s="13">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V35" s="16">
         <f>SUM(V7:V34)</f>
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="W35" s="17">
         <f>SUM(W7:W34)</f>
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="X35" s="13">
         <f t="shared" si="8"/>
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="Y35" s="17">
         <f>SUM(Y7:Y34)</f>
-        <v>77.599999999999994</v>
+        <v>75.961538461538481</v>
       </c>
       <c r="Z35" s="16">
         <f>SUM(Z7:Z34)</f>
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AA35" s="17">
         <f>SUM(AA7:AA34)</f>
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AB35" s="13">
         <f t="shared" si="10"/>
-        <v>9.1999999999999993</v>
+        <v>11.2</v>
       </c>
       <c r="AC35" s="17">
         <f>SUM(AC7:AC34)</f>
-        <v>46.399999999999991</v>
+        <v>45.576923076923087</v>
       </c>
       <c r="AD35" s="16">
         <f>SUM(AD7:AD34)</f>
@@ -32325,11 +32337,11 @@
       </c>
       <c r="AF35" s="13">
         <f t="shared" si="12"/>
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="AG35" s="17">
         <f>SUM(AG7:AG34)</f>
-        <v>4.4000000000000012</v>
+        <v>4.2307692307692317</v>
       </c>
       <c r="AH35" s="16">
         <f>SUM(AH7:AH34)</f>
@@ -32337,19 +32349,19 @@
       </c>
       <c r="AI35" s="17">
         <f>SUM(AI7:AI34)</f>
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AJ35" s="13">
         <f t="shared" si="14"/>
-        <v>17.3</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="AK35" s="16">
         <f>SUM(AK7:AK34)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AL35" s="17">
         <f>SUM(AL7:AL34)</f>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AM35" s="13">
         <f t="shared" si="15"/>
@@ -32357,23 +32369,23 @@
       </c>
       <c r="AN35" s="16">
         <f>SUM(AN7:AN34)</f>
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AO35" s="17">
         <f>SUM(AO7:AO34)</f>
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AP35" s="13">
         <f t="shared" si="16"/>
-        <v>12.3</v>
+        <v>13.7</v>
       </c>
       <c r="AQ35" s="17">
         <f>SUM(AQ7:AQ34)</f>
-        <v>33.199999999999996</v>
+        <v>33.269230769230766</v>
       </c>
       <c r="AR35" s="16">
         <f>SUM(AR7:AR34)</f>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AS35" s="17">
         <f>SUM(AS7:AS34)</f>
@@ -32381,27 +32393,27 @@
       </c>
       <c r="AT35" s="13">
         <f t="shared" si="18"/>
-        <v>26.3</v>
+        <v>28.6</v>
       </c>
       <c r="AU35" s="17">
         <f>SUM(AU7:AU34)</f>
-        <v>12</v>
+        <v>11.538461538461538</v>
       </c>
       <c r="AV35" s="16">
         <f>SUM(AV7:AV34)</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AW35" s="17">
         <f>SUM(AW7:AW34)</f>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX35" s="13">
         <f t="shared" si="20"/>
-        <v>12.3</v>
+        <v>14.4</v>
       </c>
       <c r="AY35" s="17">
         <f>SUM(AY7:AY34)</f>
-        <v>14.999999999999998</v>
+        <v>14.615384615384615</v>
       </c>
       <c r="AZ35" s="16">
         <f>SUM(AZ7:AZ34)</f>
@@ -32425,11 +32437,11 @@
       </c>
       <c r="BE35" s="13">
         <f t="shared" si="23"/>
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="BF35" s="17">
         <f>SUM(BF7:BF34)</f>
-        <v>18.880000000000006</v>
+        <v>18.153846153846153</v>
       </c>
       <c r="BG35" s="16">
         <f>SUM(BG7:BG34)</f>
@@ -32445,7 +32457,7 @@
       </c>
       <c r="BJ35" s="17">
         <f>SUM(BJ7:BJ34)</f>
-        <v>0.64</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="BK35" s="16">
         <f>SUM(BK7:BK34)</f>
@@ -32457,27 +32469,27 @@
       </c>
       <c r="BM35" s="13">
         <f t="shared" si="27"/>
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BN35" s="17">
         <f>SUM(BN7:BN34)</f>
-        <v>8.3200000000000021</v>
+        <v>7.9999999999999973</v>
       </c>
       <c r="BO35" s="16">
         <f>SUM(BO7:BO34)</f>
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="BP35" s="17">
         <f>SUM(BP7:BP34)</f>
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="BQ35" s="13">
         <f t="shared" si="29"/>
-        <v>23.7</v>
+        <v>21.6</v>
       </c>
       <c r="BR35" s="17">
         <f>SUM(BR7:BR34)</f>
-        <v>24.960000000000008</v>
+        <v>25.538461538461544</v>
       </c>
       <c r="BS35" s="16">
         <f>SUM(BS7:BS34)</f>
@@ -32489,63 +32501,63 @@
       </c>
       <c r="BU35" s="13">
         <f t="shared" si="31"/>
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="BV35" s="17">
         <f>SUM(BV7:BV34)</f>
-        <v>3.1999999999999997</v>
+        <v>3.0769230769230766</v>
       </c>
       <c r="BW35" s="16">
         <f>SUM(BW7:BW34)</f>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BX35" s="17">
         <f>SUM(BX7:BX34)</f>
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="BY35" s="13">
         <f t="shared" si="33"/>
-        <v>19.8</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="BZ35" s="17">
         <f>SUM(BZ7:BZ34)</f>
-        <v>25.92</v>
+        <v>25.84615384615385</v>
       </c>
       <c r="CA35" s="16">
         <f>SUM(CA7:CA34)</f>
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="CB35" s="17">
         <f>SUM(CB7:CB34)</f>
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="CC35" s="13">
         <f t="shared" si="35"/>
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="CD35" s="17">
         <f>SUM(CD7:CD34)</f>
-        <v>42.400000000000006</v>
+        <v>41.730769230769241</v>
       </c>
       <c r="CE35" s="16">
         <f>SUM(CE7:CE34)</f>
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CF35" s="17">
         <f>SUM(CF7:CF34)</f>
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="CG35" s="13">
         <f t="shared" si="37"/>
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="CH35" s="17">
         <f>SUM(CH7:CH34)</f>
-        <v>68.600000000000023</v>
+        <v>68.65384615384616</v>
       </c>
       <c r="CI35" s="16">
         <f>SUM(CI7:CI34)</f>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="CJ35" s="17">
         <f>SUM(CJ7:CJ34)</f>
@@ -32553,11 +32565,11 @@
       </c>
       <c r="CK35" s="13">
         <f t="shared" si="39"/>
-        <v>33.299999999999997</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="CL35" s="16">
         <f>SUM(CL7:CL34)</f>
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="CM35" s="17">
         <f>SUM(CM7:CM34)</f>
@@ -32565,35 +32577,64 @@
       </c>
       <c r="CN35" s="13">
         <f t="shared" si="40"/>
-        <v>40.700000000000003</v>
+        <v>46.1</v>
       </c>
       <c r="CO35" s="16">
         <f>SUM(CO7:CO34)</f>
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="CP35" s="17">
         <f>SUM(CP7:CP34)</f>
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="CQ35" s="13">
         <f t="shared" si="41"/>
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="CR35" s="14">
         <f>SUM(CR7:CR34)</f>
-        <v>1258</v>
+        <v>1364</v>
       </c>
       <c r="CS35" s="14">
         <f>SUM(CS7:CS34)</f>
-        <v>2604</v>
+        <v>2664</v>
       </c>
       <c r="CT35" s="14">
         <f>IF(OR(CS35="",CS35=0),"",ROUND(CR35/CS35*$B$2,1))</f>
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:K4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="P4:U4"/>
+    <mergeCell ref="V4:AG4"/>
+    <mergeCell ref="AH4:AJ4"/>
+    <mergeCell ref="AK4:AY4"/>
+    <mergeCell ref="AZ4:BJ4"/>
+    <mergeCell ref="BK4:BR4"/>
+    <mergeCell ref="BS4:BV4"/>
+    <mergeCell ref="BW4:BZ4"/>
+    <mergeCell ref="CA4:CH4"/>
+    <mergeCell ref="CI4:CK4"/>
+    <mergeCell ref="CL4:CN4"/>
+    <mergeCell ref="CO4:CQ4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="AN5:AQ5"/>
+    <mergeCell ref="AR5:AU5"/>
+    <mergeCell ref="AV5:AY5"/>
+    <mergeCell ref="AZ5:BB5"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="V5:Y5"/>
+    <mergeCell ref="Z5:AC5"/>
+    <mergeCell ref="AD5:AG5"/>
+    <mergeCell ref="AH5:AJ5"/>
     <mergeCell ref="CO5:CQ5"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="CR4:CR6"/>
@@ -32610,35 +32651,6 @@
     <mergeCell ref="BO5:BR5"/>
     <mergeCell ref="BS5:BV5"/>
     <mergeCell ref="AK5:AM5"/>
-    <mergeCell ref="AN5:AQ5"/>
-    <mergeCell ref="AR5:AU5"/>
-    <mergeCell ref="AV5:AY5"/>
-    <mergeCell ref="AZ5:BB5"/>
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="V5:Y5"/>
-    <mergeCell ref="Z5:AC5"/>
-    <mergeCell ref="AD5:AG5"/>
-    <mergeCell ref="AH5:AJ5"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="BW4:BZ4"/>
-    <mergeCell ref="CA4:CH4"/>
-    <mergeCell ref="CI4:CK4"/>
-    <mergeCell ref="CL4:CN4"/>
-    <mergeCell ref="CO4:CQ4"/>
-    <mergeCell ref="AH4:AJ4"/>
-    <mergeCell ref="AK4:AY4"/>
-    <mergeCell ref="AZ4:BJ4"/>
-    <mergeCell ref="BK4:BR4"/>
-    <mergeCell ref="BS4:BV4"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:K4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="P4:U4"/>
-    <mergeCell ref="V4:AG4"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D35">
     <cfRule type="cellIs" dxfId="89" priority="70" operator="lessThan">
